--- a/examples/tutorialModelExport.xlsx
+++ b/examples/tutorialModelExport.xlsx
@@ -5507,13 +5507,13 @@
         <v>188</v>
       </c>
       <c r="C2" s="0">
-        <v>99.88657646646881</v>
+        <v>99.886813042861874</v>
       </c>
       <c r="D2" s="0">
-        <v>27.329846181242246</v>
+        <v>27.272842169542418</v>
       </c>
       <c r="E2" s="0">
-        <v>93.659110505904195</v>
+        <v>93.67426755329295</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -5545,13 +5545,13 @@
         <v>189</v>
       </c>
       <c r="C3" s="0">
-        <v>99.947169693738843</v>
+        <v>99.9471697322126</v>
       </c>
       <c r="D3" s="0">
-        <v>12.729669927169756</v>
+        <v>12.729660656765374</v>
       </c>
       <c r="E3" s="0">
-        <v>96.326977401399148</v>
+        <v>96.326849845448649</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -5583,13 +5583,13 @@
         <v>190</v>
       </c>
       <c r="C4" s="0">
-        <v>99.95577112656359</v>
+        <v>99.955771130758947</v>
       </c>
       <c r="D4" s="0">
-        <v>10.657120882718774</v>
+        <v>10.657119871827131</v>
       </c>
       <c r="E4" s="0">
-        <v>64.932786985520053</v>
+        <v>64.931903898816117</v>
       </c>
       <c r="F4" s="0">
         <v>53.333333333333336</v>
@@ -5621,13 +5621,13 @@
         <v>188</v>
       </c>
       <c r="C5" s="0">
-        <v>99.963583891205843</v>
+        <v>99.96358393367359</v>
       </c>
       <c r="D5" s="0">
-        <v>8.774604536457213</v>
+        <v>8.7745943036879694</v>
       </c>
       <c r="E5" s="0">
-        <v>19.046856592903382</v>
+        <v>19.04513488179035</v>
       </c>
       <c r="F5" s="0">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="1">
-        <v>45867.575044658159</v>
+        <v>45935.331819999279</v>
       </c>
       <c r="E2" s="0">
         <v>23</v>
@@ -5711,11 +5711,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5743,19 +5743,19 @@
         <v>81</v>
       </c>
       <c r="B2" s="0">
-        <v>0.34081307948811906</v>
+        <v>0.04066570958280645</v>
       </c>
       <c r="C2" s="0">
-        <v>0.1034328050940562</v>
+        <v>0.34081309439093921</v>
       </c>
       <c r="D2" s="0">
-        <v>0.040665687336680835</v>
+        <v>0.10343530867223573</v>
       </c>
       <c r="E2" s="0">
-        <v>0.0035823723040500381</v>
+        <v>2.542468067793906</v>
       </c>
       <c r="F2" s="0">
-        <v>2.5424679281604541</v>
+        <v>0.0035825640867880389</v>
       </c>
     </row>
     <row r="3">
@@ -5763,19 +5763,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="0">
-        <v>0.22833400473580823</v>
+        <v>0.041960711859905811</v>
       </c>
       <c r="C3" s="0">
-        <v>0.18018174787863159</v>
+        <v>0.22833405130449971</v>
       </c>
       <c r="D3" s="0">
-        <v>0.041960669857855154</v>
+        <v>0.18018629966782695</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>2.5535010450599987</v>
       </c>
       <c r="F3" s="0">
-        <v>2.5535009305568979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5783,19 +5783,19 @@
         <v>83</v>
       </c>
       <c r="B4" s="0">
-        <v>0.043835618072770304</v>
+        <v>0.048783071294509754</v>
       </c>
       <c r="C4" s="0">
-        <v>0.027489437801288256</v>
+        <v>0.043835868251725772</v>
       </c>
       <c r="D4" s="0">
-        <v>0.048783127885402677</v>
+        <v>0.02748973224815526</v>
       </c>
       <c r="E4" s="0">
-        <v>3.1058192014149624</v>
+        <v>0.035244760886759562</v>
       </c>
       <c r="F4" s="0">
-        <v>0.035244683685815646</v>
+        <v>3.1058192066717818</v>
       </c>
     </row>
     <row r="5">
@@ -5803,19 +5803,19 @@
         <v>84</v>
       </c>
       <c r="B5" s="0">
-        <v>0.045438406420628373</v>
+        <v>0.051883210209872924</v>
       </c>
       <c r="C5" s="0">
-        <v>0.07905255312403868</v>
+        <v>0.045438634719265368</v>
       </c>
       <c r="D5" s="0">
-        <v>0.051883213354812142</v>
+        <v>0.079053982995756625</v>
       </c>
       <c r="E5" s="0">
-        <v>3.1301541724607569</v>
+        <v>0.017451932643534143</v>
       </c>
       <c r="F5" s="0">
-        <v>0.017451866261946423</v>
+        <v>3.1301541735098546</v>
       </c>
     </row>
     <row r="6">
@@ -5823,19 +5823,19 @@
         <v>85</v>
       </c>
       <c r="B6" s="0">
-        <v>0.04946192117194903</v>
+        <v>0.045976964098933523</v>
       </c>
       <c r="C6" s="0">
-        <v>1.2841600671469553</v>
+        <v>0.049461957590712299</v>
       </c>
       <c r="D6" s="0">
-        <v>0.045976940968580946</v>
+        <v>1.2841925237266749</v>
       </c>
       <c r="E6" s="0">
-        <v>0.028215543352831066</v>
+        <v>0.016490532701150067</v>
       </c>
       <c r="F6" s="0">
-        <v>0.016490458727270483</v>
+        <v>0.028215364848415438</v>
       </c>
     </row>
     <row r="7">
@@ -5843,19 +5843,19 @@
         <v>86</v>
       </c>
       <c r="B7" s="0">
-        <v>0.12474125323568266</v>
+        <v>0.061389900255794161</v>
       </c>
       <c r="C7" s="0">
-        <v>0.17115423459606022</v>
+        <v>0.12474137661228593</v>
       </c>
       <c r="D7" s="0">
-        <v>0.061389881128749595</v>
+        <v>0.17115822078115692</v>
       </c>
       <c r="E7" s="0">
-        <v>0.013779885877662513</v>
+        <v>0.96710613051085137</v>
       </c>
       <c r="F7" s="0">
-        <v>0.96710603344403867</v>
+        <v>0.013779981776166446</v>
       </c>
     </row>
     <row r="8">
@@ -5863,19 +5863,19 @@
         <v>87</v>
       </c>
       <c r="B8" s="0">
-        <v>0.16784879707079356</v>
+        <v>0.057002874248957079</v>
       </c>
       <c r="C8" s="0">
-        <v>0.19336643545550408</v>
+        <v>0.16784888432297263</v>
       </c>
       <c r="D8" s="0">
-        <v>0.057002849399802352</v>
+        <v>0.19337101462725159</v>
       </c>
       <c r="E8" s="0">
-        <v>0.0045372717501723009</v>
+        <v>1.8256988327067907</v>
       </c>
       <c r="F8" s="0">
-        <v>1.8256987030142944</v>
+        <v>0.0045374044923955238</v>
       </c>
     </row>
     <row r="9">
@@ -5883,19 +5883,19 @@
         <v>88</v>
       </c>
       <c r="B9" s="0">
-        <v>0.04515297646972774</v>
+        <v>0.048124155606215434</v>
       </c>
       <c r="C9" s="0">
-        <v>0.20075404679214504</v>
+        <v>0.045153153959481815</v>
       </c>
       <c r="D9" s="0">
-        <v>0.048124112215550185</v>
+        <v>0.2007582113639198</v>
       </c>
       <c r="E9" s="0">
-        <v>2.1447190865388191</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>0</v>
+        <v>2.1447191211148171</v>
       </c>
     </row>
     <row r="10">
@@ -5903,19 +5903,19 @@
         <v>89</v>
       </c>
       <c r="B10" s="0">
-        <v>0.096381028555558954</v>
+        <v>0.046852392846801164</v>
       </c>
       <c r="C10" s="0">
-        <v>0.39422155768073125</v>
+        <v>0.096381118119412565</v>
       </c>
       <c r="D10" s="0">
-        <v>0.046852368652965062</v>
+        <v>0.39423115333729925</v>
       </c>
       <c r="E10" s="0">
-        <v>0.72082087227777891</v>
+        <v>0.65525641840659144</v>
       </c>
       <c r="F10" s="0">
-        <v>0.65525634266775112</v>
+        <v>0.72082089342109101</v>
       </c>
     </row>
     <row r="11">
@@ -5923,19 +5923,19 @@
         <v>90</v>
       </c>
       <c r="B11" s="0">
-        <v>0.12510085160266954</v>
+        <v>0.0435529454011154</v>
       </c>
       <c r="C11" s="0">
-        <v>0.083666293042368542</v>
+        <v>0.12510091038223317</v>
       </c>
       <c r="D11" s="0">
-        <v>0.04355291147832388</v>
+        <v>0.083668218894503599</v>
       </c>
       <c r="E11" s="0">
-        <v>0.013621497329667281</v>
+        <v>1.2137398004032245</v>
       </c>
       <c r="F11" s="0">
-        <v>1.2137397233733913</v>
+        <v>0.013621594333090931</v>
       </c>
     </row>
     <row r="12">
@@ -5943,19 +5943,19 @@
         <v>91</v>
       </c>
       <c r="B12" s="0">
-        <v>0.068799984973632988</v>
+        <v>0.049107654347310598</v>
       </c>
       <c r="C12" s="0">
-        <v>0.06119824107404228</v>
+        <v>0.068800183865160292</v>
       </c>
       <c r="D12" s="0">
-        <v>0.049107653514124577</v>
+        <v>0.061199270642071438</v>
       </c>
       <c r="E12" s="0">
-        <v>2.7863301126562878</v>
+        <v>0.032835312230642927</v>
       </c>
       <c r="F12" s="0">
-        <v>0.032835235197784418</v>
+        <v>2.7863301224933577</v>
       </c>
     </row>
     <row r="13">
@@ -5963,19 +5963,19 @@
         <v>92</v>
       </c>
       <c r="B13" s="0">
-        <v>0.072461504522550194</v>
+        <v>0.051680211289558284</v>
       </c>
       <c r="C13" s="0">
-        <v>0.078385555741011817</v>
+        <v>0.07246163117635486</v>
       </c>
       <c r="D13" s="0">
-        <v>0.05168019473500441</v>
+        <v>0.078387328711269605</v>
       </c>
       <c r="E13" s="0">
-        <v>0.081989492774124387</v>
+        <v>0.0071231633121605024</v>
       </c>
       <c r="F13" s="0">
-        <v>0.0071230828688444029</v>
+        <v>0.081989527169059065</v>
       </c>
     </row>
     <row r="14">
@@ -5983,19 +5983,19 @@
         <v>93</v>
       </c>
       <c r="B14" s="0">
-        <v>0.22029210975001895</v>
+        <v>0.037081885649760365</v>
       </c>
       <c r="C14" s="0">
-        <v>0.10216157315701398</v>
+        <v>0.22029213187426608</v>
       </c>
       <c r="D14" s="0">
-        <v>0.037081821867630101</v>
+        <v>0.1021641545072991</v>
       </c>
       <c r="E14" s="0">
-        <v>0</v>
+        <v>2.5978748308092938</v>
       </c>
       <c r="F14" s="0">
-        <v>2.5978747265783766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6003,19 +6003,19 @@
         <v>94</v>
       </c>
       <c r="B15" s="0">
-        <v>0.025833298254217828</v>
+        <v>0.041742618279021732</v>
       </c>
       <c r="C15" s="0">
-        <v>0.15360834945434848</v>
+        <v>0.025833450394705047</v>
       </c>
       <c r="D15" s="0">
-        <v>0.041742536493410247</v>
+        <v>0.15361116683830314</v>
       </c>
       <c r="E15" s="0">
-        <v>3.1260244944028783</v>
+        <v>0</v>
       </c>
       <c r="F15" s="0">
-        <v>0</v>
+        <v>3.1260245087206879</v>
       </c>
     </row>
     <row r="16">
@@ -6023,19 +6023,19 @@
         <v>95</v>
       </c>
       <c r="B16" s="0">
-        <v>0.11710900197030463</v>
+        <v>0.036138545249786547</v>
       </c>
       <c r="C16" s="0">
-        <v>0.4531118740589492</v>
+        <v>0.11710906197002711</v>
       </c>
       <c r="D16" s="0">
-        <v>0.036138523980212195</v>
+        <v>0.45312307968383375</v>
       </c>
       <c r="E16" s="0">
-        <v>1.0850908330884594</v>
+        <v>0.89968531073790747</v>
       </c>
       <c r="F16" s="0">
-        <v>0.8996852383022167</v>
+        <v>1.0850908368843393</v>
       </c>
     </row>
     <row r="17">
@@ -6043,19 +6043,19 @@
         <v>96</v>
       </c>
       <c r="B17" s="0">
-        <v>0.26125295261546783</v>
+        <v>0.043518438091539734</v>
       </c>
       <c r="C17" s="0">
-        <v>0.41204470678441896</v>
+        <v>0.26125299987629208</v>
       </c>
       <c r="D17" s="0">
-        <v>0.043518441707450374</v>
+        <v>0.41205490577519605</v>
       </c>
       <c r="E17" s="0">
-        <v>0.0047172226585828741</v>
+        <v>2.556290491880747</v>
       </c>
       <c r="F17" s="0">
-        <v>2.5562903868294473</v>
+        <v>0.0047173726641874239</v>
       </c>
     </row>
     <row r="18">
@@ -6063,19 +6063,19 @@
         <v>97</v>
       </c>
       <c r="B18" s="0">
-        <v>0.034246078673652251</v>
+        <v>0.037015453424580104</v>
       </c>
       <c r="C18" s="0">
-        <v>0.07622272682020724</v>
+        <v>0.034246237884351001</v>
       </c>
       <c r="D18" s="0">
-        <v>0.037015425452262225</v>
+        <v>0.076223985556030383</v>
       </c>
       <c r="E18" s="0">
-        <v>3.173557563126038</v>
+        <v>0.011984795905234219</v>
       </c>
       <c r="F18" s="0">
-        <v>0.011984751780103577</v>
+        <v>3.1735575588486165</v>
       </c>
     </row>
     <row r="19">
@@ -6083,19 +6083,19 @@
         <v>98</v>
       </c>
       <c r="B19" s="0">
-        <v>0.12079719084995552</v>
+        <v>0.035382755257972173</v>
       </c>
       <c r="C19" s="0">
-        <v>0.42240436184799735</v>
+        <v>0.12079726393967385</v>
       </c>
       <c r="D19" s="0">
-        <v>0.035382754789219928</v>
+        <v>0.42241497697385072</v>
       </c>
       <c r="E19" s="0">
-        <v>1.0635851060412984</v>
+        <v>0.88393572199621307</v>
       </c>
       <c r="F19" s="0">
-        <v>0.88393564216635301</v>
+        <v>1.0635851005418664</v>
       </c>
     </row>
     <row r="20">
@@ -6103,19 +6103,19 @@
         <v>99</v>
       </c>
       <c r="B20" s="0">
-        <v>0.030540712635548924</v>
+        <v>0.031746227876100056</v>
       </c>
       <c r="C20" s="0">
-        <v>0.066912949627275772</v>
+        <v>0.030540779725688003</v>
       </c>
       <c r="D20" s="0">
-        <v>0.031746201004114315</v>
+        <v>0.06691444383612033</v>
       </c>
       <c r="E20" s="0">
-        <v>0.013297844430122625</v>
+        <v>0.011168253819059301</v>
       </c>
       <c r="F20" s="0">
-        <v>0.011168214196447751</v>
+        <v>0.013297864200704801</v>
       </c>
     </row>
     <row r="21">
@@ -6123,19 +6123,19 @@
         <v>100</v>
       </c>
       <c r="B21" s="0">
-        <v>0.22632883045039992</v>
+        <v>0.043748555927815888</v>
       </c>
       <c r="C21" s="0">
-        <v>0.099987340409963363</v>
+        <v>0.22632892716029557</v>
       </c>
       <c r="D21" s="0">
-        <v>0.04374851609770597</v>
+        <v>0.099989124911415706</v>
       </c>
       <c r="E21" s="0">
-        <v>2.0287691228466547</v>
+        <v>0.0028148877089835245</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0028147562191621484</v>
+        <v>2.0287691845755553</v>
       </c>
     </row>
     <row r="22">
@@ -6143,19 +6143,19 @@
         <v>101</v>
       </c>
       <c r="B22" s="0">
-        <v>0.035770547288068263</v>
+        <v>0.03635324111481307</v>
       </c>
       <c r="C22" s="0">
-        <v>0.058813596334398179</v>
+        <v>0.035770622815960704</v>
       </c>
       <c r="D22" s="0">
-        <v>0.03635321038813389</v>
+        <v>0.058814857413958671</v>
       </c>
       <c r="E22" s="0">
-        <v>0.023565300685929418</v>
+        <v>0.0012737055978383374</v>
       </c>
       <c r="F22" s="0">
-        <v>0.0012736579823379869</v>
+        <v>0.023565325623398172</v>
       </c>
     </row>
     <row r="23">
@@ -6163,19 +6163,19 @@
         <v>102</v>
       </c>
       <c r="B23" s="0">
-        <v>0.028061319261604899</v>
+        <v>0.030983983740026429</v>
       </c>
       <c r="C23" s="0">
-        <v>0.057859981267914348</v>
+        <v>0.028061388804659721</v>
       </c>
       <c r="D23" s="0">
-        <v>0.030983961693509008</v>
+        <v>0.057861277827954347</v>
       </c>
       <c r="E23" s="0">
-        <v>0.015602939903742378</v>
+        <v>0.0023874912811077307</v>
       </c>
       <c r="F23" s="0">
-        <v>0.0023874522530642132</v>
+        <v>0.015602957884624883</v>
       </c>
     </row>
     <row r="24">
@@ -6183,19 +6183,19 @@
         <v>103</v>
       </c>
       <c r="B24" s="0">
-        <v>0.054075518543625786</v>
+        <v>0.043287314307531348</v>
       </c>
       <c r="C24" s="0">
-        <v>0.078911332394685882</v>
+        <v>0.054075625935056264</v>
       </c>
       <c r="D24" s="0">
-        <v>0.043287286528946325</v>
+        <v>0.078912996670526245</v>
       </c>
       <c r="E24" s="0">
-        <v>0.50828218952543058</v>
+        <v>0.0036946765888716199</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0036946156578387241</v>
+        <v>0.50828221746888425</v>
       </c>
     </row>
     <row r="25">
@@ -6203,19 +6203,19 @@
         <v>104</v>
       </c>
       <c r="B25" s="0">
-        <v>0.033850500469772303</v>
+        <v>0.034817031329069416</v>
       </c>
       <c r="C25" s="0">
-        <v>0.048370836756604703</v>
+        <v>0.033850573546254266</v>
       </c>
       <c r="D25" s="0">
-        <v>0.034817002268361798</v>
+        <v>0.048371850700844592</v>
       </c>
       <c r="E25" s="0">
-        <v>0.018372328645918267</v>
+        <v>0.00087312563983168751</v>
       </c>
       <c r="F25" s="0">
-        <v>0.0008730801224283803</v>
+        <v>0.018372353094215914</v>
       </c>
     </row>
     <row r="26">
@@ -6223,19 +6223,19 @@
         <v>105</v>
       </c>
       <c r="B26" s="0">
-        <v>0.037649652211019576</v>
+        <v>0.04135582551571082</v>
       </c>
       <c r="C26" s="0">
-        <v>0.075797484364783563</v>
+        <v>0.037649734853769677</v>
       </c>
       <c r="D26" s="0">
-        <v>0.041355785142898026</v>
+        <v>0.075799055379936115</v>
       </c>
       <c r="E26" s="0">
-        <v>0.021111014192588786</v>
+        <v>0.00094252672643850479</v>
       </c>
       <c r="F26" s="0">
-        <v>0.00094247661189415268</v>
+        <v>0.021111048433218725</v>
       </c>
     </row>
     <row r="27">
@@ -6243,19 +6243,19 @@
         <v>106</v>
       </c>
       <c r="B27" s="0">
-        <v>0.040743869593925293</v>
+        <v>0.0424761183561366</v>
       </c>
       <c r="C27" s="0">
-        <v>0.048994333030854952</v>
+        <v>0.040743972367817287</v>
       </c>
       <c r="D27" s="0">
-        <v>0.042476097859662353</v>
+        <v>0.048995371896558115</v>
       </c>
       <c r="E27" s="0">
-        <v>0.025238458409857733</v>
+        <v>0.0015920539254998087</v>
       </c>
       <c r="F27" s="0">
-        <v>0.0015919974189564359</v>
+        <v>0.025238487551007233</v>
       </c>
     </row>
     <row r="28">
@@ -6263,19 +6263,19 @@
         <v>107</v>
       </c>
       <c r="B28" s="0">
-        <v>0.091904551214354646</v>
+        <v>0.045384135245709646</v>
       </c>
       <c r="C28" s="0">
-        <v>0.10229815644757088</v>
+        <v>0.091904631843560888</v>
       </c>
       <c r="D28" s="0">
-        <v>0.045384099482885854</v>
+        <v>0.10230050732339779</v>
       </c>
       <c r="E28" s="0">
-        <v>0.024773148632509113</v>
+        <v>0.54785106032697695</v>
       </c>
       <c r="F28" s="0">
-        <v>0.54785098922546682</v>
+        <v>0.024773207222850705</v>
       </c>
     </row>
     <row r="29">
@@ -6283,19 +6283,19 @@
         <v>108</v>
       </c>
       <c r="B29" s="0">
-        <v>0.037861426219937593</v>
+        <v>0.041481213443745453</v>
       </c>
       <c r="C29" s="0">
-        <v>0.070238234924719256</v>
+        <v>0.037861513576442692</v>
       </c>
       <c r="D29" s="0">
-        <v>0.041481179144230052</v>
+        <v>0.070239697390987233</v>
       </c>
       <c r="E29" s="0">
-        <v>0.021469185824033378</v>
+        <v>0.00032948296088918574</v>
       </c>
       <c r="F29" s="0">
-        <v>0.000329431280678328</v>
+        <v>0.02146921925568621</v>
       </c>
     </row>
     <row r="30">
@@ -6303,19 +6303,19 @@
         <v>109</v>
       </c>
       <c r="B30" s="0">
-        <v>0.042830859216848392</v>
+        <v>0.045073777333747026</v>
       </c>
       <c r="C30" s="0">
-        <v>0.059925942947858767</v>
+        <v>0.042830959751852103</v>
       </c>
       <c r="D30" s="0">
-        <v>0.045073744491735839</v>
+        <v>0.059927204835043942</v>
       </c>
       <c r="E30" s="0">
-        <v>0.027423700818795513</v>
+        <v>0.001452168173112618</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0014521100284964564</v>
+        <v>0.027423731845782125</v>
       </c>
     </row>
     <row r="31">
@@ -6323,19 +6323,19 @@
         <v>110</v>
       </c>
       <c r="B31" s="0">
-        <v>0.042211593167375619</v>
+        <v>0.041287224771766017</v>
       </c>
       <c r="C31" s="0">
-        <v>0.066499272109405039</v>
+        <v>0.04221167550002107</v>
       </c>
       <c r="D31" s="0">
-        <v>0.04128718580912915</v>
+        <v>0.06650063999229916</v>
       </c>
       <c r="E31" s="0">
-        <v>0.027477089926641399</v>
+        <v>0.00061937185342007979</v>
       </c>
       <c r="F31" s="0">
-        <v>0.00061931854548719632</v>
+        <v>0.02747712336135727</v>
       </c>
     </row>
     <row r="32">
@@ -6343,19 +6343,19 @@
         <v>111</v>
       </c>
       <c r="B32" s="0">
-        <v>0.049108385077290207</v>
+        <v>0.059764354667994131</v>
       </c>
       <c r="C32" s="0">
-        <v>0.066218752700407668</v>
+        <v>0.049108511391611119</v>
       </c>
       <c r="D32" s="0">
-        <v>0.05976430065954496</v>
+        <v>0.066220006038667983</v>
       </c>
       <c r="E32" s="0">
-        <v>0.025078291413000726</v>
+        <v>0.0017666714429694784</v>
       </c>
       <c r="F32" s="0">
-        <v>0.001766599760526412</v>
+        <v>0.025078339858418976</v>
       </c>
     </row>
     <row r="33">
@@ -6363,19 +6363,19 @@
         <v>112</v>
       </c>
       <c r="B33" s="0">
-        <v>0.036050858259913922</v>
+        <v>0.035486062036694341</v>
       </c>
       <c r="C33" s="0">
-        <v>0.066613246959039599</v>
+        <v>0.036050930282241316</v>
       </c>
       <c r="D33" s="0">
-        <v>0.035486030533245096</v>
+        <v>0.066614689766767626</v>
       </c>
       <c r="E33" s="0">
-        <v>0.023706796100207258</v>
+        <v>0.0027694407573373957</v>
       </c>
       <c r="F33" s="0">
-        <v>0.0027693944975184198</v>
+        <v>0.023706821066397658</v>
       </c>
     </row>
     <row r="34">
@@ -6383,19 +6383,19 @@
         <v>113</v>
       </c>
       <c r="B34" s="0">
-        <v>0.036155958385129881</v>
+        <v>0.043302627928385726</v>
       </c>
       <c r="C34" s="0">
-        <v>0.013621547379684381</v>
+        <v>0.03615618768679784</v>
       </c>
       <c r="D34" s="0">
-        <v>0.043302649739510951</v>
+        <v>0.013621556410449868</v>
       </c>
       <c r="E34" s="0">
-        <v>3.3498492343586577</v>
+        <v>0.031181929228912237</v>
       </c>
       <c r="F34" s="0">
-        <v>0.031181869954060033</v>
+        <v>3.3498492163399365</v>
       </c>
     </row>
     <row r="35">
@@ -6403,19 +6403,19 @@
         <v>114</v>
       </c>
       <c r="B35" s="0">
-        <v>0.00012648101724870153</v>
+        <v>0.007323831431758918</v>
       </c>
       <c r="C35" s="0">
-        <v>0.023349446185510766</v>
+        <v>0.00012647748465797034</v>
       </c>
       <c r="D35" s="0">
-        <v>0.0073237960198473629</v>
+        <v>0.023349925957317764</v>
       </c>
       <c r="E35" s="0">
-        <v>0.0021837430258831257</v>
+        <v>0</v>
       </c>
       <c r="F35" s="0">
-        <v>0</v>
+        <v>0.0021837448133254886</v>
       </c>
     </row>
     <row r="36">
@@ -6423,19 +6423,19 @@
         <v>115</v>
       </c>
       <c r="B36" s="0">
-        <v>0.094325270730279562</v>
+        <v>0.035877553377315879</v>
       </c>
       <c r="C36" s="0">
-        <v>0.46012016721836441</v>
+        <v>0.094325312378748527</v>
       </c>
       <c r="D36" s="0">
-        <v>0.035877502056433072</v>
+        <v>0.46013153303178334</v>
       </c>
       <c r="E36" s="0">
-        <v>1.0596194361914342</v>
+        <v>0.93673492174912343</v>
       </c>
       <c r="F36" s="0">
-        <v>0.93673486414110696</v>
+        <v>1.0596194314165741</v>
       </c>
     </row>
     <row r="37">
@@ -6443,19 +6443,19 @@
         <v>116</v>
       </c>
       <c r="B37" s="0">
-        <v>0.035207009683009327</v>
+        <v>0.041418214372893128</v>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>0.035207257491669051</v>
       </c>
       <c r="D37" s="0">
-        <v>0.04141826539760509</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
-        <v>3.2919534884283426</v>
+        <v>0.036937479218180795</v>
       </c>
       <c r="F37" s="0">
-        <v>0.036937413107886723</v>
+        <v>3.2919534427011055</v>
       </c>
     </row>
     <row r="38">
@@ -6463,19 +6463,19 @@
         <v>117</v>
       </c>
       <c r="B38" s="0">
-        <v>0.046490366383420731</v>
+        <v>0.067246994159386314</v>
       </c>
       <c r="C38" s="0">
-        <v>1.2478074696679631</v>
+        <v>0.046490427816674472</v>
       </c>
       <c r="D38" s="0">
-        <v>0.067246919108638711</v>
+        <v>1.2478388009360926</v>
       </c>
       <c r="E38" s="0">
-        <v>0.041806816166572371</v>
+        <v>0.0088077502992872404</v>
       </c>
       <c r="F38" s="0">
-        <v>0.0088076613887509252</v>
+        <v>0.041806657801085216</v>
       </c>
     </row>
     <row r="39">
@@ -6483,19 +6483,19 @@
         <v>118</v>
       </c>
       <c r="B39" s="0">
-        <v>1.1933070158509766</v>
+        <v>0.050473988785335232</v>
       </c>
       <c r="C39" s="0">
-        <v>0.064801721050667893</v>
+        <v>1.1933069166292432</v>
       </c>
       <c r="D39" s="0">
-        <v>0.050473970658312675</v>
+        <v>0.064802781899364656</v>
       </c>
       <c r="E39" s="0">
-        <v>0.50834502226923872</v>
+        <v>0.016713989254784616</v>
       </c>
       <c r="F39" s="0">
-        <v>0.016713431666769953</v>
+        <v>0.50834529583476995</v>
       </c>
     </row>
     <row r="40">
@@ -6503,19 +6503,19 @@
         <v>119</v>
       </c>
       <c r="B40" s="0">
-        <v>0.036169564654187525</v>
+        <v>0.04390239315036705</v>
       </c>
       <c r="C40" s="0">
-        <v>0</v>
+        <v>0.036169803132307894</v>
       </c>
       <c r="D40" s="0">
-        <v>0.043902419936383677</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
-        <v>3.3909121488832379</v>
+        <v>0.034481814111177574</v>
       </c>
       <c r="F40" s="0">
-        <v>0.034481746343216144</v>
+        <v>3.3909120958059238</v>
       </c>
     </row>
     <row r="41">
@@ -6523,19 +6523,19 @@
         <v>120</v>
       </c>
       <c r="B41" s="0">
-        <v>0.051981197867484355</v>
+        <v>0.066080137773422462</v>
       </c>
       <c r="C41" s="0">
-        <v>1.2837097717995944</v>
+        <v>0.051981249662230028</v>
       </c>
       <c r="D41" s="0">
-        <v>0.066080063435506486</v>
+        <v>1.2837419736234512</v>
       </c>
       <c r="E41" s="0">
-        <v>0.029355963740801808</v>
+        <v>0.0054519308230551481</v>
       </c>
       <c r="F41" s="0">
-        <v>0.0054518388271299015</v>
+        <v>0.029355804486800762</v>
       </c>
     </row>
     <row r="42">
@@ -6543,19 +6543,19 @@
         <v>121</v>
       </c>
       <c r="B42" s="0">
-        <v>0.10076817700949126</v>
+        <v>0.039121918422634017</v>
       </c>
       <c r="C42" s="0">
-        <v>0.47787816796643939</v>
+        <v>0.10076824698733275</v>
       </c>
       <c r="D42" s="0">
-        <v>0.039121895353756639</v>
+        <v>0.47789012851972884</v>
       </c>
       <c r="E42" s="0">
-        <v>1.0499599188742332</v>
+        <v>0.92232754419316421</v>
       </c>
       <c r="F42" s="0">
-        <v>0.92232747449126828</v>
+        <v>1.049959905138115</v>
       </c>
     </row>
     <row r="43">
@@ -6563,19 +6563,19 @@
         <v>122</v>
       </c>
       <c r="B43" s="0">
-        <v>0.033944532369389678</v>
+        <v>0.045284880525148008</v>
       </c>
       <c r="C43" s="0">
-        <v>0.0054033250181341587</v>
+        <v>0.033944780049969765</v>
       </c>
       <c r="D43" s="0">
-        <v>0.045284917195924625</v>
+        <v>0.0054032670053949091</v>
       </c>
       <c r="E43" s="0">
-        <v>3.3276065453364798</v>
+        <v>0.031650102469036899</v>
       </c>
       <c r="F43" s="0">
-        <v>0.031650038587600057</v>
+        <v>3.327606518621292</v>
       </c>
     </row>
     <row r="44">
@@ -6583,19 +6583,19 @@
         <v>123</v>
       </c>
       <c r="B44" s="0">
-        <v>0.044270812446376935</v>
+        <v>0.059763751718923321</v>
       </c>
       <c r="C44" s="0">
-        <v>1.2248219906646882</v>
+        <v>0.044270848510974514</v>
       </c>
       <c r="D44" s="0">
-        <v>0.059763675230595101</v>
+        <v>1.2248527330480343</v>
       </c>
       <c r="E44" s="0">
-        <v>0.035834407094624862</v>
+        <v>0.007588815610130085</v>
       </c>
       <c r="F44" s="0">
-        <v>0.0075887338375122968</v>
+        <v>0.035834249955395033</v>
       </c>
     </row>
     <row r="45">
@@ -6603,19 +6603,19 @@
         <v>124</v>
       </c>
       <c r="B45" s="0">
-        <v>0.70973172474142054</v>
+        <v>0.049696852421047454</v>
       </c>
       <c r="C45" s="0">
-        <v>0.13985854908006831</v>
+        <v>0.70973170190677737</v>
       </c>
       <c r="D45" s="0">
-        <v>0.049696797236010878</v>
+        <v>0.13986161542974257</v>
       </c>
       <c r="E45" s="0">
-        <v>0.75786088760846149</v>
+        <v>0.071347128915444938</v>
       </c>
       <c r="F45" s="0">
-        <v>0.071346786386139199</v>
+        <v>0.75786103518267467</v>
       </c>
     </row>
     <row r="46">
@@ -6623,19 +6623,19 @@
         <v>125</v>
       </c>
       <c r="B46" s="0">
-        <v>0.044818509237427528</v>
+        <v>0.042885517071237583</v>
       </c>
       <c r="C46" s="0">
-        <v>0.97356119321050605</v>
+        <v>0.044818524921797775</v>
       </c>
       <c r="D46" s="0">
-        <v>0.042885454859563174</v>
+        <v>0.97358552080114069</v>
       </c>
       <c r="E46" s="0">
-        <v>0.03805478193926342</v>
+        <v>0.012014510119182644</v>
       </c>
       <c r="F46" s="0">
-        <v>0.012014450564195915</v>
+        <v>0.03805466769170282</v>
       </c>
     </row>
     <row r="47">
@@ -6643,19 +6643,19 @@
         <v>126</v>
       </c>
       <c r="B47" s="0">
-        <v>0.042756325479297287</v>
+        <v>0.050986335584116499</v>
       </c>
       <c r="C47" s="0">
-        <v>0.14497335692168142</v>
+        <v>0.042756544013398096</v>
       </c>
       <c r="D47" s="0">
-        <v>0.050986280220662025</v>
+        <v>0.14497601646280076</v>
       </c>
       <c r="E47" s="0">
-        <v>3.3637626545390109</v>
+        <v>0</v>
       </c>
       <c r="F47" s="0">
-        <v>0</v>
+        <v>3.3637626720758793</v>
       </c>
     </row>
     <row r="48">
@@ -6663,19 +6663,19 @@
         <v>127</v>
       </c>
       <c r="B48" s="0">
-        <v>0.037795676547097555</v>
+        <v>0.04344686750050844</v>
       </c>
       <c r="C48" s="0">
-        <v>0.057339497553063695</v>
+        <v>0.037795769290449061</v>
       </c>
       <c r="D48" s="0">
-        <v>0.043446827445935372</v>
+        <v>0.057340614061114528</v>
       </c>
       <c r="E48" s="0">
-        <v>0.015908658143740099</v>
+        <v>0.0032348702488002369</v>
       </c>
       <c r="F48" s="0">
-        <v>0.0032348193114715832</v>
+        <v>0.015908694717071698</v>
       </c>
     </row>
     <row r="49">
@@ -6683,19 +6683,19 @@
         <v>128</v>
       </c>
       <c r="B49" s="0">
-        <v>0.043501184486117596</v>
+        <v>0.050206640515984447</v>
       </c>
       <c r="C49" s="0">
-        <v>0.089994651232797721</v>
+        <v>0.043501284379282981</v>
       </c>
       <c r="D49" s="0">
-        <v>0.050206585786894804</v>
+        <v>0.089996504539174987</v>
       </c>
       <c r="E49" s="0">
-        <v>0.030593144339576741</v>
+        <v>0.002502951802537358</v>
       </c>
       <c r="F49" s="0">
-        <v>0.002502894375827785</v>
+        <v>0.030593184303992344</v>
       </c>
     </row>
     <row r="50">
@@ -6703,19 +6703,19 @@
         <v>129</v>
       </c>
       <c r="B50" s="0">
-        <v>0.03347784545385267</v>
+        <v>0.037537978110632343</v>
       </c>
       <c r="C50" s="0">
-        <v>0.035813264685158212</v>
+        <v>0.033477934755955945</v>
       </c>
       <c r="D50" s="0">
-        <v>0.037537952926480704</v>
+        <v>0.035813955724101627</v>
       </c>
       <c r="E50" s="0">
-        <v>0.011447312695729255</v>
+        <v>0.0018691191774374211</v>
       </c>
       <c r="F50" s="0">
-        <v>0.0018690734586835598</v>
+        <v>0.011447341271217401</v>
       </c>
     </row>
     <row r="51">
@@ -6723,19 +6723,19 @@
         <v>130</v>
       </c>
       <c r="B51" s="0">
-        <v>0.025009614078602988</v>
+        <v>0.038175464584503979</v>
       </c>
       <c r="C51" s="0">
-        <v>0.20646684787533587</v>
+        <v>0.025009731911195723</v>
       </c>
       <c r="D51" s="0">
-        <v>0.038175367638620339</v>
+        <v>0.20647089407138822</v>
       </c>
       <c r="E51" s="0">
-        <v>3.0510514429662039</v>
+        <v>0</v>
       </c>
       <c r="F51" s="0">
-        <v>0</v>
+        <v>3.0510514566090885</v>
       </c>
     </row>
     <row r="52">
@@ -6743,19 +6743,19 @@
         <v>131</v>
       </c>
       <c r="B52" s="0">
-        <v>0.0337234248124871</v>
+        <v>0.041301941252688393</v>
       </c>
       <c r="C52" s="0">
-        <v>0.0050108610383730922</v>
+        <v>0.033723657839478956</v>
       </c>
       <c r="D52" s="0">
-        <v>0.041301972738471991</v>
+        <v>0.005010517973719068</v>
       </c>
       <c r="E52" s="0">
-        <v>3.3164685248249515</v>
+        <v>0.042047468717601004</v>
       </c>
       <c r="F52" s="0">
-        <v>0.042047416352301074</v>
+        <v>3.3164685240169045</v>
       </c>
     </row>
     <row r="53">
@@ -6763,19 +6763,19 @@
         <v>132</v>
       </c>
       <c r="B53" s="0">
-        <v>0.037722998790373726</v>
+        <v>0.042692061072718022</v>
       </c>
       <c r="C53" s="0">
-        <v>0.049121122183128876</v>
+        <v>0.037723091378419837</v>
       </c>
       <c r="D53" s="0">
-        <v>0.042692023224219396</v>
+        <v>0.049122041159641736</v>
       </c>
       <c r="E53" s="0">
-        <v>0.014980918558521957</v>
+        <v>0.0021431542741233932</v>
       </c>
       <c r="F53" s="0">
-        <v>0.0021431037510353879</v>
+        <v>0.014980955629219176</v>
       </c>
     </row>
     <row r="54">
@@ -6783,19 +6783,19 @@
         <v>133</v>
       </c>
       <c r="B54" s="0">
-        <v>0.042748358732591189</v>
+        <v>0.047368238623193802</v>
       </c>
       <c r="C54" s="0">
-        <v>0.087645280267625691</v>
+        <v>0.042748458079897613</v>
       </c>
       <c r="D54" s="0">
-        <v>0.047368193618583174</v>
+        <v>0.087647114505601004</v>
       </c>
       <c r="E54" s="0">
-        <v>0.031951967601725015</v>
+        <v>0.0031399734010667487</v>
       </c>
       <c r="F54" s="0">
-        <v>0.0031399178715758799</v>
+        <v>0.031952005030894425</v>
       </c>
     </row>
     <row r="55">
@@ -6803,19 +6803,19 @@
         <v>134</v>
       </c>
       <c r="B55" s="0">
-        <v>0.03464497892723143</v>
+        <v>0.035469992825744375</v>
       </c>
       <c r="C55" s="0">
-        <v>0.037203660884039674</v>
+        <v>0.03464505431205453</v>
       </c>
       <c r="D55" s="0">
-        <v>0.035469958816986655</v>
+        <v>0.037204339932558596</v>
       </c>
       <c r="E55" s="0">
-        <v>0.01448594617005209</v>
+        <v>0.0016701449921501332</v>
       </c>
       <c r="F55" s="0">
-        <v>0.0016701020403592187</v>
+        <v>0.014485976625769698</v>
       </c>
     </row>
     <row r="56">
@@ -6823,19 +6823,19 @@
         <v>135</v>
       </c>
       <c r="B56" s="0">
-        <v>0.27210547760294679</v>
+        <v>0.050160351508690325</v>
       </c>
       <c r="C56" s="0">
-        <v>0.12446452036093308</v>
+        <v>0.27210550558835872</v>
       </c>
       <c r="D56" s="0">
-        <v>0.050160295949298134</v>
+        <v>0.12446750780240061</v>
       </c>
       <c r="E56" s="0">
-        <v>0.027069576021276048</v>
+        <v>2.5850885907276546</v>
       </c>
       <c r="F56" s="0">
-        <v>2.5850884738081108</v>
+        <v>0.027069754483570688</v>
       </c>
     </row>
     <row r="57">
@@ -6843,19 +6843,19 @@
         <v>136</v>
       </c>
       <c r="B57" s="0">
-        <v>0.046056682594238001</v>
+        <v>0.046201399739598116</v>
       </c>
       <c r="C57" s="0">
-        <v>1.2299209279702237</v>
+        <v>0.046056702991696188</v>
       </c>
       <c r="D57" s="0">
-        <v>0.046201355269459614</v>
+        <v>1.2299518682477715</v>
       </c>
       <c r="E57" s="0">
-        <v>0.039191347715906343</v>
+        <v>0.003274072723645328</v>
       </c>
       <c r="F57" s="0">
-        <v>0.003274001663726368</v>
+        <v>0.039191186273853991</v>
       </c>
     </row>
     <row r="58">
@@ -6863,19 +6863,19 @@
         <v>137</v>
       </c>
       <c r="B58" s="0">
-        <v>1.2335233703349216</v>
+        <v>0.057674689645331845</v>
       </c>
       <c r="C58" s="0">
-        <v>0.11188825554267841</v>
+        <v>1.2335232601824429</v>
       </c>
       <c r="D58" s="0">
-        <v>0.057674643892153481</v>
+        <v>0.11189041219422101</v>
       </c>
       <c r="E58" s="0">
-        <v>0.45099183302684653</v>
+        <v>0.036220259498656607</v>
       </c>
       <c r="F58" s="0">
-        <v>0.036219682249585987</v>
+        <v>0.45099211497407582</v>
       </c>
     </row>
     <row r="59">
@@ -6883,19 +6883,19 @@
         <v>138</v>
       </c>
       <c r="B59" s="0">
-        <v>0.041860337161332313</v>
+        <v>0.046025353924379668</v>
       </c>
       <c r="C59" s="0">
-        <v>0.056073740237698941</v>
+        <v>0.041860556078998447</v>
       </c>
       <c r="D59" s="0">
-        <v>0.046025364666631929</v>
+        <v>0.056074510915914783</v>
       </c>
       <c r="E59" s="0">
-        <v>3.1839248282874571</v>
+        <v>0.01089253659212058</v>
       </c>
       <c r="F59" s="0">
-        <v>0.010892479115301754</v>
+        <v>3.1839248385454741</v>
       </c>
     </row>
     <row r="60">
@@ -6903,19 +6903,19 @@
         <v>139</v>
       </c>
       <c r="B60" s="0">
-        <v>0.05505900575272208</v>
+        <v>0.064191327040918303</v>
       </c>
       <c r="C60" s="0">
-        <v>0.99037761054456308</v>
+        <v>0.055059085364682625</v>
       </c>
       <c r="D60" s="0">
-        <v>0.064191269874229184</v>
+        <v>0.99040238219657839</v>
       </c>
       <c r="E60" s="0">
-        <v>0.061698562880339598</v>
+        <v>0.0019906236431508849</v>
       </c>
       <c r="F60" s="0">
-        <v>0.0019905359337971944</v>
+        <v>0.061698453919694321</v>
       </c>
     </row>
     <row r="61">
@@ -6923,19 +6923,19 @@
         <v>140</v>
       </c>
       <c r="B61" s="0">
-        <v>0.10654217386943624</v>
+        <v>0.038401528817154217</v>
       </c>
       <c r="C61" s="0">
-        <v>0.34121608536399206</v>
+        <v>0.10654226382326797</v>
       </c>
       <c r="D61" s="0">
-        <v>0.038401524071133793</v>
+        <v>0.34122461543238564</v>
       </c>
       <c r="E61" s="0">
-        <v>0.9418109363543119</v>
+        <v>0.83754434514541531</v>
       </c>
       <c r="F61" s="0">
-        <v>0.83754427350499805</v>
+        <v>0.94181094439803281</v>
       </c>
     </row>
     <row r="62">
@@ -6943,19 +6943,19 @@
         <v>141</v>
       </c>
       <c r="B62" s="0">
-        <v>0.049857918566772748</v>
+        <v>0.05259576489311274</v>
       </c>
       <c r="C62" s="0">
-        <v>0.084278659874352416</v>
+        <v>0.049858030467645302</v>
       </c>
       <c r="D62" s="0">
-        <v>0.052595719225767688</v>
+        <v>0.084280452396262334</v>
       </c>
       <c r="E62" s="0">
-        <v>0.029895854282846076</v>
+        <v>0.0019948081513775232</v>
       </c>
       <c r="F62" s="0">
-        <v>0.0019947424886786894</v>
+        <v>0.029895890888693964</v>
       </c>
     </row>
     <row r="63">
@@ -6963,19 +6963,19 @@
         <v>142</v>
       </c>
       <c r="B63" s="0">
-        <v>0.051475611576260856</v>
+        <v>0.05151191255176428</v>
       </c>
       <c r="C63" s="0">
-        <v>0.16655742515368649</v>
+        <v>0.05147572688765293</v>
       </c>
       <c r="D63" s="0">
-        <v>0.051511834891106528</v>
+        <v>0.16656100269231092</v>
       </c>
       <c r="E63" s="0">
-        <v>0.040480903261778736</v>
+        <v>0</v>
       </c>
       <c r="F63" s="0">
-        <v>0</v>
+        <v>0.040480953796164496</v>
       </c>
     </row>
     <row r="64">
@@ -6983,19 +6983,19 @@
         <v>143</v>
       </c>
       <c r="B64" s="0">
-        <v>0.17062044120013664</v>
+        <v>0.052584648089877603</v>
       </c>
       <c r="C64" s="0">
-        <v>0.10200698673341131</v>
+        <v>0.17062050921104094</v>
       </c>
       <c r="D64" s="0">
-        <v>0.052584604279489834</v>
+        <v>0.1020093290651431</v>
       </c>
       <c r="E64" s="0">
-        <v>0.011148541343475888</v>
+        <v>1.8248302919342589</v>
       </c>
       <c r="F64" s="0">
-        <v>1.8248302009741386</v>
+        <v>0.011148679471281994</v>
       </c>
     </row>
     <row r="65">
@@ -7003,19 +7003,19 @@
         <v>144</v>
       </c>
       <c r="B65" s="0">
-        <v>0.046589701485831941</v>
+        <v>0.050500741202316096</v>
       </c>
       <c r="C65" s="0">
-        <v>0.22150109569625895</v>
+        <v>0.046589852848315426</v>
       </c>
       <c r="D65" s="0">
-        <v>0.050500648514621618</v>
+        <v>0.22150582299016036</v>
       </c>
       <c r="E65" s="0">
-        <v>2.3096560152559036</v>
+        <v>0</v>
       </c>
       <c r="F65" s="0">
-        <v>0</v>
+        <v>2.3096560242032043</v>
       </c>
     </row>
     <row r="66">
@@ -7023,19 +7023,19 @@
         <v>145</v>
       </c>
       <c r="B66" s="0">
-        <v>0.061464197600135932</v>
+        <v>0.054475120027514666</v>
       </c>
       <c r="C66" s="0">
-        <v>0.70767410358500038</v>
+        <v>0.061464286514047173</v>
       </c>
       <c r="D66" s="0">
-        <v>0.054475092889783139</v>
+        <v>0.70769176844998227</v>
       </c>
       <c r="E66" s="0">
-        <v>0.034398028518693162</v>
+        <v>0.0059145835776696172</v>
       </c>
       <c r="F66" s="0">
-        <v>0.0059145020398045133</v>
+        <v>0.034397964934602447</v>
       </c>
     </row>
     <row r="67">
@@ -7043,19 +7043,19 @@
         <v>146</v>
       </c>
       <c r="B67" s="0">
-        <v>0.27775849503975736</v>
+        <v>0.047378955034158642</v>
       </c>
       <c r="C67" s="0">
-        <v>0.098381972575941626</v>
+        <v>0.27775852111890525</v>
       </c>
       <c r="D67" s="0">
-        <v>0.04737890733355829</v>
+        <v>0.098384261924148439</v>
       </c>
       <c r="E67" s="0">
-        <v>0.0053374801788501495</v>
+        <v>2.5184546708723814</v>
       </c>
       <c r="F67" s="0">
-        <v>2.5184545524449526</v>
+        <v>0.0053376654953118195</v>
       </c>
     </row>
     <row r="68">
@@ -7063,19 +7063,19 @@
         <v>147</v>
       </c>
       <c r="B68" s="0">
-        <v>0.031084322616272479</v>
+        <v>0.047561586596112475</v>
       </c>
       <c r="C68" s="0">
-        <v>0.16721970411435946</v>
+        <v>0.031084483135152455</v>
       </c>
       <c r="D68" s="0">
-        <v>0.047561490917192605</v>
+        <v>0.16722283866524496</v>
       </c>
       <c r="E68" s="0">
-        <v>2.9245497815834307</v>
+        <v>0</v>
       </c>
       <c r="F68" s="0">
-        <v>0</v>
+        <v>2.9245498006591615</v>
       </c>
     </row>
     <row r="69">
@@ -7083,19 +7083,19 @@
         <v>148</v>
       </c>
       <c r="B69" s="0">
-        <v>0.051105873596352276</v>
+        <v>0.043642850171905154</v>
       </c>
       <c r="C69" s="0">
-        <v>1.3044449983692714</v>
+        <v>0.051105884288288494</v>
       </c>
       <c r="D69" s="0">
-        <v>0.043642809336077171</v>
+        <v>1.3044778319142978</v>
       </c>
       <c r="E69" s="0">
-        <v>0.0267029416529923</v>
+        <v>0.0047444945117118493</v>
       </c>
       <c r="F69" s="0">
-        <v>0.0047444232066089723</v>
+        <v>0.026702768819104813</v>
       </c>
     </row>
     <row r="70">
@@ -7103,19 +7103,19 @@
         <v>149</v>
       </c>
       <c r="B70" s="0">
-        <v>0.29773803089641604</v>
+        <v>0.048919190597851825</v>
       </c>
       <c r="C70" s="0">
-        <v>0.10340679574163687</v>
+        <v>0.29773805711603557</v>
       </c>
       <c r="D70" s="0">
-        <v>0.048919143559162832</v>
+        <v>0.10340922416281743</v>
       </c>
       <c r="E70" s="0">
-        <v>0.0039629128789239682</v>
+        <v>2.5259295055423685</v>
       </c>
       <c r="F70" s="0">
-        <v>2.5259293765614887</v>
+        <v>0.0039631009326577356</v>
       </c>
     </row>
     <row r="71">
@@ -7123,19 +7123,19 @@
         <v>150</v>
       </c>
       <c r="B71" s="0">
-        <v>0.040863733651950923</v>
+        <v>0.046955785493553309</v>
       </c>
       <c r="C71" s="0">
-        <v>0.090704240576752748</v>
+        <v>0.040863930916330137</v>
       </c>
       <c r="D71" s="0">
-        <v>0.046955771870687099</v>
+        <v>0.090705851305388482</v>
       </c>
       <c r="E71" s="0">
-        <v>3.0879278295284829</v>
+        <v>0.0067784451352323688</v>
       </c>
       <c r="F71" s="0">
-        <v>0.0067783883989536399</v>
+        <v>3.0879278340934269</v>
       </c>
     </row>
     <row r="72">
@@ -7143,19 +7143,19 @@
         <v>151</v>
       </c>
       <c r="B72" s="0">
-        <v>0.048951772114739216</v>
+        <v>0.045644503962030202</v>
       </c>
       <c r="C72" s="0">
-        <v>1.2888679818242785</v>
+        <v>0.048951772837165272</v>
       </c>
       <c r="D72" s="0">
-        <v>0.045644446391595539</v>
+        <v>1.2889003914736203</v>
       </c>
       <c r="E72" s="0">
-        <v>0.029863767811765529</v>
+        <v>0.0066867553640865109</v>
       </c>
       <c r="F72" s="0">
-        <v>0.006686682198177204</v>
+        <v>0.029863596980931745</v>
       </c>
     </row>
     <row r="73">
@@ -7163,19 +7163,19 @@
         <v>152</v>
       </c>
       <c r="B73" s="0">
-        <v>0.088470048330507881</v>
+        <v>0.048650200228275202</v>
       </c>
       <c r="C73" s="0">
-        <v>0.073427465953971358</v>
+        <v>0.088470132522465258</v>
       </c>
       <c r="D73" s="0">
-        <v>0.048650159331723418</v>
+        <v>0.073429071275439281</v>
       </c>
       <c r="E73" s="0">
-        <v>0.014453096604457491</v>
+        <v>0.81809165443439114</v>
       </c>
       <c r="F73" s="0">
-        <v>0.81809158470670751</v>
+        <v>0.014453174471493085</v>
       </c>
     </row>
     <row r="74">
@@ -7183,19 +7183,19 @@
         <v>153</v>
       </c>
       <c r="B74" s="0">
-        <v>0.087341920174367413</v>
+        <v>0.04473289018279987</v>
       </c>
       <c r="C74" s="0">
-        <v>0.11752101339806362</v>
+        <v>0.087342044468190286</v>
       </c>
       <c r="D74" s="0">
-        <v>0.044732836215024857</v>
+        <v>0.11752325837905248</v>
       </c>
       <c r="E74" s="0">
-        <v>2.3228988173297935</v>
+        <v>0.0082003457762096065</v>
       </c>
       <c r="F74" s="0">
-        <v>0.0082002734464178932</v>
+        <v>2.3228988388115117</v>
       </c>
     </row>
     <row r="75">
@@ -7203,19 +7203,19 @@
         <v>154</v>
       </c>
       <c r="B75" s="0">
-        <v>0.13295719216190979</v>
+        <v>0.047149391841137415</v>
       </c>
       <c r="C75" s="0">
-        <v>0.11604227601316132</v>
+        <v>0.13295725144099685</v>
       </c>
       <c r="D75" s="0">
-        <v>0.047149343254019309</v>
+        <v>0.1160449607102808</v>
       </c>
       <c r="E75" s="0">
-        <v>0.021894821482855126</v>
+        <v>1.265280061112213</v>
       </c>
       <c r="F75" s="0">
-        <v>1.2652799824715604</v>
+        <v>0.021894920368175728</v>
       </c>
     </row>
     <row r="76">
@@ -7223,19 +7223,19 @@
         <v>155</v>
       </c>
       <c r="B76" s="0">
-        <v>0.039759664776663255</v>
+        <v>0.043418394280740458</v>
       </c>
       <c r="C76" s="0">
-        <v>0.067283899678362111</v>
+        <v>0.039759756821690195</v>
       </c>
       <c r="D76" s="0">
-        <v>0.04341835892224119</v>
+        <v>0.067285320542085109</v>
       </c>
       <c r="E76" s="0">
-        <v>0.019583874389813034</v>
+        <v>0.015848517180000053</v>
       </c>
       <c r="F76" s="0">
-        <v>0.015848462184437695</v>
+        <v>0.01958390631314065</v>
       </c>
     </row>
     <row r="77">
@@ -7243,19 +7243,19 @@
         <v>156</v>
       </c>
       <c r="B77" s="0">
-        <v>0.12623802415781876</v>
+        <v>0.041536477780231278</v>
       </c>
       <c r="C77" s="0">
-        <v>0.090124314846201661</v>
+        <v>0.1262381295937349</v>
       </c>
       <c r="D77" s="0">
-        <v>0.04153644393339774</v>
+        <v>0.090126049153039234</v>
       </c>
       <c r="E77" s="0">
-        <v>1.4917899790537092</v>
+        <v>0.0024260691851148092</v>
       </c>
       <c r="F77" s="0">
-        <v>0.0024259812763042354</v>
+        <v>1.4917900157881334</v>
       </c>
     </row>
     <row r="78">
@@ -7263,19 +7263,19 @@
         <v>157</v>
       </c>
       <c r="B78" s="0">
-        <v>0.044797936505684539</v>
+        <v>0.044938267483201913</v>
       </c>
       <c r="C78" s="0">
-        <v>0.09563805077213923</v>
+        <v>0.044798034241073016</v>
       </c>
       <c r="D78" s="0">
-        <v>0.044938235916603307</v>
+        <v>0.095640204898750234</v>
       </c>
       <c r="E78" s="0">
-        <v>0.025863619292943837</v>
+        <v>0.0027564207899983531</v>
       </c>
       <c r="F78" s="0">
-        <v>0.0027563616737081467</v>
+        <v>0.025863646713334788</v>
       </c>
     </row>
     <row r="79">
@@ -7283,19 +7283,19 @@
         <v>158</v>
       </c>
       <c r="B79" s="0">
-        <v>0.30424598839493838</v>
+        <v>0.042937864057602762</v>
       </c>
       <c r="C79" s="0">
-        <v>0.10069612633844401</v>
+        <v>0.30424601942337631</v>
       </c>
       <c r="D79" s="0">
-        <v>0.042937850095540867</v>
+        <v>0.10069854021861485</v>
       </c>
       <c r="E79" s="0">
-        <v>0.0068290115566596761</v>
+        <v>2.5080357438173069</v>
       </c>
       <c r="F79" s="0">
-        <v>2.5080356137031159</v>
+        <v>0.0068292006674534767</v>
       </c>
     </row>
     <row r="80">
@@ -7303,19 +7303,19 @@
         <v>159</v>
       </c>
       <c r="B80" s="0">
-        <v>0.041264520819300661</v>
+        <v>0.047608163486328764</v>
       </c>
       <c r="C80" s="0">
-        <v>0.087225115567474296</v>
+        <v>0.041264721363880215</v>
       </c>
       <c r="D80" s="0">
-        <v>0.047608151807524417</v>
+        <v>0.087226602165206904</v>
       </c>
       <c r="E80" s="0">
-        <v>3.0921484793471845</v>
+        <v>0.0063740209667502643</v>
       </c>
       <c r="F80" s="0">
-        <v>0.0063739634603824655</v>
+        <v>3.0921484890105098</v>
       </c>
     </row>
     <row r="81">
@@ -7323,19 +7323,19 @@
         <v>160</v>
       </c>
       <c r="B81" s="0">
-        <v>0.041036733472680449</v>
+        <v>0.043292415455205575</v>
       </c>
       <c r="C81" s="0">
-        <v>1.1702147127830729</v>
+        <v>0.041036747963972046</v>
       </c>
       <c r="D81" s="0">
-        <v>0.043292368436598679</v>
+        <v>1.1702440891135784</v>
       </c>
       <c r="E81" s="0">
-        <v>0.031898771910086381</v>
+        <v>0.0078340500175358308</v>
       </c>
       <c r="F81" s="0">
-        <v>0.0078339857954224344</v>
+        <v>0.031898622741476916</v>
       </c>
     </row>
     <row r="82">
@@ -7343,19 +7343,19 @@
         <v>161</v>
       </c>
       <c r="B82" s="0">
-        <v>0.038251710647667726</v>
+        <v>0.043990863210448934</v>
       </c>
       <c r="C82" s="0">
-        <v>0.06182047966589118</v>
+        <v>0.038251798795461513</v>
       </c>
       <c r="D82" s="0">
-        <v>0.043990820905740302</v>
+        <v>0.061821726898229512</v>
       </c>
       <c r="E82" s="0">
-        <v>0.019570297483254881</v>
+        <v>0.0079719449560750194</v>
       </c>
       <c r="F82" s="0">
-        <v>0.0079718905360362368</v>
+        <v>0.01957033178265281</v>
       </c>
     </row>
     <row r="83">
@@ -7363,19 +7363,19 @@
         <v>162</v>
       </c>
       <c r="B83" s="0">
-        <v>0.05365997027410499</v>
+        <v>0.050737178553781112</v>
       </c>
       <c r="C83" s="0">
-        <v>0.086569030306326261</v>
+        <v>0.053660074242197667</v>
       </c>
       <c r="D83" s="0">
-        <v>0.05073713423080202</v>
+        <v>0.086570883894358228</v>
       </c>
       <c r="E83" s="0">
-        <v>0.050768208744768277</v>
+        <v>0.0034857074964802044</v>
       </c>
       <c r="F83" s="0">
-        <v>0.0034856400556295911</v>
+        <v>0.050768244820366182</v>
       </c>
     </row>
     <row r="84">
@@ -7383,19 +7383,19 @@
         <v>163</v>
       </c>
       <c r="B84" s="0">
-        <v>0.043402878514023552</v>
+        <v>0.045902577490793559</v>
       </c>
       <c r="C84" s="0">
-        <v>0.097311721409108556</v>
+        <v>0.043402969849289409</v>
       </c>
       <c r="D84" s="0">
-        <v>0.045902534531311878</v>
+        <v>0.097313876598667789</v>
       </c>
       <c r="E84" s="0">
-        <v>0.025325796895060631</v>
+        <v>0.0025621056939965862</v>
       </c>
       <c r="F84" s="0">
-        <v>0.0025620471959513615</v>
+        <v>0.025325825604023453</v>
       </c>
     </row>
     <row r="85">
@@ -7403,19 +7403,19 @@
         <v>164</v>
       </c>
       <c r="B85" s="0">
-        <v>0.16969974964211604</v>
+        <v>0.044781946255620923</v>
       </c>
       <c r="C85" s="0">
-        <v>0.092253132259503101</v>
+        <v>0.16969979506677213</v>
       </c>
       <c r="D85" s="0">
-        <v>0.044781892934576934</v>
+        <v>0.092255174156151129</v>
       </c>
       <c r="E85" s="0">
-        <v>0.017302790357085932</v>
+        <v>1.2577500538009523</v>
       </c>
       <c r="F85" s="0">
-        <v>1.2577499645544659</v>
+        <v>0.017302900895243008</v>
       </c>
     </row>
     <row r="86">
@@ -7423,19 +7423,19 @@
         <v>165</v>
       </c>
       <c r="B86" s="0">
-        <v>0.042015554906076259</v>
+        <v>0.047237265179748147</v>
       </c>
       <c r="C86" s="0">
-        <v>0.078060214841781439</v>
+        <v>0.042015757914629824</v>
       </c>
       <c r="D86" s="0">
-        <v>0.047237253581523357</v>
+        <v>0.078061541461337772</v>
       </c>
       <c r="E86" s="0">
-        <v>3.0927573249200906</v>
+        <v>0.015964050317695152</v>
       </c>
       <c r="F86" s="0">
-        <v>0.015963992954135395</v>
+        <v>3.0927573285312997</v>
       </c>
     </row>
     <row r="87">
@@ -7443,19 +7443,19 @@
         <v>166</v>
       </c>
       <c r="B87" s="0">
-        <v>0.044818191714758149</v>
+        <v>0.042853750832802538</v>
       </c>
       <c r="C87" s="0">
-        <v>1.0348656381812482</v>
+        <v>0.044818240723997711</v>
       </c>
       <c r="D87" s="0">
-        <v>0.042853732589001187</v>
+        <v>1.0348917022464246</v>
       </c>
       <c r="E87" s="0">
-        <v>0.028029504846855586</v>
+        <v>0.0069181642808995633</v>
       </c>
       <c r="F87" s="0">
-        <v>0.0069181001157942578</v>
+        <v>0.028029372744751459</v>
       </c>
     </row>
     <row r="88">
@@ -7463,19 +7463,19 @@
         <v>167</v>
       </c>
       <c r="B88" s="0">
-        <v>0.058900094891988879</v>
+        <v>0.084522146516239932</v>
       </c>
       <c r="C88" s="0">
-        <v>0.05002085957167602</v>
+        <v>0.058900295540422427</v>
       </c>
       <c r="D88" s="0">
-        <v>0.084522088409618987</v>
+        <v>0.050021667372608616</v>
       </c>
       <c r="E88" s="0">
-        <v>0.046929022298473524</v>
+        <v>0.0050819713693327547</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0050818726215439633</v>
+        <v>0.046929085368043168</v>
       </c>
     </row>
     <row r="89">
@@ -7483,19 +7483,19 @@
         <v>168</v>
       </c>
       <c r="B89" s="0">
-        <v>0.0026714063151682776</v>
+        <v>0.0029788044760826761</v>
       </c>
       <c r="C89" s="0">
-        <v>0.011066963632800027</v>
+        <v>0.0026714115213657998</v>
       </c>
       <c r="D89" s="0">
-        <v>0.0029787979229898738</v>
+        <v>0.01106719656868994</v>
       </c>
       <c r="E89" s="0">
-        <v>0.0047042861866188803</v>
+        <v>0</v>
       </c>
       <c r="F89" s="0">
-        <v>0</v>
+        <v>0.00470428924154127</v>
       </c>
     </row>
     <row r="90">
@@ -7503,19 +7503,19 @@
         <v>169</v>
       </c>
       <c r="B90" s="0">
-        <v>0.0015558542633114898</v>
+        <v>0.0028202544498436995</v>
       </c>
       <c r="C90" s="0">
-        <v>0.075100895434309811</v>
+        <v>0.0015558532393459541</v>
       </c>
       <c r="D90" s="0">
-        <v>0.0028202452102402535</v>
+        <v>0.075102762236522708</v>
       </c>
       <c r="E90" s="0">
-        <v>0.0037744521911111059</v>
+        <v>0</v>
       </c>
       <c r="F90" s="0">
-        <v>0</v>
+        <v>0.003774442911989793</v>
       </c>
     </row>
   </sheetData>
@@ -7528,9 +7528,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
   </cols>
@@ -7560,19 +7560,19 @@
         <v>250</v>
       </c>
       <c r="B2" s="0">
-        <v>0.42631825139645524</v>
+        <v>0.35376769667477459</v>
       </c>
       <c r="C2" s="0">
-        <v>0.10787505285910304</v>
+        <v>0.42631831785643037</v>
       </c>
       <c r="D2" s="0">
-        <v>0.35376722708424568</v>
+        <v>0.10787322108366791</v>
       </c>
       <c r="E2" s="0">
-        <v>0.17989271561084325</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>0.17989271410212701</v>
       </c>
     </row>
     <row r="3">
@@ -7580,19 +7580,19 @@
         <v>255</v>
       </c>
       <c r="B3" s="0">
-        <v>0.22715216306677491</v>
+        <v>0.34031875467663764</v>
       </c>
       <c r="C3" s="0">
-        <v>0.1793248320108545</v>
+        <v>0.22715220276212178</v>
       </c>
       <c r="D3" s="0">
-        <v>0.34031825545765282</v>
+        <v>0.17932190657631109</v>
       </c>
       <c r="E3" s="0">
-        <v>0.24273462833363041</v>
+        <v>0.008632566854349006</v>
       </c>
       <c r="F3" s="0">
-        <v>0.0086325713727132478</v>
+        <v>0.24273463460965494</v>
       </c>
     </row>
     <row r="4">
@@ -7600,19 +7600,19 @@
         <v>260</v>
       </c>
       <c r="B4" s="0">
-        <v>0.10139934383033826</v>
+        <v>0.30567761429986529</v>
       </c>
       <c r="C4" s="0">
-        <v>0.27485790195265775</v>
+        <v>0.101399327308165</v>
       </c>
       <c r="D4" s="0">
-        <v>0.3056770392778384</v>
+        <v>0.27485347716186875</v>
       </c>
       <c r="E4" s="0">
-        <v>0.30708768197140285</v>
+        <v>0.032344399612226023</v>
       </c>
       <c r="F4" s="0">
-        <v>0.032344405788278574</v>
+        <v>0.30708769586639439</v>
       </c>
     </row>
     <row r="5">
@@ -7620,19 +7620,19 @@
         <v>265</v>
       </c>
       <c r="B5" s="0">
-        <v>0.053083926077768275</v>
+        <v>0.26829706466893005</v>
       </c>
       <c r="C5" s="0">
-        <v>0.39374888768019323</v>
+        <v>0.053083862598316295</v>
       </c>
       <c r="D5" s="0">
-        <v>0.26829649564815594</v>
+        <v>0.39374260794517918</v>
       </c>
       <c r="E5" s="0">
-        <v>0.36240862559916892</v>
+        <v>0.065385199307604544</v>
       </c>
       <c r="F5" s="0">
-        <v>0.065385207301123557</v>
+        <v>0.36240864793944594</v>
       </c>
     </row>
     <row r="6">
@@ -7640,19 +7640,19 @@
         <v>270</v>
       </c>
       <c r="B6" s="0">
-        <v>0.051075109131563323</v>
+        <v>0.23797783449136739</v>
       </c>
       <c r="C6" s="0">
-        <v>0.49588716898233903</v>
+        <v>0.051075019971407704</v>
       </c>
       <c r="D6" s="0">
-        <v>0.23797759321805806</v>
+        <v>0.49588265956808714</v>
       </c>
       <c r="E6" s="0">
-        <v>0.39607331047717265</v>
+        <v>0.11295327398185666</v>
       </c>
       <c r="F6" s="0">
-        <v>0.1129532778401169</v>
+        <v>0.39607332675278722</v>
       </c>
     </row>
     <row r="7">
@@ -7660,19 +7660,19 @@
         <v>275</v>
       </c>
       <c r="B7" s="0">
-        <v>0.069546816109470555</v>
+        <v>0.20932866564421201</v>
       </c>
       <c r="C7" s="0">
-        <v>0.51151627696521662</v>
+        <v>0.06954671845849976</v>
       </c>
       <c r="D7" s="0">
-        <v>0.20932884218998643</v>
+        <v>0.51151625040525994</v>
       </c>
       <c r="E7" s="0">
-        <v>0.4111951290758023</v>
+        <v>0.17998342320617405</v>
       </c>
       <c r="F7" s="0">
-        <v>0.17998342217051</v>
+        <v>0.41119512960076005</v>
       </c>
     </row>
     <row r="8">
@@ -7680,19 +7680,19 @@
         <v>280</v>
       </c>
       <c r="B8" s="0">
-        <v>0.10202893016954567</v>
+        <v>0.1884120701362671</v>
       </c>
       <c r="C8" s="0">
-        <v>0.41827220204132537</v>
+        <v>0.10202888945767283</v>
       </c>
       <c r="D8" s="0">
-        <v>0.18841338354186135</v>
+        <v>0.41828984406438835</v>
       </c>
       <c r="E8" s="0">
-        <v>0.39821658333981019</v>
+        <v>0.26321710445550717</v>
       </c>
       <c r="F8" s="0">
-        <v>0.26321708694966639</v>
+        <v>0.39821653090419751</v>
       </c>
     </row>
     <row r="9">
@@ -7700,19 +7700,19 @@
         <v>285</v>
       </c>
       <c r="B9" s="0">
-        <v>0.14627024804474645</v>
+        <v>0.16904293286400968</v>
       </c>
       <c r="C9" s="0">
-        <v>0.2019731611144541</v>
+        <v>0.14627007695355035</v>
       </c>
       <c r="D9" s="0">
-        <v>0.16904272553557526</v>
+        <v>0.20196859496559552</v>
       </c>
       <c r="E9" s="0">
-        <v>0.35078910903868482</v>
+        <v>0.35231377661117341</v>
       </c>
       <c r="F9" s="0">
-        <v>0.35231378664036084</v>
+        <v>0.3507891152447179</v>
       </c>
     </row>
     <row r="10">
@@ -7720,19 +7720,19 @@
         <v>290</v>
       </c>
       <c r="B10" s="0">
-        <v>0.19830545065564842</v>
+        <v>0.15813918887509362</v>
       </c>
       <c r="C10" s="0">
-        <v>0.045622295993947994</v>
+        <v>0.19830530054347406</v>
       </c>
       <c r="D10" s="0">
-        <v>0.15813935398950144</v>
+        <v>0.045621376834641222</v>
       </c>
       <c r="E10" s="0">
-        <v>0.24679502176545176</v>
+        <v>0.4216345041997821</v>
       </c>
       <c r="F10" s="0">
-        <v>0.42163450782588585</v>
+        <v>0.24679501964497461</v>
       </c>
     </row>
     <row r="11">
@@ -7740,19 +7740,19 @@
         <v>295</v>
       </c>
       <c r="B11" s="0">
-        <v>0.24837310053148351</v>
+        <v>0.14916599581369402</v>
       </c>
       <c r="C11" s="0">
-        <v>0.0099761949708584933</v>
+        <v>0.24837296565758848</v>
       </c>
       <c r="D11" s="0">
-        <v>0.14916626341102324</v>
+        <v>0.0099759281940742708</v>
       </c>
       <c r="E11" s="0">
-        <v>0.11180033042031384</v>
+        <v>0.44965173488418198</v>
       </c>
       <c r="F11" s="0">
-        <v>0.44965173677543713</v>
+        <v>0.111800327152031</v>
       </c>
     </row>
     <row r="12">
@@ -7760,19 +7760,19 @@
         <v>300</v>
       </c>
       <c r="B12" s="0">
-        <v>0.29129220775284753</v>
+        <v>0.14145774819681081</v>
       </c>
       <c r="C12" s="0">
-        <v>0.005853403995589963</v>
+        <v>0.29129209929768751</v>
       </c>
       <c r="D12" s="0">
-        <v>0.14145805453212138</v>
+        <v>0.0058535374303366004</v>
       </c>
       <c r="E12" s="0">
-        <v>0.042971568495828248</v>
+        <v>0.42445103703879472</v>
       </c>
       <c r="F12" s="0">
-        <v>0.42445103840084081</v>
+        <v>0.042971562586850434</v>
       </c>
     </row>
     <row r="13">
@@ -7780,19 +7780,19 @@
         <v>305</v>
       </c>
       <c r="B13" s="0">
-        <v>0.32163552587487332</v>
+        <v>0.13781277415222368</v>
       </c>
       <c r="C13" s="0">
-        <v>0.0040786814971165101</v>
+        <v>0.32163546269746146</v>
       </c>
       <c r="D13" s="0">
-        <v>0.13781306208262595</v>
+        <v>0.0040793478364449468</v>
       </c>
       <c r="E13" s="0">
-        <v>0.01448643006221023</v>
+        <v>0.34739693146960948</v>
       </c>
       <c r="F13" s="0">
-        <v>0.34739693313316039</v>
+        <v>0.014486422088431421</v>
       </c>
     </row>
     <row r="14">
@@ -7800,19 +7800,19 @@
         <v>310</v>
       </c>
       <c r="B14" s="0">
-        <v>0.33281401312624853</v>
+        <v>0.13632253943392578</v>
       </c>
       <c r="C14" s="0">
-        <v>0.0051211564777722896</v>
+        <v>0.33281405030766126</v>
       </c>
       <c r="D14" s="0">
-        <v>0.13632336303861653</v>
+        <v>0.005135433189979461</v>
       </c>
       <c r="E14" s="0">
-        <v>0.004506708935034116</v>
+        <v>0.23364971753142119</v>
       </c>
       <c r="F14" s="0">
-        <v>0.23364970965596854</v>
+        <v>0.004506667406829091</v>
       </c>
     </row>
     <row r="15">
@@ -7820,19 +7820,19 @@
         <v>315</v>
       </c>
       <c r="B15" s="0">
-        <v>0.32031584449422407</v>
+        <v>0.13795465298749604</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0043499832312706189</v>
+        <v>0.32031592781808077</v>
       </c>
       <c r="D15" s="0">
-        <v>0.13795540376942372</v>
+        <v>0.0043626119555355228</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0017713748231496036</v>
+        <v>0.12806712618501029</v>
       </c>
       <c r="F15" s="0">
-        <v>0.12806711803731666</v>
+        <v>0.001771333163468336</v>
       </c>
     </row>
     <row r="16">
@@ -7840,19 +7840,19 @@
         <v>320</v>
       </c>
       <c r="B16" s="0">
-        <v>0.28611651541753686</v>
+        <v>0.14201970929393154</v>
       </c>
       <c r="C16" s="0">
-        <v>0.0067661710183757415</v>
+        <v>0.28611662403755689</v>
       </c>
       <c r="D16" s="0">
-        <v>0.14202043697844816</v>
+        <v>0.0067833680943028473</v>
       </c>
       <c r="E16" s="0">
-        <v>0.0012378528652720411</v>
+        <v>0.059082953424401667</v>
       </c>
       <c r="F16" s="0">
-        <v>0.059082944693546857</v>
+        <v>0.0012378087508776755</v>
       </c>
     </row>
     <row r="17">
@@ -7860,19 +7860,19 @@
         <v>325</v>
       </c>
       <c r="B17" s="0">
-        <v>0.24017585967324848</v>
+        <v>0.15012313679557102</v>
       </c>
       <c r="C17" s="0">
-        <v>0</v>
+        <v>0.24017592936737123</v>
       </c>
       <c r="D17" s="0">
-        <v>0.15012323672092873</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0">
-        <v>0.0010151928458912542</v>
+        <v>0.024947210891791964</v>
       </c>
       <c r="F17" s="0">
-        <v>0.024947209530521403</v>
+        <v>0.0010151897033647073</v>
       </c>
     </row>
     <row r="18">
@@ -7880,19 +7880,19 @@
         <v>330</v>
       </c>
       <c r="B18" s="0">
-        <v>0.18975775357037333</v>
+        <v>0.15945805633356511</v>
       </c>
       <c r="C18" s="0">
-        <v>0</v>
+        <v>0.18975782197234381</v>
       </c>
       <c r="D18" s="0">
-        <v>0.15945811726851264</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>0.00085595449309716447</v>
+        <v>0.01061501256903782</v>
       </c>
       <c r="F18" s="0">
-        <v>0.010615010458185591</v>
+        <v>0.0008559539871417298</v>
       </c>
     </row>
     <row r="19">
@@ -7900,19 +7900,19 @@
         <v>335</v>
       </c>
       <c r="B19" s="0">
-        <v>0.14238249435834169</v>
+        <v>0.16559567620724894</v>
       </c>
       <c r="C19" s="0">
-        <v>0</v>
+        <v>0.14238255773836803</v>
       </c>
       <c r="D19" s="0">
-        <v>0.16559571876663448</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>0.00059239270668839863</v>
+        <v>0.0042035078694279641</v>
       </c>
       <c r="F19" s="0">
-        <v>0.004203504826351543</v>
+        <v>0.00059239561989310116</v>
       </c>
     </row>
     <row r="20">
@@ -7920,19 +7920,19 @@
         <v>340</v>
       </c>
       <c r="B20" s="0">
-        <v>0.099896604829079347</v>
+        <v>0.16867447676721614</v>
       </c>
       <c r="C20" s="0">
-        <v>0</v>
+        <v>0.099896662786215146</v>
       </c>
       <c r="D20" s="0">
-        <v>0.16867449078228267</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>0.00026147003200275009</v>
+        <v>0.00091851069339476542</v>
       </c>
       <c r="F20" s="0">
-        <v>0.00091850722251192495</v>
+        <v>0.00026147575366545334</v>
       </c>
     </row>
     <row r="21">
@@ -7940,19 +7940,19 @@
         <v>345</v>
       </c>
       <c r="B21" s="0">
-        <v>0.063555844012232743</v>
+        <v>0.16550602272032994</v>
       </c>
       <c r="C21" s="0">
-        <v>0</v>
+        <v>0.063555911647408869</v>
       </c>
       <c r="D21" s="0">
-        <v>0.16550603437589387</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0">
-        <v>0.00018704596667979963</v>
+        <v>0</v>
       </c>
       <c r="F21" s="0">
-        <v>0</v>
+        <v>0.00018704776253261935</v>
       </c>
     </row>
     <row r="22">
@@ -7960,13 +7960,13 @@
         <v>350</v>
       </c>
       <c r="B22" s="0">
-        <v>0.036661880624007166</v>
+        <v>0.15896268513896703</v>
       </c>
       <c r="C22" s="0">
-        <v>0</v>
+        <v>0.036661950352178258</v>
       </c>
       <c r="D22" s="0">
-        <v>0.15896268397906052</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -7980,13 +7980,13 @@
         <v>355</v>
       </c>
       <c r="B23" s="0">
-        <v>0.019143332176767971</v>
+        <v>0.15189954459313235</v>
       </c>
       <c r="C23" s="0">
-        <v>0</v>
+        <v>0.019143400454488802</v>
       </c>
       <c r="D23" s="0">
-        <v>0.15189955093319171</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -8000,13 +8000,13 @@
         <v>360</v>
       </c>
       <c r="B24" s="0">
-        <v>0.0078709246383262647</v>
+        <v>0.14549777194314817</v>
       </c>
       <c r="C24" s="0">
-        <v>0</v>
+        <v>0.0078709846971197622</v>
       </c>
       <c r="D24" s="0">
-        <v>0.14549777247498552</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -8020,13 +8020,13 @@
         <v>365</v>
       </c>
       <c r="B25" s="0">
-        <v>0.001818726718668105</v>
+        <v>0.1373361835235421</v>
       </c>
       <c r="C25" s="0">
-        <v>0</v>
+        <v>0.0018187757167187244</v>
       </c>
       <c r="D25" s="0">
-        <v>0.13733618713210757</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -8040,13 +8040,13 @@
         <v>370</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>0.12516962757398861</v>
       </c>
       <c r="C26" s="0">
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>0.12516959672980929</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>375</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>0.11280002090908352</v>
       </c>
       <c r="C27" s="0">
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>0.11279999391616689</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -8080,13 +8080,13 @@
         <v>380</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>0.098267353996885076</v>
       </c>
       <c r="C28" s="0">
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>0.09826731252835591</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -8100,13 +8100,13 @@
         <v>385</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>0.086818599637776703</v>
       </c>
       <c r="C29" s="0">
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>0.086818558631237192</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -8120,13 +8120,13 @@
         <v>390</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>0.073040383180702134</v>
       </c>
       <c r="C30" s="0">
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>0.073040331927945332</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -8140,13 +8140,13 @@
         <v>395</v>
       </c>
       <c r="B31" s="0">
-        <v>0</v>
+        <v>0.061338025866450617</v>
       </c>
       <c r="C31" s="0">
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>0.061337978269637605</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
@@ -8160,13 +8160,13 @@
         <v>400</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>0.05339411697054957</v>
       </c>
       <c r="C32" s="0">
         <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>0.053394065920171215</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
         <v>0</v>
@@ -8180,13 +8180,13 @@
         <v>405</v>
       </c>
       <c r="B33" s="0">
-        <v>0</v>
+        <v>0.047018510207026743</v>
       </c>
       <c r="C33" s="0">
         <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>0.047018465811128687</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
         <v>0</v>
@@ -8200,13 +8200,13 @@
         <v>410</v>
       </c>
       <c r="B34" s="0">
-        <v>0</v>
+        <v>0.039438131223805128</v>
       </c>
       <c r="C34" s="0">
         <v>0</v>
       </c>
       <c r="D34" s="0">
-        <v>0.039438089328015714</v>
+        <v>0</v>
       </c>
       <c r="E34" s="0">
         <v>0</v>
@@ -8220,13 +8220,13 @@
         <v>415</v>
       </c>
       <c r="B35" s="0">
-        <v>0</v>
+        <v>0.034678699801530273</v>
       </c>
       <c r="C35" s="0">
         <v>0</v>
       </c>
       <c r="D35" s="0">
-        <v>0.034678662385461676</v>
+        <v>0</v>
       </c>
       <c r="E35" s="0">
         <v>0</v>
@@ -8240,13 +8240,13 @@
         <v>420</v>
       </c>
       <c r="B36" s="0">
-        <v>0</v>
+        <v>0.029845041916839295</v>
       </c>
       <c r="C36" s="0">
         <v>0</v>
       </c>
       <c r="D36" s="0">
-        <v>0.029845004978104335</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0">
         <v>0</v>
@@ -8260,13 +8260,13 @@
         <v>425</v>
       </c>
       <c r="B37" s="0">
-        <v>0</v>
+        <v>0.025393545122949935</v>
       </c>
       <c r="C37" s="0">
         <v>0</v>
       </c>
       <c r="D37" s="0">
-        <v>0.025393511672309601</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
         <v>0</v>
@@ -8280,13 +8280,13 @@
         <v>430</v>
       </c>
       <c r="B38" s="0">
-        <v>0</v>
+        <v>0.021642427546618378</v>
       </c>
       <c r="C38" s="0">
         <v>0</v>
       </c>
       <c r="D38" s="0">
-        <v>0.021642396352563868</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0">
         <v>0</v>
@@ -8300,13 +8300,13 @@
         <v>435</v>
       </c>
       <c r="B39" s="0">
-        <v>0</v>
+        <v>0.018365586992200388</v>
       </c>
       <c r="C39" s="0">
         <v>0</v>
       </c>
       <c r="D39" s="0">
-        <v>0.01836555847188337</v>
+        <v>0</v>
       </c>
       <c r="E39" s="0">
         <v>0</v>
@@ -8320,13 +8320,13 @@
         <v>440</v>
       </c>
       <c r="B40" s="0">
-        <v>0</v>
+        <v>0.016523473542392538</v>
       </c>
       <c r="C40" s="0">
         <v>0</v>
       </c>
       <c r="D40" s="0">
-        <v>0.016523446172709244</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
         <v>0</v>
@@ -8340,13 +8340,13 @@
         <v>445</v>
       </c>
       <c r="B41" s="0">
-        <v>0</v>
+        <v>0.013790979508378399</v>
       </c>
       <c r="C41" s="0">
         <v>0</v>
       </c>
       <c r="D41" s="0">
-        <v>0.013790955456874069</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0">
         <v>0</v>
@@ -8360,13 +8360,13 @@
         <v>450</v>
       </c>
       <c r="B42" s="0">
-        <v>0</v>
+        <v>0.011300781717113928</v>
       </c>
       <c r="C42" s="0">
         <v>0</v>
       </c>
       <c r="D42" s="0">
-        <v>0.011300760233318653</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0">
         <v>0</v>
@@ -8385,9 +8385,9 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
   </cols>
@@ -8417,19 +8417,19 @@
         <v>301.47300000000001</v>
       </c>
       <c r="B2" s="0">
-        <v>0.0053595826256939792</v>
+        <v>0.01539538818774013</v>
       </c>
       <c r="C2" s="0">
-        <v>0.45469162390924312</v>
+        <v>0.0053599971130356269</v>
       </c>
       <c r="D2" s="0">
-        <v>0.015397195672309193</v>
+        <v>0.45469578493718971</v>
       </c>
       <c r="E2" s="0">
-        <v>0.0090362958192725575</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>0.0090363635011680397</v>
       </c>
     </row>
     <row r="3">
@@ -8437,19 +8437,19 @@
         <v>304.70800000000003</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0025254972772144682</v>
+        <v>0.016628089372153151</v>
       </c>
       <c r="C3" s="0">
-        <v>0.43645521631499928</v>
+        <v>0.0025258531331787738</v>
       </c>
       <c r="D3" s="0">
-        <v>0.016629761559659392</v>
+        <v>0.43645918683027829</v>
       </c>
       <c r="E3" s="0">
-        <v>0.014397068562421129</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>0.01439712774942783</v>
       </c>
     </row>
     <row r="4">
@@ -8457,19 +8457,19 @@
         <v>307.94499999999999</v>
       </c>
       <c r="B4" s="0">
-        <v>0.011232563174345759</v>
+        <v>0.020061527383317776</v>
       </c>
       <c r="C4" s="0">
-        <v>0.4058378707087516</v>
+        <v>0.011232772592490248</v>
       </c>
       <c r="D4" s="0">
-        <v>0.020061108167847293</v>
+        <v>0.40583775666376343</v>
       </c>
       <c r="E4" s="0">
-        <v>0.023949907010327919</v>
+        <v>0.00023394530048231167</v>
       </c>
       <c r="F4" s="0">
-        <v>0.00023389139240581679</v>
+        <v>0.023949933115265255</v>
       </c>
     </row>
     <row r="5">
@@ -8477,19 +8477,19 @@
         <v>311.18400000000003</v>
       </c>
       <c r="B5" s="0">
-        <v>0.0063847748815453725</v>
+        <v>0.021857434049355164</v>
       </c>
       <c r="C5" s="0">
-        <v>0.35556407208582847</v>
+        <v>0.0063849887057230333</v>
       </c>
       <c r="D5" s="0">
-        <v>0.021857055099013256</v>
+        <v>0.35556397576420273</v>
       </c>
       <c r="E5" s="0">
-        <v>0.036630547609316694</v>
+        <v>0.00084904582281407251</v>
       </c>
       <c r="F5" s="0">
-        <v>0.00084900021002449187</v>
+        <v>0.036630568880078429</v>
       </c>
     </row>
     <row r="6">
@@ -8497,19 +8497,19 @@
         <v>314.42500000000001</v>
       </c>
       <c r="B6" s="0">
-        <v>0.011226586553701743</v>
+        <v>0.030526076509766711</v>
       </c>
       <c r="C6" s="0">
-        <v>0.3118928477780577</v>
+        <v>0.011226613051750852</v>
       </c>
       <c r="D6" s="0">
-        <v>0.030524470861370282</v>
+        <v>0.31189075417107215</v>
       </c>
       <c r="E6" s="0">
-        <v>0.053920106527362219</v>
+        <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>0</v>
+        <v>0.053920107635733204</v>
       </c>
     </row>
     <row r="7">
@@ -8517,19 +8517,19 @@
         <v>317.66800000000001</v>
       </c>
       <c r="B7" s="0">
-        <v>0.007067496808099866</v>
+        <v>0.024089458649573247</v>
       </c>
       <c r="C7" s="0">
-        <v>0.26144245190622173</v>
+        <v>0.0070674897673474457</v>
       </c>
       <c r="D7" s="0">
-        <v>0.024088117234319056</v>
+        <v>0.2614407026874121</v>
       </c>
       <c r="E7" s="0">
-        <v>0.074050308316797056</v>
+        <v>0.00014585758751560268</v>
       </c>
       <c r="F7" s="0">
-        <v>0.00014587913178621315</v>
+        <v>0.074050308066329465</v>
       </c>
     </row>
     <row r="8">
@@ -8537,19 +8537,19 @@
         <v>320.91300000000001</v>
       </c>
       <c r="B8" s="0">
-        <v>0.0030205708002960076</v>
+        <v>0.023311097971688271</v>
       </c>
       <c r="C8" s="0">
-        <v>0.22022640092409146</v>
+        <v>0.0030203197783463852</v>
       </c>
       <c r="D8" s="0">
-        <v>0.023308417633771693</v>
+        <v>0.22022244639722924</v>
       </c>
       <c r="E8" s="0">
-        <v>0.09806220832610657</v>
+        <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>0</v>
+        <v>0.098062184415780768</v>
       </c>
     </row>
     <row r="9">
@@ -8557,19 +8557,19 @@
         <v>324.16000000000003</v>
       </c>
       <c r="B9" s="0">
-        <v>0.003021177523720883</v>
+        <v>0.033138741304400955</v>
       </c>
       <c r="C9" s="0">
-        <v>0.18562311106962104</v>
+        <v>0.0030208352941395239</v>
       </c>
       <c r="D9" s="0">
-        <v>0.033137169910253325</v>
+        <v>0.1856199041001749</v>
       </c>
       <c r="E9" s="0">
-        <v>0.12593982899055942</v>
+        <v>0.00040792823259306742</v>
       </c>
       <c r="F9" s="0">
-        <v>0.00040823226267009489</v>
+        <v>0.12593982244364066</v>
       </c>
     </row>
     <row r="10">
@@ -8577,19 +8577,19 @@
         <v>327.40899999999999</v>
       </c>
       <c r="B10" s="0">
-        <v>0.0096610428908954545</v>
+        <v>0.043074045140587901</v>
       </c>
       <c r="C10" s="0">
-        <v>0.15345633421469862</v>
+        <v>0.0096606461167223004</v>
       </c>
       <c r="D10" s="0">
-        <v>0.043073500706942124</v>
+        <v>0.15345390919553259</v>
       </c>
       <c r="E10" s="0">
-        <v>0.15430354648127648</v>
+        <v>0.00017730835260307783</v>
       </c>
       <c r="F10" s="0">
-        <v>0.00017743144899638077</v>
+        <v>0.15430355596210249</v>
       </c>
     </row>
     <row r="11">
@@ -8597,19 +8597,19 @@
         <v>330.66000000000003</v>
       </c>
       <c r="B11" s="0">
-        <v>0.0083480673038647344</v>
+        <v>0.044256995611996308</v>
       </c>
       <c r="C11" s="0">
-        <v>0.12358536297205779</v>
+        <v>0.008347653842572236</v>
       </c>
       <c r="D11" s="0">
-        <v>0.044256374474707358</v>
+        <v>0.12358341772572821</v>
       </c>
       <c r="E11" s="0">
-        <v>0.18141011507388918</v>
+        <v>0.00099482984097781996</v>
       </c>
       <c r="F11" s="0">
-        <v>0.00099499122910063796</v>
+        <v>0.18141011974882754</v>
       </c>
     </row>
     <row r="12">
@@ -8617,19 +8617,19 @@
         <v>333.91199999999998</v>
       </c>
       <c r="B12" s="0">
-        <v>0.0047407968897488183</v>
+        <v>0.039642714472589186</v>
       </c>
       <c r="C12" s="0">
-        <v>0.098401500908450901</v>
+        <v>0.0047404389636062508</v>
       </c>
       <c r="D12" s="0">
-        <v>0.039643002001690644</v>
+        <v>0.098400041942912977</v>
       </c>
       <c r="E12" s="0">
-        <v>0.20521186936838429</v>
+        <v>0.0023776084288334672</v>
       </c>
       <c r="F12" s="0">
-        <v>0.0023776658947915444</v>
+        <v>0.20521188423028367</v>
       </c>
     </row>
     <row r="13">
@@ -8637,19 +8637,19 @@
         <v>337.16699999999997</v>
       </c>
       <c r="B13" s="0">
-        <v>0.003319274326024513</v>
+        <v>0.036216949609818395</v>
       </c>
       <c r="C13" s="0">
-        <v>0.076966936647269418</v>
+        <v>0.0033190404802959433</v>
       </c>
       <c r="D13" s="0">
-        <v>0.036216774687227081</v>
+        <v>0.076965767273136893</v>
       </c>
       <c r="E13" s="0">
-        <v>0.22474466463953224</v>
+        <v>0.0032289123338697392</v>
       </c>
       <c r="F13" s="0">
-        <v>0.0032289525402679048</v>
+        <v>0.22474466784423738</v>
       </c>
     </row>
     <row r="14">
@@ -8657,19 +8657,19 @@
         <v>340.423</v>
       </c>
       <c r="B14" s="0">
-        <v>0.0080801097133998377</v>
+        <v>0.058663231231246719</v>
       </c>
       <c r="C14" s="0">
-        <v>0.059541073089029922</v>
+        <v>0.0080799433717898377</v>
       </c>
       <c r="D14" s="0">
-        <v>0.058663088866803118</v>
+        <v>0.059540165054331448</v>
       </c>
       <c r="E14" s="0">
-        <v>0.23983862893113142</v>
+        <v>0.0033245639945861587</v>
       </c>
       <c r="F14" s="0">
-        <v>0.0033245832533389716</v>
+        <v>0.23983863036183084</v>
       </c>
     </row>
     <row r="15">
@@ -8677,19 +8677,19 @@
         <v>343.68200000000002</v>
       </c>
       <c r="B15" s="0">
-        <v>0.010482432913211083</v>
+        <v>0.048297342910866493</v>
       </c>
       <c r="C15" s="0">
-        <v>0.046315202338532285</v>
+        <v>0.010482320293146259</v>
       </c>
       <c r="D15" s="0">
-        <v>0.048297070222541143</v>
+        <v>0.046314503702600173</v>
       </c>
       <c r="E15" s="0">
-        <v>0.25065990487054585</v>
+        <v>0.0045247546385001362</v>
       </c>
       <c r="F15" s="0">
-        <v>0.0045247725248032519</v>
+        <v>0.25065990162279472</v>
       </c>
     </row>
     <row r="16">
@@ -8697,19 +8697,19 @@
         <v>346.94200000000001</v>
       </c>
       <c r="B16" s="0">
-        <v>0.010058376769234144</v>
+        <v>0.045012577085043859</v>
       </c>
       <c r="C16" s="0">
-        <v>0.033535287260111901</v>
+        <v>0.010058315456145229</v>
       </c>
       <c r="D16" s="0">
-        <v>0.045012548500670102</v>
+        <v>0.033534847971081916</v>
       </c>
       <c r="E16" s="0">
-        <v>0.25760744503151606</v>
+        <v>0.0055945896099887493</v>
       </c>
       <c r="F16" s="0">
-        <v>0.0055946007456696371</v>
+        <v>0.25760744283917775</v>
       </c>
     </row>
     <row r="17">
@@ -8717,19 +8717,19 @@
         <v>350.20400000000001</v>
       </c>
       <c r="B17" s="0">
-        <v>0.017666767768880449</v>
+        <v>0.066371698435531965</v>
       </c>
       <c r="C17" s="0">
-        <v>0.025561231622131621</v>
+        <v>0.017666739404051987</v>
       </c>
       <c r="D17" s="0">
-        <v>0.066371540138204885</v>
+        <v>0.025560884769497097</v>
       </c>
       <c r="E17" s="0">
-        <v>0.26086016949814145</v>
+        <v>0.0075336074723043696</v>
       </c>
       <c r="F17" s="0">
-        <v>0.0075336175282604652</v>
+        <v>0.2608601644794159</v>
       </c>
     </row>
     <row r="18">
@@ -8737,19 +8737,19 @@
         <v>353.46699999999999</v>
       </c>
       <c r="B18" s="0">
-        <v>0.020956580670173162</v>
+        <v>0.073301685015899606</v>
       </c>
       <c r="C18" s="0">
-        <v>0.018173243274709105</v>
+        <v>0.020956568122991275</v>
       </c>
       <c r="D18" s="0">
-        <v>0.073301715004876353</v>
+        <v>0.018173048598216425</v>
       </c>
       <c r="E18" s="0">
-        <v>0.2590691634678714</v>
+        <v>0.011113951642862392</v>
       </c>
       <c r="F18" s="0">
-        <v>0.011113959221310759</v>
+        <v>0.259069160225121</v>
       </c>
     </row>
     <row r="19">
@@ -8757,19 +8757,19 @@
         <v>356.733</v>
       </c>
       <c r="B19" s="0">
-        <v>0.031464564580104944</v>
+        <v>0.071287503230961627</v>
       </c>
       <c r="C19" s="0">
-        <v>0.012120639175068249</v>
+        <v>0.031464572678767302</v>
       </c>
       <c r="D19" s="0">
-        <v>0.07128778567554675</v>
+        <v>0.012120604316236641</v>
       </c>
       <c r="E19" s="0">
-        <v>0.25264889434728416</v>
+        <v>0.016062228571040824</v>
       </c>
       <c r="F19" s="0">
-        <v>0.016062234474691302</v>
+        <v>0.25264889343721114</v>
       </c>
     </row>
     <row r="20">
@@ -8777,19 +8777,19 @@
         <v>360</v>
       </c>
       <c r="B20" s="0">
-        <v>0.05042041080563435</v>
+        <v>0.070100080810955895</v>
       </c>
       <c r="C20" s="0">
-        <v>0.0084652799521519676</v>
+        <v>0.05042043094260848</v>
       </c>
       <c r="D20" s="0">
-        <v>0.070100421203184979</v>
+        <v>0.0084653092729364797</v>
       </c>
       <c r="E20" s="0">
-        <v>0.24336838755202037</v>
+        <v>0.022790984121214438</v>
       </c>
       <c r="F20" s="0">
-        <v>0.022790988753198911</v>
+        <v>0.24336838675501213</v>
       </c>
     </row>
     <row r="21">
@@ -8797,19 +8797,19 @@
         <v>363.26900000000001</v>
       </c>
       <c r="B21" s="0">
-        <v>0.07148014943955458</v>
+        <v>0.068831463580691921</v>
       </c>
       <c r="C21" s="0">
-        <v>0.0051004202350109929</v>
+        <v>0.071480192700446518</v>
       </c>
       <c r="D21" s="0">
-        <v>0.068831974138614971</v>
+        <v>0.0051005679379856192</v>
       </c>
       <c r="E21" s="0">
-        <v>0.23136925764509622</v>
+        <v>0.03206432649525532</v>
       </c>
       <c r="F21" s="0">
-        <v>0.032064329704013642</v>
+        <v>0.23136925780574272</v>
       </c>
     </row>
     <row r="22">
@@ -8817,19 +8817,19 @@
         <v>366.53899999999999</v>
       </c>
       <c r="B22" s="0">
-        <v>0.094565115491625912</v>
+        <v>0.064401962012346922</v>
       </c>
       <c r="C22" s="0">
-        <v>0.0042416975107675307</v>
+        <v>0.094565157777054612</v>
       </c>
       <c r="D22" s="0">
-        <v>0.064402466256297128</v>
+        <v>0.0042418366583337561</v>
       </c>
       <c r="E22" s="0">
-        <v>0.21860960847948466</v>
+        <v>0.044731137557494291</v>
       </c>
       <c r="F22" s="0">
-        <v>0.04473114022041156</v>
+        <v>0.21860960845787472</v>
       </c>
     </row>
     <row r="23">
@@ -8837,19 +8837,19 @@
         <v>369.81200000000001</v>
       </c>
       <c r="B23" s="0">
-        <v>0.12777894148129143</v>
+        <v>0.06111353290398646</v>
       </c>
       <c r="C23" s="0">
-        <v>0.0031688336708428876</v>
+        <v>0.1277789932581615</v>
       </c>
       <c r="D23" s="0">
-        <v>0.061114144645857085</v>
+        <v>0.0031690337500784546</v>
       </c>
       <c r="E23" s="0">
-        <v>0.20529046850711988</v>
+        <v>0.060121939041683434</v>
       </c>
       <c r="F23" s="0">
-        <v>0.060121940878984086</v>
+        <v>0.20529046880765719</v>
       </c>
     </row>
     <row r="24">
@@ -8857,19 +8857,19 @@
         <v>373.08600000000001</v>
       </c>
       <c r="B24" s="0">
-        <v>0.15667574297796713</v>
+        <v>0.042625444301208647</v>
       </c>
       <c r="C24" s="0">
-        <v>0.00030401374975695043</v>
+        <v>0.15667580258624259</v>
       </c>
       <c r="D24" s="0">
-        <v>0.042626139266785157</v>
+        <v>0.00030428595439640452</v>
       </c>
       <c r="E24" s="0">
-        <v>0.19522292977804587</v>
+        <v>0.080755223620212022</v>
       </c>
       <c r="F24" s="0">
-        <v>0.080755225170708211</v>
+        <v>0.19522292974854699</v>
       </c>
     </row>
     <row r="25">
@@ -8877,19 +8877,19 @@
         <v>376.36200000000002</v>
       </c>
       <c r="B25" s="0">
-        <v>0.18595647143654961</v>
+        <v>0.050761399688724403</v>
       </c>
       <c r="C25" s="0">
-        <v>0.0014983893514597059</v>
+        <v>0.18595651813661346</v>
       </c>
       <c r="D25" s="0">
-        <v>0.050762043022472877</v>
+        <v>0.0014985974532698355</v>
       </c>
       <c r="E25" s="0">
-        <v>0.18225414421541311</v>
+        <v>0.10383684288045161</v>
       </c>
       <c r="F25" s="0">
-        <v>0.10383684404791599</v>
+        <v>0.18225414401023224</v>
       </c>
     </row>
     <row r="26">
@@ -8897,19 +8897,19 @@
         <v>379.63900000000001</v>
       </c>
       <c r="B26" s="0">
-        <v>0.20969560730730233</v>
+        <v>0.049653774688448372</v>
       </c>
       <c r="C26" s="0">
-        <v>0.0019366135949424391</v>
+        <v>0.20969564015318928</v>
       </c>
       <c r="D26" s="0">
-        <v>0.049654351091693562</v>
+        <v>0.0019367731713764986</v>
       </c>
       <c r="E26" s="0">
-        <v>0.16764206977266111</v>
+        <v>0.12801510149301687</v>
       </c>
       <c r="F26" s="0">
-        <v>0.12801510294085239</v>
+        <v>0.16764206891853684</v>
       </c>
     </row>
     <row r="27">
@@ -8917,19 +8917,19 @@
         <v>382.91800000000001</v>
       </c>
       <c r="B27" s="0">
-        <v>0.2387271665930428</v>
+        <v>0.046249690105294748</v>
       </c>
       <c r="C27" s="0">
-        <v>0.0011984884660710476</v>
+        <v>0.23872719248030896</v>
       </c>
       <c r="D27" s="0">
-        <v>0.046250257008243464</v>
+        <v>0.0011986408817134524</v>
       </c>
       <c r="E27" s="0">
-        <v>0.1570936208787054</v>
+        <v>0.15664652938335671</v>
       </c>
       <c r="F27" s="0">
-        <v>0.1566465309607826</v>
+        <v>0.15709361951933515</v>
       </c>
     </row>
     <row r="28">
@@ -8937,19 +8937,19 @@
         <v>386.19900000000001</v>
       </c>
       <c r="B28" s="0">
-        <v>0.25726701583831413</v>
+        <v>0.050168735923811311</v>
       </c>
       <c r="C28" s="0">
-        <v>0.00041802041543533843</v>
+        <v>0.25726703626090602</v>
       </c>
       <c r="D28" s="0">
-        <v>0.050169285460723849</v>
+        <v>0.00041816601501642309</v>
       </c>
       <c r="E28" s="0">
-        <v>0.14411709268803058</v>
+        <v>0.182785593659816</v>
       </c>
       <c r="F28" s="0">
-        <v>0.1827855950980592</v>
+        <v>0.14411709106638079</v>
       </c>
     </row>
     <row r="29">
@@ -8957,19 +8957,19 @@
         <v>389.481</v>
       </c>
       <c r="B29" s="0">
-        <v>0.26690626389159766</v>
+        <v>0.045907044652302581</v>
       </c>
       <c r="C29" s="0">
-        <v>0.00035474817308103572</v>
+        <v>0.26690627533921024</v>
       </c>
       <c r="D29" s="0">
-        <v>0.045907578001728962</v>
+        <v>0.00035488281012256294</v>
       </c>
       <c r="E29" s="0">
-        <v>0.12950894960739051</v>
+        <v>0.20432591800555908</v>
       </c>
       <c r="F29" s="0">
-        <v>0.20432591974722905</v>
+        <v>0.12950894781156339</v>
       </c>
     </row>
     <row r="30">
@@ -8977,19 +8977,19 @@
         <v>392.76499999999999</v>
       </c>
       <c r="B30" s="0">
-        <v>0.27207202903328065</v>
+        <v>0.065273957370600294</v>
       </c>
       <c r="C30" s="0">
-        <v>0.00061155453171954052</v>
+        <v>0.27207202983206236</v>
       </c>
       <c r="D30" s="0">
-        <v>0.065274402419091576</v>
+        <v>0.00061164846292394235</v>
       </c>
       <c r="E30" s="0">
-        <v>0.11733894456420678</v>
+        <v>0.22520964779698421</v>
       </c>
       <c r="F30" s="0">
-        <v>0.22520964966154733</v>
+        <v>0.11733894232435746</v>
       </c>
     </row>
     <row r="31">
@@ -8997,19 +8997,19 @@
         <v>396.05000000000001</v>
       </c>
       <c r="B31" s="0">
-        <v>0.27661719869483836</v>
+        <v>0.069010372548511126</v>
       </c>
       <c r="C31" s="0">
-        <v>0.0017328519094787032</v>
+        <v>0.27661718725410112</v>
       </c>
       <c r="D31" s="0">
-        <v>0.06901076609148811</v>
+        <v>0.0017328912365878655</v>
       </c>
       <c r="E31" s="0">
-        <v>0.1055272450685177</v>
+        <v>0.24183955473751725</v>
       </c>
       <c r="F31" s="0">
-        <v>0.24183955674726287</v>
+        <v>0.10552724289687893</v>
       </c>
     </row>
     <row r="32">
@@ -9017,19 +9017,19 @@
         <v>399.33699999999999</v>
       </c>
       <c r="B32" s="0">
-        <v>0.26938864117605721</v>
+        <v>0.084532934396441342</v>
       </c>
       <c r="C32" s="0">
-        <v>0.00038924671141648041</v>
+        <v>0.26938862736348018</v>
       </c>
       <c r="D32" s="0">
-        <v>0.084533276931016574</v>
+        <v>0.00038929601675672401</v>
       </c>
       <c r="E32" s="0">
-        <v>0.09407283879669634</v>
+        <v>0.2526006888608901</v>
       </c>
       <c r="F32" s="0">
-        <v>0.25260069059034834</v>
+        <v>0.094072836352556213</v>
       </c>
     </row>
     <row r="33">
@@ -9037,19 +9037,19 @@
         <v>402.625</v>
       </c>
       <c r="B33" s="0">
-        <v>0.26184530829608643</v>
+        <v>0.096701237385178551</v>
       </c>
       <c r="C33" s="0">
-        <v>0.0021238710948206286</v>
+        <v>0.26184528295870602</v>
       </c>
       <c r="D33" s="0">
-        <v>0.096701511263379156</v>
+        <v>0.0021238628998949158</v>
       </c>
       <c r="E33" s="0">
-        <v>0.084187133552675333</v>
+        <v>0.25994331408902904</v>
       </c>
       <c r="F33" s="0">
-        <v>0.25994331605781873</v>
+        <v>0.084187131262849893</v>
       </c>
     </row>
     <row r="34">
@@ -9057,19 +9057,19 @@
         <v>405.91500000000002</v>
       </c>
       <c r="B34" s="0">
-        <v>0.2529781849506425</v>
+        <v>0.12232120372684849</v>
       </c>
       <c r="C34" s="0">
-        <v>0.002504323660910697</v>
+        <v>0.25297815290687481</v>
       </c>
       <c r="D34" s="0">
-        <v>0.12232137879782762</v>
+        <v>0.0025042687625268512</v>
       </c>
       <c r="E34" s="0">
-        <v>0.074716896744336403</v>
+        <v>0.26375503121831662</v>
       </c>
       <c r="F34" s="0">
-        <v>0.26375503276798734</v>
+        <v>0.074716894371890538</v>
       </c>
     </row>
     <row r="35">
@@ -9077,19 +9077,19 @@
         <v>409.20699999999999</v>
       </c>
       <c r="B35" s="0">
-        <v>0.23600486376994903</v>
+        <v>0.12328914111791815</v>
       </c>
       <c r="C35" s="0">
-        <v>0.00051533618021003974</v>
+        <v>0.23600483805248382</v>
       </c>
       <c r="D35" s="0">
-        <v>0.123289337993191</v>
+        <v>0.00051533795667861549</v>
       </c>
       <c r="E35" s="0">
-        <v>0.065805436904357376</v>
+        <v>0.26184081682093552</v>
       </c>
       <c r="F35" s="0">
-        <v>0.26184081808458099</v>
+        <v>0.065805434680756197</v>
       </c>
     </row>
     <row r="36">
@@ -9097,19 +9097,19 @@
         <v>412.5</v>
       </c>
       <c r="B36" s="0">
-        <v>0.21956010459789688</v>
+        <v>0.13717028354082877</v>
       </c>
       <c r="C36" s="0">
-        <v>1.4527614910175013e-05</v>
+        <v>0.21956008336094102</v>
       </c>
       <c r="D36" s="0">
-        <v>0.1371704808458433</v>
+        <v>1.4553293964811768e-05</v>
       </c>
       <c r="E36" s="0">
-        <v>0.057611134160216446</v>
+        <v>0.25592531294625848</v>
       </c>
       <c r="F36" s="0">
-        <v>0.25592531362677112</v>
+        <v>0.057611132340342222</v>
       </c>
     </row>
     <row r="37">
@@ -9117,19 +9117,19 @@
         <v>415.79399999999998</v>
       </c>
       <c r="B37" s="0">
-        <v>0.19886590364612669</v>
+        <v>0.13434104965152727</v>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>0.19886588131871652</v>
       </c>
       <c r="D37" s="0">
-        <v>0.1343412131932126</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
-        <v>0.05056588968852585</v>
+        <v>0.24683173462351818</v>
       </c>
       <c r="F37" s="0">
-        <v>0.24683173515749482</v>
+        <v>0.050565888316887166</v>
       </c>
     </row>
     <row r="38">
@@ -9137,19 +9137,19 @@
         <v>419.08999999999998</v>
       </c>
       <c r="B38" s="0">
-        <v>0.18259922609856572</v>
+        <v>0.14674599398066257</v>
       </c>
       <c r="C38" s="0">
-        <v>0</v>
+        <v>0.18259920613553002</v>
       </c>
       <c r="D38" s="0">
-        <v>0.14674612657273045</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0">
-        <v>0.043848211604048622</v>
+        <v>0.23415437406229853</v>
       </c>
       <c r="F38" s="0">
-        <v>0.23415437408712869</v>
+        <v>0.043848210449536268</v>
       </c>
     </row>
     <row r="39">
@@ -9157,19 +9157,19 @@
         <v>422.387</v>
       </c>
       <c r="B39" s="0">
-        <v>0.16502709112577008</v>
+        <v>0.15604787790754321</v>
       </c>
       <c r="C39" s="0">
-        <v>0</v>
+        <v>0.16502707251200338</v>
       </c>
       <c r="D39" s="0">
-        <v>0.15604798538636561</v>
+        <v>0</v>
       </c>
       <c r="E39" s="0">
-        <v>0.038188895773910367</v>
+        <v>0.22114009470302282</v>
       </c>
       <c r="F39" s="0">
-        <v>0.22114009419318481</v>
+        <v>0.038188894921682592</v>
       </c>
     </row>
     <row r="40">
@@ -9177,19 +9177,19 @@
         <v>425.685</v>
       </c>
       <c r="B40" s="0">
-        <v>0.15015071914520531</v>
+        <v>0.16275420393233467</v>
       </c>
       <c r="C40" s="0">
-        <v>0</v>
+        <v>0.15015070420448043</v>
       </c>
       <c r="D40" s="0">
-        <v>0.16275428976387371</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
-        <v>0.033042114949006156</v>
+        <v>0.20638355502417466</v>
       </c>
       <c r="F40" s="0">
-        <v>0.20638355409712472</v>
+        <v>0.033042114320273222</v>
       </c>
     </row>
     <row r="41">
@@ -9197,19 +9197,19 @@
         <v>428.98500000000001</v>
       </c>
       <c r="B41" s="0">
-        <v>0.13354840315981123</v>
+        <v>0.16483144664420421</v>
       </c>
       <c r="C41" s="0">
-        <v>0</v>
+        <v>0.13354839076897968</v>
       </c>
       <c r="D41" s="0">
-        <v>0.16483151469566928</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0">
-        <v>0.028674146179462984</v>
+        <v>0.19130497587866727</v>
       </c>
       <c r="F41" s="0">
-        <v>0.19130497465329596</v>
+        <v>0.028674145814861472</v>
       </c>
     </row>
     <row r="42">
@@ -9217,19 +9217,19 @@
         <v>432.28699999999998</v>
       </c>
       <c r="B42" s="0">
-        <v>0.12163758988634762</v>
+        <v>0.18204693005633649</v>
       </c>
       <c r="C42" s="0">
-        <v>0</v>
+        <v>0.12163757991036329</v>
       </c>
       <c r="D42" s="0">
-        <v>0.18204695537193597</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0">
-        <v>0.025108098881308813</v>
+        <v>0.17688161519851572</v>
       </c>
       <c r="F42" s="0">
-        <v>0.17688161332082586</v>
+        <v>0.025108098510914889</v>
       </c>
     </row>
     <row r="43">
@@ -9237,19 +9237,19 @@
         <v>435.589</v>
       </c>
       <c r="B43" s="0">
-        <v>0.10829409930223759</v>
+        <v>0.18884164148006838</v>
       </c>
       <c r="C43" s="0">
-        <v>0</v>
+        <v>0.10829409309421682</v>
       </c>
       <c r="D43" s="0">
-        <v>0.18884165075235701</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0">
-        <v>0.021977607526352326</v>
+        <v>0.1636309822718538</v>
       </c>
       <c r="F43" s="0">
-        <v>0.16363098004227047</v>
+        <v>0.021977607395015586</v>
       </c>
     </row>
     <row r="44">
@@ -9257,19 +9257,19 @@
         <v>438.89299999999997</v>
       </c>
       <c r="B44" s="0">
-        <v>0.094002276991919931</v>
+        <v>0.18974346452901672</v>
       </c>
       <c r="C44" s="0">
-        <v>0</v>
+        <v>0.094002272630685183</v>
       </c>
       <c r="D44" s="0">
-        <v>0.18974346136611139</v>
+        <v>0</v>
       </c>
       <c r="E44" s="0">
-        <v>0.019170694037624961</v>
+        <v>0.14990355037518657</v>
       </c>
       <c r="F44" s="0">
-        <v>0.14990354778737947</v>
+        <v>0.019170694144077651</v>
       </c>
     </row>
     <row r="45">
@@ -9277,19 +9277,19 @@
         <v>442.19900000000001</v>
       </c>
       <c r="B45" s="0">
-        <v>0.086175436525345331</v>
+        <v>0.19541904132108667</v>
       </c>
       <c r="C45" s="0">
-        <v>0.001060134699066375</v>
+        <v>0.086175433133889881</v>
       </c>
       <c r="D45" s="0">
-        <v>0.19541902787813759</v>
+        <v>0.0010601234565641895</v>
       </c>
       <c r="E45" s="0">
-        <v>0.016543127736152692</v>
+        <v>0.13560820512257726</v>
       </c>
       <c r="F45" s="0">
-        <v>0.13560820224334288</v>
+        <v>0.016543128122125765</v>
       </c>
     </row>
     <row r="46">
@@ -9297,19 +9297,19 @@
         <v>445.505</v>
       </c>
       <c r="B46" s="0">
-        <v>0.076316102579787867</v>
+        <v>0.19260362945349402</v>
       </c>
       <c r="C46" s="0">
-        <v>0</v>
+        <v>0.076316102866610808</v>
       </c>
       <c r="D46" s="0">
-        <v>0.19260359355344639</v>
+        <v>0</v>
       </c>
       <c r="E46" s="0">
-        <v>0.014439513148592129</v>
+        <v>0.12264961703061368</v>
       </c>
       <c r="F46" s="0">
-        <v>0.12264961388351166</v>
+        <v>0.014439513371904097</v>
       </c>
     </row>
     <row r="47">
@@ -9317,19 +9317,19 @@
         <v>448.81299999999999</v>
       </c>
       <c r="B47" s="0">
-        <v>0.066615218325533909</v>
+        <v>0.1864596594799943</v>
       </c>
       <c r="C47" s="0">
-        <v>0.00092541624065106437</v>
+        <v>0.06661522450681584</v>
       </c>
       <c r="D47" s="0">
-        <v>0.18645969256732159</v>
+        <v>0.00092544917609857654</v>
       </c>
       <c r="E47" s="0">
-        <v>0.012334215532675276</v>
+        <v>0.10943512809949037</v>
       </c>
       <c r="F47" s="0">
-        <v>0.10943512488841527</v>
+        <v>0.012334216394639382</v>
       </c>
     </row>
     <row r="48">
@@ -9337,19 +9337,19 @@
         <v>452.12200000000001</v>
       </c>
       <c r="B48" s="0">
-        <v>0.056781056752009951</v>
+        <v>0.1967450381867871</v>
       </c>
       <c r="C48" s="0">
-        <v>0.0012225843174731943</v>
+        <v>0.056781059532905243</v>
       </c>
       <c r="D48" s="0">
-        <v>0.1967449839934593</v>
+        <v>0.001222570214566831</v>
       </c>
       <c r="E48" s="0">
-        <v>0.01100043354276763</v>
+        <v>0.097930619370825492</v>
       </c>
       <c r="F48" s="0">
-        <v>0.097930615801064255</v>
+        <v>0.011000434220830524</v>
       </c>
     </row>
     <row r="49">
@@ -9357,19 +9357,19 @@
         <v>455.43299999999999</v>
       </c>
       <c r="B49" s="0">
-        <v>0.052149993325531996</v>
+        <v>0.18760726920833729</v>
       </c>
       <c r="C49" s="0">
-        <v>0</v>
+        <v>0.05215000017600939</v>
       </c>
       <c r="D49" s="0">
-        <v>0.18760721352329501</v>
+        <v>0</v>
       </c>
       <c r="E49" s="0">
-        <v>0.0094202040962482903</v>
+        <v>0.087336545675501448</v>
       </c>
       <c r="F49" s="0">
-        <v>0.087336541770790171</v>
+        <v>0.0094202047184270866</v>
       </c>
     </row>
     <row r="50">
@@ -9377,19 +9377,19 @@
         <v>458.74400000000003</v>
       </c>
       <c r="B50" s="0">
-        <v>0.046307740500234694</v>
+        <v>0.1878819396174744</v>
       </c>
       <c r="C50" s="0">
-        <v>0.00075487780199200551</v>
+        <v>0.04630774631037865</v>
       </c>
       <c r="D50" s="0">
-        <v>0.18788186950351071</v>
+        <v>0.00075486215889336485</v>
       </c>
       <c r="E50" s="0">
-        <v>0.0084342995012283099</v>
+        <v>0.077887552468311111</v>
       </c>
       <c r="F50" s="0">
-        <v>0.077887548456126804</v>
+        <v>0.0084343002674690803</v>
       </c>
     </row>
     <row r="51">
@@ -9397,19 +9397,19 @@
         <v>462.05700000000002</v>
       </c>
       <c r="B51" s="0">
-        <v>0.0394349855004828</v>
+        <v>0.18038639386739008</v>
       </c>
       <c r="C51" s="0">
-        <v>0.00033394981980558935</v>
+        <v>0.03943499205138698</v>
       </c>
       <c r="D51" s="0">
-        <v>0.18038631590502135</v>
+        <v>0.00033393853978854555</v>
       </c>
       <c r="E51" s="0">
-        <v>0.0071004696417829045</v>
+        <v>0.069253965072112442</v>
       </c>
       <c r="F51" s="0">
-        <v>0.069253961033342387</v>
+        <v>0.0071004703507492562</v>
       </c>
     </row>
     <row r="52">
@@ -9417,19 +9417,19 @@
         <v>465.37099999999998</v>
       </c>
       <c r="B52" s="0">
-        <v>0.032013705939136536</v>
+        <v>0.1758803361481561</v>
       </c>
       <c r="C52" s="0">
-        <v>0.00056146789914996614</v>
+        <v>0.032013715226973626</v>
       </c>
       <c r="D52" s="0">
-        <v>0.17588027980217369</v>
+        <v>0.00056146516661258368</v>
       </c>
       <c r="E52" s="0">
-        <v>0.005929407679658617</v>
+        <v>0.061220246912603769</v>
       </c>
       <c r="F52" s="0">
-        <v>0.061220242788156749</v>
+        <v>0.0059294086920018505</v>
       </c>
     </row>
     <row r="53">
@@ -9437,19 +9437,19 @@
         <v>468.68599999999998</v>
       </c>
       <c r="B53" s="0">
-        <v>0.027536790782519069</v>
+        <v>0.17438023721015133</v>
       </c>
       <c r="C53" s="0">
-        <v>0.0012308043655506913</v>
+        <v>0.027536796922587585</v>
       </c>
       <c r="D53" s="0">
-        <v>0.17438014876110219</v>
+        <v>0.0012307758642425743</v>
       </c>
       <c r="E53" s="0">
-        <v>0.0052991113700356562</v>
+        <v>0.053934927000154204</v>
       </c>
       <c r="F53" s="0">
-        <v>0.053934922937238228</v>
+        <v>0.0052991123377094506</v>
       </c>
     </row>
     <row r="54">
@@ -9457,19 +9457,19 @@
         <v>472.00200000000001</v>
       </c>
       <c r="B54" s="0">
-        <v>0.025403667895903086</v>
+        <v>0.15943555673429585</v>
       </c>
       <c r="C54" s="0">
-        <v>0.00032677280462150996</v>
+        <v>0.025403678848593615</v>
       </c>
       <c r="D54" s="0">
-        <v>0.15943550587612274</v>
+        <v>0.00032677798986416833</v>
       </c>
       <c r="E54" s="0">
-        <v>0.0046283047464620647</v>
+        <v>0.047261907360227957</v>
       </c>
       <c r="F54" s="0">
-        <v>0.047261903355857726</v>
+        <v>0.0046283056917948628</v>
       </c>
     </row>
     <row r="55">
@@ -9477,19 +9477,19 @@
         <v>475.31900000000002</v>
       </c>
       <c r="B55" s="0">
-        <v>0.022341248444590782</v>
+        <v>0.15564699065678497</v>
       </c>
       <c r="C55" s="0">
-        <v>0.00021063287803320516</v>
+        <v>0.022341258379148351</v>
       </c>
       <c r="D55" s="0">
-        <v>0.15564692466257768</v>
+        <v>0.00021063126771086633</v>
       </c>
       <c r="E55" s="0">
-        <v>0.0038619499637951413</v>
+        <v>0.041833916232674843</v>
       </c>
       <c r="F55" s="0">
-        <v>0.04183391214706153</v>
+        <v>0.0038619508685573808</v>
       </c>
     </row>
     <row r="56">
@@ -9497,19 +9497,19 @@
         <v>478.63799999999998</v>
       </c>
       <c r="B56" s="0">
-        <v>0.016428872610476208</v>
+        <v>0.14511262434146885</v>
       </c>
       <c r="C56" s="0">
-        <v>0</v>
+        <v>0.016428883968729061</v>
       </c>
       <c r="D56" s="0">
-        <v>0.14511257259568561</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0">
-        <v>0.0031048043329102095</v>
+        <v>0.037006371567947748</v>
       </c>
       <c r="F56" s="0">
-        <v>0.037006367543183212</v>
+        <v>0.0031048054372007357</v>
       </c>
     </row>
     <row r="57">
@@ -9517,19 +9517,19 @@
         <v>481.95699999999999</v>
       </c>
       <c r="B57" s="0">
-        <v>0.017498556542021353</v>
+        <v>0.14486402356849351</v>
       </c>
       <c r="C57" s="0">
-        <v>0.00063071705742141163</v>
+        <v>0.017498567591267184</v>
       </c>
       <c r="D57" s="0">
-        <v>0.14486397328296888</v>
+        <v>0.00063071976688250397</v>
       </c>
       <c r="E57" s="0">
-        <v>0.0030474520296113572</v>
+        <v>0.032520018674549733</v>
       </c>
       <c r="F57" s="0">
-        <v>0.032520014805948502</v>
+        <v>0.0030474530266123242</v>
       </c>
     </row>
     <row r="58">
@@ -9537,19 +9537,19 @@
         <v>485.27699999999999</v>
       </c>
       <c r="B58" s="0">
-        <v>0.013272739283234466</v>
+        <v>0.13560388573830678</v>
       </c>
       <c r="C58" s="0">
-        <v>0.00025478281095257208</v>
+        <v>0.013272756692683121</v>
       </c>
       <c r="D58" s="0">
-        <v>0.13560381399927232</v>
+        <v>0.00025478870485834627</v>
       </c>
       <c r="E58" s="0">
-        <v>0.0026355839085684882</v>
+        <v>0.028797569978460887</v>
       </c>
       <c r="F58" s="0">
-        <v>0.028797567147945003</v>
+        <v>0.0026355846724098577</v>
       </c>
     </row>
     <row r="59">
@@ -9557,19 +9557,19 @@
         <v>488.59899999999999</v>
       </c>
       <c r="B59" s="0">
-        <v>0.010544929374004419</v>
+        <v>0.13167026230675658</v>
       </c>
       <c r="C59" s="0">
-        <v>0</v>
+        <v>0.010544947155732289</v>
       </c>
       <c r="D59" s="0">
-        <v>0.13167017942559387</v>
+        <v>0</v>
       </c>
       <c r="E59" s="0">
-        <v>0.0023348493235274847</v>
+        <v>0.025349975113526744</v>
       </c>
       <c r="F59" s="0">
-        <v>0.025349972304353968</v>
+        <v>0.0023348500613105858</v>
       </c>
     </row>
     <row r="60">
@@ -9577,19 +9577,19 @@
         <v>491.92099999999999</v>
       </c>
       <c r="B60" s="0">
-        <v>0.0099368454907479645</v>
+        <v>0.13566514522413381</v>
       </c>
       <c r="C60" s="0">
-        <v>0.0010257354059588981</v>
+        <v>0.0099368604361519952</v>
       </c>
       <c r="D60" s="0">
-        <v>0.13566505363297782</v>
+        <v>0.0010257240629318351</v>
       </c>
       <c r="E60" s="0">
-        <v>0.0021796043285137127</v>
+        <v>0.022385048181648538</v>
       </c>
       <c r="F60" s="0">
-        <v>0.022385045410577308</v>
+        <v>0.0021796050972894649</v>
       </c>
     </row>
     <row r="61">
@@ -9597,19 +9597,19 @@
         <v>495.245</v>
       </c>
       <c r="B61" s="0">
-        <v>0.0081791987348384717</v>
+        <v>0.1260759600816137</v>
       </c>
       <c r="C61" s="0">
-        <v>0.00048147021395716048</v>
+        <v>0.008179216170436503</v>
       </c>
       <c r="D61" s="0">
-        <v>0.12607584176518166</v>
+        <v>0.00048146483411118694</v>
       </c>
       <c r="E61" s="0">
-        <v>0.0019835770598906548</v>
+        <v>0.019541093067890626</v>
       </c>
       <c r="F61" s="0">
-        <v>0.019541091101834437</v>
+        <v>0.0019835776410494842</v>
       </c>
     </row>
     <row r="62">
@@ -9617,19 +9617,19 @@
         <v>498.56900000000002</v>
       </c>
       <c r="B62" s="0">
-        <v>0.0067880180873437978</v>
+        <v>0.12014989000268125</v>
       </c>
       <c r="C62" s="0">
-        <v>0.00055131756274540969</v>
+        <v>0.0067880329272882577</v>
       </c>
       <c r="D62" s="0">
-        <v>0.12014975670186311</v>
+        <v>0.00055129827128615509</v>
       </c>
       <c r="E62" s="0">
-        <v>0.0017494999081824002</v>
+        <v>0.017520388878901859</v>
       </c>
       <c r="F62" s="0">
-        <v>0.017520387023387051</v>
+        <v>0.0017495004441445635</v>
       </c>
     </row>
     <row r="63">
@@ -9637,19 +9637,19 @@
         <v>501.89499999999998</v>
       </c>
       <c r="B63" s="0">
-        <v>0.0069766032690679932</v>
+        <v>0.1237089499953872</v>
       </c>
       <c r="C63" s="0">
-        <v>0.0016551303074342301</v>
+        <v>0.0069766136356900505</v>
       </c>
       <c r="D63" s="0">
-        <v>0.12370879969961363</v>
+        <v>0.0016550842548795082</v>
       </c>
       <c r="E63" s="0">
-        <v>0.0016667282175580618</v>
+        <v>0.015438525456967611</v>
       </c>
       <c r="F63" s="0">
-        <v>0.015438523495728234</v>
+        <v>0.0016667289224894745</v>
       </c>
     </row>
     <row r="64">
@@ -9657,19 +9657,19 @@
         <v>505.221</v>
       </c>
       <c r="B64" s="0">
-        <v>0.0056306680749876621</v>
+        <v>0.11310873035774631</v>
       </c>
       <c r="C64" s="0">
-        <v>0.00092517798974023238</v>
+        <v>0.0056306804025526144</v>
       </c>
       <c r="D64" s="0">
-        <v>0.11310857814622634</v>
+        <v>0.00092515771245123995</v>
       </c>
       <c r="E64" s="0">
-        <v>0.0013242697416958674</v>
+        <v>0.013841580157199785</v>
       </c>
       <c r="F64" s="0">
-        <v>0.013841578782801164</v>
+        <v>0.0013242705736689134</v>
       </c>
     </row>
     <row r="65">
@@ -9677,19 +9677,19 @@
         <v>508.54899999999998</v>
       </c>
       <c r="B65" s="0">
-        <v>0.0045767667788800424</v>
+        <v>0.10866556221205595</v>
       </c>
       <c r="C65" s="0">
-        <v>0.0014076300710292756</v>
+        <v>0.0045767776075064243</v>
       </c>
       <c r="D65" s="0">
-        <v>0.10866542147111691</v>
+        <v>0.0014076011436016263</v>
       </c>
       <c r="E65" s="0">
-        <v>0.0011786808831086956</v>
+        <v>0.012199822853560598</v>
       </c>
       <c r="F65" s="0">
-        <v>0.012199821477002061</v>
+        <v>0.00117868184787442</v>
       </c>
     </row>
     <row r="66">
@@ -9697,19 +9697,19 @@
         <v>511.87700000000001</v>
       </c>
       <c r="B66" s="0">
-        <v>0.0034155918668952357</v>
+        <v>0.10176377384055629</v>
       </c>
       <c r="C66" s="0">
-        <v>0</v>
+        <v>0.0034156060970399905</v>
       </c>
       <c r="D66" s="0">
-        <v>0.10176362789663231</v>
+        <v>0</v>
       </c>
       <c r="E66" s="0">
-        <v>0.00097620741129300398</v>
+        <v>0.010626971875453327</v>
       </c>
       <c r="F66" s="0">
-        <v>0.010626970733373235</v>
+        <v>0.00097620791261000231</v>
       </c>
     </row>
     <row r="67">
@@ -9717,19 +9717,19 @@
         <v>515.20600000000002</v>
       </c>
       <c r="B67" s="0">
-        <v>0.0043485022941098959</v>
+        <v>0.10730526556141685</v>
       </c>
       <c r="C67" s="0">
-        <v>0.0016226509593457799</v>
+        <v>0.0043485033566249875</v>
       </c>
       <c r="D67" s="0">
-        <v>0.10730510604502148</v>
+        <v>0.0016225974280623277</v>
       </c>
       <c r="E67" s="0">
-        <v>0.0010966832032526482</v>
+        <v>0.0093477077376813381</v>
       </c>
       <c r="F67" s="0">
-        <v>0.0093477054934850597</v>
+        <v>0.0010966849193245736</v>
       </c>
     </row>
     <row r="68">
@@ -9737,19 +9737,19 @@
         <v>518.53599999999994</v>
       </c>
       <c r="B68" s="0">
-        <v>0.0019091164326943046</v>
+        <v>0.090778664666729347</v>
       </c>
       <c r="C68" s="0">
-        <v>0.00018197511795073427</v>
+        <v>0.0019091206910876667</v>
       </c>
       <c r="D68" s="0">
-        <v>0.090778544411029921</v>
+        <v>0.00018196631342415508</v>
       </c>
       <c r="E68" s="0">
-        <v>0.00073587237808458116</v>
+        <v>0.0087174147765991285</v>
       </c>
       <c r="F68" s="0">
-        <v>0.0087174127025296411</v>
+        <v>0.00073587372129496728</v>
       </c>
     </row>
     <row r="69">
@@ -9757,19 +9757,19 @@
         <v>521.86599999999999</v>
       </c>
       <c r="B69" s="0">
-        <v>0.0019864767181191345</v>
+        <v>0.092259496061567123</v>
       </c>
       <c r="C69" s="0">
-        <v>0.00064694597122250445</v>
+        <v>0.0019864809259005551</v>
       </c>
       <c r="D69" s="0">
-        <v>0.092259379719834195</v>
+        <v>0.00064693730841146086</v>
       </c>
       <c r="E69" s="0">
-        <v>0.00079579833511132087</v>
+        <v>0.0076205916324581843</v>
       </c>
       <c r="F69" s="0">
-        <v>0.0076205896583620555</v>
+        <v>0.00079579966468033489</v>
       </c>
     </row>
     <row r="70">
@@ -9777,19 +9777,19 @@
         <v>525.19799999999998</v>
       </c>
       <c r="B70" s="0">
-        <v>0.0019376670838460114</v>
+        <v>0.084998272402024247</v>
       </c>
       <c r="C70" s="0">
-        <v>0.0014711577601311334</v>
+        <v>0.0019376688740670323</v>
       </c>
       <c r="D70" s="0">
-        <v>0.084998183287333884</v>
+        <v>0.0014711135671397783</v>
       </c>
       <c r="E70" s="0">
-        <v>0.00088799526813892441</v>
+        <v>0.0066902556583655843</v>
       </c>
       <c r="F70" s="0">
-        <v>0.0066902532819683421</v>
+        <v>0.00088799725965265784</v>
       </c>
     </row>
     <row r="71">
@@ -9797,19 +9797,19 @@
         <v>528.52999999999997</v>
       </c>
       <c r="B71" s="0">
-        <v>0.0028617361175789185</v>
+        <v>0.076120231101763802</v>
       </c>
       <c r="C71" s="0">
-        <v>0.0013426397192742737</v>
+        <v>0.0028617384118655533</v>
       </c>
       <c r="D71" s="0">
-        <v>0.076120165044275712</v>
+        <v>0.0013426089305363898</v>
       </c>
       <c r="E71" s="0">
-        <v>0.00058385205011703806</v>
+        <v>0.0057467929303525733</v>
       </c>
       <c r="F71" s="0">
-        <v>0.0057467906987439515</v>
+        <v>0.00058385388463880216</v>
       </c>
     </row>
     <row r="72">
@@ -9817,19 +9817,19 @@
         <v>531.86300000000006</v>
       </c>
       <c r="B72" s="0">
-        <v>0.0016858799807987824</v>
+        <v>0.075332057888465365</v>
       </c>
       <c r="C72" s="0">
-        <v>0.0012715744308184015</v>
+        <v>0.0016858841729332297</v>
       </c>
       <c r="D72" s="0">
-        <v>0.075331958319113435</v>
+        <v>0.0012715357885409071</v>
       </c>
       <c r="E72" s="0">
-        <v>0.00050126573542539092</v>
+        <v>0.0052975224415498338</v>
       </c>
       <c r="F72" s="0">
-        <v>0.0052975208423067435</v>
+        <v>0.00050126754144686533</v>
       </c>
     </row>
     <row r="73">
@@ -9837,19 +9837,19 @@
         <v>535.197</v>
       </c>
       <c r="B73" s="0">
-        <v>0.00084420085541059081</v>
+        <v>0.074853108233273749</v>
       </c>
       <c r="C73" s="0">
-        <v>0.0016052385148639017</v>
+        <v>0.00084420156465405218</v>
       </c>
       <c r="D73" s="0">
-        <v>0.074852976661267834</v>
+        <v>0.0016051107709842112</v>
       </c>
       <c r="E73" s="0">
-        <v>0.00044796354879700649</v>
+        <v>0.004621137878461949</v>
       </c>
       <c r="F73" s="0">
-        <v>0.0046211359471793022</v>
+        <v>0.0004479651522647931</v>
       </c>
     </row>
     <row r="74">
@@ -9857,19 +9857,19 @@
         <v>538.53099999999995</v>
       </c>
       <c r="B74" s="0">
-        <v>0.0010759861507722288</v>
+        <v>0.072306369803997281</v>
       </c>
       <c r="C74" s="0">
-        <v>0.0023715228529189673</v>
+        <v>0.0010759861462545769</v>
       </c>
       <c r="D74" s="0">
-        <v>0.072306261590885157</v>
+        <v>0.0023713901131699219</v>
       </c>
       <c r="E74" s="0">
-        <v>0.00046413398960751533</v>
+        <v>0.0040784688248708609</v>
       </c>
       <c r="F74" s="0">
-        <v>0.0040784669494232408</v>
+        <v>0.00046413580359734997</v>
       </c>
     </row>
     <row r="75">
@@ -9877,19 +9877,19 @@
         <v>541.86699999999996</v>
       </c>
       <c r="B75" s="0">
-        <v>0.00032420078518270376</v>
+        <v>0.063913296775763795</v>
       </c>
       <c r="C75" s="0">
-        <v>0.0018527858339986629</v>
+        <v>0.00032420268401166756</v>
       </c>
       <c r="D75" s="0">
-        <v>0.063913219813935704</v>
+        <v>0.0018527060026657218</v>
       </c>
       <c r="E75" s="0">
-        <v>0.00030595567006289521</v>
+        <v>0.003685733223519084</v>
       </c>
       <c r="F75" s="0">
-        <v>0.0036857316362095866</v>
+        <v>0.00030595714639528504</v>
       </c>
     </row>
     <row r="76">
@@ -9897,19 +9897,19 @@
         <v>545.20299999999998</v>
       </c>
       <c r="B76" s="0">
-        <v>0.0014027263710807915</v>
+        <v>0.065667183527682083</v>
       </c>
       <c r="C76" s="0">
-        <v>0.00030949362433441851</v>
+        <v>0.0014027338434147872</v>
       </c>
       <c r="D76" s="0">
-        <v>0.065667078849079158</v>
+        <v>0.00030943480118446006</v>
       </c>
       <c r="E76" s="0">
-        <v>0.0003337726775718912</v>
+        <v>0.0032651613750190843</v>
       </c>
       <c r="F76" s="0">
-        <v>0.0032651608526751493</v>
+        <v>0.00033377110971081813</v>
       </c>
     </row>
     <row r="77">
@@ -9917,19 +9917,19 @@
         <v>548.53899999999999</v>
       </c>
       <c r="B77" s="0">
-        <v>0.00059069353846696589</v>
+        <v>0.059940342185208238</v>
       </c>
       <c r="C77" s="0">
-        <v>0.00059483201506553085</v>
+        <v>0.00059069850483855764</v>
       </c>
       <c r="D77" s="0">
-        <v>0.059940238143930083</v>
+        <v>0.00059476370213951211</v>
       </c>
       <c r="E77" s="0">
-        <v>0.00018909245350023853</v>
+        <v>0.0028226141061039522</v>
       </c>
       <c r="F77" s="0">
-        <v>0.0028226136046396078</v>
+        <v>0.00018909120240723597</v>
       </c>
     </row>
     <row r="78">
@@ -9937,19 +9937,19 @@
         <v>551.87599999999998</v>
       </c>
       <c r="B78" s="0">
-        <v>7.0125528904897049e-05</v>
+        <v>0.052534671244462171</v>
       </c>
       <c r="C78" s="0">
-        <v>0</v>
+        <v>7.0135173465456238e-05</v>
       </c>
       <c r="D78" s="0">
-        <v>0.052534618809046155</v>
+        <v>0</v>
       </c>
       <c r="E78" s="0">
-        <v>0.00036521814834744538</v>
+        <v>0.0025622368613788665</v>
       </c>
       <c r="F78" s="0">
-        <v>0.0025622364443310215</v>
+        <v>0.00036521673341627196</v>
       </c>
     </row>
     <row r="79">
@@ -9957,19 +9957,19 @@
         <v>555.21400000000006</v>
       </c>
       <c r="B79" s="0">
-        <v>0.00058075230311058147</v>
+        <v>0.054274371304722506</v>
       </c>
       <c r="C79" s="0">
-        <v>0.0014518044721333677</v>
+        <v>0.00058075625485138043</v>
       </c>
       <c r="D79" s="0">
-        <v>0.054274310185891718</v>
+        <v>0.0014517884753191155</v>
       </c>
       <c r="E79" s="0">
-        <v>0.00019619639608214177</v>
+        <v>0.0022603205666304805</v>
       </c>
       <c r="F79" s="0">
-        <v>0.0022603198073641345</v>
+        <v>0.00019619575001749245</v>
       </c>
     </row>
     <row r="80">
@@ -9977,19 +9977,19 @@
         <v>558.553</v>
       </c>
       <c r="B80" s="0">
-        <v>0.00030896041052996326</v>
+        <v>0.056915097958736685</v>
       </c>
       <c r="C80" s="0">
-        <v>0.00085874769926788913</v>
+        <v>0.00030896794697150479</v>
       </c>
       <c r="D80" s="0">
-        <v>0.056915032224986131</v>
+        <v>0.0008587369764149654</v>
       </c>
       <c r="E80" s="0">
-        <v>0.00044418689352929825</v>
+        <v>0.0019018695436448599</v>
       </c>
       <c r="F80" s="0">
-        <v>0.00190186883620033</v>
+        <v>0.00044418595259537562</v>
       </c>
     </row>
     <row r="81">
@@ -9997,19 +9997,19 @@
         <v>561.89200000000005</v>
       </c>
       <c r="B81" s="0">
-        <v>0.00041415954672061343</v>
+        <v>0.047467730158336691</v>
       </c>
       <c r="C81" s="0">
-        <v>0.0013353973931151495</v>
+        <v>0.00041416032351195698</v>
       </c>
       <c r="D81" s="0">
-        <v>0.047467677527100335</v>
+        <v>0.0013353655848031209</v>
       </c>
       <c r="E81" s="0">
-        <v>0.00019165455408470054</v>
+        <v>0.0018910757954473563</v>
       </c>
       <c r="F81" s="0">
-        <v>0.0018910748214666824</v>
+        <v>0.00019165418852626126</v>
       </c>
     </row>
     <row r="82">
@@ -10017,19 +10017,19 @@
         <v>565.231</v>
       </c>
       <c r="B82" s="0">
-        <v>0.00064893877654914329</v>
+        <v>0.049338332745796028</v>
       </c>
       <c r="C82" s="0">
-        <v>0.0018457968536781534</v>
+        <v>0.00064894016621117002</v>
       </c>
       <c r="D82" s="0">
-        <v>0.049338296610564415</v>
+        <v>0.0018457741678192972</v>
       </c>
       <c r="E82" s="0">
-        <v>0.00045068012385807523</v>
+        <v>0.0014331820958242173</v>
       </c>
       <c r="F82" s="0">
-        <v>0.0014331809706515251</v>
+        <v>0.00045068010615849504</v>
       </c>
     </row>
     <row r="83">
@@ -10037,19 +10037,19 @@
         <v>568.57100000000003</v>
       </c>
       <c r="B83" s="0">
-        <v>0</v>
+        <v>0.043748437082125488</v>
       </c>
       <c r="C83" s="0">
-        <v>0.0026933708741480366</v>
+        <v>0</v>
       </c>
       <c r="D83" s="0">
-        <v>0.043748424809743045</v>
+        <v>0.0026933448695141411</v>
       </c>
       <c r="E83" s="0">
-        <v>0.00026093751090019155</v>
+        <v>0.0013896557320464983</v>
       </c>
       <c r="F83" s="0">
-        <v>0.001389654762836656</v>
+        <v>0.00026093800897326679</v>
       </c>
     </row>
     <row r="84">
@@ -10057,19 +10057,19 @@
         <v>571.91200000000004</v>
       </c>
       <c r="B84" s="0">
-        <v>0</v>
+        <v>0.041774560584063876</v>
       </c>
       <c r="C84" s="0">
-        <v>0.0028417649162796347</v>
+        <v>0</v>
       </c>
       <c r="D84" s="0">
-        <v>0.041774529274267169</v>
+        <v>0.0028417094784938114</v>
       </c>
       <c r="E84" s="0">
-        <v>0.00034124084004033458</v>
+        <v>0.0014538211987118236</v>
       </c>
       <c r="F84" s="0">
-        <v>0.0014538205084919879</v>
+        <v>0.00034124162503438096</v>
       </c>
     </row>
     <row r="85">
@@ -10077,19 +10077,19 @@
         <v>575.25300000000004</v>
       </c>
       <c r="B85" s="0">
-        <v>0.0013314640648517508</v>
+        <v>0.035169302750748956</v>
       </c>
       <c r="C85" s="0">
-        <v>0.0028338042160731616</v>
+        <v>0.0013314615965264039</v>
       </c>
       <c r="D85" s="0">
-        <v>0.035169292034961858</v>
+        <v>0.0028337407200528624</v>
       </c>
       <c r="E85" s="0">
-        <v>0.00024002946773530199</v>
+        <v>0.0011019305641736541</v>
       </c>
       <c r="F85" s="0">
-        <v>0.0011019299355977533</v>
+        <v>0.00024003081690674965</v>
       </c>
     </row>
     <row r="86">
@@ -10097,19 +10097,19 @@
         <v>578.59400000000005</v>
       </c>
       <c r="B86" s="0">
-        <v>0.0014101976525668983</v>
+        <v>0.035254494946156609</v>
       </c>
       <c r="C86" s="0">
-        <v>0.0034008470389723616</v>
+        <v>0.001410195852725827</v>
       </c>
       <c r="D86" s="0">
-        <v>0.035254500622405018</v>
+        <v>0.0034007818700112357</v>
       </c>
       <c r="E86" s="0">
-        <v>0.0002077019888106001</v>
+        <v>0.00091429385318713959</v>
       </c>
       <c r="F86" s="0">
-        <v>0.00091429375353716501</v>
+        <v>0.00020770339382835228</v>
       </c>
     </row>
     <row r="87">
@@ -10117,19 +10117,19 @@
         <v>581.93600000000004</v>
       </c>
       <c r="B87" s="0">
-        <v>0.0014572247279746472</v>
+        <v>0.036458604256873056</v>
       </c>
       <c r="C87" s="0">
-        <v>0.0053553240010410265</v>
+        <v>0.0014572136414514553</v>
       </c>
       <c r="D87" s="0">
-        <v>0.036458549202055962</v>
+        <v>0.0053550834538324456</v>
       </c>
       <c r="E87" s="0">
-        <v>0.00050198187389282961</v>
+        <v>0.0006784573988893838</v>
       </c>
       <c r="F87" s="0">
-        <v>0.0006784572609814084</v>
+        <v>0.00050198471192215472</v>
       </c>
     </row>
     <row r="88">
@@ -10137,19 +10137,19 @@
         <v>585.279</v>
       </c>
       <c r="B88" s="0">
-        <v>0.00102272219614458</v>
+        <v>0.033514347952284467</v>
       </c>
       <c r="C88" s="0">
-        <v>0.0086195233050082275</v>
+        <v>0.0010226981331441516</v>
       </c>
       <c r="D88" s="0">
-        <v>0.033514268079686292</v>
+        <v>0.008619235286477676</v>
       </c>
       <c r="E88" s="0">
-        <v>0.00016515743428793965</v>
+        <v>0.00069007285725816595</v>
       </c>
       <c r="F88" s="0">
-        <v>0.00069007440939911156</v>
+        <v>0.00016515977777548601</v>
       </c>
     </row>
     <row r="89">
@@ -10157,19 +10157,19 @@
         <v>588.62199999999996</v>
       </c>
       <c r="B89" s="0">
-        <v>0.0020765930632400901</v>
+        <v>0.034302067204460086</v>
       </c>
       <c r="C89" s="0">
-        <v>0.0061310739586157136</v>
+        <v>0.0020765758998820172</v>
       </c>
       <c r="D89" s="0">
-        <v>0.0343019824885877</v>
+        <v>0.006130854490375471</v>
       </c>
       <c r="E89" s="0">
-        <v>0.0003977331281444775</v>
+        <v>0.00045086507938996677</v>
       </c>
       <c r="F89" s="0">
-        <v>0.00045086548594465702</v>
+        <v>0.00039773483862274922</v>
       </c>
     </row>
     <row r="90">
@@ -10177,19 +10177,19 @@
         <v>591.96500000000003</v>
       </c>
       <c r="B90" s="0">
-        <v>0</v>
+        <v>0.025254612913368786</v>
       </c>
       <c r="C90" s="0">
-        <v>0.0060985870243829982</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.025254590943637387</v>
+        <v>0.0060983505155789656</v>
       </c>
       <c r="E90" s="0">
-        <v>0.00016703935559073853</v>
+        <v>0.00069614201665530264</v>
       </c>
       <c r="F90" s="0">
-        <v>0.00069614480683595633</v>
+        <v>0.00016704138728950785</v>
       </c>
     </row>
     <row r="91">
@@ -10197,19 +10197,19 @@
         <v>595.30899999999997</v>
       </c>
       <c r="B91" s="0">
-        <v>0.0011692161803780227</v>
+        <v>0.030595746816752659</v>
       </c>
       <c r="C91" s="0">
-        <v>0.0060656074587811318</v>
+        <v>0.0011692009111676763</v>
       </c>
       <c r="D91" s="0">
-        <v>0.030595690275919622</v>
+        <v>0.0060653634707909685</v>
       </c>
       <c r="E91" s="0">
-        <v>0.00034898932006005221</v>
+        <v>0.000639409633060931</v>
       </c>
       <c r="F91" s="0">
-        <v>0.00063941008550702158</v>
+        <v>0.00034899108254492011</v>
       </c>
     </row>
     <row r="92">
@@ -10217,19 +10217,19 @@
         <v>598.65200000000004</v>
       </c>
       <c r="B92" s="0">
-        <v>0.0019747999148624308</v>
+        <v>0.027920756767199073</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0065758140673989164</v>
+        <v>0.0019747830419052591</v>
       </c>
       <c r="D92" s="0">
-        <v>0.027920732861403407</v>
+        <v>0.006575666618596653</v>
       </c>
       <c r="E92" s="0">
-        <v>0.00032333049736999234</v>
+        <v>0.00034790296191261828</v>
       </c>
       <c r="F92" s="0">
-        <v>0.00034790530243745569</v>
+        <v>0.00032333183410775915</v>
       </c>
     </row>
     <row r="93">
@@ -10237,19 +10237,19 @@
         <v>601.99699999999996</v>
       </c>
       <c r="B93" s="0">
-        <v>0.0012061077761560059</v>
+        <v>0.022412663236658376</v>
       </c>
       <c r="C93" s="0">
-        <v>0.0057585912857459482</v>
+        <v>0.0012060936139378269</v>
       </c>
       <c r="D93" s="0">
-        <v>0.022412653655201464</v>
+        <v>0.0057584696286629442</v>
       </c>
       <c r="E93" s="0">
-        <v>0.00026053820277102398</v>
+        <v>0.000525528198987125</v>
       </c>
       <c r="F93" s="0">
-        <v>0.00052553041591000855</v>
+        <v>0.00026053945936991375</v>
       </c>
     </row>
     <row r="94">
@@ -10257,19 +10257,19 @@
         <v>605.34100000000001</v>
       </c>
       <c r="B94" s="0">
-        <v>0.00034528568592551205</v>
+        <v>0.024563421669628917</v>
       </c>
       <c r="C94" s="0">
-        <v>0.0051260382699820735</v>
+        <v>0.00034528065199559662</v>
       </c>
       <c r="D94" s="0">
-        <v>0.02456346779824118</v>
+        <v>0.0051260756382463758</v>
       </c>
       <c r="E94" s="0">
-        <v>0.00028678357074483289</v>
+        <v>0.00037737624107852229</v>
       </c>
       <c r="F94" s="0">
-        <v>0.00037737519039961507</v>
+        <v>0.00028678492169362534</v>
       </c>
     </row>
     <row r="95">
@@ -10277,19 +10277,19 @@
         <v>608.68600000000004</v>
       </c>
       <c r="B95" s="0">
-        <v>0</v>
+        <v>0.024941908596236476</v>
       </c>
       <c r="C95" s="0">
-        <v>0.0065912426557817282</v>
+        <v>0</v>
       </c>
       <c r="D95" s="0">
-        <v>0.02494198921264025</v>
+        <v>0.0065913017841834802</v>
       </c>
       <c r="E95" s="0">
-        <v>0.00034585011804746897</v>
+        <v>0.00039726350344941673</v>
       </c>
       <c r="F95" s="0">
-        <v>0.0003972624431565064</v>
+        <v>0.00034585217651736448</v>
       </c>
     </row>
     <row r="96">
@@ -10297,19 +10297,19 @@
         <v>612.03099999999995</v>
       </c>
       <c r="B96" s="0">
-        <v>0.00016037578510287964</v>
+        <v>0.020773914880246547</v>
       </c>
       <c r="C96" s="0">
-        <v>0.0059774715548250538</v>
+        <v>0.00016036708526512335</v>
       </c>
       <c r="D96" s="0">
-        <v>0.020773938609180823</v>
+        <v>0.0059774626384177755</v>
       </c>
       <c r="E96" s="0">
-        <v>0.00027938040666115557</v>
+        <v>0.00035260467228299291</v>
       </c>
       <c r="F96" s="0">
-        <v>0.00035260360594334379</v>
+        <v>0.00027938167766946204</v>
       </c>
     </row>
     <row r="97">
@@ -10317,19 +10317,19 @@
         <v>615.37599999999998</v>
       </c>
       <c r="B97" s="0">
-        <v>0.00029991479430919885</v>
+        <v>0.01968448595768571</v>
       </c>
       <c r="C97" s="0">
-        <v>0.0067497610249346611</v>
+        <v>0.00029991203294132409</v>
       </c>
       <c r="D97" s="0">
-        <v>0.019684517066369821</v>
+        <v>0.0067497697155867254</v>
       </c>
       <c r="E97" s="0">
-        <v>0.00034084425946035357</v>
+        <v>0.00033458262100344305</v>
       </c>
       <c r="F97" s="0">
-        <v>0.00033458133827821287</v>
+        <v>0.00034084539253502829</v>
       </c>
     </row>
     <row r="98">
@@ -10337,19 +10337,19 @@
         <v>618.72199999999998</v>
       </c>
       <c r="B98" s="0">
-        <v>0.00049696896592231682</v>
+        <v>0.020263197059980538</v>
       </c>
       <c r="C98" s="0">
-        <v>0.0023156921382493367</v>
+        <v>0.00049696592663450571</v>
       </c>
       <c r="D98" s="0">
-        <v>0.020263176559072935</v>
+        <v>0.0023156752219300253</v>
       </c>
       <c r="E98" s="0">
-        <v>0.00039327362667747936</v>
+        <v>0.00022084201249614709</v>
       </c>
       <c r="F98" s="0">
-        <v>0.00022084140756569289</v>
+        <v>0.0003932736019590163</v>
       </c>
     </row>
   </sheetData>

--- a/examples/tutorialModelExport.xlsx
+++ b/examples/tutorialModelExport.xlsx
@@ -5507,13 +5507,13 @@
         <v>188</v>
       </c>
       <c r="C2" s="0">
-        <v>99.886813042861874</v>
+        <v>99.886855987874071</v>
       </c>
       <c r="D2" s="0">
-        <v>27.272842169542418</v>
+        <v>27.262494400070878</v>
       </c>
       <c r="E2" s="0">
-        <v>93.67426755329295</v>
+        <v>93.673445121155695</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -5545,13 +5545,13 @@
         <v>189</v>
       </c>
       <c r="C3" s="0">
-        <v>99.9471697322126</v>
+        <v>99.947169737930537</v>
       </c>
       <c r="D3" s="0">
-        <v>12.729660656765374</v>
+        <v>12.729659279007523</v>
       </c>
       <c r="E3" s="0">
-        <v>96.326849845448649</v>
+        <v>96.325806512608267</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -5583,16 +5583,16 @@
         <v>190</v>
       </c>
       <c r="C4" s="0">
-        <v>99.955771130758947</v>
+        <v>99.955771128453407</v>
       </c>
       <c r="D4" s="0">
-        <v>10.657119871827131</v>
+        <v>10.657120427358487</v>
       </c>
       <c r="E4" s="0">
-        <v>64.931903898816117</v>
+        <v>64.9319105150567</v>
       </c>
       <c r="F4" s="0">
-        <v>53.333333333333336</v>
+        <v>66.666666666666657</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>196</v>
@@ -5621,13 +5621,13 @@
         <v>188</v>
       </c>
       <c r="C5" s="0">
-        <v>99.96358393367359</v>
+        <v>99.963704315538209</v>
       </c>
       <c r="D5" s="0">
-        <v>8.7745943036879694</v>
+        <v>8.7455878202836388</v>
       </c>
       <c r="E5" s="0">
-        <v>19.04513488179035</v>
+        <v>26.778983684581071</v>
       </c>
       <c r="F5" s="0">
         <v>0</v>
@@ -5695,7 +5695,7 @@
         <v>2</v>
       </c>
       <c r="D2" s="1">
-        <v>45935.331819999279</v>
+        <v>45960.518455930636</v>
       </c>
       <c r="E2" s="0">
         <v>23</v>
@@ -5712,10 +5712,10 @@
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="true"/>
     <col min="2" max="2" width="14.7109375" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
-    <col min="6" max="6" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
+    <col min="6" max="6" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5743,19 +5743,19 @@
         <v>81</v>
       </c>
       <c r="B2" s="0">
-        <v>0.04066570958280645</v>
+        <v>0.10343524310680503</v>
       </c>
       <c r="C2" s="0">
-        <v>0.34081309439093921</v>
+        <v>0.040665531039281208</v>
       </c>
       <c r="D2" s="0">
-        <v>0.10343530867223573</v>
+        <v>0.34081339787348097</v>
       </c>
       <c r="E2" s="0">
-        <v>2.542468067793906</v>
+        <v>0.0035831856867232256</v>
       </c>
       <c r="F2" s="0">
-        <v>0.0035825640867880389</v>
+        <v>2.5424684274111891</v>
       </c>
     </row>
     <row r="3">
@@ -5763,19 +5763,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="0">
-        <v>0.041960711859905811</v>
+        <v>0.18018629605821329</v>
       </c>
       <c r="C3" s="0">
-        <v>0.22833405130449971</v>
+        <v>0.041960683497691546</v>
       </c>
       <c r="D3" s="0">
-        <v>0.18018629966782695</v>
+        <v>0.22833441443054195</v>
       </c>
       <c r="E3" s="0">
-        <v>2.5535010450599987</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>2.5535012976279732</v>
       </c>
     </row>
     <row r="4">
@@ -5783,19 +5783,19 @@
         <v>83</v>
       </c>
       <c r="B4" s="0">
-        <v>0.048783071294509754</v>
+        <v>0.027488637300593012</v>
       </c>
       <c r="C4" s="0">
-        <v>0.043835868251725772</v>
+        <v>0.048783159000334732</v>
       </c>
       <c r="D4" s="0">
-        <v>0.02748973224815526</v>
+        <v>0.043836560526903101</v>
       </c>
       <c r="E4" s="0">
-        <v>0.035244760886759562</v>
+        <v>3.1058193646582457</v>
       </c>
       <c r="F4" s="0">
-        <v>3.1058192066717818</v>
+        <v>0.035244650587653421</v>
       </c>
     </row>
     <row r="5">
@@ -5803,19 +5803,19 @@
         <v>84</v>
       </c>
       <c r="B5" s="0">
-        <v>0.051883210209872924</v>
+        <v>0.079052967781349001</v>
       </c>
       <c r="C5" s="0">
-        <v>0.045438634719265368</v>
+        <v>0.051883197024001487</v>
       </c>
       <c r="D5" s="0">
-        <v>0.079053982995756625</v>
+        <v>0.045439406759673125</v>
       </c>
       <c r="E5" s="0">
-        <v>0.017451932643534143</v>
+        <v>3.1301542477443425</v>
       </c>
       <c r="F5" s="0">
-        <v>3.1301541735098546</v>
+        <v>0.01745185385121514</v>
       </c>
     </row>
     <row r="6">
@@ -5823,19 +5823,19 @@
         <v>85</v>
       </c>
       <c r="B6" s="0">
-        <v>0.045976964098933523</v>
+        <v>1.2841915721104744</v>
       </c>
       <c r="C6" s="0">
-        <v>0.049461957590712299</v>
+        <v>0.045976791498330644</v>
       </c>
       <c r="D6" s="0">
-        <v>1.2841925237266749</v>
+        <v>0.049462397664707385</v>
       </c>
       <c r="E6" s="0">
-        <v>0.016490532701150067</v>
+        <v>0.028212562561565666</v>
       </c>
       <c r="F6" s="0">
-        <v>0.028215364848415438</v>
+        <v>0.016490833344569321</v>
       </c>
     </row>
     <row r="7">
@@ -5843,19 +5843,19 @@
         <v>86</v>
       </c>
       <c r="B7" s="0">
-        <v>0.061389900255794161</v>
+        <v>0.17115799340088195</v>
       </c>
       <c r="C7" s="0">
-        <v>0.12474137661228593</v>
+        <v>0.061389841679195943</v>
       </c>
       <c r="D7" s="0">
-        <v>0.17115822078115692</v>
+        <v>0.12474208793820311</v>
       </c>
       <c r="E7" s="0">
-        <v>0.96710613051085137</v>
+        <v>0.013780605599569279</v>
       </c>
       <c r="F7" s="0">
-        <v>0.013779981776166446</v>
+        <v>0.96710612096576387</v>
       </c>
     </row>
     <row r="8">
@@ -5863,19 +5863,19 @@
         <v>87</v>
       </c>
       <c r="B8" s="0">
-        <v>0.057002874248957079</v>
+        <v>0.19337075755237596</v>
       </c>
       <c r="C8" s="0">
-        <v>0.16784888432297263</v>
+        <v>0.057002815611295735</v>
       </c>
       <c r="D8" s="0">
-        <v>0.19337101462725159</v>
+        <v>0.16784946220815578</v>
       </c>
       <c r="E8" s="0">
-        <v>1.8256988327067907</v>
+        <v>0.0045379340655324705</v>
       </c>
       <c r="F8" s="0">
-        <v>0.0045374044923955238</v>
+        <v>1.8256989293323442</v>
       </c>
     </row>
     <row r="9">
@@ -5883,19 +5883,19 @@
         <v>88</v>
       </c>
       <c r="B9" s="0">
-        <v>0.048124155606215434</v>
+        <v>0.20075739113231325</v>
       </c>
       <c r="C9" s="0">
-        <v>0.045153153959481815</v>
+        <v>0.048124013049998575</v>
       </c>
       <c r="D9" s="0">
-        <v>0.2007582113639198</v>
+        <v>0.045153876571904644</v>
       </c>
       <c r="E9" s="0">
-        <v>0</v>
+        <v>2.1447190080516516</v>
       </c>
       <c r="F9" s="0">
-        <v>2.1447191211148171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5903,19 +5903,19 @@
         <v>89</v>
       </c>
       <c r="B10" s="0">
-        <v>0.046852392846801164</v>
+        <v>0.3942305977882446</v>
       </c>
       <c r="C10" s="0">
-        <v>0.096381118119412565</v>
+        <v>0.046852293133873929</v>
       </c>
       <c r="D10" s="0">
-        <v>0.39423115333729925</v>
+        <v>0.09638166263078872</v>
       </c>
       <c r="E10" s="0">
-        <v>0.65525641840659144</v>
+        <v>0.72082050646089768</v>
       </c>
       <c r="F10" s="0">
-        <v>0.72082089342109101</v>
+        <v>0.65525651247697003</v>
       </c>
     </row>
     <row r="11">
@@ -5923,19 +5923,19 @@
         <v>90</v>
       </c>
       <c r="B11" s="0">
-        <v>0.0435529454011154</v>
+        <v>0.083668080055449526</v>
       </c>
       <c r="C11" s="0">
-        <v>0.12510091038223317</v>
+        <v>0.043552868245559678</v>
       </c>
       <c r="D11" s="0">
-        <v>0.083668218894503599</v>
+        <v>0.12510138012731617</v>
       </c>
       <c r="E11" s="0">
-        <v>1.2137398004032245</v>
+        <v>0.013622182640642137</v>
       </c>
       <c r="F11" s="0">
-        <v>0.013621594333090931</v>
+        <v>1.2137398496635521</v>
       </c>
     </row>
     <row r="12">
@@ -5943,19 +5943,19 @@
         <v>91</v>
       </c>
       <c r="B12" s="0">
-        <v>0.049107654347310598</v>
+        <v>0.061198249949511362</v>
       </c>
       <c r="C12" s="0">
-        <v>0.068800183865160292</v>
+        <v>0.049107695180585151</v>
       </c>
       <c r="D12" s="0">
-        <v>0.061199270642071438</v>
+        <v>0.068800843447577073</v>
       </c>
       <c r="E12" s="0">
-        <v>0.032835312230642927</v>
+        <v>2.786330274850541</v>
       </c>
       <c r="F12" s="0">
-        <v>2.7863301224933577</v>
+        <v>0.032835264395733012</v>
       </c>
     </row>
     <row r="13">
@@ -5963,19 +5963,19 @@
         <v>92</v>
       </c>
       <c r="B13" s="0">
-        <v>0.051680211289558284</v>
+        <v>0.078387168834944829</v>
       </c>
       <c r="C13" s="0">
-        <v>0.07246163117635486</v>
+        <v>0.051680197150566959</v>
       </c>
       <c r="D13" s="0">
-        <v>0.078387328711269605</v>
+        <v>0.072462280112994118</v>
       </c>
       <c r="E13" s="0">
-        <v>0.0071231633121605024</v>
+        <v>0.081990180857120024</v>
       </c>
       <c r="F13" s="0">
-        <v>0.081989527169059065</v>
+        <v>0.0071230803072641199</v>
       </c>
     </row>
     <row r="14">
@@ -5983,19 +5983,19 @@
         <v>93</v>
       </c>
       <c r="B14" s="0">
-        <v>0.037081885649760365</v>
+        <v>0.1021642016848127</v>
       </c>
       <c r="C14" s="0">
-        <v>0.22029213187426608</v>
+        <v>0.037081969218623119</v>
       </c>
       <c r="D14" s="0">
-        <v>0.1021641545072991</v>
+        <v>0.22029238915176042</v>
       </c>
       <c r="E14" s="0">
-        <v>2.5978748308092938</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0">
-        <v>0</v>
+        <v>2.5978750733493365</v>
       </c>
     </row>
     <row r="15">
@@ -6003,19 +6003,19 @@
         <v>94</v>
       </c>
       <c r="B15" s="0">
-        <v>0.041742618279021732</v>
+        <v>0.15361029467454016</v>
       </c>
       <c r="C15" s="0">
-        <v>0.025833450394705047</v>
+        <v>0.041742439044137311</v>
       </c>
       <c r="D15" s="0">
-        <v>0.15361116683830314</v>
+        <v>0.025834170574371391</v>
       </c>
       <c r="E15" s="0">
-        <v>0</v>
+        <v>3.1260242238545977</v>
       </c>
       <c r="F15" s="0">
-        <v>3.1260245087206879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6023,19 +6023,19 @@
         <v>95</v>
       </c>
       <c r="B16" s="0">
-        <v>0.036138545249786547</v>
+        <v>0.45312250289895434</v>
       </c>
       <c r="C16" s="0">
-        <v>0.11710906197002711</v>
+        <v>0.036138437589388055</v>
       </c>
       <c r="D16" s="0">
-        <v>0.45312307968383375</v>
+        <v>0.11710943918492656</v>
       </c>
       <c r="E16" s="0">
-        <v>0.89968531073790747</v>
+        <v>1.0850900430340806</v>
       </c>
       <c r="F16" s="0">
-        <v>1.0850908368843393</v>
+        <v>0.89968550360560984</v>
       </c>
     </row>
     <row r="17">
@@ -6043,19 +6043,19 @@
         <v>96</v>
       </c>
       <c r="B17" s="0">
-        <v>0.043518438091539734</v>
+        <v>0.41205460408525862</v>
       </c>
       <c r="C17" s="0">
-        <v>0.26125299987629208</v>
+        <v>0.043518254800064882</v>
       </c>
       <c r="D17" s="0">
-        <v>0.41205490577519605</v>
+        <v>0.26125335971570807</v>
       </c>
       <c r="E17" s="0">
-        <v>2.556290491880747</v>
+        <v>0.004717143804679854</v>
       </c>
       <c r="F17" s="0">
-        <v>0.0047173726641874239</v>
+        <v>2.556290820383591</v>
       </c>
     </row>
     <row r="18">
@@ -6063,19 +6063,19 @@
         <v>97</v>
       </c>
       <c r="B18" s="0">
-        <v>0.037015453424580104</v>
+        <v>0.076223094070719227</v>
       </c>
       <c r="C18" s="0">
-        <v>0.034246237884351001</v>
+        <v>0.037015429049264713</v>
       </c>
       <c r="D18" s="0">
-        <v>0.076223985556030383</v>
+        <v>0.034246808935935603</v>
       </c>
       <c r="E18" s="0">
-        <v>0.011984795905234219</v>
+        <v>3.1735573744224137</v>
       </c>
       <c r="F18" s="0">
-        <v>3.1735575588486165</v>
+        <v>0.011984774481253017</v>
       </c>
     </row>
     <row r="19">
@@ -6083,19 +6083,19 @@
         <v>98</v>
       </c>
       <c r="B19" s="0">
-        <v>0.035382755257972173</v>
+        <v>0.42241454541624435</v>
       </c>
       <c r="C19" s="0">
-        <v>0.12079726393967385</v>
+        <v>0.035382654102438529</v>
       </c>
       <c r="D19" s="0">
-        <v>0.42241497697385072</v>
+        <v>0.12079763084686587</v>
       </c>
       <c r="E19" s="0">
-        <v>0.88393572199621307</v>
+        <v>1.0635843713516366</v>
       </c>
       <c r="F19" s="0">
-        <v>1.0635851005418664</v>
+        <v>0.88393591441224628</v>
       </c>
     </row>
     <row r="20">
@@ -6103,19 +6103,19 @@
         <v>99</v>
       </c>
       <c r="B20" s="0">
-        <v>0.031746227876100056</v>
+        <v>0.066914333869368445</v>
       </c>
       <c r="C20" s="0">
-        <v>0.030540779725688003</v>
+        <v>0.031746210308320949</v>
       </c>
       <c r="D20" s="0">
-        <v>0.06691444383612033</v>
+        <v>0.030541191524429252</v>
       </c>
       <c r="E20" s="0">
-        <v>0.011168253819059301</v>
+        <v>0.013298217417821388</v>
       </c>
       <c r="F20" s="0">
-        <v>0.013297864200704801</v>
+        <v>0.011168189196908691</v>
       </c>
     </row>
     <row r="21">
@@ -6123,19 +6123,19 @@
         <v>100</v>
       </c>
       <c r="B21" s="0">
-        <v>0.043748555927815888</v>
+        <v>0.099988250428801009</v>
       </c>
       <c r="C21" s="0">
-        <v>0.22632892716029557</v>
+        <v>0.043748453271240419</v>
       </c>
       <c r="D21" s="0">
-        <v>0.099989124911415706</v>
+        <v>0.22632940961023099</v>
       </c>
       <c r="E21" s="0">
-        <v>0.0028148877089835245</v>
+        <v>2.0287693937172287</v>
       </c>
       <c r="F21" s="0">
-        <v>2.0287691845755553</v>
+        <v>0.0028151114734700153</v>
       </c>
     </row>
     <row r="22">
@@ -6143,19 +6143,19 @@
         <v>101</v>
       </c>
       <c r="B22" s="0">
-        <v>0.03635324111481307</v>
+        <v>0.058814763816281528</v>
       </c>
       <c r="C22" s="0">
-        <v>0.035770622815960704</v>
+        <v>0.036353214986514837</v>
       </c>
       <c r="D22" s="0">
-        <v>0.058814857413958671</v>
+        <v>0.035771094736491635</v>
       </c>
       <c r="E22" s="0">
-        <v>0.0012737055978383374</v>
+        <v>0.023565778679807813</v>
       </c>
       <c r="F22" s="0">
-        <v>0.023565325623398172</v>
+        <v>0.0012736329780514085</v>
       </c>
     </row>
     <row r="23">
@@ -6163,19 +6163,19 @@
         <v>102</v>
       </c>
       <c r="B23" s="0">
-        <v>0.030983983740026429</v>
+        <v>0.057861153458283694</v>
       </c>
       <c r="C23" s="0">
-        <v>0.028061388804659721</v>
+        <v>0.030983969959624037</v>
       </c>
       <c r="D23" s="0">
-        <v>0.057861277827954347</v>
+        <v>0.028061789853740311</v>
       </c>
       <c r="E23" s="0">
-        <v>0.0023874912811077307</v>
+        <v>0.015603323719389888</v>
       </c>
       <c r="F23" s="0">
-        <v>0.015602957884624883</v>
+        <v>0.0023874239203339844</v>
       </c>
     </row>
     <row r="24">
@@ -6183,19 +6183,19 @@
         <v>103</v>
       </c>
       <c r="B24" s="0">
-        <v>0.043287314307531348</v>
+        <v>0.078912665669054929</v>
       </c>
       <c r="C24" s="0">
-        <v>0.054075625935056264</v>
+        <v>0.043287292847907208</v>
       </c>
       <c r="D24" s="0">
-        <v>0.078912996670526245</v>
+        <v>0.054076188727313429</v>
       </c>
       <c r="E24" s="0">
-        <v>0.0036946765888716199</v>
+        <v>0.50828265267687223</v>
       </c>
       <c r="F24" s="0">
-        <v>0.50828221746888425</v>
+        <v>0.0036946100938242471</v>
       </c>
     </row>
     <row r="25">
@@ -6203,19 +6203,19 @@
         <v>104</v>
       </c>
       <c r="B25" s="0">
-        <v>0.034817031329069416</v>
+        <v>0.048371725250913017</v>
       </c>
       <c r="C25" s="0">
-        <v>0.033850573546254266</v>
+        <v>0.034817013480450056</v>
       </c>
       <c r="D25" s="0">
-        <v>0.048371850700844592</v>
+        <v>0.033851021432321792</v>
       </c>
       <c r="E25" s="0">
-        <v>0.00087312563983168751</v>
+        <v>0.018372812711561829</v>
       </c>
       <c r="F25" s="0">
-        <v>0.018372353094215914</v>
+        <v>0.00087305197522710145</v>
       </c>
     </row>
     <row r="26">
@@ -6223,19 +6223,19 @@
         <v>105</v>
       </c>
       <c r="B26" s="0">
-        <v>0.04135582551571082</v>
+        <v>0.075798921760556026</v>
       </c>
       <c r="C26" s="0">
-        <v>0.037649734853769677</v>
+        <v>0.041355788358532875</v>
       </c>
       <c r="D26" s="0">
-        <v>0.075799055379936115</v>
+        <v>0.037650278562426115</v>
       </c>
       <c r="E26" s="0">
-        <v>0.00094252672643850479</v>
+        <v>0.02111154282382248</v>
       </c>
       <c r="F26" s="0">
-        <v>0.021111048433218725</v>
+        <v>0.00094244215135648446</v>
       </c>
     </row>
     <row r="27">
@@ -6243,19 +6243,19 @@
         <v>106</v>
       </c>
       <c r="B27" s="0">
-        <v>0.0424761183561366</v>
+        <v>0.048995254278068383</v>
       </c>
       <c r="C27" s="0">
-        <v>0.040743972367817287</v>
+        <v>0.042476096679397529</v>
       </c>
       <c r="D27" s="0">
-        <v>0.048995371896558115</v>
+        <v>0.040744528699388473</v>
       </c>
       <c r="E27" s="0">
-        <v>0.0015920539254998087</v>
+        <v>0.025239071897706734</v>
       </c>
       <c r="F27" s="0">
-        <v>0.025238487551007233</v>
+        <v>0.0015919564445716612</v>
       </c>
     </row>
     <row r="28">
@@ -6263,19 +6263,19 @@
         <v>107</v>
       </c>
       <c r="B28" s="0">
-        <v>0.045384135245709646</v>
+        <v>0.10230035925837429</v>
       </c>
       <c r="C28" s="0">
-        <v>0.091904631843560888</v>
+        <v>0.045384064858068576</v>
       </c>
       <c r="D28" s="0">
-        <v>0.10230050732339779</v>
+        <v>0.091905182730771681</v>
       </c>
       <c r="E28" s="0">
-        <v>0.54785106032697695</v>
+        <v>0.024773736713030122</v>
       </c>
       <c r="F28" s="0">
-        <v>0.024773207222850705</v>
+        <v>0.54785104945609131</v>
       </c>
     </row>
     <row r="29">
@@ -6283,19 +6283,19 @@
         <v>108</v>
       </c>
       <c r="B29" s="0">
-        <v>0.041481213443745453</v>
+        <v>0.070239581745746654</v>
       </c>
       <c r="C29" s="0">
-        <v>0.037861513576442692</v>
+        <v>0.041481170771236302</v>
       </c>
       <c r="D29" s="0">
-        <v>0.070239697390987233</v>
+        <v>0.037862062106725318</v>
       </c>
       <c r="E29" s="0">
-        <v>0.00032948296088918574</v>
+        <v>0.021469731502666463</v>
       </c>
       <c r="F29" s="0">
-        <v>0.02146921925568621</v>
+        <v>0.00032939829850060629</v>
       </c>
     </row>
     <row r="30">
@@ -6303,19 +6303,19 @@
         <v>109</v>
       </c>
       <c r="B30" s="0">
-        <v>0.045073777333747026</v>
+        <v>0.059927085451426811</v>
       </c>
       <c r="C30" s="0">
-        <v>0.042830959751852103</v>
+        <v>0.045073764731783809</v>
       </c>
       <c r="D30" s="0">
-        <v>0.059927204835043942</v>
+        <v>0.042831541486700306</v>
       </c>
       <c r="E30" s="0">
-        <v>0.001452168173112618</v>
+        <v>0.027424325585841243</v>
       </c>
       <c r="F30" s="0">
-        <v>0.027423731845782125</v>
+        <v>0.0014520660421506017</v>
       </c>
     </row>
     <row r="31">
@@ -6323,19 +6323,19 @@
         <v>110</v>
       </c>
       <c r="B31" s="0">
-        <v>0.041287224771766017</v>
+        <v>0.066500516834140808</v>
       </c>
       <c r="C31" s="0">
-        <v>0.04221167550002107</v>
+        <v>0.041287193527390888</v>
       </c>
       <c r="D31" s="0">
-        <v>0.06650063999229916</v>
+        <v>0.042212212417945705</v>
       </c>
       <c r="E31" s="0">
-        <v>0.00061937185342007979</v>
+        <v>0.027477641388761132</v>
       </c>
       <c r="F31" s="0">
-        <v>0.02747712336135727</v>
+        <v>0.00061929050032952541</v>
       </c>
     </row>
     <row r="32">
@@ -6343,19 +6343,19 @@
         <v>111</v>
       </c>
       <c r="B32" s="0">
-        <v>0.059764354667994131</v>
+        <v>0.066219808248560178</v>
       </c>
       <c r="C32" s="0">
-        <v>0.049108511391611119</v>
+        <v>0.059764327074572105</v>
       </c>
       <c r="D32" s="0">
-        <v>0.066220006038667983</v>
+        <v>0.049109295857836861</v>
       </c>
       <c r="E32" s="0">
-        <v>0.0017666714429694784</v>
+        <v>0.025079172125716694</v>
       </c>
       <c r="F32" s="0">
-        <v>0.025078339858418976</v>
+        <v>0.0017665229677794373</v>
       </c>
     </row>
     <row r="33">
@@ -6363,19 +6363,19 @@
         <v>112</v>
       </c>
       <c r="B33" s="0">
-        <v>0.035486062036694341</v>
+        <v>0.066614585421713238</v>
       </c>
       <c r="C33" s="0">
-        <v>0.036050930282241316</v>
+        <v>0.035486027960553689</v>
       </c>
       <c r="D33" s="0">
-        <v>0.066614689766767626</v>
+        <v>0.036051394674826237</v>
       </c>
       <c r="E33" s="0">
-        <v>0.0027694407573373957</v>
+        <v>0.023707240574130435</v>
       </c>
       <c r="F33" s="0">
-        <v>0.023706821066397658</v>
+        <v>0.0027693744997002159</v>
       </c>
     </row>
     <row r="34">
@@ -6383,19 +6383,19 @@
         <v>113</v>
       </c>
       <c r="B34" s="0">
-        <v>0.043302627928385726</v>
+        <v>0.013620633283479535</v>
       </c>
       <c r="C34" s="0">
-        <v>0.03615618768679784</v>
+        <v>0.043302757070093477</v>
       </c>
       <c r="D34" s="0">
-        <v>0.013621556410449868</v>
+        <v>0.036156798561966061</v>
       </c>
       <c r="E34" s="0">
-        <v>0.031181929228912237</v>
+        <v>3.3498492384041905</v>
       </c>
       <c r="F34" s="0">
-        <v>3.3498492163399365</v>
+        <v>0.031181827866268018</v>
       </c>
     </row>
     <row r="35">
@@ -6403,19 +6403,19 @@
         <v>114</v>
       </c>
       <c r="B35" s="0">
-        <v>0.007323831431758918</v>
+        <v>0.023349939840410779</v>
       </c>
       <c r="C35" s="0">
-        <v>0.00012647748465797034</v>
+        <v>0.0073238242394507297</v>
       </c>
       <c r="D35" s="0">
-        <v>0.023349925957317764</v>
+        <v>0.00012656348964335047</v>
       </c>
       <c r="E35" s="0">
-        <v>0</v>
+        <v>0.0021837968264859513</v>
       </c>
       <c r="F35" s="0">
-        <v>0.0021837448133254886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -6423,19 +6423,19 @@
         <v>115</v>
       </c>
       <c r="B36" s="0">
-        <v>0.035877553377315879</v>
+        <v>0.46013101821463648</v>
       </c>
       <c r="C36" s="0">
-        <v>0.094325312378748527</v>
+        <v>0.035877443813167993</v>
       </c>
       <c r="D36" s="0">
-        <v>0.46013153303178334</v>
+        <v>0.094325692910143574</v>
       </c>
       <c r="E36" s="0">
-        <v>0.93673492174912343</v>
+        <v>1.0596186056721366</v>
       </c>
       <c r="F36" s="0">
-        <v>1.0596194314165741</v>
+        <v>0.93673509406358269</v>
       </c>
     </row>
     <row r="37">
@@ -6443,19 +6443,19 @@
         <v>116</v>
       </c>
       <c r="B37" s="0">
-        <v>0.041418214372893128</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>0.035207257491669051</v>
+        <v>0.041418372363111244</v>
       </c>
       <c r="D37" s="0">
-        <v>0</v>
+        <v>0.03520784708913749</v>
       </c>
       <c r="E37" s="0">
-        <v>0.036937479218180795</v>
+        <v>3.2919533797841427</v>
       </c>
       <c r="F37" s="0">
-        <v>3.2919534427011055</v>
+        <v>0.036937384174370223</v>
       </c>
     </row>
     <row r="38">
@@ -6463,19 +6463,19 @@
         <v>117</v>
       </c>
       <c r="B38" s="0">
-        <v>0.067246994159386314</v>
+        <v>1.2478379619874316</v>
       </c>
       <c r="C38" s="0">
-        <v>0.046490427816674472</v>
+        <v>0.067246822718292701</v>
       </c>
       <c r="D38" s="0">
-        <v>1.2478388009360926</v>
+        <v>0.046491164148724035</v>
       </c>
       <c r="E38" s="0">
-        <v>0.0088077502992872404</v>
+        <v>0.041804293790898998</v>
       </c>
       <c r="F38" s="0">
-        <v>0.041806657801085216</v>
+        <v>0.0088079573061367895</v>
       </c>
     </row>
     <row r="39">
@@ -6483,19 +6483,19 @@
         <v>118</v>
       </c>
       <c r="B39" s="0">
-        <v>0.050473988785335232</v>
+        <v>0.064801460064669122</v>
       </c>
       <c r="C39" s="0">
-        <v>1.1933069166292432</v>
+        <v>0.050473859712009329</v>
       </c>
       <c r="D39" s="0">
-        <v>0.064802781899364656</v>
+        <v>1.193306588058328</v>
       </c>
       <c r="E39" s="0">
-        <v>0.016713989254784616</v>
+        <v>0.50834651985060253</v>
       </c>
       <c r="F39" s="0">
-        <v>0.50834529583476995</v>
+        <v>0.016715488646895878</v>
       </c>
     </row>
     <row r="40">
@@ -6503,19 +6503,19 @@
         <v>119</v>
       </c>
       <c r="B40" s="0">
-        <v>0.04390239315036705</v>
+        <v>0</v>
       </c>
       <c r="C40" s="0">
-        <v>0.036169803132307894</v>
+        <v>0.043902525841546754</v>
       </c>
       <c r="D40" s="0">
-        <v>0</v>
+        <v>0.036170431751560726</v>
       </c>
       <c r="E40" s="0">
-        <v>0.034481814111177574</v>
+        <v>3.3909120611246326</v>
       </c>
       <c r="F40" s="0">
-        <v>3.3909120958059238</v>
+        <v>0.034481723606229364</v>
       </c>
     </row>
     <row r="41">
@@ -6523,19 +6523,19 @@
         <v>120</v>
       </c>
       <c r="B41" s="0">
-        <v>0.066080137773422462</v>
+        <v>1.2837410585081224</v>
       </c>
       <c r="C41" s="0">
-        <v>0.051981249662230028</v>
+        <v>0.066079954274240058</v>
       </c>
       <c r="D41" s="0">
-        <v>1.2837419736234512</v>
+        <v>0.051981956792404721</v>
       </c>
       <c r="E41" s="0">
-        <v>0.0054519308230551481</v>
+        <v>0.029353333786996474</v>
       </c>
       <c r="F41" s="0">
-        <v>0.029355804486800762</v>
+        <v>0.0054521668618494872</v>
       </c>
     </row>
     <row r="42">
@@ -6543,19 +6543,19 @@
         <v>121</v>
       </c>
       <c r="B42" s="0">
-        <v>0.039121918422634017</v>
+        <v>0.47788951990353346</v>
       </c>
       <c r="C42" s="0">
-        <v>0.10076824698733275</v>
+        <v>0.039121824772704157</v>
       </c>
       <c r="D42" s="0">
-        <v>0.47789012851972884</v>
+        <v>0.10076865789818561</v>
       </c>
       <c r="E42" s="0">
-        <v>0.92232754419316421</v>
+        <v>1.0499590904215015</v>
       </c>
       <c r="F42" s="0">
-        <v>1.049959905138115</v>
+        <v>0.92232771106315725</v>
       </c>
     </row>
     <row r="43">
@@ -6563,19 +6563,19 @@
         <v>122</v>
       </c>
       <c r="B43" s="0">
-        <v>0.045284880525148008</v>
+        <v>0.0054022779315693534</v>
       </c>
       <c r="C43" s="0">
-        <v>0.033944780049969765</v>
+        <v>0.045285036065000069</v>
       </c>
       <c r="D43" s="0">
-        <v>0.0054032670053949091</v>
+        <v>0.033945407684714587</v>
       </c>
       <c r="E43" s="0">
-        <v>0.031650102469036899</v>
+        <v>3.3276066003622304</v>
       </c>
       <c r="F43" s="0">
-        <v>3.327606518621292</v>
+        <v>0.031649980027504313</v>
       </c>
     </row>
     <row r="44">
@@ -6583,19 +6583,19 @@
         <v>123</v>
       </c>
       <c r="B44" s="0">
-        <v>0.059763751718923321</v>
+        <v>1.2248519150459822</v>
       </c>
       <c r="C44" s="0">
-        <v>0.044270848510974514</v>
+        <v>0.059763564659069082</v>
       </c>
       <c r="D44" s="0">
-        <v>1.2248527330480343</v>
+        <v>0.044271483597632805</v>
       </c>
       <c r="E44" s="0">
-        <v>0.007588815610130085</v>
+        <v>0.035831832736541926</v>
       </c>
       <c r="F44" s="0">
-        <v>0.035834249955395033</v>
+        <v>0.0075890535540645088</v>
       </c>
     </row>
     <row r="45">
@@ -6603,19 +6603,19 @@
         <v>124</v>
       </c>
       <c r="B45" s="0">
-        <v>0.049696852421047454</v>
+        <v>0.13986063650981481</v>
       </c>
       <c r="C45" s="0">
-        <v>0.70973170190677737</v>
+        <v>0.04969677152007345</v>
       </c>
       <c r="D45" s="0">
-        <v>0.13986161542974257</v>
+        <v>0.70973177959447942</v>
       </c>
       <c r="E45" s="0">
-        <v>0.071347128915444938</v>
+        <v>0.7578617164811059</v>
       </c>
       <c r="F45" s="0">
-        <v>0.75786103518267467</v>
+        <v>0.071347975303856212</v>
       </c>
     </row>
     <row r="46">
@@ -6623,19 +6623,19 @@
         <v>125</v>
       </c>
       <c r="B46" s="0">
-        <v>0.042885517071237583</v>
+        <v>0.97358452474937263</v>
       </c>
       <c r="C46" s="0">
-        <v>0.044818524921797775</v>
+        <v>0.042885408241997346</v>
       </c>
       <c r="D46" s="0">
-        <v>0.97358552080114069</v>
+        <v>0.044818944742938911</v>
       </c>
       <c r="E46" s="0">
-        <v>0.012014510119182644</v>
+        <v>0.038052697611377646</v>
       </c>
       <c r="F46" s="0">
-        <v>0.03805466769170282</v>
+        <v>0.012014710184460693</v>
       </c>
     </row>
     <row r="47">
@@ -6643,19 +6643,19 @@
         <v>126</v>
       </c>
       <c r="B47" s="0">
-        <v>0.050986335584116499</v>
+        <v>0.14497469062741952</v>
       </c>
       <c r="C47" s="0">
-        <v>0.042756544013398096</v>
+        <v>0.050986279946028709</v>
       </c>
       <c r="D47" s="0">
-        <v>0.14497601646280076</v>
+        <v>0.042757290082394213</v>
       </c>
       <c r="E47" s="0">
-        <v>0</v>
+        <v>3.3637625293923321</v>
       </c>
       <c r="F47" s="0">
-        <v>3.3637626720758793</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -6663,19 +6663,19 @@
         <v>127</v>
       </c>
       <c r="B48" s="0">
-        <v>0.04344686750050844</v>
+        <v>0.057340305503721011</v>
       </c>
       <c r="C48" s="0">
-        <v>0.037795769290449061</v>
+        <v>0.043446872715484586</v>
       </c>
       <c r="D48" s="0">
-        <v>0.057340614061114528</v>
+        <v>0.037796324607386002</v>
       </c>
       <c r="E48" s="0">
-        <v>0.0032348702488002369</v>
+        <v>0.015909284521787709</v>
       </c>
       <c r="F48" s="0">
-        <v>0.015908694717071698</v>
+        <v>0.0032347580668137185</v>
       </c>
     </row>
     <row r="49">
@@ -6683,19 +6683,19 @@
         <v>128</v>
       </c>
       <c r="B49" s="0">
-        <v>0.050206640515984447</v>
+        <v>0.089996122834657202</v>
       </c>
       <c r="C49" s="0">
-        <v>0.043501284379282981</v>
+        <v>0.050206647223536155</v>
       </c>
       <c r="D49" s="0">
-        <v>0.089996504539174987</v>
+        <v>0.043501920541337412</v>
       </c>
       <c r="E49" s="0">
-        <v>0.002502951802537358</v>
+        <v>0.030593797306224076</v>
       </c>
       <c r="F49" s="0">
-        <v>0.030593184303992344</v>
+        <v>0.0025028294916022145</v>
       </c>
     </row>
     <row r="50">
@@ -6703,19 +6703,19 @@
         <v>129</v>
       </c>
       <c r="B50" s="0">
-        <v>0.037537978110632343</v>
+        <v>0.035813705131992384</v>
       </c>
       <c r="C50" s="0">
-        <v>0.033477934755955945</v>
+        <v>0.037537996298843704</v>
       </c>
       <c r="D50" s="0">
-        <v>0.035813955724101627</v>
+        <v>0.033478411344056394</v>
       </c>
       <c r="E50" s="0">
-        <v>0.0018691191774374211</v>
+        <v>0.011447885861028113</v>
       </c>
       <c r="F50" s="0">
-        <v>0.011447341271217401</v>
+        <v>0.0018690154676473641</v>
       </c>
     </row>
     <row r="51">
@@ -6723,19 +6723,19 @@
         <v>130</v>
       </c>
       <c r="B51" s="0">
-        <v>0.038175464584503979</v>
+        <v>0.20646971288232785</v>
       </c>
       <c r="C51" s="0">
-        <v>0.025009731911195723</v>
+        <v>0.038175233421777581</v>
       </c>
       <c r="D51" s="0">
-        <v>0.20647089407138822</v>
+        <v>0.025010423409934032</v>
       </c>
       <c r="E51" s="0">
-        <v>0</v>
+        <v>3.051051029155901</v>
       </c>
       <c r="F51" s="0">
-        <v>3.0510514566090885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -6743,19 +6743,19 @@
         <v>131</v>
       </c>
       <c r="B52" s="0">
-        <v>0.041301941252688393</v>
+        <v>0.0050091908827803629</v>
       </c>
       <c r="C52" s="0">
-        <v>0.033723657839478956</v>
+        <v>0.041302133568272281</v>
       </c>
       <c r="D52" s="0">
-        <v>0.005010517973719068</v>
+        <v>0.033724209242332867</v>
       </c>
       <c r="E52" s="0">
-        <v>0.042047468717601004</v>
+        <v>3.3164685691614304</v>
       </c>
       <c r="F52" s="0">
-        <v>3.3164685240169045</v>
+        <v>0.04204734799740302</v>
       </c>
     </row>
     <row r="53">
@@ -6763,19 +6763,19 @@
         <v>132</v>
       </c>
       <c r="B53" s="0">
-        <v>0.042692061072718022</v>
+        <v>0.049121745090763502</v>
       </c>
       <c r="C53" s="0">
-        <v>0.037723091378419837</v>
+        <v>0.042692069784400578</v>
       </c>
       <c r="D53" s="0">
-        <v>0.049122041159641736</v>
+        <v>0.037723637182564329</v>
       </c>
       <c r="E53" s="0">
-        <v>0.0021431542741233932</v>
+        <v>0.014981554713559638</v>
       </c>
       <c r="F53" s="0">
-        <v>0.014980955629219176</v>
+        <v>0.0021430413143526694</v>
       </c>
     </row>
     <row r="54">
@@ -6783,19 +6783,19 @@
         <v>133</v>
       </c>
       <c r="B54" s="0">
-        <v>0.047368238623193802</v>
+        <v>0.087646756563382361</v>
       </c>
       <c r="C54" s="0">
-        <v>0.042748458079897613</v>
+        <v>0.047368226856095534</v>
       </c>
       <c r="D54" s="0">
-        <v>0.087647114505601004</v>
+        <v>0.042749069066420051</v>
       </c>
       <c r="E54" s="0">
-        <v>0.0031399734010667487</v>
+        <v>0.031952579663412299</v>
       </c>
       <c r="F54" s="0">
-        <v>0.031952005030894425</v>
+        <v>0.0031398630329721915</v>
       </c>
     </row>
     <row r="55">
@@ -6803,19 +6803,19 @@
         <v>134</v>
       </c>
       <c r="B55" s="0">
-        <v>0.035469992825744375</v>
+        <v>0.037204084185478506</v>
       </c>
       <c r="C55" s="0">
-        <v>0.03464505431205453</v>
+        <v>0.035470006716549339</v>
       </c>
       <c r="D55" s="0">
-        <v>0.037204339932558596</v>
+        <v>0.034645503359447737</v>
       </c>
       <c r="E55" s="0">
-        <v>0.0016701449921501332</v>
+        <v>0.014486484792582251</v>
       </c>
       <c r="F55" s="0">
-        <v>0.014485976625769698</v>
+        <v>0.0016700523415565318</v>
       </c>
     </row>
     <row r="56">
@@ -6823,19 +6823,19 @@
         <v>135</v>
       </c>
       <c r="B56" s="0">
-        <v>0.050160351508690325</v>
+        <v>0.12446743650277843</v>
       </c>
       <c r="C56" s="0">
-        <v>0.27210550558835872</v>
+        <v>0.050160202664672499</v>
       </c>
       <c r="D56" s="0">
-        <v>0.12446750780240061</v>
+        <v>0.27210595529338921</v>
       </c>
       <c r="E56" s="0">
-        <v>2.5850885907276546</v>
+        <v>0.027070434909731437</v>
       </c>
       <c r="F56" s="0">
-        <v>0.027069754483570688</v>
+        <v>2.5850888334663167</v>
       </c>
     </row>
     <row r="57">
@@ -6843,19 +6843,19 @@
         <v>136</v>
       </c>
       <c r="B57" s="0">
-        <v>0.046201399739598116</v>
+        <v>1.229950956791789</v>
       </c>
       <c r="C57" s="0">
-        <v>0.046056702991696188</v>
+        <v>0.046201218063285185</v>
       </c>
       <c r="D57" s="0">
-        <v>1.2299518682477715</v>
+        <v>0.046057150615747208</v>
       </c>
       <c r="E57" s="0">
-        <v>0.003274072723645328</v>
+        <v>0.039188540405626159</v>
       </c>
       <c r="F57" s="0">
-        <v>0.039191186273853991</v>
+        <v>0.0032743624130367357</v>
       </c>
     </row>
     <row r="58">
@@ -6863,19 +6863,19 @@
         <v>137</v>
       </c>
       <c r="B58" s="0">
-        <v>0.057674689645331845</v>
+        <v>0.11188893184555455</v>
       </c>
       <c r="C58" s="0">
-        <v>1.2335232601824429</v>
+        <v>0.057674576528891526</v>
       </c>
       <c r="D58" s="0">
-        <v>0.11189041219422101</v>
+        <v>1.2335229706354047</v>
       </c>
       <c r="E58" s="0">
-        <v>0.036220259498656607</v>
+        <v>0.45099336502457393</v>
       </c>
       <c r="F58" s="0">
-        <v>0.45099211497407582</v>
+        <v>0.036221795095643904</v>
       </c>
     </row>
     <row r="59">
@@ -6883,19 +6883,19 @@
         <v>138</v>
       </c>
       <c r="B59" s="0">
-        <v>0.046025353924379668</v>
+        <v>0.056073582518556625</v>
       </c>
       <c r="C59" s="0">
-        <v>0.041860556078998447</v>
+        <v>0.046025362466826716</v>
       </c>
       <c r="D59" s="0">
-        <v>0.056074510915914783</v>
+        <v>0.04186124999503895</v>
       </c>
       <c r="E59" s="0">
-        <v>0.01089253659212058</v>
+        <v>3.1839248546799954</v>
       </c>
       <c r="F59" s="0">
-        <v>3.1839248385454741</v>
+        <v>0.010892464728694921</v>
       </c>
     </row>
     <row r="60">
@@ -6903,19 +6903,19 @@
         <v>139</v>
       </c>
       <c r="B60" s="0">
-        <v>0.064191327040918303</v>
+        <v>0.99040163459615072</v>
       </c>
       <c r="C60" s="0">
-        <v>0.055059085364682625</v>
+        <v>0.064191155887343032</v>
       </c>
       <c r="D60" s="0">
-        <v>0.99040238219657839</v>
+        <v>0.055059824126480216</v>
       </c>
       <c r="E60" s="0">
-        <v>0.0019906236431508849</v>
+        <v>0.061696774836367173</v>
       </c>
       <c r="F60" s="0">
-        <v>0.061698453919694321</v>
+        <v>0.0019907739779960682</v>
       </c>
     </row>
     <row r="61">
@@ -6923,19 +6923,19 @@
         <v>140</v>
       </c>
       <c r="B61" s="0">
-        <v>0.038401528817154217</v>
+        <v>0.34122406031108249</v>
       </c>
       <c r="C61" s="0">
-        <v>0.10654226382326797</v>
+        <v>0.038401497507125966</v>
       </c>
       <c r="D61" s="0">
-        <v>0.34122461543238564</v>
+        <v>0.10654267283332675</v>
       </c>
       <c r="E61" s="0">
-        <v>0.83754434514541531</v>
+        <v>0.9418105123915177</v>
       </c>
       <c r="F61" s="0">
-        <v>0.94181094439803281</v>
+        <v>0.83754445312381476</v>
       </c>
     </row>
     <row r="62">
@@ -6943,19 +6943,19 @@
         <v>141</v>
       </c>
       <c r="B62" s="0">
-        <v>0.05259576489311274</v>
+        <v>0.084280318024008649</v>
       </c>
       <c r="C62" s="0">
-        <v>0.049858030467645302</v>
+        <v>0.052595737769887713</v>
       </c>
       <c r="D62" s="0">
-        <v>0.084280452396262334</v>
+        <v>0.049858715911621755</v>
       </c>
       <c r="E62" s="0">
-        <v>0.0019948081513775232</v>
+        <v>0.029896545263983609</v>
       </c>
       <c r="F62" s="0">
-        <v>0.029895890888693964</v>
+        <v>0.001994694040049998</v>
       </c>
     </row>
     <row r="63">
@@ -6963,19 +6963,19 @@
         <v>142</v>
       </c>
       <c r="B63" s="0">
-        <v>0.05151191255176428</v>
+        <v>0.16656080425225028</v>
       </c>
       <c r="C63" s="0">
-        <v>0.05147572688765293</v>
+        <v>0.051511817449263107</v>
       </c>
       <c r="D63" s="0">
-        <v>0.16656100269231092</v>
+        <v>0.051476370153510011</v>
       </c>
       <c r="E63" s="0">
-        <v>0</v>
+        <v>0.040481371332429607</v>
       </c>
       <c r="F63" s="0">
-        <v>0.040480953796164496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -6983,19 +6983,19 @@
         <v>143</v>
       </c>
       <c r="B64" s="0">
-        <v>0.052584648089877603</v>
+        <v>0.10200912738497245</v>
       </c>
       <c r="C64" s="0">
-        <v>0.17062050921104094</v>
+        <v>0.05258458629379275</v>
       </c>
       <c r="D64" s="0">
-        <v>0.1020093290651431</v>
+        <v>0.17062104663290903</v>
       </c>
       <c r="E64" s="0">
-        <v>1.8248302919342589</v>
+        <v>0.011149399224892043</v>
       </c>
       <c r="F64" s="0">
-        <v>0.011148679471281994</v>
+        <v>1.8248303639391079</v>
       </c>
     </row>
     <row r="65">
@@ -7003,19 +7003,19 @@
         <v>144</v>
       </c>
       <c r="B65" s="0">
-        <v>0.050500741202316096</v>
+        <v>0.22150499619372466</v>
       </c>
       <c r="C65" s="0">
-        <v>0.046589852848315426</v>
+        <v>0.050500566252343657</v>
       </c>
       <c r="D65" s="0">
-        <v>0.22150582299016036</v>
+        <v>0.046590620615628416</v>
       </c>
       <c r="E65" s="0">
-        <v>0</v>
+        <v>2.3096558691946134</v>
       </c>
       <c r="F65" s="0">
-        <v>2.3096560242032043</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -7023,19 +7023,19 @@
         <v>145</v>
       </c>
       <c r="B66" s="0">
-        <v>0.054475120027514666</v>
+        <v>0.70769116062004234</v>
       </c>
       <c r="C66" s="0">
-        <v>0.061464286514047173</v>
+        <v>0.054475024856464133</v>
       </c>
       <c r="D66" s="0">
-        <v>0.70769176844998227</v>
+        <v>0.061464898682111857</v>
       </c>
       <c r="E66" s="0">
-        <v>0.0059145835776696172</v>
+        <v>0.034396918107398623</v>
       </c>
       <c r="F66" s="0">
-        <v>0.034397964934602447</v>
+        <v>0.0059146806725886812</v>
       </c>
     </row>
     <row r="67">
@@ -7043,19 +7043,19 @@
         <v>146</v>
       </c>
       <c r="B67" s="0">
-        <v>0.047378955034158642</v>
+        <v>0.098384170130393023</v>
       </c>
       <c r="C67" s="0">
-        <v>0.27775852111890525</v>
+        <v>0.047378835502278199</v>
       </c>
       <c r="D67" s="0">
-        <v>0.098384261924148439</v>
+        <v>0.27775892512350708</v>
       </c>
       <c r="E67" s="0">
-        <v>2.5184546708723814</v>
+        <v>0.0053383737393373158</v>
       </c>
       <c r="F67" s="0">
-        <v>0.0053376654953118195</v>
+        <v>2.5184549140896202</v>
       </c>
     </row>
     <row r="68">
@@ -7063,19 +7063,19 @@
         <v>147</v>
       </c>
       <c r="B68" s="0">
-        <v>0.047561586596112475</v>
+        <v>0.16722198254231327</v>
       </c>
       <c r="C68" s="0">
-        <v>0.031084483135152455</v>
+        <v>0.04756137492733379</v>
       </c>
       <c r="D68" s="0">
-        <v>0.16722283866524496</v>
+        <v>0.031085291298670707</v>
       </c>
       <c r="E68" s="0">
-        <v>0</v>
+        <v>2.9245496223696512</v>
       </c>
       <c r="F68" s="0">
-        <v>2.9245498006591615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -7083,19 +7083,19 @@
         <v>148</v>
       </c>
       <c r="B69" s="0">
-        <v>0.043642850171905154</v>
+        <v>1.3044768285810413</v>
       </c>
       <c r="C69" s="0">
-        <v>0.051105884288288494</v>
+        <v>0.043642666298532903</v>
       </c>
       <c r="D69" s="0">
-        <v>1.3044778319142978</v>
+        <v>0.051106285688492396</v>
       </c>
       <c r="E69" s="0">
-        <v>0.0047444945117118493</v>
+        <v>0.026699879275276832</v>
       </c>
       <c r="F69" s="0">
-        <v>0.026702768819104813</v>
+        <v>0.0047448189156843379</v>
       </c>
     </row>
     <row r="70">
@@ -7103,19 +7103,19 @@
         <v>149</v>
       </c>
       <c r="B70" s="0">
-        <v>0.048919190597851825</v>
+        <v>0.10340916369839988</v>
       </c>
       <c r="C70" s="0">
-        <v>0.29773805711603557</v>
+        <v>0.048919045254225614</v>
       </c>
       <c r="D70" s="0">
-        <v>0.10340922416281743</v>
+        <v>0.29773847839631523</v>
       </c>
       <c r="E70" s="0">
-        <v>2.5259295055423685</v>
+        <v>0.0039638325035983076</v>
       </c>
       <c r="F70" s="0">
-        <v>0.0039631009326577356</v>
+        <v>2.5259297766726689</v>
       </c>
     </row>
     <row r="71">
@@ -7123,19 +7123,19 @@
         <v>150</v>
       </c>
       <c r="B71" s="0">
-        <v>0.046955785493553309</v>
+        <v>0.090704947174385722</v>
       </c>
       <c r="C71" s="0">
-        <v>0.040863930916330137</v>
+        <v>0.046955705007349913</v>
       </c>
       <c r="D71" s="0">
-        <v>0.090705851305388482</v>
+        <v>0.040864665641216338</v>
       </c>
       <c r="E71" s="0">
-        <v>0.0067784451352323688</v>
+        <v>3.0879278079318113</v>
       </c>
       <c r="F71" s="0">
-        <v>3.0879278340934269</v>
+        <v>0.0067784013635067636</v>
       </c>
     </row>
     <row r="72">
@@ -7143,19 +7143,19 @@
         <v>151</v>
       </c>
       <c r="B72" s="0">
-        <v>0.045644503962030202</v>
+        <v>1.2888994656714008</v>
       </c>
       <c r="C72" s="0">
-        <v>0.048951772837165272</v>
+        <v>0.04564429719151715</v>
       </c>
       <c r="D72" s="0">
-        <v>1.2889003914736203</v>
+        <v>0.04895220677410899</v>
       </c>
       <c r="E72" s="0">
-        <v>0.0066867553640865109</v>
+        <v>0.029860783070003352</v>
       </c>
       <c r="F72" s="0">
-        <v>0.029863596980931745</v>
+        <v>0.0066870774840712037</v>
       </c>
     </row>
     <row r="73">
@@ -7163,19 +7163,19 @@
         <v>152</v>
       </c>
       <c r="B73" s="0">
-        <v>0.048650200228275202</v>
+        <v>0.073428939474189423</v>
       </c>
       <c r="C73" s="0">
-        <v>0.088470132522465258</v>
+        <v>0.048650143354714189</v>
       </c>
       <c r="D73" s="0">
-        <v>0.073429071275439281</v>
+        <v>0.088470711713146577</v>
       </c>
       <c r="E73" s="0">
-        <v>0.81809165443439114</v>
+        <v>0.014453844083484537</v>
       </c>
       <c r="F73" s="0">
-        <v>0.014453174471493085</v>
+        <v>0.81809162210086461</v>
       </c>
     </row>
     <row r="74">
@@ -7183,19 +7183,19 @@
         <v>153</v>
       </c>
       <c r="B74" s="0">
-        <v>0.04473289018279987</v>
+        <v>0.11752246401277167</v>
       </c>
       <c r="C74" s="0">
-        <v>0.087342044468190286</v>
+        <v>0.044732770371691578</v>
       </c>
       <c r="D74" s="0">
-        <v>0.11752325837905248</v>
+        <v>0.08734268384483608</v>
       </c>
       <c r="E74" s="0">
-        <v>0.0082003457762096065</v>
+        <v>2.3228988854169295</v>
       </c>
       <c r="F74" s="0">
-        <v>2.3228988388115117</v>
+        <v>0.0082003868667314111</v>
       </c>
     </row>
     <row r="75">
@@ -7203,19 +7203,19 @@
         <v>154</v>
       </c>
       <c r="B75" s="0">
-        <v>0.047149391841137415</v>
+        <v>0.11604481813434793</v>
       </c>
       <c r="C75" s="0">
-        <v>0.13295725144099685</v>
+        <v>0.047149299039134417</v>
       </c>
       <c r="D75" s="0">
-        <v>0.1160449607102808</v>
+        <v>0.13295777790621649</v>
       </c>
       <c r="E75" s="0">
-        <v>1.265280061112213</v>
+        <v>0.021895480026317294</v>
       </c>
       <c r="F75" s="0">
-        <v>0.021894920368175728</v>
+        <v>1.2652801122742321</v>
       </c>
     </row>
     <row r="76">
@@ -7223,19 +7223,19 @@
         <v>155</v>
       </c>
       <c r="B76" s="0">
-        <v>0.043418394280740458</v>
+        <v>0.067285193903274476</v>
       </c>
       <c r="C76" s="0">
-        <v>0.039759756821690195</v>
+        <v>0.043418357204559568</v>
       </c>
       <c r="D76" s="0">
-        <v>0.067285320542085109</v>
+        <v>0.03976032862882227</v>
       </c>
       <c r="E76" s="0">
-        <v>0.015848517180000053</v>
+        <v>0.019584459715354597</v>
       </c>
       <c r="F76" s="0">
-        <v>0.01958390631314065</v>
+        <v>0.015848424596831095</v>
       </c>
     </row>
     <row r="77">
@@ -7243,19 +7243,19 @@
         <v>156</v>
       </c>
       <c r="B77" s="0">
-        <v>0.041536477780231278</v>
+        <v>0.090125424010133404</v>
       </c>
       <c r="C77" s="0">
-        <v>0.1262381295937349</v>
+        <v>0.041536394967849034</v>
       </c>
       <c r="D77" s="0">
-        <v>0.090126049153039234</v>
+        <v>0.12623865956987812</v>
       </c>
       <c r="E77" s="0">
-        <v>0.0024260691851148092</v>
+        <v>1.4917902566900323</v>
       </c>
       <c r="F77" s="0">
-        <v>1.4917900157881334</v>
+        <v>0.002426141979152772</v>
       </c>
     </row>
     <row r="78">
@@ -7263,19 +7263,19 @@
         <v>157</v>
       </c>
       <c r="B78" s="0">
-        <v>0.044938267483201913</v>
+        <v>0.09564007598560631</v>
       </c>
       <c r="C78" s="0">
-        <v>0.044798034241073016</v>
+        <v>0.044938220654948666</v>
       </c>
       <c r="D78" s="0">
-        <v>0.095640204898750234</v>
+        <v>0.044798623839680987</v>
       </c>
       <c r="E78" s="0">
-        <v>0.0027564207899983531</v>
+        <v>0.02586414620914353</v>
       </c>
       <c r="F78" s="0">
-        <v>0.025863646713334788</v>
+        <v>0.002756339297960278</v>
       </c>
     </row>
     <row r="79">
@@ -7283,19 +7283,19 @@
         <v>158</v>
       </c>
       <c r="B79" s="0">
-        <v>0.042937864057602762</v>
+        <v>0.10069853711908247</v>
       </c>
       <c r="C79" s="0">
-        <v>0.30424601942337631</v>
+        <v>0.042937661655922603</v>
       </c>
       <c r="D79" s="0">
-        <v>0.10069854021861485</v>
+        <v>0.30424638915545022</v>
       </c>
       <c r="E79" s="0">
-        <v>2.5080357438173069</v>
+        <v>0.0068298514419807051</v>
       </c>
       <c r="F79" s="0">
-        <v>0.0068292006674534767</v>
+        <v>2.5080360562801665</v>
       </c>
     </row>
     <row r="80">
@@ -7303,19 +7303,19 @@
         <v>159</v>
       </c>
       <c r="B80" s="0">
-        <v>0.047608163486328764</v>
+        <v>0.087225633637330005</v>
       </c>
       <c r="C80" s="0">
-        <v>0.041264721363880215</v>
+        <v>0.047608111167531372</v>
       </c>
       <c r="D80" s="0">
-        <v>0.087226602165206904</v>
+        <v>0.041265450821730783</v>
       </c>
       <c r="E80" s="0">
-        <v>0.0063740209667502643</v>
+        <v>3.0921484818799225</v>
       </c>
       <c r="F80" s="0">
-        <v>3.0921484890105098</v>
+        <v>0.0063739673379557236</v>
       </c>
     </row>
     <row r="81">
@@ -7323,19 +7323,19 @@
         <v>160</v>
       </c>
       <c r="B81" s="0">
-        <v>0.043292415455205575</v>
+        <v>1.1702432211442968</v>
       </c>
       <c r="C81" s="0">
-        <v>0.041036747963972046</v>
+        <v>0.043292207105628713</v>
       </c>
       <c r="D81" s="0">
-        <v>1.1702440891135784</v>
+        <v>0.041037195233352648</v>
       </c>
       <c r="E81" s="0">
-        <v>0.0078340500175358308</v>
+        <v>0.03189610268629367</v>
       </c>
       <c r="F81" s="0">
-        <v>0.031898622741476916</v>
+        <v>0.007834325403729088</v>
       </c>
     </row>
     <row r="82">
@@ -7343,19 +7343,19 @@
         <v>161</v>
       </c>
       <c r="B82" s="0">
-        <v>0.043990863210448934</v>
+        <v>0.061821596858628529</v>
       </c>
       <c r="C82" s="0">
-        <v>0.038251798795461513</v>
+        <v>0.043990826808235302</v>
       </c>
       <c r="D82" s="0">
-        <v>0.061821726898229512</v>
+        <v>0.038252378416439151</v>
       </c>
       <c r="E82" s="0">
-        <v>0.0079719449560750194</v>
+        <v>0.019570909899271832</v>
       </c>
       <c r="F82" s="0">
-        <v>0.01957033178265281</v>
+        <v>0.0079718474201984375</v>
       </c>
     </row>
     <row r="83">
@@ -7363,19 +7363,19 @@
         <v>162</v>
       </c>
       <c r="B83" s="0">
-        <v>0.050737178553781112</v>
+        <v>0.086570703917936004</v>
       </c>
       <c r="C83" s="0">
-        <v>0.053660074242197667</v>
+        <v>0.050737139457392853</v>
       </c>
       <c r="D83" s="0">
-        <v>0.086570883894358228</v>
+        <v>0.053660731177461583</v>
       </c>
       <c r="E83" s="0">
-        <v>0.0034857074964802044</v>
+        <v>0.05076886758350644</v>
       </c>
       <c r="F83" s="0">
-        <v>0.050768244820366182</v>
+        <v>0.0034856122276299417</v>
       </c>
     </row>
     <row r="84">
@@ -7383,19 +7383,19 @@
         <v>163</v>
       </c>
       <c r="B84" s="0">
-        <v>0.045902577490793559</v>
+        <v>0.097313784581165158</v>
       </c>
       <c r="C84" s="0">
-        <v>0.043402969849289409</v>
+        <v>0.045902529962794696</v>
       </c>
       <c r="D84" s="0">
-        <v>0.097313876598667789</v>
+        <v>0.043403572072165372</v>
       </c>
       <c r="E84" s="0">
-        <v>0.0025621056939965862</v>
+        <v>0.025326332200421395</v>
       </c>
       <c r="F84" s="0">
-        <v>0.025325825604023453</v>
+        <v>0.0025620211190931297</v>
       </c>
     </row>
     <row r="85">
@@ -7403,19 +7403,19 @@
         <v>164</v>
       </c>
       <c r="B85" s="0">
-        <v>0.044781946255620923</v>
+        <v>0.092255139955141147</v>
       </c>
       <c r="C85" s="0">
-        <v>0.16969979506677213</v>
+        <v>0.044781820309335481</v>
       </c>
       <c r="D85" s="0">
-        <v>0.092255174156151129</v>
+        <v>0.16970028781703825</v>
       </c>
       <c r="E85" s="0">
-        <v>1.2577500538009523</v>
+        <v>0.017303502297080366</v>
       </c>
       <c r="F85" s="0">
-        <v>0.017302900895243008</v>
+        <v>1.2577501612517701</v>
       </c>
     </row>
     <row r="86">
@@ -7423,19 +7423,19 @@
         <v>165</v>
       </c>
       <c r="B86" s="0">
-        <v>0.047237265179748147</v>
+        <v>0.078060577993129543</v>
       </c>
       <c r="C86" s="0">
-        <v>0.042015757914629824</v>
+        <v>0.047237270256856451</v>
       </c>
       <c r="D86" s="0">
-        <v>0.078061541461337772</v>
+        <v>0.042016458858067048</v>
       </c>
       <c r="E86" s="0">
-        <v>0.015964050317695152</v>
+        <v>3.0927573253423537</v>
       </c>
       <c r="F86" s="0">
-        <v>3.0927573285312997</v>
+        <v>0.015963981941844917</v>
       </c>
     </row>
     <row r="87">
@@ -7443,19 +7443,19 @@
         <v>166</v>
       </c>
       <c r="B87" s="0">
-        <v>0.042853750832802538</v>
+        <v>1.0348909051419632</v>
       </c>
       <c r="C87" s="0">
-        <v>0.044818240723997711</v>
+        <v>0.042853602812995897</v>
       </c>
       <c r="D87" s="0">
-        <v>1.0348917022464246</v>
+        <v>0.044818682940884265</v>
       </c>
       <c r="E87" s="0">
-        <v>0.0069181642808995633</v>
+        <v>0.028027215491216641</v>
       </c>
       <c r="F87" s="0">
-        <v>0.028029372744751459</v>
+        <v>0.0069183871327619046</v>
       </c>
     </row>
     <row r="88">
@@ -7463,19 +7463,19 @@
         <v>167</v>
       </c>
       <c r="B88" s="0">
-        <v>0.084522146516239932</v>
+        <v>0.050021419315698951</v>
       </c>
       <c r="C88" s="0">
-        <v>0.058900295540422427</v>
+        <v>0.084522126898130171</v>
       </c>
       <c r="D88" s="0">
-        <v>0.050021667372608616</v>
+        <v>0.058901421620564408</v>
       </c>
       <c r="E88" s="0">
-        <v>0.0050819713693327547</v>
+        <v>0.046930372492058024</v>
       </c>
       <c r="F88" s="0">
-        <v>0.046929085368043168</v>
+        <v>0.0050817244555328494</v>
       </c>
     </row>
     <row r="89">
@@ -7483,19 +7483,19 @@
         <v>168</v>
       </c>
       <c r="B89" s="0">
-        <v>0.0029788044760826761</v>
+        <v>0.011067204178288539</v>
       </c>
       <c r="C89" s="0">
-        <v>0.0026714115213657998</v>
+        <v>0.0029787854940463978</v>
       </c>
       <c r="D89" s="0">
-        <v>0.01106719656868994</v>
+        <v>0.0026714589173331155</v>
       </c>
       <c r="E89" s="0">
-        <v>0</v>
+        <v>0.0047043104339666558</v>
       </c>
       <c r="F89" s="0">
-        <v>0.00470428924154127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -7503,19 +7503,19 @@
         <v>169</v>
       </c>
       <c r="B90" s="0">
-        <v>0.0028202544498436995</v>
+        <v>0.075102703583200495</v>
       </c>
       <c r="C90" s="0">
-        <v>0.0015558532393459541</v>
+        <v>0.0028202448601010659</v>
       </c>
       <c r="D90" s="0">
-        <v>0.075102762236522708</v>
+        <v>0.0015558923596606811</v>
       </c>
       <c r="E90" s="0">
-        <v>0</v>
+        <v>0.0037742814490101754</v>
       </c>
       <c r="F90" s="0">
-        <v>0.003774442911989793</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7528,8 +7528,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
+    <col min="2" max="2" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
@@ -7560,19 +7560,19 @@
         <v>250</v>
       </c>
       <c r="B2" s="0">
-        <v>0.35376769667477459</v>
+        <v>0.10787322100198998</v>
       </c>
       <c r="C2" s="0">
-        <v>0.42631831785643037</v>
+        <v>0.35376835961152875</v>
       </c>
       <c r="D2" s="0">
-        <v>0.10787322108366791</v>
+        <v>0.42631845232809818</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>0.17989277582248933</v>
       </c>
       <c r="F2" s="0">
-        <v>0.17989271410212701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -7580,19 +7580,19 @@
         <v>255</v>
       </c>
       <c r="B3" s="0">
-        <v>0.34031875467663764</v>
+        <v>0.17932184297225357</v>
       </c>
       <c r="C3" s="0">
-        <v>0.22715220276212178</v>
+        <v>0.34031964466006093</v>
       </c>
       <c r="D3" s="0">
-        <v>0.17932190657631109</v>
+        <v>0.22715233039389168</v>
       </c>
       <c r="E3" s="0">
-        <v>0.008632566854349006</v>
+        <v>0.24273468880276208</v>
       </c>
       <c r="F3" s="0">
-        <v>0.24273463460965494</v>
+        <v>0.0086325709202982551</v>
       </c>
     </row>
     <row r="4">
@@ -7600,19 +7600,19 @@
         <v>260</v>
       </c>
       <c r="B4" s="0">
-        <v>0.30567761429986529</v>
+        <v>0.27485329043019247</v>
       </c>
       <c r="C4" s="0">
-        <v>0.101399327308165</v>
+        <v>0.30567822104627218</v>
       </c>
       <c r="D4" s="0">
-        <v>0.27485347716186875</v>
+        <v>0.10139935746998513</v>
       </c>
       <c r="E4" s="0">
-        <v>0.032344399612226023</v>
+        <v>0.30708773000354228</v>
       </c>
       <c r="F4" s="0">
-        <v>0.30708769586639439</v>
+        <v>0.032344415648043426</v>
       </c>
     </row>
     <row r="5">
@@ -7620,19 +7620,19 @@
         <v>265</v>
       </c>
       <c r="B5" s="0">
-        <v>0.26829706466893005</v>
+        <v>0.39374222256996389</v>
       </c>
       <c r="C5" s="0">
-        <v>0.053083862598316295</v>
+        <v>0.26829733108204956</v>
       </c>
       <c r="D5" s="0">
-        <v>0.39374260794517918</v>
+        <v>0.053083750760502903</v>
       </c>
       <c r="E5" s="0">
-        <v>0.065385199307604544</v>
+        <v>0.3624086543403916</v>
       </c>
       <c r="F5" s="0">
-        <v>0.36240864793944594</v>
+        <v>0.065385215091541313</v>
       </c>
     </row>
     <row r="6">
@@ -7640,19 +7640,19 @@
         <v>270</v>
       </c>
       <c r="B6" s="0">
-        <v>0.23797783449136739</v>
+        <v>0.49588201173148688</v>
       </c>
       <c r="C6" s="0">
-        <v>0.051075019971407704</v>
+        <v>0.23797779460401958</v>
       </c>
       <c r="D6" s="0">
-        <v>0.49588265956808714</v>
+        <v>0.051074757641923443</v>
       </c>
       <c r="E6" s="0">
-        <v>0.11295327398185666</v>
+        <v>0.39607330937263724</v>
       </c>
       <c r="F6" s="0">
-        <v>0.39607332675278722</v>
+        <v>0.11295328500220733</v>
       </c>
     </row>
     <row r="7">
@@ -7660,19 +7660,19 @@
         <v>275</v>
       </c>
       <c r="B7" s="0">
-        <v>0.20932866564421201</v>
+        <v>0.51151549165870847</v>
       </c>
       <c r="C7" s="0">
-        <v>0.06954671845849976</v>
+        <v>0.20932843416030655</v>
       </c>
       <c r="D7" s="0">
-        <v>0.51151625040525994</v>
+        <v>0.069546335718425251</v>
       </c>
       <c r="E7" s="0">
-        <v>0.17998342320617405</v>
+        <v>0.4111950966115438</v>
       </c>
       <c r="F7" s="0">
-        <v>0.41119512960076005</v>
+        <v>0.17998342844809539</v>
       </c>
     </row>
     <row r="8">
@@ -7680,19 +7680,19 @@
         <v>280</v>
       </c>
       <c r="B8" s="0">
-        <v>0.1884120701362671</v>
+        <v>0.41828933783560229</v>
       </c>
       <c r="C8" s="0">
-        <v>0.10202888945767283</v>
+        <v>0.18841192588212954</v>
       </c>
       <c r="D8" s="0">
-        <v>0.41828984406438835</v>
+        <v>0.10202842759529576</v>
       </c>
       <c r="E8" s="0">
-        <v>0.26321710445550717</v>
+        <v>0.39821649644168117</v>
       </c>
       <c r="F8" s="0">
-        <v>0.39821653090419751</v>
+        <v>0.26321710387470876</v>
       </c>
     </row>
     <row r="9">
@@ -7700,19 +7700,19 @@
         <v>285</v>
       </c>
       <c r="B9" s="0">
-        <v>0.16904293286400968</v>
+        <v>0.20196865138505954</v>
       </c>
       <c r="C9" s="0">
-        <v>0.14627007695355035</v>
+        <v>0.16904301298225832</v>
       </c>
       <c r="D9" s="0">
-        <v>0.20196859496559552</v>
+        <v>0.14626960276289172</v>
       </c>
       <c r="E9" s="0">
-        <v>0.35231377661117341</v>
+        <v>0.35078909671404834</v>
       </c>
       <c r="F9" s="0">
-        <v>0.3507891152447179</v>
+        <v>0.35231377254220314</v>
       </c>
     </row>
     <row r="10">
@@ -7720,19 +7720,19 @@
         <v>290</v>
       </c>
       <c r="B10" s="0">
-        <v>0.15813918887509362</v>
+        <v>0.045621554015969346</v>
       </c>
       <c r="C10" s="0">
-        <v>0.19830530054347406</v>
+        <v>0.15813921202019471</v>
       </c>
       <c r="D10" s="0">
-        <v>0.045621376834641222</v>
+        <v>0.19830486457004404</v>
       </c>
       <c r="E10" s="0">
-        <v>0.4216345041997821</v>
+        <v>0.24679502629507144</v>
       </c>
       <c r="F10" s="0">
-        <v>0.24679501964497461</v>
+        <v>0.42163449983343976</v>
       </c>
     </row>
     <row r="11">
@@ -7740,19 +7740,19 @@
         <v>295</v>
       </c>
       <c r="B11" s="0">
-        <v>0.14916599581369402</v>
+        <v>0.0099760210809921694</v>
       </c>
       <c r="C11" s="0">
-        <v>0.24837296565758848</v>
+        <v>0.14916555836239531</v>
       </c>
       <c r="D11" s="0">
-        <v>0.0099759281940742708</v>
+        <v>0.24837259710988399</v>
       </c>
       <c r="E11" s="0">
-        <v>0.44965173488418198</v>
+        <v>0.1118003446821703</v>
       </c>
       <c r="F11" s="0">
-        <v>0.111800327152031</v>
+        <v>0.44965173241557971</v>
       </c>
     </row>
     <row r="12">
@@ -7760,19 +7760,19 @@
         <v>300</v>
       </c>
       <c r="B12" s="0">
-        <v>0.14145774819681081</v>
+        <v>0.0058537342052801724</v>
       </c>
       <c r="C12" s="0">
-        <v>0.29129209929768751</v>
+        <v>0.14145699517724691</v>
       </c>
       <c r="D12" s="0">
-        <v>0.0058535374303366004</v>
+        <v>0.29129180046192998</v>
       </c>
       <c r="E12" s="0">
-        <v>0.42445103703879472</v>
+        <v>0.042971572734842138</v>
       </c>
       <c r="F12" s="0">
-        <v>0.042971562586850434</v>
+        <v>0.42445103275648699</v>
       </c>
     </row>
     <row r="13">
@@ -7780,19 +7780,19 @@
         <v>305</v>
       </c>
       <c r="B13" s="0">
-        <v>0.13781277415222368</v>
+        <v>0.0040803243957458889</v>
       </c>
       <c r="C13" s="0">
-        <v>0.32163546269746146</v>
+        <v>0.13781185968674442</v>
       </c>
       <c r="D13" s="0">
-        <v>0.0040793478364449468</v>
+        <v>0.3216352754182954</v>
       </c>
       <c r="E13" s="0">
-        <v>0.34739693146960948</v>
+        <v>0.014486428568905686</v>
       </c>
       <c r="F13" s="0">
-        <v>0.014486422088431421</v>
+        <v>0.34739692319874493</v>
       </c>
     </row>
     <row r="14">
@@ -7800,19 +7800,19 @@
         <v>310</v>
       </c>
       <c r="B14" s="0">
-        <v>0.13632253943392578</v>
+        <v>0.0051534403223415471</v>
       </c>
       <c r="C14" s="0">
-        <v>0.33281405030766126</v>
+        <v>0.13632086257307777</v>
       </c>
       <c r="D14" s="0">
-        <v>0.005135433189979461</v>
+        <v>0.33281405600758424</v>
       </c>
       <c r="E14" s="0">
-        <v>0.23364971753142119</v>
+        <v>0.004506640646714982</v>
       </c>
       <c r="F14" s="0">
-        <v>0.004506667406829091</v>
+        <v>0.23364971759843339</v>
       </c>
     </row>
     <row r="15">
@@ -7820,19 +7820,19 @@
         <v>315</v>
       </c>
       <c r="B15" s="0">
-        <v>0.13795465298749604</v>
+        <v>0.0044117857705328039</v>
       </c>
       <c r="C15" s="0">
-        <v>0.32031592781808077</v>
+        <v>0.13795164362346571</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0043626119555355228</v>
+        <v>0.32031617489799724</v>
       </c>
       <c r="E15" s="0">
-        <v>0.12806712618501029</v>
+        <v>0.0017712217508633189</v>
       </c>
       <c r="F15" s="0">
-        <v>0.001771333163468336</v>
+        <v>0.12806714750566706</v>
       </c>
     </row>
     <row r="16">
@@ -7840,19 +7840,19 @@
         <v>320</v>
       </c>
       <c r="B16" s="0">
-        <v>0.14201970929393154</v>
+        <v>0.0069005387098740349</v>
       </c>
       <c r="C16" s="0">
-        <v>0.28611662403755689</v>
+        <v>0.14201506348294821</v>
       </c>
       <c r="D16" s="0">
-        <v>0.0067833680943028473</v>
+        <v>0.28611709782238853</v>
       </c>
       <c r="E16" s="0">
-        <v>0.059082953424401667</v>
+        <v>0.0012375732611067138</v>
       </c>
       <c r="F16" s="0">
-        <v>0.0012378087508776755</v>
+        <v>0.05908299908878633</v>
       </c>
     </row>
     <row r="17">
@@ -7860,19 +7860,19 @@
         <v>325</v>
       </c>
       <c r="B17" s="0">
-        <v>0.15012313679557102</v>
+        <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0.24017592936737123</v>
+        <v>0.15012250987834166</v>
       </c>
       <c r="D17" s="0">
-        <v>0</v>
+        <v>0.24017613223751924</v>
       </c>
       <c r="E17" s="0">
-        <v>0.024947210891791964</v>
+        <v>0.0010152267317375477</v>
       </c>
       <c r="F17" s="0">
-        <v>0.0010151897033647073</v>
+        <v>0.024947208422109513</v>
       </c>
     </row>
     <row r="18">
@@ -7880,19 +7880,19 @@
         <v>330</v>
       </c>
       <c r="B18" s="0">
-        <v>0.15945805633356511</v>
+        <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0.18975782197234381</v>
+        <v>0.15945760931972974</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>0.18975805149721942</v>
       </c>
       <c r="E18" s="0">
-        <v>0.01061501256903782</v>
+        <v>0.00085598112949947073</v>
       </c>
       <c r="F18" s="0">
-        <v>0.0008559539871417298</v>
+        <v>0.010615015605891915</v>
       </c>
     </row>
     <row r="19">
@@ -7900,19 +7900,19 @@
         <v>335</v>
       </c>
       <c r="B19" s="0">
-        <v>0.16559567620724894</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0.14238255773836803</v>
+        <v>0.16559544049728706</v>
       </c>
       <c r="D19" s="0">
-        <v>0</v>
+        <v>0.14238279058012804</v>
       </c>
       <c r="E19" s="0">
-        <v>0.0042035078694279641</v>
+        <v>0.0005924196326158724</v>
       </c>
       <c r="F19" s="0">
-        <v>0.00059239561989310116</v>
+        <v>0.0042035151155822553</v>
       </c>
     </row>
     <row r="20">
@@ -7920,19 +7920,19 @@
         <v>340</v>
       </c>
       <c r="B20" s="0">
-        <v>0.16867447676721614</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0.099896662786215146</v>
+        <v>0.16867446215374662</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>0.099896894885018309</v>
       </c>
       <c r="E20" s="0">
-        <v>0.00091851069339476542</v>
+        <v>0.00026150765624186572</v>
       </c>
       <c r="F20" s="0">
-        <v>0.00026147575366545334</v>
+        <v>0.00091852059220804663</v>
       </c>
     </row>
     <row r="21">
@@ -7940,19 +7940,19 @@
         <v>345</v>
       </c>
       <c r="B21" s="0">
-        <v>0.16550602272032994</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0">
-        <v>0.063555911647408869</v>
+        <v>0.16550618461621913</v>
       </c>
       <c r="D21" s="0">
-        <v>0</v>
+        <v>0.063556164066434287</v>
       </c>
       <c r="E21" s="0">
-        <v>0</v>
+        <v>0.00018708648120560755</v>
       </c>
       <c r="F21" s="0">
-        <v>0.00018704776253261935</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -7960,13 +7960,13 @@
         <v>350</v>
       </c>
       <c r="B22" s="0">
-        <v>0.15896268513896703</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0">
-        <v>0.036661950352178258</v>
+        <v>0.15896306495394511</v>
       </c>
       <c r="D22" s="0">
-        <v>0</v>
+        <v>0.036662224844489819</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -7980,13 +7980,13 @@
         <v>355</v>
       </c>
       <c r="B23" s="0">
-        <v>0.15189954459313235</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0.019143400454488802</v>
+        <v>0.15190010716130908</v>
       </c>
       <c r="D23" s="0">
-        <v>0</v>
+        <v>0.019143654961226296</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -8000,13 +8000,13 @@
         <v>360</v>
       </c>
       <c r="B24" s="0">
-        <v>0.14549777194314817</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>0.0078709846971197622</v>
+        <v>0.14549845606150982</v>
       </c>
       <c r="D24" s="0">
-        <v>0</v>
+        <v>0.0078712158018317113</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -8020,13 +8020,13 @@
         <v>365</v>
       </c>
       <c r="B25" s="0">
-        <v>0.1373361835235421</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>0.0018187757167187244</v>
+        <v>0.13733706358764625</v>
       </c>
       <c r="D25" s="0">
-        <v>0</v>
+        <v>0.0018189529182098094</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -8040,10 +8040,10 @@
         <v>370</v>
       </c>
       <c r="B26" s="0">
-        <v>0.12516962757398861</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>0</v>
+        <v>0.12517066341396752</v>
       </c>
       <c r="D26" s="0">
         <v>0</v>
@@ -8060,10 +8060,10 @@
         <v>375</v>
       </c>
       <c r="B27" s="0">
-        <v>0.11280002090908352</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
-        <v>0</v>
+        <v>0.11280107624462878</v>
       </c>
       <c r="D27" s="0">
         <v>0</v>
@@ -8080,10 +8080,10 @@
         <v>380</v>
       </c>
       <c r="B28" s="0">
-        <v>0.098267353996885076</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>0</v>
+        <v>0.09826839747868249</v>
       </c>
       <c r="D28" s="0">
         <v>0</v>
@@ -8100,10 +8100,10 @@
         <v>385</v>
       </c>
       <c r="B29" s="0">
-        <v>0.086818599637776703</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0">
-        <v>0</v>
+        <v>0.086819546360835775</v>
       </c>
       <c r="D29" s="0">
         <v>0</v>
@@ -8120,10 +8120,10 @@
         <v>390</v>
       </c>
       <c r="B30" s="0">
-        <v>0.073040383180702134</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>0</v>
+        <v>0.073041249987827406</v>
       </c>
       <c r="D30" s="0">
         <v>0</v>
@@ -8140,10 +8140,10 @@
         <v>395</v>
       </c>
       <c r="B31" s="0">
-        <v>0.061338025866450617</v>
+        <v>0</v>
       </c>
       <c r="C31" s="0">
-        <v>0</v>
+        <v>0.061338753050552308</v>
       </c>
       <c r="D31" s="0">
         <v>0</v>
@@ -8160,10 +8160,10 @@
         <v>400</v>
       </c>
       <c r="B32" s="0">
-        <v>0.05339411697054957</v>
+        <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>0</v>
+        <v>0.053394782519766156</v>
       </c>
       <c r="D32" s="0">
         <v>0</v>
@@ -8180,10 +8180,10 @@
         <v>405</v>
       </c>
       <c r="B33" s="0">
-        <v>0.047018510207026743</v>
+        <v>0</v>
       </c>
       <c r="C33" s="0">
-        <v>0</v>
+        <v>0.047019096840707098</v>
       </c>
       <c r="D33" s="0">
         <v>0</v>
@@ -8200,10 +8200,10 @@
         <v>410</v>
       </c>
       <c r="B34" s="0">
-        <v>0.039438131223805128</v>
+        <v>0</v>
       </c>
       <c r="C34" s="0">
-        <v>0</v>
+        <v>0.039438643192413775</v>
       </c>
       <c r="D34" s="0">
         <v>0</v>
@@ -8220,10 +8220,10 @@
         <v>415</v>
       </c>
       <c r="B35" s="0">
-        <v>0.034678699801530273</v>
+        <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>0</v>
+        <v>0.03467916912472524</v>
       </c>
       <c r="D35" s="0">
         <v>0</v>
@@ -8240,10 +8240,10 @@
         <v>420</v>
       </c>
       <c r="B36" s="0">
-        <v>0.029845041916839295</v>
+        <v>0</v>
       </c>
       <c r="C36" s="0">
-        <v>0</v>
+        <v>0.029845471497698811</v>
       </c>
       <c r="D36" s="0">
         <v>0</v>
@@ -8260,10 +8260,10 @@
         <v>425</v>
       </c>
       <c r="B37" s="0">
-        <v>0.025393545122949935</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>0.025393941759195581</v>
       </c>
       <c r="D37" s="0">
         <v>0</v>
@@ -8280,10 +8280,10 @@
         <v>430</v>
       </c>
       <c r="B38" s="0">
-        <v>0.021642427546618378</v>
+        <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>0</v>
+        <v>0.021642786658472267</v>
       </c>
       <c r="D38" s="0">
         <v>0</v>
@@ -8300,10 +8300,10 @@
         <v>435</v>
       </c>
       <c r="B39" s="0">
-        <v>0.018365586992200388</v>
+        <v>0</v>
       </c>
       <c r="C39" s="0">
-        <v>0</v>
+        <v>0.018365918444750003</v>
       </c>
       <c r="D39" s="0">
         <v>0</v>
@@ -8320,10 +8320,10 @@
         <v>440</v>
       </c>
       <c r="B40" s="0">
-        <v>0.016523473542392538</v>
+        <v>0</v>
       </c>
       <c r="C40" s="0">
-        <v>0</v>
+        <v>0.016523773615636731</v>
       </c>
       <c r="D40" s="0">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>445</v>
       </c>
       <c r="B41" s="0">
-        <v>0.013790979508378399</v>
+        <v>0</v>
       </c>
       <c r="C41" s="0">
-        <v>0</v>
+        <v>0.013791246802470737</v>
       </c>
       <c r="D41" s="0">
         <v>0</v>
@@ -8360,10 +8360,10 @@
         <v>450</v>
       </c>
       <c r="B42" s="0">
-        <v>0.011300781717113928</v>
+        <v>0</v>
       </c>
       <c r="C42" s="0">
-        <v>0</v>
+        <v>0.011300996821322325</v>
       </c>
       <c r="D42" s="0">
         <v>0</v>
@@ -8385,8 +8385,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
     <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
@@ -8417,19 +8417,19 @@
         <v>301.47300000000001</v>
       </c>
       <c r="B2" s="0">
-        <v>0.01539538818774013</v>
+        <v>0.45469508889374594</v>
       </c>
       <c r="C2" s="0">
-        <v>0.0053599971130356269</v>
+        <v>0.015396410954838203</v>
       </c>
       <c r="D2" s="0">
-        <v>0.45469578493718971</v>
+        <v>0.0053604739583629707</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>0.0090363821502696846</v>
       </c>
       <c r="F2" s="0">
-        <v>0.0090363635011680397</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -8437,19 +8437,19 @@
         <v>304.70800000000003</v>
       </c>
       <c r="B3" s="0">
-        <v>0.016628089372153151</v>
+        <v>0.43645853599449341</v>
       </c>
       <c r="C3" s="0">
-        <v>0.0025258531331787738</v>
+        <v>0.016629064450998699</v>
       </c>
       <c r="D3" s="0">
-        <v>0.43645918683027829</v>
+        <v>0.0025262393142864129</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>0.01439714057464306</v>
       </c>
       <c r="F3" s="0">
-        <v>0.01439712774942783</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -8457,19 +8457,19 @@
         <v>307.94499999999999</v>
       </c>
       <c r="B4" s="0">
-        <v>0.020061527383317776</v>
+        <v>0.40583728792793888</v>
       </c>
       <c r="C4" s="0">
-        <v>0.011232772592490248</v>
+        <v>0.020062326139725847</v>
       </c>
       <c r="D4" s="0">
-        <v>0.40583775666376343</v>
+        <v>0.011233161264929589</v>
       </c>
       <c r="E4" s="0">
-        <v>0.00023394530048231167</v>
+        <v>0.023949950837154916</v>
       </c>
       <c r="F4" s="0">
-        <v>0.023949933115265255</v>
+        <v>0.00023395229681400713</v>
       </c>
     </row>
     <row r="5">
@@ -8477,19 +8477,19 @@
         <v>311.18400000000003</v>
       </c>
       <c r="B5" s="0">
-        <v>0.021857434049355164</v>
+        <v>0.35556363375824257</v>
       </c>
       <c r="C5" s="0">
-        <v>0.0063849887057230333</v>
+        <v>0.021858075195036693</v>
       </c>
       <c r="D5" s="0">
-        <v>0.35556397576420273</v>
+        <v>0.0063853767964037215</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00084904582281407251</v>
+        <v>0.036630580968153484</v>
       </c>
       <c r="F5" s="0">
-        <v>0.036630568880078429</v>
+        <v>0.00084904918453544383</v>
       </c>
     </row>
     <row r="6">
@@ -8497,19 +8497,19 @@
         <v>314.42500000000001</v>
       </c>
       <c r="B6" s="0">
-        <v>0.030526076509766711</v>
+        <v>0.31189059540236136</v>
       </c>
       <c r="C6" s="0">
-        <v>0.011226613051750852</v>
+        <v>0.030526506912948111</v>
       </c>
       <c r="D6" s="0">
-        <v>0.31189075417107215</v>
+        <v>0.011226926045820498</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>0.053920124404246705</v>
       </c>
       <c r="F6" s="0">
-        <v>0.053920107635733204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8517,19 +8517,19 @@
         <v>317.66800000000001</v>
       </c>
       <c r="B7" s="0">
-        <v>0.024089458649573247</v>
+        <v>0.26144069340354065</v>
       </c>
       <c r="C7" s="0">
-        <v>0.0070674897673474457</v>
+        <v>0.024089627795929873</v>
       </c>
       <c r="D7" s="0">
-        <v>0.2614407026874121</v>
+        <v>0.0070676672995503937</v>
       </c>
       <c r="E7" s="0">
-        <v>0.00014585758751560268</v>
+        <v>0.074050318325146775</v>
       </c>
       <c r="F7" s="0">
-        <v>0.074050308066329465</v>
+        <v>0.00014584558292291829</v>
       </c>
     </row>
     <row r="8">
@@ -8537,19 +8537,19 @@
         <v>320.91300000000001</v>
       </c>
       <c r="B8" s="0">
-        <v>0.023311097971688271</v>
+        <v>0.22022259935105271</v>
       </c>
       <c r="C8" s="0">
-        <v>0.0030203197783463852</v>
+        <v>0.023310990968675706</v>
       </c>
       <c r="D8" s="0">
-        <v>0.22022244639722924</v>
+        <v>0.0030204828771749101</v>
       </c>
       <c r="E8" s="0">
-        <v>0</v>
+        <v>0.098062190526460119</v>
       </c>
       <c r="F8" s="0">
-        <v>0.098062184415780768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -8557,19 +8557,19 @@
         <v>324.16000000000003</v>
       </c>
       <c r="B9" s="0">
-        <v>0.033138741304400955</v>
+        <v>0.18562036950558633</v>
       </c>
       <c r="C9" s="0">
-        <v>0.0030208352941395239</v>
+        <v>0.033137308879992208</v>
       </c>
       <c r="D9" s="0">
-        <v>0.1856199041001749</v>
+        <v>0.0030206527858187469</v>
       </c>
       <c r="E9" s="0">
-        <v>0.00040792823259306742</v>
+        <v>0.12593984291463561</v>
       </c>
       <c r="F9" s="0">
-        <v>0.12593982244364066</v>
+        <v>0.00040778727033743311</v>
       </c>
     </row>
     <row r="10">
@@ -8577,19 +8577,19 @@
         <v>327.40899999999999</v>
       </c>
       <c r="B10" s="0">
-        <v>0.043074045140587901</v>
+        <v>0.15345481865465474</v>
       </c>
       <c r="C10" s="0">
-        <v>0.0096606461167223004</v>
+        <v>0.043069734393423931</v>
       </c>
       <c r="D10" s="0">
-        <v>0.15345390919553259</v>
+        <v>0.0096599782860168904</v>
       </c>
       <c r="E10" s="0">
-        <v>0.00017730835260307783</v>
+        <v>0.15430361402371567</v>
       </c>
       <c r="F10" s="0">
-        <v>0.15430355596210249</v>
+        <v>0.00017722381107222529</v>
       </c>
     </row>
     <row r="11">
@@ -8597,19 +8597,19 @@
         <v>330.66000000000003</v>
       </c>
       <c r="B11" s="0">
-        <v>0.044256995611996308</v>
+        <v>0.12358445246126253</v>
       </c>
       <c r="C11" s="0">
-        <v>0.008347653842572236</v>
+        <v>0.04425301280034024</v>
       </c>
       <c r="D11" s="0">
-        <v>0.12358341772572821</v>
+        <v>0.0083469723102134359</v>
       </c>
       <c r="E11" s="0">
-        <v>0.00099482984097781996</v>
+        <v>0.18141016215122738</v>
       </c>
       <c r="F11" s="0">
-        <v>0.18141011974882754</v>
+        <v>0.00099468393230541918</v>
       </c>
     </row>
     <row r="12">
@@ -8617,19 +8617,19 @@
         <v>333.91199999999998</v>
       </c>
       <c r="B12" s="0">
-        <v>0.039642714472589186</v>
+        <v>0.098401602506718033</v>
       </c>
       <c r="C12" s="0">
-        <v>0.0047404389636062508</v>
+        <v>0.03963459835174956</v>
       </c>
       <c r="D12" s="0">
-        <v>0.098400041942912977</v>
+        <v>0.0047394205914387724</v>
       </c>
       <c r="E12" s="0">
-        <v>0.0023776084288334672</v>
+        <v>0.20521198468593152</v>
       </c>
       <c r="F12" s="0">
-        <v>0.20521188423028367</v>
+        <v>0.002377619842853871</v>
       </c>
     </row>
     <row r="13">
@@ -8637,19 +8637,19 @@
         <v>337.16699999999997</v>
       </c>
       <c r="B13" s="0">
-        <v>0.036216949609818395</v>
+        <v>0.076967267308833062</v>
       </c>
       <c r="C13" s="0">
-        <v>0.0033190404802959433</v>
+        <v>0.036210554181189104</v>
       </c>
       <c r="D13" s="0">
-        <v>0.076965767273136893</v>
+        <v>0.003318298111527505</v>
       </c>
       <c r="E13" s="0">
-        <v>0.0032289123338697392</v>
+        <v>0.22474473042230161</v>
       </c>
       <c r="F13" s="0">
-        <v>0.22474466784423738</v>
+        <v>0.0032289055489714219</v>
       </c>
     </row>
     <row r="14">
@@ -8657,19 +8657,19 @@
         <v>340.423</v>
       </c>
       <c r="B14" s="0">
-        <v>0.058663231231246719</v>
+        <v>0.059541631570739516</v>
       </c>
       <c r="C14" s="0">
-        <v>0.0080799433717898377</v>
+        <v>0.058657879041693076</v>
       </c>
       <c r="D14" s="0">
-        <v>0.059540165054331448</v>
+        <v>0.0080794970837950938</v>
       </c>
       <c r="E14" s="0">
-        <v>0.0033245639945861587</v>
+        <v>0.23983867060282618</v>
       </c>
       <c r="F14" s="0">
-        <v>0.23983863036183084</v>
+        <v>0.0033245812936477616</v>
       </c>
     </row>
     <row r="15">
@@ -8677,19 +8677,19 @@
         <v>343.68200000000002</v>
       </c>
       <c r="B15" s="0">
-        <v>0.048297342910866493</v>
+        <v>0.046315885115497418</v>
       </c>
       <c r="C15" s="0">
-        <v>0.010482320293146259</v>
+        <v>0.048293639144419427</v>
       </c>
       <c r="D15" s="0">
-        <v>0.046314503702600173</v>
+        <v>0.010482064034091481</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0045247546385001362</v>
+        <v>0.2506599074912883</v>
       </c>
       <c r="F15" s="0">
-        <v>0.25065990162279472</v>
+        <v>0.0045247542163831776</v>
       </c>
     </row>
     <row r="16">
@@ -8697,19 +8697,19 @@
         <v>346.94200000000001</v>
       </c>
       <c r="B16" s="0">
-        <v>0.045012577085043859</v>
+        <v>0.033536325572576103</v>
       </c>
       <c r="C16" s="0">
-        <v>0.010058315456145229</v>
+        <v>0.045009101559672894</v>
       </c>
       <c r="D16" s="0">
-        <v>0.033534847971081916</v>
+        <v>0.0100582229134992</v>
       </c>
       <c r="E16" s="0">
-        <v>0.0055945896099887493</v>
+        <v>0.25760743858676671</v>
       </c>
       <c r="F16" s="0">
-        <v>0.25760744283917775</v>
+        <v>0.0055945926568131497</v>
       </c>
     </row>
     <row r="17">
@@ -8717,19 +8717,19 @@
         <v>350.20400000000001</v>
       </c>
       <c r="B17" s="0">
-        <v>0.066371698435531965</v>
+        <v>0.025562094746305577</v>
       </c>
       <c r="C17" s="0">
-        <v>0.017666739404051987</v>
+        <v>0.066370058762311848</v>
       </c>
       <c r="D17" s="0">
-        <v>0.025560884769497097</v>
+        <v>0.017666799570397469</v>
       </c>
       <c r="E17" s="0">
-        <v>0.0075336074723043696</v>
+        <v>0.26086013089151278</v>
       </c>
       <c r="F17" s="0">
-        <v>0.2608601644794159</v>
+        <v>0.0075335943399553662</v>
       </c>
     </row>
     <row r="18">
@@ -8737,19 +8737,19 @@
         <v>353.46699999999999</v>
       </c>
       <c r="B18" s="0">
-        <v>0.073301685015899606</v>
+        <v>0.018174256949641927</v>
       </c>
       <c r="C18" s="0">
-        <v>0.020956568122991275</v>
+        <v>0.07330012238404969</v>
       </c>
       <c r="D18" s="0">
-        <v>0.018173048598216425</v>
+        <v>0.020956627279831754</v>
       </c>
       <c r="E18" s="0">
-        <v>0.011113951642862392</v>
+        <v>0.25906912541740851</v>
       </c>
       <c r="F18" s="0">
-        <v>0.259069160225121</v>
+        <v>0.011113938429545684</v>
       </c>
     </row>
     <row r="19">
@@ -8757,19 +8757,19 @@
         <v>356.733</v>
       </c>
       <c r="B19" s="0">
-        <v>0.071287503230961627</v>
+        <v>0.012121883859312463</v>
       </c>
       <c r="C19" s="0">
-        <v>0.031464572678767302</v>
+        <v>0.07128561278124039</v>
       </c>
       <c r="D19" s="0">
-        <v>0.012120604316236641</v>
+        <v>0.031464661924073587</v>
       </c>
       <c r="E19" s="0">
-        <v>0.016062228571040824</v>
+        <v>0.25264886248170371</v>
       </c>
       <c r="F19" s="0">
-        <v>0.25264889343721114</v>
+        <v>0.016062218358935562</v>
       </c>
     </row>
     <row r="20">
@@ -8777,19 +8777,19 @@
         <v>360</v>
       </c>
       <c r="B20" s="0">
-        <v>0.070100080810955895</v>
+        <v>0.0084665446433513005</v>
       </c>
       <c r="C20" s="0">
-        <v>0.05042043094260848</v>
+        <v>0.070098271411610569</v>
       </c>
       <c r="D20" s="0">
-        <v>0.0084653092729364797</v>
+        <v>0.050420517584998659</v>
       </c>
       <c r="E20" s="0">
-        <v>0.022790984121214438</v>
+        <v>0.2433683552243695</v>
       </c>
       <c r="F20" s="0">
-        <v>0.24336838675501213</v>
+        <v>0.022790973669215651</v>
       </c>
     </row>
     <row r="21">
@@ -8797,19 +8797,19 @@
         <v>363.26900000000001</v>
       </c>
       <c r="B21" s="0">
-        <v>0.068831463580691921</v>
+        <v>0.005101951726301711</v>
       </c>
       <c r="C21" s="0">
-        <v>0.071480192700446518</v>
+        <v>0.06882928192804845</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0051005679379856192</v>
+        <v>0.071480323939854068</v>
       </c>
       <c r="E21" s="0">
-        <v>0.03206432649525532</v>
+        <v>0.23136923006287186</v>
       </c>
       <c r="F21" s="0">
-        <v>0.23136925780574272</v>
+        <v>0.032064317358178239</v>
       </c>
     </row>
     <row r="22">
@@ -8817,19 +8817,19 @@
         <v>366.53899999999999</v>
       </c>
       <c r="B22" s="0">
-        <v>0.064401962012346922</v>
+        <v>0.0042432205900465592</v>
       </c>
       <c r="C22" s="0">
-        <v>0.094565157777054612</v>
+        <v>0.064399542950354674</v>
       </c>
       <c r="D22" s="0">
-        <v>0.0042418366583337561</v>
+        <v>0.094565304858260091</v>
       </c>
       <c r="E22" s="0">
-        <v>0.044731137557494291</v>
+        <v>0.21860958500690497</v>
       </c>
       <c r="F22" s="0">
-        <v>0.21860960845787472</v>
+        <v>0.044731130267777884</v>
       </c>
     </row>
     <row r="23">
@@ -8837,19 +8837,19 @@
         <v>369.81200000000001</v>
       </c>
       <c r="B23" s="0">
-        <v>0.06111353290398646</v>
+        <v>0.0031707091179134783</v>
       </c>
       <c r="C23" s="0">
-        <v>0.1277789932581615</v>
+        <v>0.061110448901550436</v>
       </c>
       <c r="D23" s="0">
-        <v>0.0031690337500784546</v>
+        <v>0.12777918430656302</v>
       </c>
       <c r="E23" s="0">
-        <v>0.060121939041683434</v>
+        <v>0.20529045122969295</v>
       </c>
       <c r="F23" s="0">
-        <v>0.20529046880765719</v>
+        <v>0.060121933503692909</v>
       </c>
     </row>
     <row r="24">
@@ -8857,19 +8857,19 @@
         <v>373.08600000000001</v>
       </c>
       <c r="B24" s="0">
-        <v>0.042625444301208647</v>
+        <v>0.00030592152476177447</v>
       </c>
       <c r="C24" s="0">
-        <v>0.15667580258624259</v>
+        <v>0.042622345867361362</v>
       </c>
       <c r="D24" s="0">
-        <v>0.00030428595439640452</v>
+        <v>0.15667598149623269</v>
       </c>
       <c r="E24" s="0">
-        <v>0.080755223620212022</v>
+        <v>0.19522291097644104</v>
       </c>
       <c r="F24" s="0">
-        <v>0.19522292974854699</v>
+        <v>0.080755215822186338</v>
       </c>
     </row>
     <row r="25">
@@ -8877,19 +8877,19 @@
         <v>376.36200000000002</v>
       </c>
       <c r="B25" s="0">
-        <v>0.050761399688724403</v>
+        <v>0.001500192067614686</v>
       </c>
       <c r="C25" s="0">
-        <v>0.18595651813661346</v>
+        <v>0.050758106194450647</v>
       </c>
       <c r="D25" s="0">
-        <v>0.0014985974532698355</v>
+        <v>0.18595668198129942</v>
       </c>
       <c r="E25" s="0">
-        <v>0.10383684288045161</v>
+        <v>0.18225413097478033</v>
       </c>
       <c r="F25" s="0">
-        <v>0.18225414401023224</v>
+        <v>0.10383683900586756</v>
       </c>
     </row>
     <row r="26">
@@ -8897,19 +8897,19 @@
         <v>379.63900000000001</v>
       </c>
       <c r="B26" s="0">
-        <v>0.049653774688448372</v>
+        <v>0.0019381593394607133</v>
       </c>
       <c r="C26" s="0">
-        <v>0.20969564015318928</v>
+        <v>0.049650750811194168</v>
       </c>
       <c r="D26" s="0">
-        <v>0.0019367731713764986</v>
+        <v>0.20969574643904163</v>
       </c>
       <c r="E26" s="0">
-        <v>0.12801510149301687</v>
+        <v>0.16764205658189041</v>
       </c>
       <c r="F26" s="0">
-        <v>0.16764206891853684</v>
+        <v>0.12801509754427057</v>
       </c>
     </row>
     <row r="27">
@@ -8917,19 +8917,19 @@
         <v>382.91800000000001</v>
       </c>
       <c r="B27" s="0">
-        <v>0.046249690105294748</v>
+        <v>0.00119989712888502</v>
       </c>
       <c r="C27" s="0">
-        <v>0.23872719248030896</v>
+        <v>0.046246779811094485</v>
       </c>
       <c r="D27" s="0">
-        <v>0.0011986408817134524</v>
+        <v>0.23872725871105971</v>
       </c>
       <c r="E27" s="0">
-        <v>0.15664652938335671</v>
+        <v>0.15709360759202592</v>
       </c>
       <c r="F27" s="0">
-        <v>0.15709361951933515</v>
+        <v>0.15664652493353509</v>
       </c>
     </row>
     <row r="28">
@@ -8937,19 +8937,19 @@
         <v>386.19900000000001</v>
       </c>
       <c r="B28" s="0">
-        <v>0.050168735923811311</v>
+        <v>0.00041920599617046206</v>
       </c>
       <c r="C28" s="0">
-        <v>0.25726703626090602</v>
+        <v>0.050166191046575728</v>
       </c>
       <c r="D28" s="0">
-        <v>0.00041816601501642309</v>
+        <v>0.25726705654538551</v>
       </c>
       <c r="E28" s="0">
-        <v>0.182785593659816</v>
+        <v>0.14411707862804721</v>
       </c>
       <c r="F28" s="0">
-        <v>0.14411709106638079</v>
+        <v>0.18278558851734744</v>
       </c>
     </row>
     <row r="29">
@@ -8957,19 +8957,19 @@
         <v>389.481</v>
       </c>
       <c r="B29" s="0">
-        <v>0.045907044652302581</v>
+        <v>0.00035579003967406149</v>
       </c>
       <c r="C29" s="0">
-        <v>0.26690627533921024</v>
+        <v>0.045904630006391174</v>
       </c>
       <c r="D29" s="0">
-        <v>0.00035488281012256294</v>
+        <v>0.26690626003716478</v>
       </c>
       <c r="E29" s="0">
-        <v>0.20432591800555908</v>
+        <v>0.12950893750254414</v>
       </c>
       <c r="F29" s="0">
-        <v>0.12950894781156339</v>
+        <v>0.20432591296734026</v>
       </c>
     </row>
     <row r="30">
@@ -8977,19 +8977,19 @@
         <v>392.76499999999999</v>
       </c>
       <c r="B30" s="0">
-        <v>0.065273957370600294</v>
+        <v>0.00061244530572640782</v>
       </c>
       <c r="C30" s="0">
-        <v>0.27207202983206236</v>
+        <v>0.065271836100818895</v>
       </c>
       <c r="D30" s="0">
-        <v>0.00061164846292394235</v>
+        <v>0.27207199728366172</v>
       </c>
       <c r="E30" s="0">
-        <v>0.22520964779698421</v>
+        <v>0.11733893298203013</v>
       </c>
       <c r="F30" s="0">
-        <v>0.11733894232435746</v>
+        <v>0.22520964336972471</v>
       </c>
     </row>
     <row r="31">
@@ -8997,19 +8997,19 @@
         <v>396.05000000000001</v>
       </c>
       <c r="B31" s="0">
-        <v>0.069010372548511126</v>
+        <v>0.0017335480051053067</v>
       </c>
       <c r="C31" s="0">
-        <v>0.27661718725410112</v>
+        <v>0.069008392306587882</v>
       </c>
       <c r="D31" s="0">
-        <v>0.0017328912365878655</v>
+        <v>0.27661712009055933</v>
       </c>
       <c r="E31" s="0">
-        <v>0.24183955473751725</v>
+        <v>0.10552723635229035</v>
       </c>
       <c r="F31" s="0">
-        <v>0.10552724289687893</v>
+        <v>0.24183955170444779</v>
       </c>
     </row>
     <row r="32">
@@ -9017,19 +9017,19 @@
         <v>399.33699999999999</v>
       </c>
       <c r="B32" s="0">
-        <v>0.084532934396441342</v>
+        <v>0.00038984162695152231</v>
       </c>
       <c r="C32" s="0">
-        <v>0.26938862736348018</v>
+        <v>0.084531377299925506</v>
       </c>
       <c r="D32" s="0">
-        <v>0.00038929601675672401</v>
+        <v>0.26938855317636518</v>
       </c>
       <c r="E32" s="0">
-        <v>0.2526006888608901</v>
+        <v>0.094072828492915705</v>
       </c>
       <c r="F32" s="0">
-        <v>0.094072836352556213</v>
+        <v>0.25260068544474112</v>
       </c>
     </row>
     <row r="33">
@@ -9037,19 +9037,19 @@
         <v>402.625</v>
       </c>
       <c r="B33" s="0">
-        <v>0.096701237385178551</v>
+        <v>0.0021243677478362641</v>
       </c>
       <c r="C33" s="0">
-        <v>0.26184528295870602</v>
+        <v>0.096699776223072936</v>
       </c>
       <c r="D33" s="0">
-        <v>0.0021238628998949158</v>
+        <v>0.26184519445042076</v>
       </c>
       <c r="E33" s="0">
-        <v>0.25994331408902904</v>
+        <v>0.084187126403045501</v>
       </c>
       <c r="F33" s="0">
-        <v>0.084187131262849893</v>
+        <v>0.25994331228757872</v>
       </c>
     </row>
     <row r="34">
@@ -9057,19 +9057,19 @@
         <v>405.91500000000002</v>
       </c>
       <c r="B34" s="0">
-        <v>0.12232120372684849</v>
+        <v>0.0025046369157798463</v>
       </c>
       <c r="C34" s="0">
-        <v>0.25297815290687481</v>
+        <v>0.1223201886172746</v>
       </c>
       <c r="D34" s="0">
-        <v>0.0025042687625268512</v>
+        <v>0.25297805716400212</v>
       </c>
       <c r="E34" s="0">
-        <v>0.26375503121831662</v>
+        <v>0.074716889190894212</v>
       </c>
       <c r="F34" s="0">
-        <v>0.074716894371890538</v>
+        <v>0.26375503035742182</v>
       </c>
     </row>
     <row r="35">
@@ -9077,19 +9077,19 @@
         <v>409.20699999999999</v>
       </c>
       <c r="B35" s="0">
-        <v>0.12328914111791815</v>
+        <v>0.0005157298757625825</v>
       </c>
       <c r="C35" s="0">
-        <v>0.23600483805248382</v>
+        <v>0.12328824580148212</v>
       </c>
       <c r="D35" s="0">
-        <v>0.00051533795667861549</v>
+        <v>0.23600476606716839</v>
       </c>
       <c r="E35" s="0">
-        <v>0.26184081682093552</v>
+        <v>0.065805429333246068</v>
       </c>
       <c r="F35" s="0">
-        <v>0.065805434680756197</v>
+        <v>0.26184081519497682</v>
       </c>
     </row>
     <row r="36">
@@ -9097,19 +9097,19 @@
         <v>412.5</v>
       </c>
       <c r="B36" s="0">
-        <v>0.13717028354082877</v>
+        <v>1.4910389670404396e-05</v>
       </c>
       <c r="C36" s="0">
-        <v>0.21956008336094102</v>
+        <v>0.1371696519148595</v>
       </c>
       <c r="D36" s="0">
-        <v>1.4553293964811768e-05</v>
+        <v>0.21956002275892286</v>
       </c>
       <c r="E36" s="0">
-        <v>0.25592531294625848</v>
+        <v>0.057611126874537871</v>
       </c>
       <c r="F36" s="0">
-        <v>0.057611132340342222</v>
+        <v>0.25592531195713047</v>
       </c>
     </row>
     <row r="37">
@@ -9117,19 +9117,19 @@
         <v>415.79399999999998</v>
       </c>
       <c r="B37" s="0">
-        <v>0.13434104965152727</v>
+        <v>0</v>
       </c>
       <c r="C37" s="0">
-        <v>0.19886588131871652</v>
+        <v>0.13434098000076541</v>
       </c>
       <c r="D37" s="0">
-        <v>0</v>
+        <v>0.19886578446423817</v>
       </c>
       <c r="E37" s="0">
-        <v>0.24683173462351818</v>
+        <v>0.0505658823140369</v>
       </c>
       <c r="F37" s="0">
-        <v>0.050565888316887166</v>
+        <v>0.24683173422333818</v>
       </c>
     </row>
     <row r="38">
@@ -9137,19 +9137,19 @@
         <v>419.08999999999998</v>
       </c>
       <c r="B38" s="0">
-        <v>0.14674599398066257</v>
+        <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>0.18259920613553002</v>
+        <v>0.14674609759603607</v>
       </c>
       <c r="D38" s="0">
-        <v>0</v>
+        <v>0.18259912823738608</v>
       </c>
       <c r="E38" s="0">
-        <v>0.23415437406229853</v>
+        <v>0.043848204757443547</v>
       </c>
       <c r="F38" s="0">
-        <v>0.043848210449536268</v>
+        <v>0.23415437447583257</v>
       </c>
     </row>
     <row r="39">
@@ -9157,19 +9157,19 @@
         <v>422.387</v>
       </c>
       <c r="B39" s="0">
-        <v>0.15604787790754321</v>
+        <v>0</v>
       </c>
       <c r="C39" s="0">
-        <v>0.16502707251200338</v>
+        <v>0.15604812903345314</v>
       </c>
       <c r="D39" s="0">
-        <v>0</v>
+        <v>0.16502700867037429</v>
       </c>
       <c r="E39" s="0">
-        <v>0.22114009470302282</v>
+        <v>0.038188889577947811</v>
       </c>
       <c r="F39" s="0">
-        <v>0.038188894921682592</v>
+        <v>0.22114009622191969</v>
       </c>
     </row>
     <row r="40">
@@ -9177,19 +9177,19 @@
         <v>425.685</v>
       </c>
       <c r="B40" s="0">
-        <v>0.16275420393233467</v>
+        <v>0</v>
       </c>
       <c r="C40" s="0">
-        <v>0.15015070420448043</v>
+        <v>0.16275459611309431</v>
       </c>
       <c r="D40" s="0">
-        <v>0</v>
+        <v>0.15015065693549523</v>
       </c>
       <c r="E40" s="0">
-        <v>0.20638355502417466</v>
+        <v>0.033042108937997562</v>
       </c>
       <c r="F40" s="0">
-        <v>0.033042114320273222</v>
+        <v>0.2063835568523037</v>
       </c>
     </row>
     <row r="41">
@@ -9197,19 +9197,19 @@
         <v>428.98500000000001</v>
       </c>
       <c r="B41" s="0">
-        <v>0.16483144664420421</v>
+        <v>0</v>
       </c>
       <c r="C41" s="0">
-        <v>0.13354839076897968</v>
+        <v>0.16483194588136724</v>
       </c>
       <c r="D41" s="0">
-        <v>0</v>
+        <v>0.13354835504437421</v>
       </c>
       <c r="E41" s="0">
-        <v>0.19130497587866727</v>
+        <v>0.028674140773660563</v>
       </c>
       <c r="F41" s="0">
-        <v>0.028674145814861472</v>
+        <v>0.19130497804221908</v>
       </c>
     </row>
     <row r="42">
@@ -9217,19 +9217,19 @@
         <v>432.28699999999998</v>
       </c>
       <c r="B42" s="0">
-        <v>0.18204693005633649</v>
+        <v>0</v>
       </c>
       <c r="C42" s="0">
-        <v>0.12163757991036329</v>
+        <v>0.18204762609667244</v>
       </c>
       <c r="D42" s="0">
-        <v>0</v>
+        <v>0.12163756435713331</v>
       </c>
       <c r="E42" s="0">
-        <v>0.17688161519851572</v>
+        <v>0.025108092877090406</v>
       </c>
       <c r="F42" s="0">
-        <v>0.025108098510914889</v>
+        <v>0.17688161860170057</v>
       </c>
     </row>
     <row r="43">
@@ -9237,19 +9237,19 @@
         <v>435.589</v>
       </c>
       <c r="B43" s="0">
-        <v>0.18884164148006838</v>
+        <v>0</v>
       </c>
       <c r="C43" s="0">
-        <v>0.10829409309421682</v>
+        <v>0.18884245829848859</v>
       </c>
       <c r="D43" s="0">
-        <v>0</v>
+        <v>0.10829409452427965</v>
       </c>
       <c r="E43" s="0">
-        <v>0.1636309822718538</v>
+        <v>0.021977601602610967</v>
       </c>
       <c r="F43" s="0">
-        <v>0.021977607395015586</v>
+        <v>0.16363098585799635</v>
       </c>
     </row>
     <row r="44">
@@ -9257,19 +9257,19 @@
         <v>438.89299999999997</v>
       </c>
       <c r="B44" s="0">
-        <v>0.18974346452901672</v>
+        <v>0</v>
       </c>
       <c r="C44" s="0">
-        <v>0.094002272630685183</v>
+        <v>0.1897443200667199</v>
       </c>
       <c r="D44" s="0">
-        <v>0</v>
+        <v>0.094002288570235543</v>
       </c>
       <c r="E44" s="0">
-        <v>0.14990355037518657</v>
+        <v>0.019170689121091971</v>
       </c>
       <c r="F44" s="0">
-        <v>0.019170694144077651</v>
+        <v>0.14990355485319448</v>
       </c>
     </row>
     <row r="45">
@@ -9277,19 +9277,19 @@
         <v>442.19900000000001</v>
       </c>
       <c r="B45" s="0">
-        <v>0.19541904132108667</v>
+        <v>0.0010602715269705475</v>
       </c>
       <c r="C45" s="0">
-        <v>0.086175433133889881</v>
+        <v>0.19541976474495693</v>
       </c>
       <c r="D45" s="0">
-        <v>0.0010601234565641895</v>
+        <v>0.086175468433568867</v>
       </c>
       <c r="E45" s="0">
-        <v>0.13560820512257726</v>
+        <v>0.016543124113497031</v>
       </c>
       <c r="F45" s="0">
-        <v>0.016543128122125765</v>
+        <v>0.13560821043853513</v>
       </c>
     </row>
     <row r="46">
@@ -9297,19 +9297,19 @@
         <v>445.505</v>
       </c>
       <c r="B46" s="0">
-        <v>0.19260362945349402</v>
+        <v>0</v>
       </c>
       <c r="C46" s="0">
-        <v>0.076316102866610808</v>
+        <v>0.19260464841784217</v>
       </c>
       <c r="D46" s="0">
-        <v>0</v>
+        <v>0.076316133828200281</v>
       </c>
       <c r="E46" s="0">
-        <v>0.12264961703061368</v>
+        <v>0.014439507555237301</v>
       </c>
       <c r="F46" s="0">
-        <v>0.014439513371904097</v>
+        <v>0.12264962205826259</v>
       </c>
     </row>
     <row r="47">
@@ -9317,19 +9317,19 @@
         <v>448.81299999999999</v>
       </c>
       <c r="B47" s="0">
-        <v>0.1864596594799943</v>
+        <v>0.00092556124206526842</v>
       </c>
       <c r="C47" s="0">
-        <v>0.06661522450681584</v>
+        <v>0.18646045582362927</v>
       </c>
       <c r="D47" s="0">
-        <v>0.00092544917609857654</v>
+        <v>0.066615271055284989</v>
       </c>
       <c r="E47" s="0">
-        <v>0.10943512809949037</v>
+        <v>0.01233421278927903</v>
       </c>
       <c r="F47" s="0">
-        <v>0.012334216394639382</v>
+        <v>0.10943513402469675</v>
       </c>
     </row>
     <row r="48">
@@ -9337,19 +9337,19 @@
         <v>452.12200000000001</v>
       </c>
       <c r="B48" s="0">
-        <v>0.1967450381867871</v>
+        <v>0.0012227368690137482</v>
       </c>
       <c r="C48" s="0">
-        <v>0.056781059532905243</v>
+        <v>0.19674585828242394</v>
       </c>
       <c r="D48" s="0">
-        <v>0.001222570214566831</v>
+        <v>0.056781130479365428</v>
       </c>
       <c r="E48" s="0">
-        <v>0.097930619370825492</v>
+        <v>0.01100043092167219</v>
       </c>
       <c r="F48" s="0">
-        <v>0.011000434220830524</v>
+        <v>0.097930626059340969</v>
       </c>
     </row>
     <row r="49">
@@ -9357,19 +9357,19 @@
         <v>455.43299999999999</v>
       </c>
       <c r="B49" s="0">
-        <v>0.18760726920833729</v>
+        <v>0</v>
       </c>
       <c r="C49" s="0">
-        <v>0.05215000017600939</v>
+        <v>0.18760833719186296</v>
       </c>
       <c r="D49" s="0">
-        <v>0</v>
+        <v>0.052150058690977698</v>
       </c>
       <c r="E49" s="0">
-        <v>0.087336545675501448</v>
+        <v>0.0094201997972020914</v>
       </c>
       <c r="F49" s="0">
-        <v>0.0094202047184270866</v>
+        <v>0.087336552007219084</v>
       </c>
     </row>
     <row r="50">
@@ -9377,19 +9377,19 @@
         <v>458.74400000000003</v>
       </c>
       <c r="B50" s="0">
-        <v>0.1878819396174744</v>
+        <v>0.00075496306093034615</v>
       </c>
       <c r="C50" s="0">
-        <v>0.04630774631037865</v>
+        <v>0.18788289095557048</v>
       </c>
       <c r="D50" s="0">
-        <v>0.00075486215889336485</v>
+        <v>0.046307814279097401</v>
       </c>
       <c r="E50" s="0">
-        <v>0.077887552468311111</v>
+        <v>0.008434296123801718</v>
       </c>
       <c r="F50" s="0">
-        <v>0.0084343002674690803</v>
+        <v>0.077887559291931502</v>
       </c>
     </row>
     <row r="51">
@@ -9397,19 +9397,19 @@
         <v>462.05700000000002</v>
       </c>
       <c r="B51" s="0">
-        <v>0.18038639386739008</v>
+        <v>0.00033402991499678175</v>
       </c>
       <c r="C51" s="0">
-        <v>0.03943499205138698</v>
+        <v>0.18038733503513138</v>
       </c>
       <c r="D51" s="0">
-        <v>0.00033393853978854555</v>
+        <v>0.039435065869301907</v>
       </c>
       <c r="E51" s="0">
-        <v>0.069253965072112442</v>
+        <v>0.0071004663583359856</v>
       </c>
       <c r="F51" s="0">
-        <v>0.0071004703507492562</v>
+        <v>0.06925397186339996</v>
       </c>
     </row>
     <row r="52">
@@ -9417,19 +9417,19 @@
         <v>465.37099999999998</v>
       </c>
       <c r="B52" s="0">
-        <v>0.1758803361481561</v>
+        <v>0.00056154710144812575</v>
       </c>
       <c r="C52" s="0">
-        <v>0.032013715226973626</v>
+        <v>0.17588127089400094</v>
       </c>
       <c r="D52" s="0">
-        <v>0.00056146516661258368</v>
+        <v>0.032013791863120172</v>
       </c>
       <c r="E52" s="0">
-        <v>0.061220246912603769</v>
+        <v>0.0059294052459728675</v>
       </c>
       <c r="F52" s="0">
-        <v>0.0059294086920018505</v>
+        <v>0.061220253877451732</v>
       </c>
     </row>
     <row r="53">
@@ -9437,19 +9437,19 @@
         <v>468.68599999999998</v>
       </c>
       <c r="B53" s="0">
-        <v>0.17438023721015133</v>
+        <v>0.0012308847697919656</v>
       </c>
       <c r="C53" s="0">
-        <v>0.027536796922587585</v>
+        <v>0.17438112771557382</v>
       </c>
       <c r="D53" s="0">
-        <v>0.0012307758642425743</v>
+        <v>0.027536874175890024</v>
       </c>
       <c r="E53" s="0">
-        <v>0.053934927000154204</v>
+        <v>0.0052991094785151882</v>
       </c>
       <c r="F53" s="0">
-        <v>0.0052991123377094506</v>
+        <v>0.053934934401132416</v>
       </c>
     </row>
     <row r="54">
@@ -9457,19 +9457,19 @@
         <v>472.00200000000001</v>
       </c>
       <c r="B54" s="0">
-        <v>0.15943555673429585</v>
+        <v>0.00032685698809371393</v>
       </c>
       <c r="C54" s="0">
-        <v>0.025403678848593615</v>
+        <v>0.15943644190623618</v>
       </c>
       <c r="D54" s="0">
-        <v>0.00032677798986416833</v>
+        <v>0.025403752191980607</v>
       </c>
       <c r="E54" s="0">
-        <v>0.047261907360227957</v>
+        <v>0.0046283021130098818</v>
       </c>
       <c r="F54" s="0">
-        <v>0.0046283056917948628</v>
+        <v>0.04726191387131027</v>
       </c>
     </row>
     <row r="55">
@@ -9477,19 +9477,19 @@
         <v>475.31900000000002</v>
       </c>
       <c r="B55" s="0">
-        <v>0.15564699065678497</v>
+        <v>0.0002106779146726155</v>
       </c>
       <c r="C55" s="0">
-        <v>0.022341258379148351</v>
+        <v>0.15564790270822379</v>
       </c>
       <c r="D55" s="0">
-        <v>0.00021063126771086633</v>
+        <v>0.022341329488648674</v>
       </c>
       <c r="E55" s="0">
-        <v>0.041833916232674843</v>
+        <v>0.0038619474575810561</v>
       </c>
       <c r="F55" s="0">
-        <v>0.0038619508685573808</v>
+        <v>0.041833923007823022</v>
       </c>
     </row>
     <row r="56">
@@ -9497,19 +9497,19 @@
         <v>478.63799999999998</v>
       </c>
       <c r="B56" s="0">
-        <v>0.14511262434146885</v>
+        <v>0</v>
       </c>
       <c r="C56" s="0">
-        <v>0.016428883968729061</v>
+        <v>0.14511353620293205</v>
       </c>
       <c r="D56" s="0">
-        <v>0</v>
+        <v>0.016428951767988649</v>
       </c>
       <c r="E56" s="0">
-        <v>0.037006371567947748</v>
+        <v>0.0031048023021587302</v>
       </c>
       <c r="F56" s="0">
-        <v>0.0031048054372007357</v>
+        <v>0.037006378071997484</v>
       </c>
     </row>
     <row r="57">
@@ -9517,19 +9517,19 @@
         <v>481.95699999999999</v>
       </c>
       <c r="B57" s="0">
-        <v>0.14486402356849351</v>
+        <v>0.00063077778760401088</v>
       </c>
       <c r="C57" s="0">
-        <v>0.017498567591267184</v>
+        <v>0.14486485993468104</v>
       </c>
       <c r="D57" s="0">
-        <v>0.00063071976688250397</v>
+        <v>0.017498636075199445</v>
       </c>
       <c r="E57" s="0">
-        <v>0.032520018674549733</v>
+        <v>0.00304745010941287</v>
       </c>
       <c r="F57" s="0">
-        <v>0.0030474530266123242</v>
+        <v>0.032520025316081225</v>
       </c>
     </row>
     <row r="58">
@@ -9537,19 +9537,19 @@
         <v>485.27699999999999</v>
       </c>
       <c r="B58" s="0">
-        <v>0.13560388573830678</v>
+        <v>0.00025483372997299497</v>
       </c>
       <c r="C58" s="0">
-        <v>0.013272756692683121</v>
+        <v>0.13560474048154511</v>
       </c>
       <c r="D58" s="0">
-        <v>0.00025478870485834627</v>
+        <v>0.013272842640176861</v>
       </c>
       <c r="E58" s="0">
-        <v>0.028797569978460887</v>
+        <v>0.0026355815075329914</v>
       </c>
       <c r="F58" s="0">
-        <v>0.0026355846724098577</v>
+        <v>0.028797573977867488</v>
       </c>
     </row>
     <row r="59">
@@ -9557,19 +9557,19 @@
         <v>488.59899999999999</v>
       </c>
       <c r="B59" s="0">
-        <v>0.13167026230675658</v>
+        <v>0</v>
       </c>
       <c r="C59" s="0">
-        <v>0.010544947155732289</v>
+        <v>0.13167118028697944</v>
       </c>
       <c r="D59" s="0">
-        <v>0</v>
+        <v>0.010545030279597646</v>
       </c>
       <c r="E59" s="0">
-        <v>0.025349975113526744</v>
+        <v>0.0023348465067768026</v>
       </c>
       <c r="F59" s="0">
-        <v>0.0023348500613105858</v>
+        <v>0.025349978732714482</v>
       </c>
     </row>
     <row r="60">
@@ -9577,19 +9577,19 @@
         <v>491.92099999999999</v>
       </c>
       <c r="B60" s="0">
-        <v>0.13566514522413381</v>
+        <v>0.0010258012289685822</v>
       </c>
       <c r="C60" s="0">
-        <v>0.0099368604361519952</v>
+        <v>0.13566593435289554</v>
       </c>
       <c r="D60" s="0">
-        <v>0.0010257240629318351</v>
+        <v>0.0099369480372536716</v>
       </c>
       <c r="E60" s="0">
-        <v>0.022385048181648538</v>
+        <v>0.0021796027708820809</v>
       </c>
       <c r="F60" s="0">
-        <v>0.0021796050972894649</v>
+        <v>0.022385052977391837</v>
       </c>
     </row>
     <row r="61">
@@ -9597,19 +9597,19 @@
         <v>495.245</v>
       </c>
       <c r="B61" s="0">
-        <v>0.1260759600816137</v>
+        <v>0.0004814751944203394</v>
       </c>
       <c r="C61" s="0">
-        <v>0.008179216170436503</v>
+        <v>0.12607687776693455</v>
       </c>
       <c r="D61" s="0">
-        <v>0.00048146483411118694</v>
+        <v>0.0081792981692706632</v>
       </c>
       <c r="E61" s="0">
-        <v>0.019541093067890626</v>
+        <v>0.0019835745968630409</v>
       </c>
       <c r="F61" s="0">
-        <v>0.0019835776410494842</v>
+        <v>0.019541095649644003</v>
       </c>
     </row>
     <row r="62">
@@ -9617,19 +9617,19 @@
         <v>498.56900000000002</v>
       </c>
       <c r="B62" s="0">
-        <v>0.12014989000268125</v>
+        <v>0.00055128663218158595</v>
       </c>
       <c r="C62" s="0">
-        <v>0.0067880329272882577</v>
+        <v>0.12015079382951288</v>
       </c>
       <c r="D62" s="0">
-        <v>0.00055129827128615509</v>
+        <v>0.0067881085088644178</v>
       </c>
       <c r="E62" s="0">
-        <v>0.017520388878901859</v>
+        <v>0.0017494976098740623</v>
       </c>
       <c r="F62" s="0">
-        <v>0.0017495004441445635</v>
+        <v>0.017520391460117329</v>
       </c>
     </row>
     <row r="63">
@@ -9637,19 +9637,19 @@
         <v>501.89499999999998</v>
       </c>
       <c r="B63" s="0">
-        <v>0.1237089499953872</v>
+        <v>0.0016551000780813294</v>
       </c>
       <c r="C63" s="0">
-        <v>0.0069766136356900505</v>
+        <v>0.1237097908807101</v>
       </c>
       <c r="D63" s="0">
-        <v>0.0016550842548795082</v>
+        <v>0.0069766819447145238</v>
       </c>
       <c r="E63" s="0">
-        <v>0.015438525456967611</v>
+        <v>0.0016667270724607674</v>
       </c>
       <c r="F63" s="0">
-        <v>0.0016667289224894745</v>
+        <v>0.015438529402669239</v>
       </c>
     </row>
     <row r="64">
@@ -9657,19 +9657,19 @@
         <v>505.221</v>
       </c>
       <c r="B64" s="0">
-        <v>0.11310873035774631</v>
+        <v>0.00092514207582364923</v>
       </c>
       <c r="C64" s="0">
-        <v>0.0056306804025526144</v>
+        <v>0.11310960878630165</v>
       </c>
       <c r="D64" s="0">
-        <v>0.00092515771245123995</v>
+        <v>0.0056307462156685775</v>
       </c>
       <c r="E64" s="0">
-        <v>0.013841580157199785</v>
+        <v>0.0013242686322816498</v>
       </c>
       <c r="F64" s="0">
-        <v>0.0013242705736689134</v>
+        <v>0.013841582605371569</v>
       </c>
     </row>
     <row r="65">
@@ -9677,19 +9677,19 @@
         <v>508.54899999999998</v>
       </c>
       <c r="B65" s="0">
-        <v>0.10866556221205595</v>
+        <v>0.0014076214204319713</v>
       </c>
       <c r="C65" s="0">
-        <v>0.0045767776075064243</v>
+        <v>0.10866631569399886</v>
       </c>
       <c r="D65" s="0">
-        <v>0.0014076011436016263</v>
+        <v>0.0045768421731179499</v>
       </c>
       <c r="E65" s="0">
-        <v>0.012199822853560598</v>
+        <v>0.0011786806817227448</v>
       </c>
       <c r="F65" s="0">
-        <v>0.00117868184787442</v>
+        <v>0.012199825875753127</v>
       </c>
     </row>
     <row r="66">
@@ -9697,19 +9697,19 @@
         <v>511.87700000000001</v>
       </c>
       <c r="B66" s="0">
-        <v>0.10176377384055629</v>
+        <v>0</v>
       </c>
       <c r="C66" s="0">
-        <v>0.0034156060970399905</v>
+        <v>0.10176460338872403</v>
       </c>
       <c r="D66" s="0">
-        <v>0</v>
+        <v>0.0034156780765598367</v>
       </c>
       <c r="E66" s="0">
-        <v>0.010626971875453327</v>
+        <v>0.00097620530391374428</v>
       </c>
       <c r="F66" s="0">
-        <v>0.00097620791261000231</v>
+        <v>0.01062697314345626</v>
       </c>
     </row>
     <row r="67">
@@ -9717,19 +9717,19 @@
         <v>515.20600000000002</v>
       </c>
       <c r="B67" s="0">
-        <v>0.10730526556141685</v>
+        <v>0.0016226263066142232</v>
       </c>
       <c r="C67" s="0">
-        <v>0.0043485033566249875</v>
+        <v>0.10730595999661281</v>
       </c>
       <c r="D67" s="0">
-        <v>0.0016225974280623277</v>
+        <v>0.0043485551152105421</v>
       </c>
       <c r="E67" s="0">
-        <v>0.0093477077376813381</v>
+        <v>0.0010966841150780542</v>
       </c>
       <c r="F67" s="0">
-        <v>0.0010966849193245736</v>
+        <v>0.0093477125017109846</v>
       </c>
     </row>
     <row r="68">
@@ -9737,19 +9737,19 @@
         <v>518.53599999999994</v>
       </c>
       <c r="B68" s="0">
-        <v>0.090778664666729347</v>
+        <v>0.00018194050492926434</v>
       </c>
       <c r="C68" s="0">
-        <v>0.0019091206910876667</v>
+        <v>0.090779383537761077</v>
       </c>
       <c r="D68" s="0">
-        <v>0.00018196631342415508</v>
+        <v>0.0019091644105086079</v>
       </c>
       <c r="E68" s="0">
-        <v>0.0087174147765991285</v>
+        <v>0.00073587207514445256</v>
       </c>
       <c r="F68" s="0">
-        <v>0.00073587372129496728</v>
+        <v>0.0087174184023631335</v>
       </c>
     </row>
     <row r="69">
@@ -9757,19 +9757,19 @@
         <v>521.86599999999999</v>
       </c>
       <c r="B69" s="0">
-        <v>0.092259496061567123</v>
+        <v>0.0006469500510325189</v>
       </c>
       <c r="C69" s="0">
-        <v>0.0019864809259005551</v>
+        <v>0.092260150110664907</v>
       </c>
       <c r="D69" s="0">
-        <v>0.00064693730841146086</v>
+        <v>0.0019865289982001024</v>
       </c>
       <c r="E69" s="0">
-        <v>0.0076205916324581843</v>
+        <v>0.00079579841578730271</v>
       </c>
       <c r="F69" s="0">
-        <v>0.00079579966468033489</v>
+        <v>0.0076205955023162112</v>
       </c>
     </row>
     <row r="70">
@@ -9777,19 +9777,19 @@
         <v>525.19799999999998</v>
       </c>
       <c r="B70" s="0">
-        <v>0.084998272402024247</v>
+        <v>0.0014711205294665756</v>
       </c>
       <c r="C70" s="0">
-        <v>0.0019376688740670323</v>
+        <v>0.084998785431139978</v>
       </c>
       <c r="D70" s="0">
-        <v>0.0014711135671397783</v>
+        <v>0.0019377085404944647</v>
       </c>
       <c r="E70" s="0">
-        <v>0.0066902556583655843</v>
+        <v>0.00088799672556425489</v>
       </c>
       <c r="F70" s="0">
-        <v>0.00088799725965265784</v>
+        <v>0.0066902604277167144</v>
       </c>
     </row>
     <row r="71">
@@ -9797,19 +9797,19 @@
         <v>528.52999999999997</v>
       </c>
       <c r="B71" s="0">
-        <v>0.076120231101763802</v>
+        <v>0.0013425948559395333</v>
       </c>
       <c r="C71" s="0">
-        <v>0.0028617384118655533</v>
+        <v>0.076120721143698042</v>
       </c>
       <c r="D71" s="0">
-        <v>0.0013426089305363898</v>
+        <v>0.0028617675466731337</v>
       </c>
       <c r="E71" s="0">
-        <v>0.0057467929303525733</v>
+        <v>0.00058385327512154735</v>
       </c>
       <c r="F71" s="0">
-        <v>0.00058385388463880216</v>
+        <v>0.0057467973823124938</v>
       </c>
     </row>
     <row r="72">
@@ -9817,19 +9817,19 @@
         <v>531.86300000000006</v>
       </c>
       <c r="B72" s="0">
-        <v>0.075332057888465365</v>
+        <v>0.0012715009482270122</v>
       </c>
       <c r="C72" s="0">
-        <v>0.0016858841729332297</v>
+        <v>0.075332578299232025</v>
       </c>
       <c r="D72" s="0">
-        <v>0.0012715357885409071</v>
+        <v>0.0016859224815699955</v>
       </c>
       <c r="E72" s="0">
-        <v>0.0052975224415498338</v>
+        <v>0.00050126728308824123</v>
       </c>
       <c r="F72" s="0">
-        <v>0.00050126754144686533</v>
+        <v>0.0052975259476122829</v>
       </c>
     </row>
     <row r="73">
@@ -9837,19 +9837,19 @@
         <v>535.197</v>
       </c>
       <c r="B73" s="0">
-        <v>0.074853108233273749</v>
+        <v>0.0016050210436321666</v>
       </c>
       <c r="C73" s="0">
-        <v>0.00084420156465405218</v>
+        <v>0.074853624381895897</v>
       </c>
       <c r="D73" s="0">
-        <v>0.0016051107709842112</v>
+        <v>0.00084423673754884659</v>
       </c>
       <c r="E73" s="0">
-        <v>0.004621137878461949</v>
+        <v>0.00044796435315749817</v>
       </c>
       <c r="F73" s="0">
-        <v>0.0004479651522647931</v>
+        <v>0.0046211417464302584</v>
       </c>
     </row>
     <row r="74">
@@ -9857,19 +9857,19 @@
         <v>538.53099999999995</v>
       </c>
       <c r="B74" s="0">
-        <v>0.072306369803997281</v>
+        <v>0.002371205091799639</v>
       </c>
       <c r="C74" s="0">
-        <v>0.0010759861462545769</v>
+        <v>0.072306896904510573</v>
       </c>
       <c r="D74" s="0">
-        <v>0.0023713901131699219</v>
+        <v>0.0010760062467332632</v>
       </c>
       <c r="E74" s="0">
-        <v>0.0040784688248708609</v>
+        <v>0.00046413616532258313</v>
       </c>
       <c r="F74" s="0">
-        <v>0.00046413580359734997</v>
+        <v>0.0040784734100967517</v>
       </c>
     </row>
     <row r="75">
@@ -9877,19 +9877,19 @@
         <v>541.86699999999996</v>
       </c>
       <c r="B75" s="0">
-        <v>0.063913296775763795</v>
+        <v>0.0018526681606027635</v>
       </c>
       <c r="C75" s="0">
-        <v>0.00032420268401166756</v>
+        <v>0.06391367952370744</v>
       </c>
       <c r="D75" s="0">
-        <v>0.0018527060026657218</v>
+        <v>0.00032423077680050104</v>
       </c>
       <c r="E75" s="0">
-        <v>0.003685733223519084</v>
+        <v>0.00030595709290721299</v>
       </c>
       <c r="F75" s="0">
-        <v>0.00030595714639528504</v>
+        <v>0.003685736871979965</v>
       </c>
     </row>
     <row r="76">
@@ -9897,19 +9897,19 @@
         <v>545.20299999999998</v>
       </c>
       <c r="B76" s="0">
-        <v>0.065667183527682083</v>
+        <v>0.00030929031003583337</v>
       </c>
       <c r="C76" s="0">
-        <v>0.0014027338434147872</v>
+        <v>0.065667802023267399</v>
       </c>
       <c r="D76" s="0">
-        <v>0.00030943480118446006</v>
+        <v>0.0014027708358326214</v>
       </c>
       <c r="E76" s="0">
-        <v>0.0032651613750190843</v>
+        <v>0.00033376813227519787</v>
       </c>
       <c r="F76" s="0">
-        <v>0.00033377110971081813</v>
+        <v>0.0032651627989989081</v>
       </c>
     </row>
     <row r="77">
@@ -9917,19 +9917,19 @@
         <v>548.53899999999999</v>
       </c>
       <c r="B77" s="0">
-        <v>0.059940342185208238</v>
+        <v>0.00059456961342091636</v>
       </c>
       <c r="C77" s="0">
-        <v>0.00059069850483855764</v>
+        <v>0.059940926672682873</v>
       </c>
       <c r="D77" s="0">
-        <v>0.00059476370213951211</v>
+        <v>0.00059072654345416955</v>
       </c>
       <c r="E77" s="0">
-        <v>0.0028226141061039522</v>
+        <v>0.0001890891919409924</v>
       </c>
       <c r="F77" s="0">
-        <v>0.00018909120240723597</v>
+        <v>0.0028226156491077056</v>
       </c>
     </row>
     <row r="78">
@@ -9937,19 +9937,19 @@
         <v>551.87599999999998</v>
       </c>
       <c r="B78" s="0">
-        <v>0.052534671244462171</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>7.0135173465456238e-05</v>
+        <v>0.052535101704494484</v>
       </c>
       <c r="D78" s="0">
-        <v>0</v>
+        <v>7.0175417567986087e-05</v>
       </c>
       <c r="E78" s="0">
-        <v>0.0025622368613788665</v>
+        <v>0.0003652138755704275</v>
       </c>
       <c r="F78" s="0">
-        <v>0.00036521673341627196</v>
+        <v>0.0025622378104047808</v>
       </c>
     </row>
     <row r="79">
@@ -9957,19 +9957,19 @@
         <v>555.21400000000006</v>
       </c>
       <c r="B79" s="0">
-        <v>0.054274371304722506</v>
+        <v>0.001451780470611154</v>
       </c>
       <c r="C79" s="0">
-        <v>0.00058075625485138043</v>
+        <v>0.054274723493999803</v>
       </c>
       <c r="D79" s="0">
-        <v>0.0014517884753191155</v>
+        <v>0.00058078121383877887</v>
       </c>
       <c r="E79" s="0">
-        <v>0.0022603205666304805</v>
+        <v>0.00019619591390490019</v>
       </c>
       <c r="F79" s="0">
-        <v>0.00019619575001749245</v>
+        <v>0.0022603235369240801</v>
       </c>
     </row>
     <row r="80">
@@ -9977,19 +9977,19 @@
         <v>558.553</v>
       </c>
       <c r="B80" s="0">
-        <v>0.056915097958736685</v>
+        <v>0.00085876155541683057</v>
       </c>
       <c r="C80" s="0">
-        <v>0.00030896794697150479</v>
+        <v>0.056915500516412511</v>
       </c>
       <c r="D80" s="0">
-        <v>0.0008587369764149654</v>
+        <v>0.00030900470995853997</v>
       </c>
       <c r="E80" s="0">
-        <v>0.0019018695436448599</v>
+        <v>0.00044418464795985773</v>
       </c>
       <c r="F80" s="0">
-        <v>0.00044418595259537562</v>
+        <v>0.0019018718198314504</v>
       </c>
     </row>
     <row r="81">
@@ -9997,19 +9997,19 @@
         <v>561.89200000000005</v>
       </c>
       <c r="B81" s="0">
-        <v>0.047467730158336691</v>
+        <v>0.0013352749228141038</v>
       </c>
       <c r="C81" s="0">
-        <v>0.00041416032351195698</v>
+        <v>0.047468095640945972</v>
       </c>
       <c r="D81" s="0">
-        <v>0.0013353655848031209</v>
+        <v>0.00041417182005039837</v>
       </c>
       <c r="E81" s="0">
-        <v>0.0018910757954473563</v>
+        <v>0.00019165438921999635</v>
       </c>
       <c r="F81" s="0">
-        <v>0.00019165418852626126</v>
+        <v>0.0018910786840235982</v>
       </c>
     </row>
     <row r="82">
@@ -10017,19 +10017,19 @@
         <v>565.231</v>
       </c>
       <c r="B82" s="0">
-        <v>0.049338332745796028</v>
+        <v>0.0018457767722352047</v>
       </c>
       <c r="C82" s="0">
-        <v>0.00064894016621117002</v>
+        <v>0.049338608616486104</v>
       </c>
       <c r="D82" s="0">
-        <v>0.0018457741678192972</v>
+        <v>0.00064895700685406053</v>
       </c>
       <c r="E82" s="0">
-        <v>0.0014331820958242173</v>
+        <v>0.00045068088541909765</v>
       </c>
       <c r="F82" s="0">
-        <v>0.00045068010615849504</v>
+        <v>0.0014331863722548441</v>
       </c>
     </row>
     <row r="83">
@@ -10037,19 +10037,19 @@
         <v>568.57100000000003</v>
       </c>
       <c r="B83" s="0">
-        <v>0.043748437082125488</v>
+        <v>0.0026933638097548199</v>
       </c>
       <c r="C83" s="0">
-        <v>0</v>
+        <v>0.043748592530460741</v>
       </c>
       <c r="D83" s="0">
-        <v>0.0026933448695141411</v>
+        <v>0</v>
       </c>
       <c r="E83" s="0">
-        <v>0.0013896557320464983</v>
+        <v>0.00026094056561914427</v>
       </c>
       <c r="F83" s="0">
-        <v>0.00026093800897326679</v>
+        <v>0.0013896608736762327</v>
       </c>
     </row>
     <row r="84">
@@ -10057,19 +10057,19 @@
         <v>571.91200000000004</v>
       </c>
       <c r="B84" s="0">
-        <v>0.041774560584063876</v>
+        <v>0.0028416292875372167</v>
       </c>
       <c r="C84" s="0">
-        <v>0</v>
+        <v>0.041774759322370285</v>
       </c>
       <c r="D84" s="0">
-        <v>0.0028417094784938114</v>
+        <v>0</v>
       </c>
       <c r="E84" s="0">
-        <v>0.0014538211987118236</v>
+        <v>0.00034124548148303628</v>
       </c>
       <c r="F84" s="0">
-        <v>0.00034124162503438096</v>
+        <v>0.0014538258027054747</v>
       </c>
     </row>
     <row r="85">
@@ -10077,19 +10077,19 @@
         <v>575.25300000000004</v>
       </c>
       <c r="B85" s="0">
-        <v>0.035169302750748956</v>
+        <v>0.0028337318553315794</v>
       </c>
       <c r="C85" s="0">
-        <v>0.0013314615965264039</v>
+        <v>0.03516939995622035</v>
       </c>
       <c r="D85" s="0">
-        <v>0.0028337407200528624</v>
+        <v>0.0013314612368583556</v>
       </c>
       <c r="E85" s="0">
-        <v>0.0011019305641736541</v>
+        <v>0.00024003348806289157</v>
       </c>
       <c r="F85" s="0">
-        <v>0.00024003081690674965</v>
+        <v>0.0011019348299672088</v>
       </c>
     </row>
     <row r="86">
@@ -10097,19 +10097,19 @@
         <v>578.59400000000005</v>
       </c>
       <c r="B86" s="0">
-        <v>0.035254494946156609</v>
+        <v>0.0034007898519327006</v>
       </c>
       <c r="C86" s="0">
-        <v>0.001410195852725827</v>
+        <v>0.035254536524574914</v>
       </c>
       <c r="D86" s="0">
-        <v>0.0034007818700112357</v>
+        <v>0.0014101957068145929</v>
       </c>
       <c r="E86" s="0">
-        <v>0.00091429385318713959</v>
+        <v>0.0002077067297788986</v>
       </c>
       <c r="F86" s="0">
-        <v>0.00020770339382835228</v>
+        <v>0.00091429786472915721</v>
       </c>
     </row>
     <row r="87">
@@ -10117,19 +10117,19 @@
         <v>581.93600000000004</v>
       </c>
       <c r="B87" s="0">
-        <v>0.036458604256873056</v>
+        <v>0.0053549148327951823</v>
       </c>
       <c r="C87" s="0">
-        <v>0.0014572136414514553</v>
+        <v>0.036458679160386774</v>
       </c>
       <c r="D87" s="0">
-        <v>0.0053550834538324456</v>
+        <v>0.0014571878569841084</v>
       </c>
       <c r="E87" s="0">
-        <v>0.0006784573988893838</v>
+        <v>0.00050199187908677616</v>
       </c>
       <c r="F87" s="0">
-        <v>0.00050198471192215472</v>
+        <v>0.00067846306904047573</v>
       </c>
     </row>
     <row r="88">
@@ -10137,19 +10137,19 @@
         <v>585.279</v>
       </c>
       <c r="B88" s="0">
-        <v>0.033514347952284467</v>
+        <v>0.008619235382875191</v>
       </c>
       <c r="C88" s="0">
-        <v>0.0010226981331441516</v>
+        <v>0.03351411025414467</v>
       </c>
       <c r="D88" s="0">
-        <v>0.008619235286477676</v>
+        <v>0.0010226529926096295</v>
       </c>
       <c r="E88" s="0">
-        <v>0.00069007285725816595</v>
+        <v>0.00016516884665752977</v>
       </c>
       <c r="F88" s="0">
-        <v>0.00016515977777548601</v>
+        <v>0.00069007475677469244</v>
       </c>
     </row>
     <row r="89">
@@ -10157,19 +10157,19 @@
         <v>588.62199999999996</v>
       </c>
       <c r="B89" s="0">
-        <v>0.034302067204460086</v>
+        <v>0.0061307465695343479</v>
       </c>
       <c r="C89" s="0">
-        <v>0.0020765758998820172</v>
+        <v>0.034302083166391058</v>
       </c>
       <c r="D89" s="0">
-        <v>0.006130854490375471</v>
+        <v>0.0020765424037054239</v>
       </c>
       <c r="E89" s="0">
-        <v>0.00045086507938996677</v>
+        <v>0.00039774086860018521</v>
       </c>
       <c r="F89" s="0">
-        <v>0.00039773483862274922</v>
+        <v>0.00045086893286449544</v>
       </c>
     </row>
     <row r="90">
@@ -10177,19 +10177,19 @@
         <v>591.96500000000003</v>
       </c>
       <c r="B90" s="0">
-        <v>0.025254612913368786</v>
+        <v>0.006098374176115526</v>
       </c>
       <c r="C90" s="0">
-        <v>0</v>
+        <v>0.025254377717718424</v>
       </c>
       <c r="D90" s="0">
-        <v>0.0060983505155789656</v>
+        <v>0</v>
       </c>
       <c r="E90" s="0">
-        <v>0.00069614201665530264</v>
+        <v>0.0001670491269959558</v>
       </c>
       <c r="F90" s="0">
-        <v>0.00016704138728950785</v>
+        <v>0.00069614028928778442</v>
       </c>
     </row>
     <row r="91">
@@ -10197,19 +10197,19 @@
         <v>595.30899999999997</v>
       </c>
       <c r="B91" s="0">
-        <v>0.030595746816752659</v>
+        <v>0.0060652661252774036</v>
       </c>
       <c r="C91" s="0">
-        <v>0.0011692009111676763</v>
+        <v>0.030595681149501314</v>
       </c>
       <c r="D91" s="0">
-        <v>0.0060653634707909685</v>
+        <v>0.0011691649863919996</v>
       </c>
       <c r="E91" s="0">
-        <v>0.000639409633060931</v>
+        <v>0.0003489979118477544</v>
       </c>
       <c r="F91" s="0">
-        <v>0.00034899108254492011</v>
+        <v>0.00063941151498650862</v>
       </c>
     </row>
     <row r="92">
@@ -10217,19 +10217,19 @@
         <v>598.65200000000004</v>
       </c>
       <c r="B92" s="0">
-        <v>0.027920756767199073</v>
+        <v>0.0065756332303658714</v>
       </c>
       <c r="C92" s="0">
-        <v>0.0019747830419052591</v>
+        <v>0.027920640133381601</v>
       </c>
       <c r="D92" s="0">
-        <v>0.006575666618596653</v>
+        <v>0.0019747388688178087</v>
       </c>
       <c r="E92" s="0">
-        <v>0.00034790296191261828</v>
+        <v>0.00032333850503951076</v>
       </c>
       <c r="F92" s="0">
-        <v>0.00032333183410775915</v>
+        <v>0.00034790390324489559</v>
       </c>
     </row>
     <row r="93">
@@ -10237,19 +10237,19 @@
         <v>601.99699999999996</v>
       </c>
       <c r="B93" s="0">
-        <v>0.022412663236658376</v>
+        <v>0.0057584230215834663</v>
       </c>
       <c r="C93" s="0">
-        <v>0.0012060936139378269</v>
+        <v>0.022412550829069254</v>
       </c>
       <c r="D93" s="0">
-        <v>0.0057584696286629442</v>
+        <v>0.0012060533112573572</v>
       </c>
       <c r="E93" s="0">
-        <v>0.000525528198987125</v>
+        <v>0.00026054566747667993</v>
       </c>
       <c r="F93" s="0">
-        <v>0.00026053945936991375</v>
+        <v>0.00052552928412642915</v>
       </c>
     </row>
     <row r="94">
@@ -10257,19 +10257,19 @@
         <v>605.34100000000001</v>
       </c>
       <c r="B94" s="0">
-        <v>0.024563421669628917</v>
+        <v>0.0051261000234090496</v>
       </c>
       <c r="C94" s="0">
-        <v>0.00034528065199559662</v>
+        <v>0.024563303254200586</v>
       </c>
       <c r="D94" s="0">
-        <v>0.0051260756382463758</v>
+        <v>0.00034525552039774409</v>
       </c>
       <c r="E94" s="0">
-        <v>0.00037737624107852229</v>
+        <v>0.00028679079530987306</v>
       </c>
       <c r="F94" s="0">
-        <v>0.00028678492169362534</v>
+        <v>0.00037737827598626394</v>
       </c>
     </row>
     <row r="95">
@@ -10277,19 +10277,19 @@
         <v>608.68600000000004</v>
       </c>
       <c r="B95" s="0">
-        <v>0.024941908596236476</v>
+        <v>0.0065913384113972066</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>0.02494167496998121</v>
       </c>
       <c r="D95" s="0">
-        <v>0.0065913017841834802</v>
+        <v>0</v>
       </c>
       <c r="E95" s="0">
-        <v>0.00039726350344941673</v>
+        <v>0.0003458602141129712</v>
       </c>
       <c r="F95" s="0">
-        <v>0.00034585217651736448</v>
+        <v>0.00039726406504009336</v>
       </c>
     </row>
     <row r="96">
@@ -10297,19 +10297,19 @@
         <v>612.03099999999995</v>
       </c>
       <c r="B96" s="0">
-        <v>0.020773914880246547</v>
+        <v>0.0059774430148244115</v>
       </c>
       <c r="C96" s="0">
-        <v>0.00016036708526512335</v>
+        <v>0.020773793200021609</v>
       </c>
       <c r="D96" s="0">
-        <v>0.0059774626384177755</v>
+        <v>0.00016032543530721154</v>
       </c>
       <c r="E96" s="0">
-        <v>0.00035260467228299291</v>
+        <v>0.00027938785263713871</v>
       </c>
       <c r="F96" s="0">
-        <v>0.00027938167766946204</v>
+        <v>0.00035260712137610172</v>
       </c>
     </row>
     <row r="97">
@@ -10317,19 +10317,19 @@
         <v>615.37599999999998</v>
       </c>
       <c r="B97" s="0">
-        <v>0.01968448595768571</v>
+        <v>0.0067498523385579384</v>
       </c>
       <c r="C97" s="0">
-        <v>0.00029991203294132409</v>
+        <v>0.019684284579076745</v>
       </c>
       <c r="D97" s="0">
-        <v>0.0067497697155867254</v>
+        <v>0.00029989307795251594</v>
       </c>
       <c r="E97" s="0">
-        <v>0.00033458262100344305</v>
+        <v>0.00034085107976183454</v>
       </c>
       <c r="F97" s="0">
-        <v>0.00034084539253502829</v>
+        <v>0.00033458661259524975</v>
       </c>
     </row>
     <row r="98">
@@ -10337,19 +10337,19 @@
         <v>618.72199999999998</v>
       </c>
       <c r="B98" s="0">
-        <v>0.020263197059980538</v>
+        <v>0.0023155955103405707</v>
       </c>
       <c r="C98" s="0">
-        <v>0.00049696592663450571</v>
+        <v>0.020263319987047772</v>
       </c>
       <c r="D98" s="0">
-        <v>0.0023156752219300253</v>
+        <v>0.00049695649772705803</v>
       </c>
       <c r="E98" s="0">
-        <v>0.00022084201249614709</v>
+        <v>0.0003932750703624516</v>
       </c>
       <c r="F98" s="0">
-        <v>0.0003932736019590163</v>
+        <v>0.00022084374948886003</v>
       </c>
     </row>
   </sheetData>

--- a/examples/tutorialModelExport.xlsx
+++ b/examples/tutorialModelExport.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="353" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="358" uniqueCount="221">
   <si>
     <t>#</t>
   </si>
@@ -630,6 +630,12 @@
   </si>
   <si>
     <t>parafac3w</t>
+  </si>
+  <si>
+    <t>modelName</t>
+  </si>
+  <si>
+    <t>PARAFAC</t>
   </si>
   <si>
     <t>selected for export</t>
@@ -5444,7 +5450,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.85546875" customWidth="true"/>
@@ -5458,7 +5464,8 @@
     <col min="9" max="9" width="12.42578125" customWidth="true"/>
     <col min="10" max="10" width="13.42578125" customWidth="true"/>
     <col min="11" max="11" width="10.140625" customWidth="true"/>
-    <col min="12" max="12" width="18" customWidth="true"/>
+    <col min="12" max="12" width="12.140625" customWidth="true"/>
+    <col min="13" max="13" width="18" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5498,6 +5505,9 @@
       <c r="L1" s="0" t="s">
         <v>203</v>
       </c>
+      <c r="M1" s="0" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
@@ -5507,13 +5517,13 @@
         <v>188</v>
       </c>
       <c r="C2" s="0">
-        <v>99.886855987874071</v>
+        <v>99.886219894903434</v>
       </c>
       <c r="D2" s="0">
-        <v>27.262494400070878</v>
+        <v>27.41576350131507</v>
       </c>
       <c r="E2" s="0">
-        <v>93.673445121155695</v>
+        <v>93.617405245455117</v>
       </c>
       <c r="F2" s="0">
         <v>0</v>
@@ -5535,6 +5545,9 @@
       </c>
       <c r="L2" s="0" t="s">
         <v>204</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="3">
@@ -5545,13 +5558,13 @@
         <v>189</v>
       </c>
       <c r="C3" s="0">
-        <v>99.947169737930537</v>
+        <v>99.947169738616211</v>
       </c>
       <c r="D3" s="0">
-        <v>12.729659279007523</v>
+        <v>12.729659113793881</v>
       </c>
       <c r="E3" s="0">
-        <v>96.325806512608267</v>
+        <v>96.327067327953287</v>
       </c>
       <c r="F3" s="0">
         <v>0</v>
@@ -5572,7 +5585,10 @@
         <v>202</v>
       </c>
       <c r="L3" s="0" t="s">
-        <v>205</v>
+        <v>204</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="4">
@@ -5583,16 +5599,16 @@
         <v>190</v>
       </c>
       <c r="C4" s="0">
-        <v>99.955771128453407</v>
+        <v>99.955771131825216</v>
       </c>
       <c r="D4" s="0">
-        <v>10.657120427358487</v>
+        <v>10.657119614909803</v>
       </c>
       <c r="E4" s="0">
-        <v>64.9319105150567</v>
+        <v>64.934621023819574</v>
       </c>
       <c r="F4" s="0">
-        <v>66.666666666666657</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>196</v>
@@ -5611,6 +5627,9 @@
       </c>
       <c r="L4" s="0" t="s">
         <v>204</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -5621,13 +5640,13 @@
         <v>188</v>
       </c>
       <c r="C5" s="0">
-        <v>99.963704315538209</v>
+        <v>99.963703943524905</v>
       </c>
       <c r="D5" s="0">
-        <v>8.7455878202836388</v>
+        <v>8.745677458349304</v>
       </c>
       <c r="E5" s="0">
-        <v>26.778983684581071</v>
+        <v>26.796528126574991</v>
       </c>
       <c r="F5" s="0">
         <v>0</v>
@@ -5649,6 +5668,9 @@
       </c>
       <c r="L5" s="0" t="s">
         <v>204</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -5669,33 +5691,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C2" s="0">
         <v>2</v>
       </c>
       <c r="D2" s="1">
-        <v>45960.518455930636</v>
+        <v>46073.468091633484</v>
       </c>
       <c r="E2" s="0">
         <v>23</v>
@@ -5712,30 +5734,30 @@
   <cols>
     <col min="1" max="1" width="18.140625" customWidth="true"/>
     <col min="2" max="2" width="14.7109375" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
-    <col min="5" max="5" width="14.7109375" customWidth="true"/>
-    <col min="6" max="6" width="15.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -5743,19 +5765,19 @@
         <v>81</v>
       </c>
       <c r="B2" s="0">
-        <v>0.10343524310680503</v>
+        <v>0.040665759056655357</v>
       </c>
       <c r="C2" s="0">
-        <v>0.040665531039281208</v>
+        <v>2.5424679965886674</v>
       </c>
       <c r="D2" s="0">
-        <v>0.34081339787348097</v>
+        <v>0.10343587625511673</v>
       </c>
       <c r="E2" s="0">
-        <v>0.0035831856867232256</v>
+        <v>0.3408130268599181</v>
       </c>
       <c r="F2" s="0">
-        <v>2.5424684274111891</v>
+        <v>0.0035824467627092516</v>
       </c>
     </row>
     <row r="3">
@@ -5763,19 +5785,19 @@
         <v>82</v>
       </c>
       <c r="B3" s="0">
-        <v>0.18018629605821329</v>
+        <v>0.041960728271143707</v>
       </c>
       <c r="C3" s="0">
-        <v>0.041960683497691546</v>
+        <v>2.5535009983540147</v>
       </c>
       <c r="D3" s="0">
-        <v>0.22833441443054195</v>
+        <v>0.18018734277693413</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>0.22833397573776273</v>
       </c>
       <c r="F3" s="0">
-        <v>2.5535012976279732</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -5783,19 +5805,19 @@
         <v>83</v>
       </c>
       <c r="B4" s="0">
-        <v>0.027488637300593012</v>
+        <v>0.048783033265628384</v>
       </c>
       <c r="C4" s="0">
-        <v>0.048783159000334732</v>
+        <v>0.035244797024246433</v>
       </c>
       <c r="D4" s="0">
-        <v>0.043836560526903101</v>
+        <v>0.027489930686867694</v>
       </c>
       <c r="E4" s="0">
-        <v>3.1058193646582457</v>
+        <v>0.043835750073147342</v>
       </c>
       <c r="F4" s="0">
-        <v>0.035244650587653421</v>
+        <v>3.1058191788527725</v>
       </c>
     </row>
     <row r="5">
@@ -5803,19 +5825,19 @@
         <v>84</v>
       </c>
       <c r="B5" s="0">
-        <v>0.079052967781349001</v>
+        <v>0.051883210189253716</v>
       </c>
       <c r="C5" s="0">
-        <v>0.051883197024001487</v>
+        <v>0.017451957493535623</v>
       </c>
       <c r="D5" s="0">
-        <v>0.045439406759673125</v>
+        <v>0.079054422496421223</v>
       </c>
       <c r="E5" s="0">
-        <v>3.1301542477443425</v>
+        <v>0.045438491120123922</v>
       </c>
       <c r="F5" s="0">
-        <v>0.01745185385121514</v>
+        <v>3.1301541716981314</v>
       </c>
     </row>
     <row r="6">
@@ -5823,19 +5845,19 @@
         <v>85</v>
       </c>
       <c r="B6" s="0">
-        <v>1.2841915721104744</v>
+        <v>0.045977010291739791</v>
       </c>
       <c r="C6" s="0">
-        <v>0.045976791498330644</v>
+        <v>0.016490456701754915</v>
       </c>
       <c r="D6" s="0">
-        <v>0.049462397664707385</v>
+        <v>1.2842003798767103</v>
       </c>
       <c r="E6" s="0">
-        <v>0.028212562561565666</v>
+        <v>0.049461855488068626</v>
       </c>
       <c r="F6" s="0">
-        <v>0.016490833344569321</v>
+        <v>0.028216161379618219</v>
       </c>
     </row>
     <row r="7">
@@ -5843,19 +5865,19 @@
         <v>86</v>
       </c>
       <c r="B7" s="0">
-        <v>0.17115799340088195</v>
+        <v>0.061389917272124742</v>
       </c>
       <c r="C7" s="0">
-        <v>0.061389841679195943</v>
+        <v>0.96710614498672143</v>
       </c>
       <c r="D7" s="0">
-        <v>0.12474208793820311</v>
+        <v>0.17115919930242299</v>
       </c>
       <c r="E7" s="0">
-        <v>0.013780605599569279</v>
+        <v>0.12474122960465173</v>
       </c>
       <c r="F7" s="0">
-        <v>0.96710612096576387</v>
+        <v>0.013779859442626366</v>
       </c>
     </row>
     <row r="8">
@@ -5863,19 +5885,19 @@
         <v>87</v>
       </c>
       <c r="B8" s="0">
-        <v>0.19337075755237596</v>
+        <v>0.05700289394035829</v>
       </c>
       <c r="C8" s="0">
-        <v>0.057002815611295735</v>
+        <v>1.8256988150557252</v>
       </c>
       <c r="D8" s="0">
-        <v>0.16784946220815578</v>
+        <v>0.19337213061735276</v>
       </c>
       <c r="E8" s="0">
-        <v>0.0045379340655324705</v>
+        <v>0.16784876349368716</v>
       </c>
       <c r="F8" s="0">
-        <v>1.8256989293323442</v>
+        <v>0.0045373130940480804</v>
       </c>
     </row>
     <row r="9">
@@ -5883,19 +5905,19 @@
         <v>88</v>
       </c>
       <c r="B9" s="0">
-        <v>0.20075739113231325</v>
+        <v>0.048124199561724902</v>
       </c>
       <c r="C9" s="0">
-        <v>0.048124013049998575</v>
+        <v>0</v>
       </c>
       <c r="D9" s="0">
-        <v>0.045153876571904644</v>
+        <v>0.20075930458093505</v>
       </c>
       <c r="E9" s="0">
-        <v>2.1447190080516516</v>
+        <v>0.045153005859285639</v>
       </c>
       <c r="F9" s="0">
-        <v>0</v>
+        <v>2.1447191822117184</v>
       </c>
     </row>
     <row r="10">
@@ -5903,19 +5925,19 @@
         <v>89</v>
       </c>
       <c r="B10" s="0">
-        <v>0.3942305977882446</v>
+        <v>0.04685242205224998</v>
       </c>
       <c r="C10" s="0">
-        <v>0.046852293133873929</v>
+        <v>0.65525640073964719</v>
       </c>
       <c r="D10" s="0">
-        <v>0.09638166263078872</v>
+        <v>0.39423350475960617</v>
       </c>
       <c r="E10" s="0">
-        <v>0.72082050646089768</v>
+        <v>0.096381003472123181</v>
       </c>
       <c r="F10" s="0">
-        <v>0.65525651247697003</v>
+        <v>0.72082103416712451</v>
       </c>
     </row>
     <row r="11">
@@ -5923,19 +5945,19 @@
         <v>90</v>
       </c>
       <c r="B11" s="0">
-        <v>0.083668080055449526</v>
+        <v>0.043552972544957019</v>
       </c>
       <c r="C11" s="0">
-        <v>0.043552868245559678</v>
+        <v>1.2137397974467699</v>
       </c>
       <c r="D11" s="0">
-        <v>0.12510138012731617</v>
+        <v>0.083668680819901739</v>
       </c>
       <c r="E11" s="0">
-        <v>0.013622182640642137</v>
+        <v>0.12510080909722643</v>
       </c>
       <c r="F11" s="0">
-        <v>1.2137398496635521</v>
+        <v>0.013621470971087176</v>
       </c>
     </row>
     <row r="12">
@@ -5943,19 +5965,19 @@
         <v>91</v>
       </c>
       <c r="B12" s="0">
-        <v>0.061198249949511362</v>
+        <v>0.049107642063092385</v>
       </c>
       <c r="C12" s="0">
-        <v>0.049107695180585151</v>
+        <v>0.032835331367229471</v>
       </c>
       <c r="D12" s="0">
-        <v>0.068800843447577073</v>
+        <v>0.061199634196810661</v>
       </c>
       <c r="E12" s="0">
-        <v>2.786330274850541</v>
+        <v>0.068800062756733074</v>
       </c>
       <c r="F12" s="0">
-        <v>0.032835264395733012</v>
+        <v>2.786330099768799</v>
       </c>
     </row>
     <row r="13">
@@ -5963,19 +5985,19 @@
         <v>92</v>
       </c>
       <c r="B13" s="0">
-        <v>0.078387168834944829</v>
+        <v>0.051680217099094289</v>
       </c>
       <c r="C13" s="0">
-        <v>0.051680197150566959</v>
+        <v>0.0071231947335411014</v>
       </c>
       <c r="D13" s="0">
-        <v>0.072462280112994118</v>
+        <v>0.078387767004578515</v>
       </c>
       <c r="E13" s="0">
-        <v>0.081990180857120024</v>
+        <v>0.072461498265176713</v>
       </c>
       <c r="F13" s="0">
-        <v>0.0071230803072641199</v>
+        <v>0.081989380220920338</v>
       </c>
     </row>
     <row r="14">
@@ -5983,19 +6005,19 @@
         <v>93</v>
       </c>
       <c r="B14" s="0">
-        <v>0.1021642016848127</v>
+        <v>0.037081878377382062</v>
       </c>
       <c r="C14" s="0">
-        <v>0.037081969218623119</v>
+        <v>2.597874784459401</v>
       </c>
       <c r="D14" s="0">
-        <v>0.22029238915176042</v>
+        <v>0.10216471611068376</v>
       </c>
       <c r="E14" s="0">
-        <v>0</v>
+        <v>0.22029207689247279</v>
       </c>
       <c r="F14" s="0">
-        <v>2.5978750733493365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -6003,19 +6025,19 @@
         <v>94</v>
       </c>
       <c r="B15" s="0">
-        <v>0.15361029467454016</v>
+        <v>0.041742682716551745</v>
       </c>
       <c r="C15" s="0">
-        <v>0.041742439044137311</v>
+        <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>0.025834170574371391</v>
+        <v>0.15361189617942084</v>
       </c>
       <c r="E15" s="0">
-        <v>3.1260242238545977</v>
+        <v>0.025833294760408416</v>
       </c>
       <c r="F15" s="0">
-        <v>0</v>
+        <v>3.1260246067898141</v>
       </c>
     </row>
     <row r="16">
@@ -6023,19 +6045,19 @@
         <v>95</v>
       </c>
       <c r="B16" s="0">
-        <v>0.45312250289895434</v>
+        <v>0.03613857681872102</v>
       </c>
       <c r="C16" s="0">
-        <v>0.036138437589388055</v>
+        <v>0.89968526683146322</v>
       </c>
       <c r="D16" s="0">
-        <v>0.11710943918492656</v>
+        <v>0.45312578891318778</v>
       </c>
       <c r="E16" s="0">
-        <v>1.0850900430340806</v>
+        <v>0.11710898189570285</v>
       </c>
       <c r="F16" s="0">
-        <v>0.89968550360560984</v>
+        <v>1.0850910816635477</v>
       </c>
     </row>
     <row r="17">
@@ -6043,19 +6065,19 @@
         <v>96</v>
       </c>
       <c r="B17" s="0">
-        <v>0.41205460408525862</v>
+        <v>0.043518482835799753</v>
       </c>
       <c r="C17" s="0">
-        <v>0.043518254800064882</v>
+        <v>2.5562904214555404</v>
       </c>
       <c r="D17" s="0">
-        <v>0.26125335971570807</v>
+        <v>0.412057348250287</v>
       </c>
       <c r="E17" s="0">
-        <v>0.004717143804679854</v>
+        <v>0.26125292253505578</v>
       </c>
       <c r="F17" s="0">
-        <v>2.556290820383591</v>
+        <v>0.0047174916105314777</v>
       </c>
     </row>
     <row r="18">
@@ -6063,19 +6085,19 @@
         <v>97</v>
       </c>
       <c r="B18" s="0">
-        <v>0.076223094070719227</v>
+        <v>0.0370154651494706</v>
       </c>
       <c r="C18" s="0">
-        <v>0.037015429049264713</v>
+        <v>0.011984802055707372</v>
       </c>
       <c r="D18" s="0">
-        <v>0.034246808935935603</v>
+        <v>0.076224351936414955</v>
       </c>
       <c r="E18" s="0">
-        <v>3.1735573744224137</v>
+        <v>0.034246128777899149</v>
       </c>
       <c r="F18" s="0">
-        <v>0.011984774481253017</v>
+        <v>3.173557620316148</v>
       </c>
     </row>
     <row r="19">
@@ -6083,19 +6105,19 @@
         <v>98</v>
       </c>
       <c r="B19" s="0">
-        <v>0.42241454541624435</v>
+        <v>0.035382780159546712</v>
       </c>
       <c r="C19" s="0">
-        <v>0.035382654102438529</v>
+        <v>0.88393568023933733</v>
       </c>
       <c r="D19" s="0">
-        <v>0.12079763084686587</v>
+        <v>0.42241751125625959</v>
       </c>
       <c r="E19" s="0">
-        <v>1.0635843713516366</v>
+        <v>0.12079718953915289</v>
       </c>
       <c r="F19" s="0">
-        <v>0.88393591441224628</v>
+        <v>1.0635853238029638</v>
       </c>
     </row>
     <row r="20">
@@ -6103,19 +6125,19 @@
         <v>99</v>
       </c>
       <c r="B20" s="0">
-        <v>0.066914333869368445</v>
+        <v>0.031746238121603453</v>
       </c>
       <c r="C20" s="0">
-        <v>0.031746210308320949</v>
+        <v>0.011168274387514996</v>
       </c>
       <c r="D20" s="0">
-        <v>0.030541191524429252</v>
+        <v>0.066914811237410415</v>
       </c>
       <c r="E20" s="0">
-        <v>0.013298217417821388</v>
+        <v>0.030540692140284216</v>
       </c>
       <c r="F20" s="0">
-        <v>0.011168189196908691</v>
+        <v>0.013297787785492537</v>
       </c>
     </row>
     <row r="21">
@@ -6123,19 +6145,19 @@
         <v>100</v>
       </c>
       <c r="B21" s="0">
-        <v>0.099988250428801009</v>
+        <v>0.043748590400004131</v>
       </c>
       <c r="C21" s="0">
-        <v>0.043748453271240419</v>
+        <v>0.0028148466214906109</v>
       </c>
       <c r="D21" s="0">
-        <v>0.22632940961023099</v>
+        <v>0.099989670925507646</v>
       </c>
       <c r="E21" s="0">
-        <v>2.0287693937172287</v>
+        <v>0.22632882828046072</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0028151114734700153</v>
+        <v>2.0287691588483376</v>
       </c>
     </row>
     <row r="22">
@@ -6143,19 +6165,19 @@
         <v>101</v>
       </c>
       <c r="B22" s="0">
-        <v>0.058814763816281528</v>
+        <v>0.036353254065534447</v>
       </c>
       <c r="C22" s="0">
-        <v>0.036353214986514837</v>
+        <v>0.0012737294035884031</v>
       </c>
       <c r="D22" s="0">
-        <v>0.035771094736491635</v>
+        <v>0.058815165400180218</v>
       </c>
       <c r="E22" s="0">
-        <v>0.023565778679807813</v>
+        <v>0.035770522438747281</v>
       </c>
       <c r="F22" s="0">
-        <v>0.0012736329780514085</v>
+        <v>0.023565224591842449</v>
       </c>
     </row>
     <row r="23">
@@ -6163,19 +6185,19 @@
         <v>102</v>
       </c>
       <c r="B23" s="0">
-        <v>0.057861153458283694</v>
+        <v>0.030983991318882954</v>
       </c>
       <c r="C23" s="0">
-        <v>0.030983969959624037</v>
+        <v>0.0023875128816498088</v>
       </c>
       <c r="D23" s="0">
-        <v>0.028061789853740311</v>
+        <v>0.057861604139381725</v>
       </c>
       <c r="E23" s="0">
-        <v>0.015603323719389888</v>
+        <v>0.028061304603300606</v>
       </c>
       <c r="F23" s="0">
-        <v>0.0023874239203339844</v>
+        <v>0.015602877009344049</v>
       </c>
     </row>
     <row r="24">
@@ -6183,19 +6205,19 @@
         <v>103</v>
       </c>
       <c r="B24" s="0">
-        <v>0.078912665669054929</v>
+        <v>0.043287325312788921</v>
       </c>
       <c r="C24" s="0">
-        <v>0.043287292847907208</v>
+        <v>0.003694700003306935</v>
       </c>
       <c r="D24" s="0">
-        <v>0.054076188727313429</v>
+        <v>0.078913437759990879</v>
       </c>
       <c r="E24" s="0">
-        <v>0.50828265267687223</v>
+        <v>0.054075509582273293</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0036946100938242471</v>
+        <v>0.50828212455781086</v>
       </c>
     </row>
     <row r="25">
@@ -6203,19 +6225,19 @@
         <v>104</v>
       </c>
       <c r="B25" s="0">
-        <v>0.048371725250913017</v>
+        <v>0.034817041717853915</v>
       </c>
       <c r="C25" s="0">
-        <v>0.034817013480450056</v>
+        <v>0.00087314958056244874</v>
       </c>
       <c r="D25" s="0">
-        <v>0.033851021432321792</v>
+        <v>0.048372109493975392</v>
       </c>
       <c r="E25" s="0">
-        <v>0.018372812711561829</v>
+        <v>0.033850478694524816</v>
       </c>
       <c r="F25" s="0">
-        <v>0.00087305197522710145</v>
+        <v>0.018372249187928864</v>
       </c>
     </row>
     <row r="26">
@@ -6223,19 +6245,19 @@
         <v>105</v>
       </c>
       <c r="B26" s="0">
-        <v>0.075798921760556026</v>
+        <v>0.041355843302363395</v>
       </c>
       <c r="C26" s="0">
-        <v>0.041355788358532875</v>
+        <v>0.00094255352711256318</v>
       </c>
       <c r="D26" s="0">
-        <v>0.037650278562426115</v>
+        <v>0.075799448590444185</v>
       </c>
       <c r="E26" s="0">
-        <v>0.02111154282382248</v>
+        <v>0.037649618087078077</v>
       </c>
       <c r="F26" s="0">
-        <v>0.00094244215135648446</v>
+        <v>0.021110940774471593</v>
       </c>
     </row>
     <row r="27">
@@ -6243,19 +6265,19 @@
         <v>106</v>
       </c>
       <c r="B27" s="0">
-        <v>0.048995254278068383</v>
+        <v>0.042476127851237513</v>
       </c>
       <c r="C27" s="0">
-        <v>0.042476096679397529</v>
+        <v>0.0015920855167009661</v>
       </c>
       <c r="D27" s="0">
-        <v>0.040744528699388473</v>
+        <v>0.048995631704134068</v>
       </c>
       <c r="E27" s="0">
-        <v>0.025239071897706734</v>
+        <v>0.04074385680010649</v>
       </c>
       <c r="F27" s="0">
-        <v>0.0015919564445716612</v>
+        <v>0.025238353622045726</v>
       </c>
     </row>
     <row r="28">
@@ -6263,19 +6285,19 @@
         <v>107</v>
       </c>
       <c r="B28" s="0">
-        <v>0.10230035925837429</v>
+        <v>0.045384160928030042</v>
       </c>
       <c r="C28" s="0">
-        <v>0.045384064858068576</v>
+        <v>0.54785107142128042</v>
       </c>
       <c r="D28" s="0">
-        <v>0.091905182730771681</v>
+        <v>0.10230107479212658</v>
       </c>
       <c r="E28" s="0">
-        <v>0.024773736713030122</v>
+        <v>0.091904513598891138</v>
       </c>
       <c r="F28" s="0">
-        <v>0.54785104945609131</v>
+        <v>0.024773096052218932</v>
       </c>
     </row>
     <row r="29">
@@ -6283,19 +6305,19 @@
         <v>108</v>
       </c>
       <c r="B29" s="0">
-        <v>0.070239581745746654</v>
+        <v>0.041481231403749618</v>
       </c>
       <c r="C29" s="0">
-        <v>0.041481170771236302</v>
+        <v>0.00032951011753189891</v>
       </c>
       <c r="D29" s="0">
-        <v>0.037862062106725318</v>
+        <v>0.070240058740356742</v>
       </c>
       <c r="E29" s="0">
-        <v>0.021469731502666463</v>
+        <v>0.037861396582117284</v>
       </c>
       <c r="F29" s="0">
-        <v>0.00032939829850060629</v>
+        <v>0.02146910646463613</v>
       </c>
     </row>
     <row r="30">
@@ -6303,19 +6325,19 @@
         <v>109</v>
       </c>
       <c r="B30" s="0">
-        <v>0.059927085451426811</v>
+        <v>0.045073786946280718</v>
       </c>
       <c r="C30" s="0">
-        <v>0.045073764731783809</v>
+        <v>0.0014522008735770463</v>
       </c>
       <c r="D30" s="0">
-        <v>0.042831541486700306</v>
+        <v>0.05992751717513687</v>
       </c>
       <c r="E30" s="0">
-        <v>0.027424325585841243</v>
+        <v>0.042830837680534979</v>
       </c>
       <c r="F30" s="0">
-        <v>0.0014520660421506017</v>
+        <v>0.027423597261785497</v>
       </c>
     </row>
     <row r="31">
@@ -6323,19 +6345,19 @@
         <v>110</v>
       </c>
       <c r="B31" s="0">
-        <v>0.066500516834140808</v>
+        <v>0.041287241008496914</v>
       </c>
       <c r="C31" s="0">
-        <v>0.041287193527390888</v>
+        <v>0.00061939828441496907</v>
       </c>
       <c r="D31" s="0">
-        <v>0.042212212417945705</v>
+        <v>0.066500980807863958</v>
       </c>
       <c r="E31" s="0">
-        <v>0.027477641388761132</v>
+        <v>0.042211560518670518</v>
       </c>
       <c r="F31" s="0">
-        <v>0.00061929050032952541</v>
+        <v>0.027477008646816591</v>
       </c>
     </row>
     <row r="32">
@@ -6343,19 +6365,19 @@
         <v>111</v>
       </c>
       <c r="B32" s="0">
-        <v>0.066219808248560178</v>
+        <v>0.059764373279507128</v>
       </c>
       <c r="C32" s="0">
-        <v>0.059764327074572105</v>
+        <v>0.0017667169257945799</v>
       </c>
       <c r="D32" s="0">
-        <v>0.049109295857836861</v>
+        <v>0.066220333191411199</v>
       </c>
       <c r="E32" s="0">
-        <v>0.025079172125716694</v>
+        <v>0.049108344538639666</v>
       </c>
       <c r="F32" s="0">
-        <v>0.0017665229677794373</v>
+        <v>0.025078150181405058</v>
       </c>
     </row>
     <row r="33">
@@ -6363,19 +6385,19 @@
         <v>112</v>
       </c>
       <c r="B33" s="0">
-        <v>0.066614585421713238</v>
+        <v>0.035486077243689795</v>
       </c>
       <c r="C33" s="0">
-        <v>0.035486027960553689</v>
+        <v>0.0027694627060631349</v>
       </c>
       <c r="D33" s="0">
-        <v>0.036051394674826237</v>
+        <v>0.066615044316673713</v>
       </c>
       <c r="E33" s="0">
-        <v>0.023707240574130435</v>
+        <v>0.036050830873792405</v>
       </c>
       <c r="F33" s="0">
-        <v>0.0027693744997002159</v>
+        <v>0.023706729136093948</v>
       </c>
     </row>
     <row r="34">
@@ -6383,19 +6405,19 @@
         <v>113</v>
       </c>
       <c r="B34" s="0">
-        <v>0.013620633283479535</v>
+        <v>0.043302588171467975</v>
       </c>
       <c r="C34" s="0">
-        <v>0.043302757070093477</v>
+        <v>0.031181959221826462</v>
       </c>
       <c r="D34" s="0">
-        <v>0.036156798561966061</v>
+        <v>0.013621621532925071</v>
       </c>
       <c r="E34" s="0">
-        <v>3.3498492384041905</v>
+        <v>0.036156084628113358</v>
       </c>
       <c r="F34" s="0">
-        <v>0.031181827866268018</v>
+        <v>3.3498492175816712</v>
       </c>
     </row>
     <row r="35">
@@ -6403,19 +6425,19 @@
         <v>114</v>
       </c>
       <c r="B35" s="0">
-        <v>0.023349939840410779</v>
+        <v>0.007323841167306556</v>
       </c>
       <c r="C35" s="0">
-        <v>0.0073238242394507297</v>
+        <v>0</v>
       </c>
       <c r="D35" s="0">
-        <v>0.00012656348964335047</v>
+        <v>0.023350030623885677</v>
       </c>
       <c r="E35" s="0">
-        <v>0.0021837968264859513</v>
+        <v>0.00012645476341332829</v>
       </c>
       <c r="F35" s="0">
-        <v>0</v>
+        <v>0.0021837350349048846</v>
       </c>
     </row>
     <row r="36">
@@ -6423,19 +6445,19 @@
         <v>115</v>
       </c>
       <c r="B36" s="0">
-        <v>0.46013101821463648</v>
+        <v>0.035877591948916911</v>
       </c>
       <c r="C36" s="0">
-        <v>0.035877443813167993</v>
+        <v>0.93673488054949683</v>
       </c>
       <c r="D36" s="0">
-        <v>0.094325692910143574</v>
+        <v>0.46013426192005902</v>
       </c>
       <c r="E36" s="0">
-        <v>1.0596186056721366</v>
+        <v>0.094325227287120242</v>
       </c>
       <c r="F36" s="0">
-        <v>0.93673509406358269</v>
+        <v>1.0596196834358966</v>
       </c>
     </row>
     <row r="37">
@@ -6443,19 +6465,19 @@
         <v>116</v>
       </c>
       <c r="B37" s="0">
-        <v>0</v>
+        <v>0.041418159676594554</v>
       </c>
       <c r="C37" s="0">
-        <v>0.041418372363111244</v>
+        <v>0.036937512507178138</v>
       </c>
       <c r="D37" s="0">
-        <v>0.03520784708913749</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
-        <v>3.2919533797841427</v>
+        <v>0.035207165940459632</v>
       </c>
       <c r="F37" s="0">
-        <v>0.036937384174370223</v>
+        <v>3.2919534416984977</v>
       </c>
     </row>
     <row r="38">
@@ -6463,19 +6485,19 @@
         <v>117</v>
       </c>
       <c r="B38" s="0">
-        <v>1.2478379619874316</v>
+        <v>0.067247053062778353</v>
       </c>
       <c r="C38" s="0">
-        <v>0.067246822718292701</v>
+        <v>0.008807698448199109</v>
       </c>
       <c r="D38" s="0">
-        <v>0.046491164148724035</v>
+        <v>1.2478463520701058</v>
       </c>
       <c r="E38" s="0">
-        <v>0.041804293790898998</v>
+        <v>0.046490257877874808</v>
       </c>
       <c r="F38" s="0">
-        <v>0.0088079573061367895</v>
+        <v>0.041807346128229922</v>
       </c>
     </row>
     <row r="39">
@@ -6483,19 +6505,19 @@
         <v>118</v>
       </c>
       <c r="B39" s="0">
-        <v>0.064801460064669122</v>
+        <v>0.050474023129391012</v>
       </c>
       <c r="C39" s="0">
-        <v>0.050473859712009329</v>
+        <v>0.016713697437471368</v>
       </c>
       <c r="D39" s="0">
-        <v>1.193306588058328</v>
+        <v>0.064803368826756053</v>
       </c>
       <c r="E39" s="0">
-        <v>0.50834651985060253</v>
+        <v>1.1933069831423913</v>
       </c>
       <c r="F39" s="0">
-        <v>0.016715488646895878</v>
+        <v>0.50834504196057784</v>
       </c>
     </row>
     <row r="40">
@@ -6503,19 +6525,19 @@
         <v>119</v>
       </c>
       <c r="B40" s="0">
-        <v>0</v>
+        <v>0.04390235098070179</v>
       </c>
       <c r="C40" s="0">
-        <v>0.043902525841546754</v>
+        <v>0.034481846038859731</v>
       </c>
       <c r="D40" s="0">
-        <v>0.036170431751560726</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
-        <v>3.3909120611246326</v>
+        <v>0.036169699767455182</v>
       </c>
       <c r="F40" s="0">
-        <v>0.034481723606229364</v>
+        <v>3.3909120856313471</v>
       </c>
     </row>
     <row r="41">
@@ -6523,19 +6545,19 @@
         <v>120</v>
       </c>
       <c r="B41" s="0">
-        <v>1.2837410585081224</v>
+        <v>0.066080198964003023</v>
       </c>
       <c r="C41" s="0">
-        <v>0.066079954274240058</v>
+        <v>0.00545187212885756</v>
       </c>
       <c r="D41" s="0">
-        <v>0.051981956792404721</v>
+        <v>1.2837497562964033</v>
       </c>
       <c r="E41" s="0">
-        <v>0.029353333786996474</v>
+        <v>0.051981085268106339</v>
       </c>
       <c r="F41" s="0">
-        <v>0.0054521668618494872</v>
+        <v>0.029356522486126604</v>
       </c>
     </row>
     <row r="42">
@@ -6543,19 +6565,19 @@
         <v>121</v>
       </c>
       <c r="B42" s="0">
-        <v>0.47788951990353346</v>
+        <v>0.039121945729098384</v>
       </c>
       <c r="C42" s="0">
-        <v>0.039121824772704157</v>
+        <v>0.92232750676274911</v>
       </c>
       <c r="D42" s="0">
-        <v>0.10076865789818561</v>
+        <v>0.47789302050544208</v>
       </c>
       <c r="E42" s="0">
-        <v>1.0499590904215015</v>
+        <v>0.10076816087998138</v>
       </c>
       <c r="F42" s="0">
-        <v>0.92232771106315725</v>
+        <v>1.0499601543488244</v>
       </c>
     </row>
     <row r="43">
@@ -6563,19 +6585,19 @@
         <v>122</v>
       </c>
       <c r="B43" s="0">
-        <v>0.0054022779315693534</v>
+        <v>0.045284830725432511</v>
       </c>
       <c r="C43" s="0">
-        <v>0.045285036065000069</v>
+        <v>0.031650138861104016</v>
       </c>
       <c r="D43" s="0">
-        <v>0.033945407684714587</v>
+        <v>0.0054033301096177936</v>
       </c>
       <c r="E43" s="0">
-        <v>3.3276066003622304</v>
+        <v>0.033944676823857281</v>
       </c>
       <c r="F43" s="0">
-        <v>0.031649980027504313</v>
+        <v>3.3276065023210064</v>
       </c>
     </row>
     <row r="44">
@@ -6583,19 +6605,19 @@
         <v>123</v>
       </c>
       <c r="B44" s="0">
-        <v>1.2248519150459822</v>
+        <v>0.059763814942252282</v>
       </c>
       <c r="C44" s="0">
-        <v>0.059763564659069082</v>
+        <v>0.0075887552092407783</v>
       </c>
       <c r="D44" s="0">
-        <v>0.044271483597632805</v>
+        <v>1.2248601423928511</v>
       </c>
       <c r="E44" s="0">
-        <v>0.035831832736541926</v>
+        <v>0.044270698384364766</v>
       </c>
       <c r="F44" s="0">
-        <v>0.0075890535540645088</v>
+        <v>0.035834949406722189</v>
       </c>
     </row>
     <row r="45">
@@ -6603,19 +6625,19 @@
         <v>124</v>
       </c>
       <c r="B45" s="0">
-        <v>0.13986063650981481</v>
+        <v>0.049696885172176374</v>
       </c>
       <c r="C45" s="0">
-        <v>0.04969677152007345</v>
+        <v>0.071346965423368422</v>
       </c>
       <c r="D45" s="0">
-        <v>0.70973177959447942</v>
+        <v>0.13986254254499439</v>
       </c>
       <c r="E45" s="0">
-        <v>0.7578617164811059</v>
+        <v>0.70973168029360678</v>
       </c>
       <c r="F45" s="0">
-        <v>0.071347975303856212</v>
+        <v>0.75786090560711517</v>
       </c>
     </row>
     <row r="46">
@@ -6623,19 +6645,19 @@
         <v>125</v>
       </c>
       <c r="B46" s="0">
-        <v>0.97358452474937263</v>
+        <v>0.042885557820815094</v>
       </c>
       <c r="C46" s="0">
-        <v>0.042885408241997346</v>
+        <v>0.012014458570910958</v>
       </c>
       <c r="D46" s="0">
-        <v>0.044818944742938911</v>
+        <v>0.97359148609130231</v>
       </c>
       <c r="E46" s="0">
-        <v>0.038052697611377646</v>
+        <v>0.044818423747982304</v>
       </c>
       <c r="F46" s="0">
-        <v>0.012014710184460693</v>
+        <v>0.038055236719098599</v>
       </c>
     </row>
     <row r="47">
@@ -6643,19 +6665,19 @@
         <v>126</v>
       </c>
       <c r="B47" s="0">
-        <v>0.14497469062741952</v>
+        <v>0.050986361361697673</v>
       </c>
       <c r="C47" s="0">
-        <v>0.050986279946028709</v>
+        <v>0</v>
       </c>
       <c r="D47" s="0">
-        <v>0.042757290082394213</v>
+        <v>0.14497682485028496</v>
       </c>
       <c r="E47" s="0">
-        <v>3.3637625293923321</v>
+        <v>0.042756396903225795</v>
       </c>
       <c r="F47" s="0">
-        <v>0</v>
+        <v>3.3637627336398612</v>
       </c>
     </row>
     <row r="48">
@@ -6663,19 +6685,19 @@
         <v>127</v>
       </c>
       <c r="B48" s="0">
-        <v>0.057340305503721011</v>
+        <v>0.043446874578620974</v>
       </c>
       <c r="C48" s="0">
-        <v>0.043446872715484586</v>
+        <v>0.0032349042236193672</v>
       </c>
       <c r="D48" s="0">
-        <v>0.037796324607386002</v>
+        <v>0.057340945909768924</v>
       </c>
       <c r="E48" s="0">
-        <v>0.015909284521787709</v>
+        <v>0.037795651916820147</v>
       </c>
       <c r="F48" s="0">
-        <v>0.0032347580668137185</v>
+        <v>0.015908561548415797</v>
       </c>
     </row>
     <row r="49">
@@ -6683,19 +6705,19 @@
         <v>128</v>
       </c>
       <c r="B49" s="0">
-        <v>0.089996122834657202</v>
+        <v>0.050206650566815572</v>
       </c>
       <c r="C49" s="0">
-        <v>0.050206647223536155</v>
+        <v>0.0025029886192053843</v>
       </c>
       <c r="D49" s="0">
-        <v>0.043501920541337412</v>
+        <v>0.089997026375000538</v>
       </c>
       <c r="E49" s="0">
-        <v>0.030593797306224076</v>
+        <v>0.043501148418104652</v>
       </c>
       <c r="F49" s="0">
-        <v>0.0025028294916022145</v>
+        <v>0.030593049569570853</v>
       </c>
     </row>
     <row r="50">
@@ -6703,19 +6725,19 @@
         <v>129</v>
       </c>
       <c r="B50" s="0">
-        <v>0.035813705131992384</v>
+        <v>0.037537978219046898</v>
       </c>
       <c r="C50" s="0">
-        <v>0.037537996298843704</v>
+        <v>0.0018691509797572278</v>
       </c>
       <c r="D50" s="0">
-        <v>0.033478411344056394</v>
+        <v>0.035814173080413438</v>
       </c>
       <c r="E50" s="0">
-        <v>0.011447885861028113</v>
+        <v>0.033477836173324553</v>
       </c>
       <c r="F50" s="0">
-        <v>0.0018690154676473641</v>
+        <v>0.01144721550340819</v>
       </c>
     </row>
     <row r="51">
@@ -6723,19 +6745,19 @@
         <v>130</v>
       </c>
       <c r="B51" s="0">
-        <v>0.20646971288232785</v>
+        <v>0.038175545324658534</v>
       </c>
       <c r="C51" s="0">
-        <v>0.038175233421777581</v>
+        <v>0</v>
       </c>
       <c r="D51" s="0">
-        <v>0.025010423409934032</v>
+        <v>0.20647200914785707</v>
       </c>
       <c r="E51" s="0">
-        <v>3.051051029155901</v>
+        <v>0.025009576256112644</v>
       </c>
       <c r="F51" s="0">
-        <v>0</v>
+        <v>3.05105159411925</v>
       </c>
     </row>
     <row r="52">
@@ -6743,19 +6765,19 @@
         <v>131</v>
       </c>
       <c r="B52" s="0">
-        <v>0.0050091908827803629</v>
+        <v>0.041301882666585285</v>
       </c>
       <c r="C52" s="0">
-        <v>0.041302133568272281</v>
+        <v>0.042047503148409958</v>
       </c>
       <c r="D52" s="0">
-        <v>0.033724209242332867</v>
+        <v>0.0050106304010559587</v>
       </c>
       <c r="E52" s="0">
-        <v>3.3164685691614304</v>
+        <v>0.03372357085686354</v>
       </c>
       <c r="F52" s="0">
-        <v>0.04204734799740302</v>
+        <v>3.3164685199510888</v>
       </c>
     </row>
     <row r="53">
@@ -6763,19 +6785,19 @@
         <v>132</v>
       </c>
       <c r="B53" s="0">
-        <v>0.049121745090763502</v>
+        <v>0.042692066507458236</v>
       </c>
       <c r="C53" s="0">
-        <v>0.042692069784400578</v>
+        <v>0.0021431885585892216</v>
       </c>
       <c r="D53" s="0">
-        <v>0.037723637182564329</v>
+        <v>0.049122324783215127</v>
       </c>
       <c r="E53" s="0">
-        <v>0.014981554713559638</v>
+        <v>0.037722976516956101</v>
       </c>
       <c r="F53" s="0">
-        <v>0.0021430413143526694</v>
+        <v>0.014980819328205955</v>
       </c>
     </row>
     <row r="54">
@@ -6783,19 +6805,19 @@
         <v>133</v>
       </c>
       <c r="B54" s="0">
-        <v>0.087646756563382361</v>
+        <v>0.047368250814844859</v>
       </c>
       <c r="C54" s="0">
-        <v>0.047368226856095534</v>
+        <v>0.0031400073268313023</v>
       </c>
       <c r="D54" s="0">
-        <v>0.042749069066420051</v>
+        <v>0.087647626740448237</v>
       </c>
       <c r="E54" s="0">
-        <v>0.031952579663412299</v>
+        <v>0.042748328149195013</v>
       </c>
       <c r="F54" s="0">
-        <v>0.0031398630329721915</v>
+        <v>0.03195187910010569</v>
       </c>
     </row>
     <row r="55">
@@ -6803,19 +6825,19 @@
         <v>134</v>
       </c>
       <c r="B55" s="0">
-        <v>0.037204084185478506</v>
+        <v>0.035469996276163214</v>
       </c>
       <c r="C55" s="0">
-        <v>0.035470006716549339</v>
+        <v>0.0016701733230531175</v>
       </c>
       <c r="D55" s="0">
-        <v>0.034645503359447737</v>
+        <v>0.037204557252966036</v>
       </c>
       <c r="E55" s="0">
-        <v>0.014486484792582251</v>
+        <v>0.034644959611774558</v>
       </c>
       <c r="F55" s="0">
-        <v>0.0016700523415565318</v>
+        <v>0.014485860360274886</v>
       </c>
     </row>
     <row r="56">
@@ -6823,19 +6845,19 @@
         <v>135</v>
       </c>
       <c r="B56" s="0">
-        <v>0.12446743650277843</v>
+        <v>0.050160401851295416</v>
       </c>
       <c r="C56" s="0">
-        <v>0.050160202664672499</v>
+        <v>2.5850885443614606</v>
       </c>
       <c r="D56" s="0">
-        <v>0.27210595529338921</v>
+        <v>0.12446818004972271</v>
       </c>
       <c r="E56" s="0">
-        <v>0.027070434909731437</v>
+        <v>0.27210540420723728</v>
       </c>
       <c r="F56" s="0">
-        <v>2.5850888334663167</v>
+        <v>0.027069622826254212</v>
       </c>
     </row>
     <row r="57">
@@ -6843,19 +6865,19 @@
         <v>136</v>
       </c>
       <c r="B57" s="0">
-        <v>1.229950956791789</v>
+        <v>0.046201454169095386</v>
       </c>
       <c r="C57" s="0">
-        <v>0.046201218063285185</v>
+        <v>0.003273998770117257</v>
       </c>
       <c r="D57" s="0">
-        <v>0.046057150615747208</v>
+        <v>1.2299593601506875</v>
       </c>
       <c r="E57" s="0">
-        <v>0.039188540405626159</v>
+        <v>0.046056595516803515</v>
       </c>
       <c r="F57" s="0">
-        <v>0.0032743624130367357</v>
+        <v>0.039191941441259121</v>
       </c>
     </row>
     <row r="58">
@@ -6863,19 +6885,19 @@
         <v>137</v>
       </c>
       <c r="B58" s="0">
-        <v>0.11188893184555455</v>
+        <v>0.057674728300747602</v>
       </c>
       <c r="C58" s="0">
-        <v>0.057674576528891526</v>
+        <v>0.036219960102592201</v>
       </c>
       <c r="D58" s="0">
-        <v>1.2335229706354047</v>
+        <v>0.11189129285835991</v>
       </c>
       <c r="E58" s="0">
-        <v>0.45099336502457393</v>
+        <v>1.2335233139864605</v>
       </c>
       <c r="F58" s="0">
-        <v>0.036221795095643904</v>
+        <v>0.45099186071246133</v>
       </c>
     </row>
     <row r="59">
@@ -6883,19 +6905,19 @@
         <v>138</v>
       </c>
       <c r="B59" s="0">
-        <v>0.056073582518556625</v>
+        <v>0.046025349109257381</v>
       </c>
       <c r="C59" s="0">
-        <v>0.046025362466826716</v>
+        <v>0.010892557947333388</v>
       </c>
       <c r="D59" s="0">
-        <v>0.04186124999503895</v>
+        <v>0.056074772411962674</v>
       </c>
       <c r="E59" s="0">
-        <v>3.1839248546799954</v>
+        <v>0.041860428820154436</v>
       </c>
       <c r="F59" s="0">
-        <v>0.010892464728694921</v>
+        <v>3.1839248505358819</v>
       </c>
     </row>
     <row r="60">
@@ -6903,19 +6925,19 @@
         <v>139</v>
       </c>
       <c r="B60" s="0">
-        <v>0.99040163459615072</v>
+        <v>0.064191383548770631</v>
       </c>
       <c r="C60" s="0">
-        <v>0.064191155887343032</v>
+        <v>0.0019905880258766543</v>
       </c>
       <c r="D60" s="0">
-        <v>0.055059824126480216</v>
+        <v>0.99040836753996042</v>
       </c>
       <c r="E60" s="0">
-        <v>0.061696774836367173</v>
+        <v>0.055058917997654833</v>
       </c>
       <c r="F60" s="0">
-        <v>0.0019907739779960682</v>
+        <v>0.061698954542781022</v>
       </c>
     </row>
     <row r="61">
@@ -6923,19 +6945,19 @@
         <v>140</v>
       </c>
       <c r="B61" s="0">
-        <v>0.34122406031108249</v>
+        <v>0.03840153796102614</v>
       </c>
       <c r="C61" s="0">
-        <v>0.038401497507125966</v>
+        <v>0.83754432369173071</v>
       </c>
       <c r="D61" s="0">
-        <v>0.10654267283332675</v>
+        <v>0.34122669256251059</v>
       </c>
       <c r="E61" s="0">
-        <v>0.9418105123915177</v>
+        <v>0.10654218216468957</v>
       </c>
       <c r="F61" s="0">
-        <v>0.83754445312381476</v>
+        <v>0.94181108810732128</v>
       </c>
     </row>
     <row r="62">
@@ -6943,19 +6965,19 @@
         <v>141</v>
       </c>
       <c r="B62" s="0">
-        <v>0.084280318024008649</v>
+        <v>0.052595781144573278</v>
       </c>
       <c r="C62" s="0">
-        <v>0.052595737769887713</v>
+        <v>0.00199484436094671</v>
       </c>
       <c r="D62" s="0">
-        <v>0.049858715911621755</v>
+        <v>0.084280890645865844</v>
       </c>
       <c r="E62" s="0">
-        <v>0.029896545263983609</v>
+        <v>0.049857884995982836</v>
       </c>
       <c r="F62" s="0">
-        <v>0.001994694040049998</v>
+        <v>0.029895745064728377</v>
       </c>
     </row>
     <row r="63">
@@ -6963,19 +6985,19 @@
         <v>142</v>
       </c>
       <c r="B63" s="0">
-        <v>0.16656080425225028</v>
+        <v>0.051511953517730559</v>
       </c>
       <c r="C63" s="0">
-        <v>0.051511817449263107</v>
+        <v>0</v>
       </c>
       <c r="D63" s="0">
-        <v>0.051476370153510011</v>
+        <v>0.16656188321627394</v>
       </c>
       <c r="E63" s="0">
-        <v>0.040481371332429607</v>
+        <v>0.05147558740980563</v>
       </c>
       <c r="F63" s="0">
-        <v>0</v>
+        <v>0.040480877899467783</v>
       </c>
     </row>
     <row r="64">
@@ -6983,19 +7005,19 @@
         <v>143</v>
       </c>
       <c r="B64" s="0">
-        <v>0.10200912738497245</v>
+        <v>0.052584673793752847</v>
       </c>
       <c r="C64" s="0">
-        <v>0.05258458629379275</v>
+        <v>1.8248302847655873</v>
       </c>
       <c r="D64" s="0">
-        <v>0.17062104663290903</v>
+        <v>0.10200989577401455</v>
       </c>
       <c r="E64" s="0">
-        <v>0.011149399224892043</v>
+        <v>0.17062039375796453</v>
       </c>
       <c r="F64" s="0">
-        <v>1.8248303639391079</v>
+        <v>0.011148531001502768</v>
       </c>
     </row>
     <row r="65">
@@ -7003,19 +7025,19 @@
         <v>144</v>
       </c>
       <c r="B65" s="0">
-        <v>0.22150499619372466</v>
+        <v>0.050500808008750023</v>
       </c>
       <c r="C65" s="0">
-        <v>0.050500566252343657</v>
+        <v>0</v>
       </c>
       <c r="D65" s="0">
-        <v>0.046590620615628416</v>
+        <v>0.22150701676196893</v>
       </c>
       <c r="E65" s="0">
-        <v>2.3096558691946134</v>
+        <v>0.046589684890749363</v>
       </c>
       <c r="F65" s="0">
-        <v>0</v>
+        <v>2.3096560938287452</v>
       </c>
     </row>
     <row r="66">
@@ -7023,19 +7045,19 @@
         <v>145</v>
       </c>
       <c r="B66" s="0">
-        <v>0.70769116062004234</v>
+        <v>0.054475149063844923</v>
       </c>
       <c r="C66" s="0">
-        <v>0.054475024856464133</v>
+        <v>0.005914564201945284</v>
       </c>
       <c r="D66" s="0">
-        <v>0.061464898682111857</v>
+        <v>0.70769606180097933</v>
       </c>
       <c r="E66" s="0">
-        <v>0.034396918107398623</v>
+        <v>0.061464153499743886</v>
       </c>
       <c r="F66" s="0">
-        <v>0.0059146806725886812</v>
+        <v>0.034398286988845207</v>
       </c>
     </row>
     <row r="67">
@@ -7043,19 +7065,19 @@
         <v>146</v>
       </c>
       <c r="B67" s="0">
-        <v>0.098384170130393023</v>
+        <v>0.047378995131559604</v>
       </c>
       <c r="C67" s="0">
-        <v>0.047378835502278199</v>
+        <v>2.5184546251566911</v>
       </c>
       <c r="D67" s="0">
-        <v>0.27775892512350708</v>
+        <v>0.098384783450183769</v>
       </c>
       <c r="E67" s="0">
-        <v>0.0053383737393373158</v>
+        <v>0.27775843135432465</v>
       </c>
       <c r="F67" s="0">
-        <v>2.5184549140896202</v>
+        <v>0.0053375256178734851</v>
       </c>
     </row>
     <row r="68">
@@ -7063,19 +7085,19 @@
         <v>147</v>
       </c>
       <c r="B68" s="0">
-        <v>0.16722198254231327</v>
+        <v>0.047561661582823558</v>
       </c>
       <c r="C68" s="0">
-        <v>0.04756137492733379</v>
+        <v>0</v>
       </c>
       <c r="D68" s="0">
-        <v>0.031085291298670707</v>
+        <v>0.16722364772088061</v>
       </c>
       <c r="E68" s="0">
-        <v>2.9245496223696512</v>
+        <v>0.03108430759426354</v>
       </c>
       <c r="F68" s="0">
-        <v>0</v>
+        <v>2.9245498741094167</v>
       </c>
     </row>
     <row r="69">
@@ -7083,19 +7105,19 @@
         <v>148</v>
       </c>
       <c r="B69" s="0">
-        <v>1.3044768285810413</v>
+        <v>0.043642903821302544</v>
       </c>
       <c r="C69" s="0">
-        <v>0.043642666298532903</v>
+        <v>0.0047444113399501657</v>
       </c>
       <c r="D69" s="0">
-        <v>0.051106285688492396</v>
+        <v>1.3044857987300338</v>
       </c>
       <c r="E69" s="0">
-        <v>0.026699879275276832</v>
+        <v>0.051105786579330022</v>
       </c>
       <c r="F69" s="0">
-        <v>0.0047448189156843379</v>
+        <v>0.026703589667335805</v>
       </c>
     </row>
     <row r="70">
@@ -7103,19 +7125,19 @@
         <v>149</v>
       </c>
       <c r="B70" s="0">
-        <v>0.10340916369839988</v>
+        <v>0.048919237313409907</v>
       </c>
       <c r="C70" s="0">
-        <v>0.048919045254225614</v>
+        <v>2.5259294544363047</v>
       </c>
       <c r="D70" s="0">
-        <v>0.29773847839631523</v>
+        <v>0.10340976963581938</v>
       </c>
       <c r="E70" s="0">
-        <v>0.0039638325035983076</v>
+        <v>0.29773796288320909</v>
       </c>
       <c r="F70" s="0">
-        <v>2.5259297766726689</v>
+        <v>0.0039629560861943174</v>
       </c>
     </row>
     <row r="71">
@@ -7123,19 +7145,19 @@
         <v>150</v>
       </c>
       <c r="B71" s="0">
-        <v>0.090704947174385722</v>
+        <v>0.046955806936702468</v>
       </c>
       <c r="C71" s="0">
-        <v>0.046955705007349913</v>
+        <v>0.0067784592762550966</v>
       </c>
       <c r="D71" s="0">
-        <v>0.040864665641216338</v>
+        <v>0.090706309738183222</v>
       </c>
       <c r="E71" s="0">
-        <v>3.0879278079318113</v>
+        <v>0.040863789584214785</v>
       </c>
       <c r="F71" s="0">
-        <v>0.0067784013635067636</v>
+        <v>3.0879278591320549</v>
       </c>
     </row>
     <row r="72">
@@ -7143,19 +7165,19 @@
         <v>151</v>
       </c>
       <c r="B72" s="0">
-        <v>1.2888994656714008</v>
+        <v>0.045644567049822997</v>
       </c>
       <c r="C72" s="0">
-        <v>0.04564429719151715</v>
+        <v>0.0066866728814400332</v>
       </c>
       <c r="D72" s="0">
-        <v>0.04895220677410899</v>
+        <v>1.2889082379201733</v>
       </c>
       <c r="E72" s="0">
-        <v>0.029860783070003352</v>
+        <v>0.048951665453460427</v>
       </c>
       <c r="F72" s="0">
-        <v>0.0066870774840712037</v>
+        <v>0.029864397807759974</v>
       </c>
     </row>
     <row r="73">
@@ -7163,19 +7185,19 @@
         <v>152</v>
       </c>
       <c r="B73" s="0">
-        <v>0.073428939474189423</v>
+        <v>0.048650222055857471</v>
       </c>
       <c r="C73" s="0">
-        <v>0.048650143354714189</v>
+        <v>0.81809167132573746</v>
       </c>
       <c r="D73" s="0">
-        <v>0.088470711713146577</v>
+        <v>0.073429461637731522</v>
       </c>
       <c r="E73" s="0">
-        <v>0.014453844083484537</v>
+        <v>0.088470009274313199</v>
       </c>
       <c r="F73" s="0">
-        <v>0.81809162210086461</v>
+        <v>0.014453028150668885</v>
       </c>
     </row>
     <row r="74">
@@ -7183,19 +7205,19 @@
         <v>153</v>
       </c>
       <c r="B74" s="0">
-        <v>0.11752246401277167</v>
+        <v>0.044732932479331758</v>
       </c>
       <c r="C74" s="0">
-        <v>0.044732770371691578</v>
+        <v>0.0082003405739373321</v>
       </c>
       <c r="D74" s="0">
-        <v>0.08734268384483608</v>
+        <v>0.11752387156903878</v>
       </c>
       <c r="E74" s="0">
-        <v>2.3228988854169295</v>
+        <v>0.087341911485943849</v>
       </c>
       <c r="F74" s="0">
-        <v>0.0082003868667314111</v>
+        <v>2.3228988495495964</v>
       </c>
     </row>
     <row r="75">
@@ -7203,19 +7225,19 @@
         <v>154</v>
       </c>
       <c r="B75" s="0">
-        <v>0.11604481813434793</v>
+        <v>0.047149425624269152</v>
       </c>
       <c r="C75" s="0">
-        <v>0.047149299039134417</v>
+        <v>1.265280057471156</v>
       </c>
       <c r="D75" s="0">
-        <v>0.13295777790621649</v>
+        <v>0.11604560015153675</v>
       </c>
       <c r="E75" s="0">
-        <v>0.021895480026317294</v>
+        <v>0.13295713616627564</v>
       </c>
       <c r="F75" s="0">
-        <v>1.2652801122742321</v>
+        <v>0.021894807979399127</v>
       </c>
     </row>
     <row r="76">
@@ -7223,19 +7245,19 @@
         <v>155</v>
       </c>
       <c r="B76" s="0">
-        <v>0.067285193903274476</v>
+        <v>0.043418410798064418</v>
       </c>
       <c r="C76" s="0">
-        <v>0.043418357204559568</v>
+        <v>0.015848546897072061</v>
       </c>
       <c r="D76" s="0">
-        <v>0.03976032862882227</v>
+        <v>0.067285673884355357</v>
       </c>
       <c r="E76" s="0">
-        <v>0.019584459715354597</v>
+        <v>0.039759635310862983</v>
       </c>
       <c r="F76" s="0">
-        <v>0.015848424596831095</v>
+        <v>0.019583782569567137</v>
       </c>
     </row>
     <row r="77">
@@ -7243,19 +7265,19 @@
         <v>156</v>
       </c>
       <c r="B77" s="0">
-        <v>0.090125424010133404</v>
+        <v>0.041536505373822023</v>
       </c>
       <c r="C77" s="0">
-        <v>0.041536394967849034</v>
+        <v>0.0024260604448318327</v>
       </c>
       <c r="D77" s="0">
-        <v>0.12623865956987812</v>
+        <v>0.090126541174694458</v>
       </c>
       <c r="E77" s="0">
-        <v>1.4917902566900323</v>
+        <v>0.12623802063749701</v>
       </c>
       <c r="F77" s="0">
-        <v>0.002426141979152772</v>
+        <v>1.491789975838735</v>
       </c>
     </row>
     <row r="78">
@@ -7263,19 +7285,19 @@
         <v>157</v>
       </c>
       <c r="B78" s="0">
-        <v>0.09564007598560631</v>
+        <v>0.044938285748330212</v>
       </c>
       <c r="C78" s="0">
-        <v>0.044938220654948666</v>
+        <v>0.0027564481146509371</v>
       </c>
       <c r="D78" s="0">
-        <v>0.044798623839680987</v>
+        <v>0.095640728840214642</v>
       </c>
       <c r="E78" s="0">
-        <v>0.02586414620914353</v>
+        <v>0.044797909302830966</v>
       </c>
       <c r="F78" s="0">
-        <v>0.002756339297960278</v>
+        <v>0.025863538596190578</v>
       </c>
     </row>
     <row r="79">
@@ -7283,19 +7305,19 @@
         <v>158</v>
       </c>
       <c r="B79" s="0">
-        <v>0.10069853711908247</v>
+        <v>0.042937917741877864</v>
       </c>
       <c r="C79" s="0">
-        <v>0.042937661655922603</v>
+        <v>2.5080356832587105</v>
       </c>
       <c r="D79" s="0">
-        <v>0.30424638915545022</v>
+        <v>0.10069907305824768</v>
       </c>
       <c r="E79" s="0">
-        <v>0.0068298514419807051</v>
+        <v>0.30424593860725624</v>
       </c>
       <c r="F79" s="0">
-        <v>2.5080360562801665</v>
+        <v>0.0068290755304356741</v>
       </c>
     </row>
     <row r="80">
@@ -7303,19 +7325,19 @@
         <v>159</v>
       </c>
       <c r="B80" s="0">
-        <v>0.087225633637330005</v>
+        <v>0.047608178127277127</v>
       </c>
       <c r="C80" s="0">
-        <v>0.047608111167531372</v>
+        <v>0.0063740374844283888</v>
       </c>
       <c r="D80" s="0">
-        <v>0.041265450821730783</v>
+        <v>0.087227048255729939</v>
       </c>
       <c r="E80" s="0">
-        <v>3.0921484818799225</v>
+        <v>0.041264581790996582</v>
       </c>
       <c r="F80" s="0">
-        <v>0.0063739673379557236</v>
+        <v>3.0921485098463721</v>
       </c>
     </row>
     <row r="81">
@@ -7323,19 +7345,19 @@
         <v>160</v>
       </c>
       <c r="B81" s="0">
-        <v>1.1702432211442968</v>
+        <v>0.043292477894773869</v>
       </c>
       <c r="C81" s="0">
-        <v>0.043292207105628713</v>
+        <v>0.0078339788616753302</v>
       </c>
       <c r="D81" s="0">
-        <v>0.041037195233352648</v>
+        <v>1.1702512076426008</v>
       </c>
       <c r="E81" s="0">
-        <v>0.03189610268629367</v>
+        <v>0.04103663910474567</v>
       </c>
       <c r="F81" s="0">
-        <v>0.007834325403729088</v>
+        <v>0.031899342334916245</v>
       </c>
     </row>
     <row r="82">
@@ -7343,19 +7365,19 @@
         <v>161</v>
       </c>
       <c r="B82" s="0">
-        <v>0.061821596858628529</v>
+        <v>0.043990881481029073</v>
       </c>
       <c r="C82" s="0">
-        <v>0.043990826808235302</v>
+        <v>0.007971975526944659</v>
       </c>
       <c r="D82" s="0">
-        <v>0.038252378416439151</v>
+        <v>0.061822040267729979</v>
       </c>
       <c r="E82" s="0">
-        <v>0.019570909899271832</v>
+        <v>0.038251674624465597</v>
       </c>
       <c r="F82" s="0">
-        <v>0.0079718474201984375</v>
+        <v>0.019570201785709722</v>
       </c>
     </row>
     <row r="83">
@@ -7363,19 +7385,19 @@
         <v>162</v>
       </c>
       <c r="B83" s="0">
-        <v>0.086570703917936004</v>
+        <v>0.05073719771007585</v>
       </c>
       <c r="C83" s="0">
-        <v>0.050737139457392853</v>
+        <v>0.0034857391709556028</v>
       </c>
       <c r="D83" s="0">
-        <v>0.053660731177461583</v>
+        <v>0.08657134843467533</v>
       </c>
       <c r="E83" s="0">
-        <v>0.05076886758350644</v>
+        <v>0.053659934319783789</v>
       </c>
       <c r="F83" s="0">
-        <v>0.0034856122276299417</v>
+        <v>0.050768106816942084</v>
       </c>
     </row>
     <row r="84">
@@ -7383,19 +7405,19 @@
         <v>163</v>
       </c>
       <c r="B84" s="0">
-        <v>0.097313784581165158</v>
+        <v>0.045902598644746225</v>
       </c>
       <c r="C84" s="0">
-        <v>0.045902529962794696</v>
+        <v>0.0025621333712947583</v>
       </c>
       <c r="D84" s="0">
-        <v>0.043403572072165372</v>
+        <v>0.097314390118425784</v>
       </c>
       <c r="E84" s="0">
-        <v>0.025326332200421395</v>
+        <v>0.04340284047655376</v>
       </c>
       <c r="F84" s="0">
-        <v>0.0025620211190931297</v>
+        <v>0.025325716320561936</v>
       </c>
     </row>
     <row r="85">
@@ -7403,19 +7425,19 @@
         <v>164</v>
       </c>
       <c r="B85" s="0">
-        <v>0.092255139955141147</v>
+        <v>0.044781989395801497</v>
       </c>
       <c r="C85" s="0">
-        <v>0.044781820309335481</v>
+        <v>1.2577500379216602</v>
       </c>
       <c r="D85" s="0">
-        <v>0.16970028781703825</v>
+        <v>0.092255638057667719</v>
       </c>
       <c r="E85" s="0">
-        <v>0.017303502297080366</v>
+        <v>0.16969968501903321</v>
       </c>
       <c r="F85" s="0">
-        <v>1.2577501612517701</v>
+        <v>0.017302777667651335</v>
       </c>
     </row>
     <row r="86">
@@ -7423,19 +7445,19 @@
         <v>165</v>
       </c>
       <c r="B86" s="0">
-        <v>0.078060577993129543</v>
+        <v>0.047237264476766239</v>
       </c>
       <c r="C86" s="0">
-        <v>0.047237270256856451</v>
+        <v>0.015964070790751288</v>
       </c>
       <c r="D86" s="0">
-        <v>0.042016458858067048</v>
+        <v>0.078061947804474508</v>
       </c>
       <c r="E86" s="0">
-        <v>3.0927573253423537</v>
+        <v>0.042015626484397363</v>
       </c>
       <c r="F86" s="0">
-        <v>0.015963981941844917</v>
+        <v>3.0927573462951976</v>
       </c>
     </row>
     <row r="87">
@@ -7443,19 +7465,19 @@
         <v>166</v>
       </c>
       <c r="B87" s="0">
-        <v>1.0348909051419632</v>
+        <v>0.042853790826033876</v>
       </c>
       <c r="C87" s="0">
-        <v>0.042853602812995897</v>
+        <v>0.0069181082783098249</v>
       </c>
       <c r="D87" s="0">
-        <v>0.044818682940884265</v>
+        <v>1.0348980216624077</v>
       </c>
       <c r="E87" s="0">
-        <v>0.028027215491216641</v>
+        <v>0.044818140521276799</v>
       </c>
       <c r="F87" s="0">
-        <v>0.0069183871327619046</v>
+        <v>0.028029991579441763</v>
       </c>
     </row>
     <row r="88">
@@ -7463,19 +7485,19 @@
         <v>167</v>
       </c>
       <c r="B88" s="0">
-        <v>0.050021419315698951</v>
+        <v>0.084522162576357501</v>
       </c>
       <c r="C88" s="0">
-        <v>0.084522126898130171</v>
+        <v>0.0050820455794932081</v>
       </c>
       <c r="D88" s="0">
-        <v>0.058901421620564408</v>
+        <v>0.050021892703333633</v>
       </c>
       <c r="E88" s="0">
-        <v>0.046930372492058024</v>
+        <v>0.058900060639319921</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0050817244555328494</v>
+        <v>0.04692878432236592</v>
       </c>
     </row>
     <row r="89">
@@ -7483,19 +7505,19 @@
         <v>168</v>
       </c>
       <c r="B89" s="0">
-        <v>0.011067204178288539</v>
+        <v>0.0029788106299861129</v>
       </c>
       <c r="C89" s="0">
-        <v>0.0029787854940463978</v>
+        <v>0</v>
       </c>
       <c r="D89" s="0">
-        <v>0.0026714589173331155</v>
+        <v>0.011067249374684559</v>
       </c>
       <c r="E89" s="0">
-        <v>0.0047043104339666558</v>
+        <v>0.0026714005728333047</v>
       </c>
       <c r="F89" s="0">
-        <v>0</v>
+        <v>0.0047042857453708266</v>
       </c>
     </row>
     <row r="90">
@@ -7503,19 +7525,19 @@
         <v>169</v>
       </c>
       <c r="B90" s="0">
-        <v>0.075102703583200495</v>
+        <v>0.0028202588529198389</v>
       </c>
       <c r="C90" s="0">
-        <v>0.0028202448601010659</v>
+        <v>0</v>
       </c>
       <c r="D90" s="0">
-        <v>0.0015558923596606811</v>
+        <v>0.075103216087843067</v>
       </c>
       <c r="E90" s="0">
-        <v>0.0037742814490101754</v>
+        <v>0.0015558425974885328</v>
       </c>
       <c r="F90" s="0">
-        <v>0</v>
+        <v>0.0037744889903081275</v>
       </c>
     </row>
   </sheetData>
@@ -7528,31 +7550,31 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="true"/>
-    <col min="2" max="2" width="14.7109375" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -7560,19 +7582,19 @@
         <v>250</v>
       </c>
       <c r="B2" s="0">
-        <v>0.10787322100198998</v>
+        <v>0.35376762196218203</v>
       </c>
       <c r="C2" s="0">
-        <v>0.35376835961152875</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>0.42631845232809818</v>
+        <v>0.1078728452811332</v>
       </c>
       <c r="E2" s="0">
-        <v>0.17989277582248933</v>
+        <v>0.42631829060281906</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>0.1798926974182769</v>
       </c>
     </row>
     <row r="3">
@@ -7580,19 +7602,19 @@
         <v>255</v>
       </c>
       <c r="B3" s="0">
-        <v>0.17932184297225357</v>
+        <v>0.34031862450303535</v>
       </c>
       <c r="C3" s="0">
-        <v>0.34031964466006093</v>
+        <v>0.0086325650503279484</v>
       </c>
       <c r="D3" s="0">
-        <v>0.22715233039389168</v>
+        <v>0.17932133104895284</v>
       </c>
       <c r="E3" s="0">
-        <v>0.24273468880276208</v>
+        <v>0.22715217692033079</v>
       </c>
       <c r="F3" s="0">
-        <v>0.0086325709202982551</v>
+        <v>0.24273462161178838</v>
       </c>
     </row>
     <row r="4">
@@ -7600,19 +7622,19 @@
         <v>260</v>
       </c>
       <c r="B4" s="0">
-        <v>0.27485329043019247</v>
+        <v>0.30567757418633662</v>
       </c>
       <c r="C4" s="0">
-        <v>0.30567822104627218</v>
+        <v>0.032344394653990131</v>
       </c>
       <c r="D4" s="0">
-        <v>0.10139935746998513</v>
+        <v>0.27485263841243202</v>
       </c>
       <c r="E4" s="0">
-        <v>0.30708773000354228</v>
+        <v>0.10139931806829687</v>
       </c>
       <c r="F4" s="0">
-        <v>0.032344415648043426</v>
+        <v>0.30708768977930417</v>
       </c>
     </row>
     <row r="5">
@@ -7620,19 +7642,19 @@
         <v>265</v>
       </c>
       <c r="B5" s="0">
-        <v>0.39374222256996389</v>
+        <v>0.2682971112078843</v>
       </c>
       <c r="C5" s="0">
-        <v>0.26829733108204956</v>
+        <v>0.065385194186390161</v>
       </c>
       <c r="D5" s="0">
-        <v>0.053083750760502903</v>
+        <v>0.39374145741677108</v>
       </c>
       <c r="E5" s="0">
-        <v>0.3624086543403916</v>
+        <v>0.053083881653692488</v>
       </c>
       <c r="F5" s="0">
-        <v>0.065385215091541313</v>
+        <v>0.36240865113125109</v>
       </c>
     </row>
     <row r="6">
@@ -7640,19 +7662,19 @@
         <v>270</v>
       </c>
       <c r="B6" s="0">
-        <v>0.49588201173148688</v>
+        <v>0.23797787793565328</v>
       </c>
       <c r="C6" s="0">
-        <v>0.23797779460401958</v>
+        <v>0.11295327131726167</v>
       </c>
       <c r="D6" s="0">
-        <v>0.051074757641923443</v>
+        <v>0.49588206949644698</v>
       </c>
       <c r="E6" s="0">
-        <v>0.39607330937263724</v>
+        <v>0.051075074117904566</v>
       </c>
       <c r="F6" s="0">
-        <v>0.11295328500220733</v>
+        <v>0.39607333475262008</v>
       </c>
     </row>
     <row r="7">
@@ -7660,19 +7682,19 @@
         <v>275</v>
       </c>
       <c r="B7" s="0">
-        <v>0.51151549165870847</v>
+        <v>0.20932866139714873</v>
       </c>
       <c r="C7" s="0">
-        <v>0.20932843416030655</v>
+        <v>0.17998342326177258</v>
       </c>
       <c r="D7" s="0">
-        <v>0.069546335718425251</v>
+        <v>0.51151673486568017</v>
       </c>
       <c r="E7" s="0">
-        <v>0.4111950966115438</v>
+        <v>0.069546802788090764</v>
       </c>
       <c r="F7" s="0">
-        <v>0.17998342844809539</v>
+        <v>0.41119513773988314</v>
       </c>
     </row>
     <row r="8">
@@ -7680,19 +7702,19 @@
         <v>280</v>
       </c>
       <c r="B8" s="0">
-        <v>0.41828933783560229</v>
+        <v>0.18841187312090918</v>
       </c>
       <c r="C8" s="0">
-        <v>0.18841192588212954</v>
+        <v>0.26321710828056061</v>
       </c>
       <c r="D8" s="0">
-        <v>0.10202842759529576</v>
+        <v>0.41829299708211837</v>
       </c>
       <c r="E8" s="0">
-        <v>0.39821649644168117</v>
+        <v>0.10202900118466353</v>
       </c>
       <c r="F8" s="0">
-        <v>0.26321710387470876</v>
+        <v>0.39821653061984963</v>
       </c>
     </row>
     <row r="9">
@@ -7700,19 +7722,19 @@
         <v>285</v>
       </c>
       <c r="B9" s="0">
-        <v>0.20196865138505954</v>
+        <v>0.16904295175284778</v>
       </c>
       <c r="C9" s="0">
-        <v>0.16904301298225832</v>
+        <v>0.35231377620038479</v>
       </c>
       <c r="D9" s="0">
-        <v>0.14626960276289172</v>
+        <v>0.20196758440706147</v>
       </c>
       <c r="E9" s="0">
-        <v>0.35078909671404834</v>
+        <v>0.14627016746436342</v>
       </c>
       <c r="F9" s="0">
-        <v>0.35231377254220314</v>
+        <v>0.35078912053128769</v>
       </c>
     </row>
     <row r="10">
@@ -7720,19 +7742,19 @@
         <v>290</v>
       </c>
       <c r="B10" s="0">
-        <v>0.045621554015969346</v>
+        <v>0.15813914845730937</v>
       </c>
       <c r="C10" s="0">
-        <v>0.15813921202019471</v>
+        <v>0.4216345048506478</v>
       </c>
       <c r="D10" s="0">
-        <v>0.19830486457004404</v>
+        <v>0.045621146729618735</v>
       </c>
       <c r="E10" s="0">
-        <v>0.24679502629507144</v>
+        <v>0.19830538595884586</v>
       </c>
       <c r="F10" s="0">
-        <v>0.42163449983343976</v>
+        <v>0.24679501681626437</v>
       </c>
     </row>
     <row r="11">
@@ -7740,19 +7762,19 @@
         <v>295</v>
       </c>
       <c r="B11" s="0">
-        <v>0.0099760210809921694</v>
+        <v>0.14916606466243687</v>
       </c>
       <c r="C11" s="0">
-        <v>0.14916555836239531</v>
+        <v>0.44965173511281648</v>
       </c>
       <c r="D11" s="0">
-        <v>0.24837259710988399</v>
+        <v>0.0099758532934088994</v>
       </c>
       <c r="E11" s="0">
-        <v>0.1118003446821703</v>
+        <v>0.24837303745080161</v>
       </c>
       <c r="F11" s="0">
-        <v>0.44965173241557971</v>
+        <v>0.11180032186749447</v>
       </c>
     </row>
     <row r="12">
@@ -7760,19 +7782,19 @@
         <v>300</v>
       </c>
       <c r="B12" s="0">
-        <v>0.0058537342052801724</v>
+        <v>0.14145789934259279</v>
       </c>
       <c r="C12" s="0">
-        <v>0.14145699517724691</v>
+        <v>0.42445103758926744</v>
       </c>
       <c r="D12" s="0">
-        <v>0.29129180046192998</v>
+        <v>0.0058533207957240756</v>
       </c>
       <c r="E12" s="0">
-        <v>0.042971572734842138</v>
+        <v>0.29129215730826719</v>
       </c>
       <c r="F12" s="0">
-        <v>0.42445103275648699</v>
+        <v>0.042971559073723048</v>
       </c>
     </row>
     <row r="13">
@@ -7780,19 +7802,19 @@
         <v>305</v>
       </c>
       <c r="B13" s="0">
-        <v>0.0040803243957458889</v>
+        <v>0.13781296874397464</v>
       </c>
       <c r="C13" s="0">
-        <v>0.13781185968674442</v>
+        <v>0.3473969328977875</v>
       </c>
       <c r="D13" s="0">
-        <v>0.3216352754182954</v>
+        <v>0.0040789085146778863</v>
       </c>
       <c r="E13" s="0">
-        <v>0.014486428568905686</v>
+        <v>0.32163549906930089</v>
       </c>
       <c r="F13" s="0">
-        <v>0.34739692319874493</v>
+        <v>0.014486419155505368</v>
       </c>
     </row>
     <row r="14">
@@ -7800,19 +7822,19 @@
         <v>310</v>
       </c>
       <c r="B14" s="0">
-        <v>0.0051534403223415471</v>
+        <v>0.13632292758020015</v>
       </c>
       <c r="C14" s="0">
-        <v>0.13632086257307777</v>
+        <v>0.23364971690372316</v>
       </c>
       <c r="D14" s="0">
-        <v>0.33281405600758424</v>
+        <v>0.0051307069350660026</v>
       </c>
       <c r="E14" s="0">
-        <v>0.004506640646714982</v>
+        <v>0.33281404632211231</v>
       </c>
       <c r="F14" s="0">
-        <v>0.23364971759843339</v>
+        <v>0.004506673117781166</v>
       </c>
     </row>
     <row r="15">
@@ -7820,19 +7842,19 @@
         <v>315</v>
       </c>
       <c r="B15" s="0">
-        <v>0.0044117857705328039</v>
+        <v>0.13795524647127549</v>
       </c>
       <c r="C15" s="0">
-        <v>0.13795164362346571</v>
+        <v>0.12806712243632459</v>
       </c>
       <c r="D15" s="0">
-        <v>0.32031617489799724</v>
+        <v>0.0043531088150173319</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0017712217508633189</v>
+        <v>0.32031588148275869</v>
       </c>
       <c r="F15" s="0">
-        <v>0.12806714750566706</v>
+        <v>0.0017713517390068434</v>
       </c>
     </row>
     <row r="16">
@@ -7840,19 +7862,19 @@
         <v>320</v>
       </c>
       <c r="B16" s="0">
-        <v>0.0069005387098740349</v>
+        <v>0.14202066876333541</v>
       </c>
       <c r="C16" s="0">
-        <v>0.14201506348294821</v>
+        <v>0.059082944247886814</v>
       </c>
       <c r="D16" s="0">
-        <v>0.28611709782238853</v>
+        <v>0.006759337915928915</v>
       </c>
       <c r="E16" s="0">
-        <v>0.0012375732611067138</v>
+        <v>0.2861165291403624</v>
       </c>
       <c r="F16" s="0">
-        <v>0.05908299908878633</v>
+        <v>0.0012378550553930601</v>
       </c>
     </row>
     <row r="17">
@@ -7860,19 +7882,19 @@
         <v>325</v>
       </c>
       <c r="B17" s="0">
-        <v>0</v>
+        <v>0.15012327574574527</v>
       </c>
       <c r="C17" s="0">
-        <v>0.15012250987834166</v>
+        <v>0.024947211480200022</v>
       </c>
       <c r="D17" s="0">
-        <v>0.24017613223751924</v>
+        <v>0</v>
       </c>
       <c r="E17" s="0">
-        <v>0.0010152267317375477</v>
+        <v>0.24017588944609397</v>
       </c>
       <c r="F17" s="0">
-        <v>0.024947208422109513</v>
+        <v>0.0010151804776474477</v>
       </c>
     </row>
     <row r="18">
@@ -7880,19 +7902,19 @@
         <v>330</v>
       </c>
       <c r="B18" s="0">
-        <v>0</v>
+        <v>0.15945815630703608</v>
       </c>
       <c r="C18" s="0">
-        <v>0.15945760931972974</v>
+        <v>0.010615012013610221</v>
       </c>
       <c r="D18" s="0">
-        <v>0.18975805149721942</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>0.00085598112949947073</v>
+        <v>0.18975777616851316</v>
       </c>
       <c r="F18" s="0">
-        <v>0.010615015605891915</v>
+        <v>0.00085594747094248848</v>
       </c>
     </row>
     <row r="19">
@@ -7900,19 +7922,19 @@
         <v>335</v>
       </c>
       <c r="B19" s="0">
-        <v>0</v>
+        <v>0.16559572480727183</v>
       </c>
       <c r="C19" s="0">
-        <v>0.16559544049728706</v>
+        <v>0.0042035065455338638</v>
       </c>
       <c r="D19" s="0">
-        <v>0.14238279058012804</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>0.0005924196326158724</v>
+        <v>0.14238251125940205</v>
       </c>
       <c r="F19" s="0">
-        <v>0.0042035151155822553</v>
+        <v>0.00059239034694071242</v>
       </c>
     </row>
     <row r="20">
@@ -7920,19 +7942,19 @@
         <v>340</v>
       </c>
       <c r="B20" s="0">
-        <v>0</v>
+        <v>0.16867447411086836</v>
       </c>
       <c r="C20" s="0">
-        <v>0.16867446215374662</v>
+        <v>0.00091850889315793992</v>
       </c>
       <c r="D20" s="0">
-        <v>0.099896894885018309</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>0.00026150765624186572</v>
+        <v>0.099896616345015107</v>
       </c>
       <c r="F20" s="0">
-        <v>0.00091852059220804663</v>
+        <v>0.00026146913680824633</v>
       </c>
     </row>
     <row r="21">
@@ -7940,19 +7962,19 @@
         <v>345</v>
       </c>
       <c r="B21" s="0">
-        <v>0</v>
+        <v>0.16550597266958295</v>
       </c>
       <c r="C21" s="0">
-        <v>0.16550618461621913</v>
+        <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0.063556164066434287</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0">
-        <v>0.00018708648120560755</v>
+        <v>0.063555862603130925</v>
       </c>
       <c r="F21" s="0">
-        <v>0</v>
+        <v>0.00018704004292942789</v>
       </c>
     </row>
     <row r="22">
@@ -7960,16 +7982,16 @@
         <v>350</v>
       </c>
       <c r="B22" s="0">
-        <v>0</v>
+        <v>0.15896258207868244</v>
       </c>
       <c r="C22" s="0">
-        <v>0.15896306495394511</v>
+        <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>0.036662224844489819</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>0</v>
+        <v>0.036661897679826562</v>
       </c>
       <c r="F22" s="0">
         <v>0</v>
@@ -7980,16 +8002,16 @@
         <v>355</v>
       </c>
       <c r="B23" s="0">
-        <v>0</v>
+        <v>0.15189939257134855</v>
       </c>
       <c r="C23" s="0">
-        <v>0.15190010716130908</v>
+        <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>0.019143654961226296</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0">
-        <v>0</v>
+        <v>0.019143352804574475</v>
       </c>
       <c r="F23" s="0">
         <v>0</v>
@@ -8000,16 +8022,16 @@
         <v>360</v>
       </c>
       <c r="B24" s="0">
-        <v>0</v>
+        <v>0.14549759191060674</v>
       </c>
       <c r="C24" s="0">
-        <v>0.14549845606150982</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>0.0078712158018317113</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
-        <v>0</v>
+        <v>0.007870940967016838</v>
       </c>
       <c r="F24" s="0">
         <v>0</v>
@@ -8020,16 +8042,16 @@
         <v>365</v>
       </c>
       <c r="B25" s="0">
-        <v>0</v>
+        <v>0.13733595644176891</v>
       </c>
       <c r="C25" s="0">
-        <v>0.13733706358764625</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>0.0018189529182098094</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>0</v>
+        <v>0.0018187429588395108</v>
       </c>
       <c r="F25" s="0">
         <v>0</v>
@@ -8040,10 +8062,10 @@
         <v>370</v>
       </c>
       <c r="B26" s="0">
-        <v>0</v>
+        <v>0.12516937059613112</v>
       </c>
       <c r="C26" s="0">
-        <v>0.12517066341396752</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0">
         <v>0</v>
@@ -8060,10 +8082,10 @@
         <v>375</v>
       </c>
       <c r="B27" s="0">
-        <v>0</v>
+        <v>0.11279975934235977</v>
       </c>
       <c r="C27" s="0">
-        <v>0.11280107624462878</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0">
         <v>0</v>
@@ -8080,10 +8102,10 @@
         <v>380</v>
       </c>
       <c r="B28" s="0">
-        <v>0</v>
+        <v>0.098267098588471685</v>
       </c>
       <c r="C28" s="0">
-        <v>0.09826839747868249</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
         <v>0</v>
@@ -8100,10 +8122,10 @@
         <v>385</v>
       </c>
       <c r="B29" s="0">
-        <v>0</v>
+        <v>0.086818368774784022</v>
       </c>
       <c r="C29" s="0">
-        <v>0.086819546360835775</v>
+        <v>0</v>
       </c>
       <c r="D29" s="0">
         <v>0</v>
@@ -8120,10 +8142,10 @@
         <v>390</v>
       </c>
       <c r="B30" s="0">
-        <v>0</v>
+        <v>0.073040175043509348</v>
       </c>
       <c r="C30" s="0">
-        <v>0.073041249987827406</v>
+        <v>0</v>
       </c>
       <c r="D30" s="0">
         <v>0</v>
@@ -8140,10 +8162,10 @@
         <v>395</v>
       </c>
       <c r="B31" s="0">
-        <v>0</v>
+        <v>0.061337852097604062</v>
       </c>
       <c r="C31" s="0">
-        <v>0.061338753050552308</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0">
         <v>0</v>
@@ -8160,10 +8182,10 @@
         <v>400</v>
       </c>
       <c r="B32" s="0">
-        <v>0</v>
+        <v>0.053393959615956013</v>
       </c>
       <c r="C32" s="0">
-        <v>0.053394782519766156</v>
+        <v>0</v>
       </c>
       <c r="D32" s="0">
         <v>0</v>
@@ -8180,10 +8202,10 @@
         <v>405</v>
       </c>
       <c r="B33" s="0">
-        <v>0</v>
+        <v>0.047018371112056527</v>
       </c>
       <c r="C33" s="0">
-        <v>0.047019096840707098</v>
+        <v>0</v>
       </c>
       <c r="D33" s="0">
         <v>0</v>
@@ -8200,10 +8222,10 @@
         <v>410</v>
       </c>
       <c r="B34" s="0">
-        <v>0</v>
+        <v>0.039438010575529633</v>
       </c>
       <c r="C34" s="0">
-        <v>0.039438643192413775</v>
+        <v>0</v>
       </c>
       <c r="D34" s="0">
         <v>0</v>
@@ -8220,10 +8242,10 @@
         <v>415</v>
       </c>
       <c r="B35" s="0">
-        <v>0</v>
+        <v>0.03467858875277411</v>
       </c>
       <c r="C35" s="0">
-        <v>0.03467916912472524</v>
+        <v>0</v>
       </c>
       <c r="D35" s="0">
         <v>0</v>
@@ -8240,10 +8262,10 @@
         <v>420</v>
       </c>
       <c r="B36" s="0">
-        <v>0</v>
+        <v>0.0298449410503423</v>
       </c>
       <c r="C36" s="0">
-        <v>0.029845471497698811</v>
+        <v>0</v>
       </c>
       <c r="D36" s="0">
         <v>0</v>
@@ -8260,10 +8282,10 @@
         <v>425</v>
       </c>
       <c r="B37" s="0">
-        <v>0</v>
+        <v>0.025393451823130131</v>
       </c>
       <c r="C37" s="0">
-        <v>0.025393941759195581</v>
+        <v>0</v>
       </c>
       <c r="D37" s="0">
         <v>0</v>
@@ -8280,10 +8302,10 @@
         <v>430</v>
       </c>
       <c r="B38" s="0">
-        <v>0</v>
+        <v>0.021642343505952014</v>
       </c>
       <c r="C38" s="0">
-        <v>0.021642786658472267</v>
+        <v>0</v>
       </c>
       <c r="D38" s="0">
         <v>0</v>
@@ -8300,10 +8322,10 @@
         <v>435</v>
       </c>
       <c r="B39" s="0">
-        <v>0</v>
+        <v>0.01836550946240097</v>
       </c>
       <c r="C39" s="0">
-        <v>0.018365918444750003</v>
+        <v>0</v>
       </c>
       <c r="D39" s="0">
         <v>0</v>
@@ -8320,10 +8342,10 @@
         <v>440</v>
       </c>
       <c r="B40" s="0">
-        <v>0</v>
+        <v>0.016523403996286986</v>
       </c>
       <c r="C40" s="0">
-        <v>0.016523773615636731</v>
+        <v>0</v>
       </c>
       <c r="D40" s="0">
         <v>0</v>
@@ -8340,10 +8362,10 @@
         <v>445</v>
       </c>
       <c r="B41" s="0">
-        <v>0</v>
+        <v>0.01379091761328044</v>
       </c>
       <c r="C41" s="0">
-        <v>0.013791246802470737</v>
+        <v>0</v>
       </c>
       <c r="D41" s="0">
         <v>0</v>
@@ -8360,10 +8382,10 @@
         <v>450</v>
       </c>
       <c r="B42" s="0">
-        <v>0</v>
+        <v>0.011300732507467205</v>
       </c>
       <c r="C42" s="0">
-        <v>0.011300996821322325</v>
+        <v>0</v>
       </c>
       <c r="D42" s="0">
         <v>0</v>
@@ -8385,8 +8407,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" customWidth="true"/>
-    <col min="2" max="2" width="15.7109375" customWidth="true"/>
-    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
     <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="15.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
@@ -8394,22 +8416,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
@@ -8417,19 +8439,19 @@
         <v>301.47300000000001</v>
       </c>
       <c r="B2" s="0">
-        <v>0.45469508889374594</v>
+        <v>0.015394706445289535</v>
       </c>
       <c r="C2" s="0">
-        <v>0.015396410954838203</v>
+        <v>0</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0053604739583629707</v>
+        <v>0.45469695037629232</v>
       </c>
       <c r="E2" s="0">
-        <v>0.0090363821502696846</v>
+        <v>0.00535994082593386</v>
       </c>
       <c r="F2" s="0">
-        <v>0</v>
+        <v>0.0090363764011170741</v>
       </c>
     </row>
     <row r="3">
@@ -8437,19 +8459,19 @@
         <v>304.70800000000003</v>
       </c>
       <c r="B3" s="0">
-        <v>0.43645853599449341</v>
+        <v>0.016627452574747507</v>
       </c>
       <c r="C3" s="0">
-        <v>0.016629064450998699</v>
+        <v>0</v>
       </c>
       <c r="D3" s="0">
-        <v>0.0025262393142864129</v>
+        <v>0.43646029406251347</v>
       </c>
       <c r="E3" s="0">
-        <v>0.01439714057464306</v>
+        <v>0.0025258102547414886</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>0.014397139281160626</v>
       </c>
     </row>
     <row r="4">
@@ -8457,19 +8479,19 @@
         <v>307.94499999999999</v>
       </c>
       <c r="B4" s="0">
-        <v>0.40583728792793888</v>
+        <v>0.020061445290433782</v>
       </c>
       <c r="C4" s="0">
-        <v>0.020062326139725847</v>
+        <v>0.0002339462421261673</v>
       </c>
       <c r="D4" s="0">
-        <v>0.011233161264929589</v>
+        <v>0.40583780155881877</v>
       </c>
       <c r="E4" s="0">
-        <v>0.023949950837154916</v>
+        <v>0.011232687485458373</v>
       </c>
       <c r="F4" s="0">
-        <v>0.00023395229681400713</v>
+        <v>0.023949941207599579</v>
       </c>
     </row>
     <row r="5">
@@ -8477,19 +8499,19 @@
         <v>311.18400000000003</v>
       </c>
       <c r="B5" s="0">
-        <v>0.35556363375824257</v>
+        <v>0.021857383578407108</v>
       </c>
       <c r="C5" s="0">
-        <v>0.021858075195036693</v>
+        <v>0.00084904706209128179</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0063853767964037215</v>
+        <v>0.35556399465077931</v>
       </c>
       <c r="E5" s="0">
-        <v>0.036630580968153484</v>
+        <v>0.0063849012645403307</v>
       </c>
       <c r="F5" s="0">
-        <v>0.00084904918453544383</v>
+        <v>0.036630576439713389</v>
       </c>
     </row>
     <row r="6">
@@ -8497,19 +8519,19 @@
         <v>314.42500000000001</v>
       </c>
       <c r="B6" s="0">
-        <v>0.31189059540236136</v>
+        <v>0.030526364156508237</v>
       </c>
       <c r="C6" s="0">
-        <v>0.030526506912948111</v>
+        <v>0</v>
       </c>
       <c r="D6" s="0">
-        <v>0.011226926045820498</v>
+        <v>0.31189026620231536</v>
       </c>
       <c r="E6" s="0">
-        <v>0.053920124404246705</v>
+        <v>0.011226527065694679</v>
       </c>
       <c r="F6" s="0">
-        <v>0</v>
+        <v>0.053920110867147444</v>
       </c>
     </row>
     <row r="7">
@@ -8517,19 +8539,19 @@
         <v>317.66800000000001</v>
       </c>
       <c r="B7" s="0">
-        <v>0.26144069340354065</v>
+        <v>0.024089779772666305</v>
       </c>
       <c r="C7" s="0">
-        <v>0.024089627795929873</v>
+        <v>0.00014585818902965885</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0070676672995503937</v>
+        <v>0.26144025392604281</v>
       </c>
       <c r="E7" s="0">
-        <v>0.074050318325146775</v>
+        <v>0.0070674440030472699</v>
       </c>
       <c r="F7" s="0">
-        <v>0.00014584558292291829</v>
+        <v>0.074050310624261609</v>
       </c>
     </row>
     <row r="8">
@@ -8537,19 +8559,19 @@
         <v>320.91300000000001</v>
       </c>
       <c r="B8" s="0">
-        <v>0.22022259935105271</v>
+        <v>0.023311702291593701</v>
       </c>
       <c r="C8" s="0">
-        <v>0.023310990968675706</v>
+        <v>0</v>
       </c>
       <c r="D8" s="0">
-        <v>0.0030204828771749101</v>
+        <v>0.22022160370308158</v>
       </c>
       <c r="E8" s="0">
-        <v>0.098062190526460119</v>
+        <v>0.0030202420036640268</v>
       </c>
       <c r="F8" s="0">
-        <v>0</v>
+        <v>0.098062182878448881</v>
       </c>
     </row>
     <row r="9">
@@ -8557,19 +8579,19 @@
         <v>324.16000000000003</v>
       </c>
       <c r="B9" s="0">
-        <v>0.18562036950558633</v>
+        <v>0.033139617795541088</v>
       </c>
       <c r="C9" s="0">
-        <v>0.033137308879992208</v>
+        <v>0.00040793434980573721</v>
       </c>
       <c r="D9" s="0">
-        <v>0.0030206527858187469</v>
+        <v>0.18561910221353559</v>
       </c>
       <c r="E9" s="0">
-        <v>0.12593984291463561</v>
+        <v>0.0030208697088563905</v>
       </c>
       <c r="F9" s="0">
-        <v>0.00040778727033743311</v>
+        <v>0.12593981647823432</v>
       </c>
     </row>
     <row r="10">
@@ -8577,19 +8599,19 @@
         <v>327.40899999999999</v>
       </c>
       <c r="B10" s="0">
-        <v>0.15345481865465474</v>
+        <v>0.043075399142119851</v>
       </c>
       <c r="C10" s="0">
-        <v>0.043069734393423931</v>
+        <v>0.00017731758679602014</v>
       </c>
       <c r="D10" s="0">
-        <v>0.0096599782860168904</v>
+        <v>0.15345315576620644</v>
       </c>
       <c r="E10" s="0">
-        <v>0.15430361402371567</v>
+        <v>0.0096607653357033505</v>
       </c>
       <c r="F10" s="0">
-        <v>0.00017722381107222529</v>
+        <v>0.15430354329456869</v>
       </c>
     </row>
     <row r="11">
@@ -8597,19 +8619,19 @@
         <v>330.66000000000003</v>
       </c>
       <c r="B11" s="0">
-        <v>0.12358445246126253</v>
+        <v>0.044258236158443716</v>
       </c>
       <c r="C11" s="0">
-        <v>0.04425301280034024</v>
+        <v>0.0009948501474003192</v>
       </c>
       <c r="D11" s="0">
-        <v>0.0083469723102134359</v>
+        <v>0.1235827239130268</v>
       </c>
       <c r="E11" s="0">
-        <v>0.18141016215122738</v>
+        <v>0.0083477724203456765</v>
       </c>
       <c r="F11" s="0">
-        <v>0.00099468393230541918</v>
+        <v>0.18141010988210654</v>
       </c>
     </row>
     <row r="12">
@@ -8617,19 +8639,19 @@
         <v>333.91199999999998</v>
       </c>
       <c r="B12" s="0">
-        <v>0.098401602506718033</v>
+        <v>0.039644712567901641</v>
       </c>
       <c r="C12" s="0">
-        <v>0.03963459835174956</v>
+        <v>0.0023776008438165489</v>
       </c>
       <c r="D12" s="0">
-        <v>0.0047394205914387724</v>
+        <v>0.098399317252964441</v>
       </c>
       <c r="E12" s="0">
-        <v>0.20521198468593152</v>
+        <v>0.0047406296077313736</v>
       </c>
       <c r="F12" s="0">
-        <v>0.002377619842853871</v>
+        <v>0.2052118626833653</v>
       </c>
     </row>
     <row r="13">
@@ -8637,19 +8659,19 @@
         <v>337.16699999999997</v>
       </c>
       <c r="B13" s="0">
-        <v>0.076967267308833062</v>
+        <v>0.03621851534552014</v>
       </c>
       <c r="C13" s="0">
-        <v>0.036210554181189104</v>
+        <v>0.0032289080181538239</v>
       </c>
       <c r="D13" s="0">
-        <v>0.003318298111527505</v>
+        <v>0.07696512277830822</v>
       </c>
       <c r="E13" s="0">
-        <v>0.22474473042230161</v>
+        <v>0.0033191684403650226</v>
       </c>
       <c r="F13" s="0">
-        <v>0.0032289055489714219</v>
+        <v>0.22474465450571662</v>
       </c>
     </row>
     <row r="14">
@@ -8657,19 +8679,19 @@
         <v>340.423</v>
       </c>
       <c r="B14" s="0">
-        <v>0.059541631570739516</v>
+        <v>0.05866453942479382</v>
       </c>
       <c r="C14" s="0">
-        <v>0.058657879041693076</v>
+        <v>0.0033245571380091259</v>
       </c>
       <c r="D14" s="0">
-        <v>0.0080794970837950938</v>
+        <v>0.059539575911013227</v>
       </c>
       <c r="E14" s="0">
-        <v>0.23983867060282618</v>
+        <v>0.0080800151098748378</v>
       </c>
       <c r="F14" s="0">
-        <v>0.0033245812936477616</v>
+        <v>0.23983862158127603</v>
       </c>
     </row>
     <row r="15">
@@ -8677,19 +8699,19 @@
         <v>343.68200000000002</v>
       </c>
       <c r="B15" s="0">
-        <v>0.046315885115497418</v>
+        <v>0.048298278016361315</v>
       </c>
       <c r="C15" s="0">
-        <v>0.048293639144419427</v>
+        <v>0.0045247522555755511</v>
       </c>
       <c r="D15" s="0">
-        <v>0.010482064034091481</v>
+        <v>0.046313974616922784</v>
       </c>
       <c r="E15" s="0">
-        <v>0.2506599074912883</v>
+        <v>0.01048235759456</v>
       </c>
       <c r="F15" s="0">
-        <v>0.0045247542163831776</v>
+        <v>0.25065989987185894</v>
       </c>
     </row>
     <row r="16">
@@ -8697,19 +8719,19 @@
         <v>346.94200000000001</v>
       </c>
       <c r="B16" s="0">
-        <v>0.033536325572576103</v>
+        <v>0.045013414226613778</v>
       </c>
       <c r="C16" s="0">
-        <v>0.045009101559672894</v>
+        <v>0.0055945875272466498</v>
       </c>
       <c r="D16" s="0">
-        <v>0.0100582229134992</v>
+        <v>0.033534344248856658</v>
       </c>
       <c r="E16" s="0">
-        <v>0.25760743858676671</v>
+        <v>0.010058325143976015</v>
       </c>
       <c r="F16" s="0">
-        <v>0.0055945926568131497</v>
+        <v>0.25760744334240715</v>
       </c>
     </row>
     <row r="17">
@@ -8717,19 +8739,19 @@
         <v>350.20400000000001</v>
       </c>
       <c r="B17" s="0">
-        <v>0.025562094746305577</v>
+        <v>0.066372135134754526</v>
       </c>
       <c r="C17" s="0">
-        <v>0.066370058762311848</v>
+        <v>0.0075336092392773646</v>
       </c>
       <c r="D17" s="0">
-        <v>0.017666799570397469</v>
+        <v>0.025560459291215715</v>
       </c>
       <c r="E17" s="0">
-        <v>0.26086013089151278</v>
+        <v>0.01766671932110855</v>
       </c>
       <c r="F17" s="0">
-        <v>0.0075335943399553662</v>
+        <v>0.26086017107202836</v>
       </c>
     </row>
     <row r="18">
@@ -8737,19 +8759,19 @@
         <v>353.46699999999999</v>
       </c>
       <c r="B18" s="0">
-        <v>0.018174256949641927</v>
+        <v>0.073302062988046354</v>
       </c>
       <c r="C18" s="0">
-        <v>0.07330012238404969</v>
+        <v>0.011113953825809686</v>
       </c>
       <c r="D18" s="0">
-        <v>0.020956627279831754</v>
+        <v>0.018172653741522379</v>
       </c>
       <c r="E18" s="0">
-        <v>0.25906912541740851</v>
+        <v>0.020956551598625674</v>
       </c>
       <c r="F18" s="0">
-        <v>0.011113938429545684</v>
+        <v>0.25906916736158564</v>
       </c>
     </row>
     <row r="19">
@@ -8757,19 +8779,19 @@
         <v>356.733</v>
       </c>
       <c r="B19" s="0">
-        <v>0.012121883859312463</v>
+        <v>0.071287945885785159</v>
       </c>
       <c r="C19" s="0">
-        <v>0.07128561278124039</v>
+        <v>0.01606223031076625</v>
       </c>
       <c r="D19" s="0">
-        <v>0.031464661924073587</v>
+        <v>0.012120211733488206</v>
       </c>
       <c r="E19" s="0">
-        <v>0.25264886248170371</v>
+        <v>0.031464550683218753</v>
       </c>
       <c r="F19" s="0">
-        <v>0.016062218358935562</v>
+        <v>0.25264889963027037</v>
       </c>
     </row>
     <row r="20">
@@ -8777,19 +8799,19 @@
         <v>360</v>
       </c>
       <c r="B20" s="0">
-        <v>0.0084665446433513005</v>
+        <v>0.070100480567201973</v>
       </c>
       <c r="C20" s="0">
-        <v>0.070098271411610569</v>
+        <v>0.022790986121832096</v>
       </c>
       <c r="D20" s="0">
-        <v>0.050420517584998659</v>
+        <v>0.0084649436630020031</v>
       </c>
       <c r="E20" s="0">
-        <v>0.2433683552243695</v>
+        <v>0.050420411833135351</v>
       </c>
       <c r="F20" s="0">
-        <v>0.022790973669215651</v>
+        <v>0.24336839325200868</v>
       </c>
     </row>
     <row r="21">
@@ -8797,19 +8819,19 @@
         <v>363.26900000000001</v>
       </c>
       <c r="B21" s="0">
-        <v>0.005101951726301711</v>
+        <v>0.068831917039158461</v>
       </c>
       <c r="C21" s="0">
-        <v>0.06882928192804845</v>
+        <v>0.032064328329014867</v>
       </c>
       <c r="D21" s="0">
-        <v>0.071480323939854068</v>
+        <v>0.0051001924137134263</v>
       </c>
       <c r="E21" s="0">
-        <v>0.23136923006287186</v>
+        <v>0.071480166561518968</v>
       </c>
       <c r="F21" s="0">
-        <v>0.032064317358178239</v>
+        <v>0.23136926361593455</v>
       </c>
     </row>
     <row r="22">
@@ -8817,19 +8839,19 @@
         <v>366.53899999999999</v>
       </c>
       <c r="B22" s="0">
-        <v>0.0042432205900465592</v>
+        <v>0.064402473267410679</v>
       </c>
       <c r="C22" s="0">
-        <v>0.064399542950354674</v>
+        <v>0.04473113899285653</v>
       </c>
       <c r="D22" s="0">
-        <v>0.094565304858260091</v>
+        <v>0.0042414636683760611</v>
       </c>
       <c r="E22" s="0">
-        <v>0.21860958500690497</v>
+        <v>0.094565127427880258</v>
       </c>
       <c r="F22" s="0">
-        <v>0.044731130267777884</v>
+        <v>0.21860961323033579</v>
       </c>
     </row>
     <row r="23">
@@ -8837,19 +8859,19 @@
         <v>369.81200000000001</v>
       </c>
       <c r="B23" s="0">
-        <v>0.0031707091179134783</v>
+        <v>0.061114172750879582</v>
       </c>
       <c r="C23" s="0">
-        <v>0.061110448901550436</v>
+        <v>0.060121940165272864</v>
       </c>
       <c r="D23" s="0">
-        <v>0.12777918430656302</v>
+        <v>0.0031686109588538462</v>
       </c>
       <c r="E23" s="0">
-        <v>0.20529045122969295</v>
+        <v>0.12777895482858767</v>
       </c>
       <c r="F23" s="0">
-        <v>0.060121933503692909</v>
+        <v>0.20529047235097817</v>
       </c>
     </row>
     <row r="24">
@@ -8857,19 +8879,19 @@
         <v>373.08600000000001</v>
       </c>
       <c r="B24" s="0">
-        <v>0.00030592152476177447</v>
+        <v>0.042626069932126837</v>
       </c>
       <c r="C24" s="0">
-        <v>0.042622345867361362</v>
+        <v>0.080755225271839995</v>
       </c>
       <c r="D24" s="0">
-        <v>0.15667598149623269</v>
+        <v>0.00030388998734797254</v>
       </c>
       <c r="E24" s="0">
-        <v>0.19522291097644104</v>
+        <v>0.15667576858186935</v>
       </c>
       <c r="F24" s="0">
-        <v>0.080755215822186338</v>
+        <v>0.19522293352418679</v>
       </c>
     </row>
     <row r="25">
@@ -8877,19 +8899,19 @@
         <v>376.36200000000002</v>
       </c>
       <c r="B25" s="0">
-        <v>0.001500192067614686</v>
+        <v>0.050762079224156341</v>
       </c>
       <c r="C25" s="0">
-        <v>0.050758106194450647</v>
+        <v>0.10383684365877086</v>
       </c>
       <c r="D25" s="0">
-        <v>0.18595668198129942</v>
+        <v>0.0014982045998530561</v>
       </c>
       <c r="E25" s="0">
-        <v>0.18225413097478033</v>
+        <v>0.1859564858171141</v>
       </c>
       <c r="F25" s="0">
-        <v>0.10383683900586756</v>
+        <v>0.18225414646324198</v>
       </c>
     </row>
     <row r="26">
@@ -8897,19 +8919,19 @@
         <v>379.63900000000001</v>
       </c>
       <c r="B26" s="0">
-        <v>0.0019381593394607133</v>
+        <v>0.049654399537328704</v>
       </c>
       <c r="C26" s="0">
-        <v>0.049650750811194168</v>
+        <v>0.12801510225279095</v>
       </c>
       <c r="D26" s="0">
-        <v>0.20969574643904163</v>
+        <v>0.0019364269373420308</v>
       </c>
       <c r="E26" s="0">
-        <v>0.16764205658189041</v>
+        <v>0.2096956195812224</v>
       </c>
       <c r="F26" s="0">
-        <v>0.12801509754427057</v>
+        <v>0.16764207116023139</v>
       </c>
     </row>
     <row r="27">
@@ -8917,19 +8939,19 @@
         <v>382.91800000000001</v>
       </c>
       <c r="B27" s="0">
-        <v>0.00119989712888502</v>
+        <v>0.046250287537044271</v>
       </c>
       <c r="C27" s="0">
-        <v>0.046246779811094485</v>
+        <v>0.15664653022434488</v>
       </c>
       <c r="D27" s="0">
-        <v>0.23872725871105971</v>
+        <v>0.0011983290167739457</v>
       </c>
       <c r="E27" s="0">
-        <v>0.15709360759202592</v>
+        <v>0.23872718059469056</v>
       </c>
       <c r="F27" s="0">
-        <v>0.15664652493353509</v>
+        <v>0.15709362160557369</v>
       </c>
     </row>
     <row r="28">
@@ -8937,19 +8959,19 @@
         <v>386.19900000000001</v>
       </c>
       <c r="B28" s="0">
-        <v>0.00041920599617046206</v>
+        <v>0.050169243076090941</v>
       </c>
       <c r="C28" s="0">
-        <v>0.050166191046575728</v>
+        <v>0.18278559466385183</v>
       </c>
       <c r="D28" s="0">
-        <v>0.25726705654538551</v>
+        <v>0.00041791073974124939</v>
       </c>
       <c r="E28" s="0">
-        <v>0.14411707862804721</v>
+        <v>0.25726703507840326</v>
       </c>
       <c r="F28" s="0">
-        <v>0.18278558851734744</v>
+        <v>0.1441170933203906</v>
       </c>
     </row>
     <row r="29">
@@ -8957,19 +8979,19 @@
         <v>389.481</v>
       </c>
       <c r="B29" s="0">
-        <v>0.00035579003967406149</v>
+        <v>0.045907522158487132</v>
       </c>
       <c r="C29" s="0">
-        <v>0.045904630006391174</v>
+        <v>0.20432591893505447</v>
       </c>
       <c r="D29" s="0">
-        <v>0.26690626003716478</v>
+        <v>0.00035466255894360825</v>
       </c>
       <c r="E29" s="0">
-        <v>0.12950893750254414</v>
+        <v>0.26690628154475082</v>
       </c>
       <c r="F29" s="0">
-        <v>0.20432591296734026</v>
+        <v>0.12950894958085596</v>
       </c>
     </row>
     <row r="30">
@@ -8977,19 +8999,19 @@
         <v>392.76499999999999</v>
       </c>
       <c r="B30" s="0">
-        <v>0.00061244530572640782</v>
+        <v>0.06527438138059373</v>
       </c>
       <c r="C30" s="0">
-        <v>0.065271836100818895</v>
+        <v>0.22520964855977926</v>
       </c>
       <c r="D30" s="0">
-        <v>0.27207199728366172</v>
+        <v>0.0006114497375610035</v>
       </c>
       <c r="E30" s="0">
-        <v>0.11733893298203013</v>
+        <v>0.27207203817808417</v>
       </c>
       <c r="F30" s="0">
-        <v>0.22520964336972471</v>
+        <v>0.11733894384007228</v>
       </c>
     </row>
     <row r="31">
@@ -8997,19 +9019,19 @@
         <v>396.05000000000001</v>
       </c>
       <c r="B31" s="0">
-        <v>0.0017335480051053067</v>
+        <v>0.069010772751537844</v>
       </c>
       <c r="C31" s="0">
-        <v>0.069008392306587882</v>
+        <v>0.24183955516921188</v>
       </c>
       <c r="D31" s="0">
-        <v>0.27661712009055933</v>
+        <v>0.0017327191363209265</v>
       </c>
       <c r="E31" s="0">
-        <v>0.10552723635229035</v>
+        <v>0.27661720198795187</v>
       </c>
       <c r="F31" s="0">
-        <v>0.24183955170444779</v>
+        <v>0.10552724381745235</v>
       </c>
     </row>
     <row r="32">
@@ -9017,19 +9039,19 @@
         <v>399.33699999999999</v>
       </c>
       <c r="B32" s="0">
-        <v>0.00038984162695152231</v>
+        <v>0.08453323871789542</v>
       </c>
       <c r="C32" s="0">
-        <v>0.084531377299925506</v>
+        <v>0.25260068940411251</v>
       </c>
       <c r="D32" s="0">
-        <v>0.26938855317636518</v>
+        <v>0.00038915661523519513</v>
       </c>
       <c r="E32" s="0">
-        <v>0.094072828492915705</v>
+        <v>0.26938864356966591</v>
       </c>
       <c r="F32" s="0">
-        <v>0.25260068544474112</v>
+        <v>0.094072837601398077</v>
       </c>
     </row>
     <row r="33">
@@ -9037,19 +9059,19 @@
         <v>402.625</v>
       </c>
       <c r="B33" s="0">
-        <v>0.0021243677478362641</v>
+        <v>0.096701532148443653</v>
       </c>
       <c r="C33" s="0">
-        <v>0.096699776223072936</v>
+        <v>0.25994331425778405</v>
       </c>
       <c r="D33" s="0">
-        <v>0.26184519445042076</v>
+        <v>0.0021237245163133411</v>
       </c>
       <c r="E33" s="0">
-        <v>0.084187126403045501</v>
+        <v>0.26184530071460571</v>
       </c>
       <c r="F33" s="0">
-        <v>0.25994331228757872</v>
+        <v>0.084187131890432809</v>
       </c>
     </row>
     <row r="34">
@@ -9057,19 +9079,19 @@
         <v>405.91500000000002</v>
       </c>
       <c r="B34" s="0">
-        <v>0.0025046369157798463</v>
+        <v>0.12232140963094894</v>
       </c>
       <c r="C34" s="0">
-        <v>0.1223201886172746</v>
+        <v>0.26375503123348831</v>
       </c>
       <c r="D34" s="0">
-        <v>0.25297805716400212</v>
+        <v>0.0025041559747247823</v>
       </c>
       <c r="E34" s="0">
-        <v>0.074716889190894212</v>
+        <v>0.25297817094431629</v>
       </c>
       <c r="F34" s="0">
-        <v>0.26375503035742182</v>
+        <v>0.074716895127198244</v>
       </c>
     </row>
     <row r="35">
@@ -9077,19 +9099,19 @@
         <v>409.20699999999999</v>
       </c>
       <c r="B35" s="0">
-        <v>0.0005157298757625825</v>
+        <v>0.12328931343330406</v>
       </c>
       <c r="C35" s="0">
-        <v>0.12328824580148212</v>
+        <v>0.26184081703368017</v>
       </c>
       <c r="D35" s="0">
-        <v>0.23600476606716839</v>
+        <v>0.00051523240745309114</v>
       </c>
       <c r="E35" s="0">
-        <v>0.065805429333246068</v>
+        <v>0.2360048514513613</v>
       </c>
       <c r="F35" s="0">
-        <v>0.26184081519497682</v>
+        <v>0.065805435509111138</v>
       </c>
     </row>
     <row r="36">
@@ -9097,19 +9119,19 @@
         <v>412.5</v>
       </c>
       <c r="B36" s="0">
-        <v>1.4910389670404396e-05</v>
+        <v>0.13717039085432845</v>
       </c>
       <c r="C36" s="0">
-        <v>0.1371696519148595</v>
+        <v>0.25592531308311001</v>
       </c>
       <c r="D36" s="0">
-        <v>0.21956002275892286</v>
+        <v>1.4462717519846166e-05</v>
       </c>
       <c r="E36" s="0">
-        <v>0.057611126874537871</v>
+        <v>0.21956009484892691</v>
       </c>
       <c r="F36" s="0">
-        <v>0.25592531195713047</v>
+        <v>0.057611133312662197</v>
       </c>
     </row>
     <row r="37">
@@ -9117,19 +9139,19 @@
         <v>415.79399999999998</v>
       </c>
       <c r="B37" s="0">
-        <v>0</v>
+        <v>0.13434101726958328</v>
       </c>
       <c r="C37" s="0">
-        <v>0.13434098000076541</v>
+        <v>0.2468317346433494</v>
       </c>
       <c r="D37" s="0">
-        <v>0.19886578446423817</v>
+        <v>0</v>
       </c>
       <c r="E37" s="0">
-        <v>0.0505658823140369</v>
+        <v>0.19886590249484879</v>
       </c>
       <c r="F37" s="0">
-        <v>0.24683173422333818</v>
+        <v>0.050565889555141304</v>
       </c>
     </row>
     <row r="38">
@@ -9137,19 +9159,19 @@
         <v>419.08999999999998</v>
       </c>
       <c r="B38" s="0">
-        <v>0</v>
+        <v>0.14674592718893179</v>
       </c>
       <c r="C38" s="0">
-        <v>0.14674609759603607</v>
+        <v>0.23415437395893318</v>
       </c>
       <c r="D38" s="0">
-        <v>0.18259912823738608</v>
+        <v>0</v>
       </c>
       <c r="E38" s="0">
-        <v>0.043848204757443547</v>
+        <v>0.18259922277653237</v>
       </c>
       <c r="F38" s="0">
-        <v>0.23415437447583257</v>
+        <v>0.043848211678840399</v>
       </c>
     </row>
     <row r="39">
@@ -9157,19 +9179,19 @@
         <v>422.387</v>
       </c>
       <c r="B39" s="0">
-        <v>0</v>
+        <v>0.15604778193476196</v>
       </c>
       <c r="C39" s="0">
-        <v>0.15604812903345314</v>
+        <v>0.22114009440583082</v>
       </c>
       <c r="D39" s="0">
-        <v>0.16502700867037429</v>
+        <v>0</v>
       </c>
       <c r="E39" s="0">
-        <v>0.038188889577947811</v>
+        <v>0.16502708572728495</v>
       </c>
       <c r="F39" s="0">
-        <v>0.22114009622191969</v>
+        <v>0.038188896140359856</v>
       </c>
     </row>
     <row r="40">
@@ -9177,19 +9199,19 @@
         <v>425.685</v>
       </c>
       <c r="B40" s="0">
-        <v>0</v>
+        <v>0.16275407858327137</v>
       </c>
       <c r="C40" s="0">
-        <v>0.16275459611309431</v>
+        <v>0.20638355471758066</v>
       </c>
       <c r="D40" s="0">
-        <v>0.15015065693549523</v>
+        <v>0</v>
       </c>
       <c r="E40" s="0">
-        <v>0.033042108937997562</v>
+        <v>0.15015071384349232</v>
       </c>
       <c r="F40" s="0">
-        <v>0.2063835568523037</v>
+        <v>0.03304211561377423</v>
       </c>
     </row>
     <row r="41">
@@ -9197,19 +9219,19 @@
         <v>428.98500000000001</v>
       </c>
       <c r="B41" s="0">
-        <v>0</v>
+        <v>0.164831300532433</v>
       </c>
       <c r="C41" s="0">
-        <v>0.16483194588136724</v>
+        <v>0.19130497552921907</v>
       </c>
       <c r="D41" s="0">
-        <v>0.13354835504437421</v>
+        <v>0</v>
       </c>
       <c r="E41" s="0">
-        <v>0.028674140773660563</v>
+        <v>0.1335483978386523</v>
       </c>
       <c r="F41" s="0">
-        <v>0.19130497804221908</v>
+        <v>0.028674147063622465</v>
       </c>
     </row>
     <row r="42">
@@ -9217,19 +9239,19 @@
         <v>432.28699999999998</v>
       </c>
       <c r="B42" s="0">
-        <v>0</v>
+        <v>0.18204674448125738</v>
       </c>
       <c r="C42" s="0">
-        <v>0.18204762609667244</v>
+        <v>0.176881614627803</v>
       </c>
       <c r="D42" s="0">
-        <v>0.12163756435713331</v>
+        <v>0</v>
       </c>
       <c r="E42" s="0">
-        <v>0.025108092877090406</v>
+        <v>0.12163758215728497</v>
       </c>
       <c r="F42" s="0">
-        <v>0.17688161860170057</v>
+        <v>0.025108099932149366</v>
       </c>
     </row>
     <row r="43">
@@ -9237,19 +9259,19 @@
         <v>435.589</v>
       </c>
       <c r="B43" s="0">
-        <v>0</v>
+        <v>0.18884143005485379</v>
       </c>
       <c r="C43" s="0">
-        <v>0.18884245829848859</v>
+        <v>0.16363098172674601</v>
       </c>
       <c r="D43" s="0">
-        <v>0.10829409452427965</v>
+        <v>0</v>
       </c>
       <c r="E43" s="0">
-        <v>0.021977601602610967</v>
+        <v>0.10829409169821191</v>
       </c>
       <c r="F43" s="0">
-        <v>0.16363098585799635</v>
+        <v>0.021977608913111339</v>
       </c>
     </row>
     <row r="44">
@@ -9257,19 +9279,19 @@
         <v>438.89299999999997</v>
       </c>
       <c r="B44" s="0">
-        <v>0</v>
+        <v>0.18974324767795312</v>
       </c>
       <c r="C44" s="0">
-        <v>0.1897443200667199</v>
+        <v>0.14990354965611869</v>
       </c>
       <c r="D44" s="0">
-        <v>0.094002288570235543</v>
+        <v>0</v>
       </c>
       <c r="E44" s="0">
-        <v>0.019170689121091971</v>
+        <v>0.094002267841700071</v>
       </c>
       <c r="F44" s="0">
-        <v>0.14990355485319448</v>
+        <v>0.019170695508718871</v>
       </c>
     </row>
     <row r="45">
@@ -9277,19 +9299,19 @@
         <v>442.19900000000001</v>
       </c>
       <c r="B45" s="0">
-        <v>0.0010602715269705475</v>
+        <v>0.1954188638737438</v>
       </c>
       <c r="C45" s="0">
-        <v>0.19541976474495693</v>
+        <v>0.1356082042854054</v>
       </c>
       <c r="D45" s="0">
-        <v>0.086175468433568867</v>
+        <v>0.0010600815857334128</v>
       </c>
       <c r="E45" s="0">
-        <v>0.016543124113497031</v>
+        <v>0.086175423262542933</v>
       </c>
       <c r="F45" s="0">
-        <v>0.13560821043853513</v>
+        <v>0.016543129313136746</v>
       </c>
     </row>
     <row r="46">
@@ -9297,19 +9319,19 @@
         <v>445.505</v>
       </c>
       <c r="B46" s="0">
-        <v>0</v>
+        <v>0.19260337997190377</v>
       </c>
       <c r="C46" s="0">
-        <v>0.19260464841784217</v>
+        <v>0.12264961626961132</v>
       </c>
       <c r="D46" s="0">
-        <v>0.076316133828200281</v>
+        <v>0</v>
       </c>
       <c r="E46" s="0">
-        <v>0.014439507555237301</v>
+        <v>0.076316094897989795</v>
       </c>
       <c r="F46" s="0">
-        <v>0.12264962205826259</v>
+        <v>0.014439514963782764</v>
       </c>
     </row>
     <row r="47">
@@ -9317,19 +9339,19 @@
         <v>448.81299999999999</v>
       </c>
       <c r="B47" s="0">
-        <v>0.00092556124206526842</v>
+        <v>0.18645945622438742</v>
       </c>
       <c r="C47" s="0">
-        <v>0.18646045582362927</v>
+        <v>0.10943512715344807</v>
       </c>
       <c r="D47" s="0">
-        <v>0.066615271055284989</v>
+        <v>0.00092542495765438092</v>
       </c>
       <c r="E47" s="0">
-        <v>0.01233421278927903</v>
+        <v>0.066615213522460082</v>
       </c>
       <c r="F47" s="0">
-        <v>0.10943513402469675</v>
+        <v>0.012334217571530659</v>
       </c>
     </row>
     <row r="48">
@@ -9337,19 +9359,19 @@
         <v>452.12200000000001</v>
       </c>
       <c r="B48" s="0">
-        <v>0.0012227368690137482</v>
+        <v>0.19674484645409315</v>
       </c>
       <c r="C48" s="0">
-        <v>0.19674585828242394</v>
+        <v>0.097930618281266923</v>
       </c>
       <c r="D48" s="0">
-        <v>0.056781130479365428</v>
+        <v>0.0012225236797765791</v>
       </c>
       <c r="E48" s="0">
-        <v>0.01100043092167219</v>
+        <v>0.05678104167974226</v>
       </c>
       <c r="F48" s="0">
-        <v>0.097930626059340969</v>
+        <v>0.011000435291734998</v>
       </c>
     </row>
     <row r="49">
@@ -9357,19 +9379,19 @@
         <v>455.43299999999999</v>
       </c>
       <c r="B49" s="0">
-        <v>0</v>
+        <v>0.18760701279735784</v>
       </c>
       <c r="C49" s="0">
-        <v>0.18760833719186296</v>
+        <v>0.087336544687153211</v>
       </c>
       <c r="D49" s="0">
-        <v>0.052150058690977698</v>
+        <v>0</v>
       </c>
       <c r="E49" s="0">
-        <v>0.0094201997972020914</v>
+        <v>0.052149986405140549</v>
       </c>
       <c r="F49" s="0">
-        <v>0.087336552007219084</v>
+        <v>0.0094202061680667814</v>
       </c>
     </row>
     <row r="50">
@@ -9377,19 +9399,19 @@
         <v>458.74400000000003</v>
       </c>
       <c r="B50" s="0">
-        <v>0.00075496306093034615</v>
+        <v>0.18788171784570407</v>
       </c>
       <c r="C50" s="0">
-        <v>0.18788289095557048</v>
+        <v>0.077887551395307397</v>
       </c>
       <c r="D50" s="0">
-        <v>0.046307814279097401</v>
+        <v>0.00075483199868371946</v>
       </c>
       <c r="E50" s="0">
-        <v>0.008434296123801718</v>
+        <v>0.046307729737722472</v>
       </c>
       <c r="F50" s="0">
-        <v>0.077887559291931502</v>
+        <v>0.008434301563734127</v>
       </c>
     </row>
     <row r="51">
@@ -9397,19 +9419,19 @@
         <v>462.05700000000002</v>
       </c>
       <c r="B51" s="0">
-        <v>0.00033402991499678175</v>
+        <v>0.18038617465148912</v>
       </c>
       <c r="C51" s="0">
-        <v>0.18038733503513138</v>
+        <v>0.069253963998556309</v>
       </c>
       <c r="D51" s="0">
-        <v>0.039435065869301907</v>
+        <v>0.00033391284525831165</v>
       </c>
       <c r="E51" s="0">
-        <v>0.0071004663583359856</v>
+        <v>0.039434974307570238</v>
       </c>
       <c r="F51" s="0">
-        <v>0.06925397186339996</v>
+        <v>0.0071004715949195543</v>
       </c>
     </row>
     <row r="52">
@@ -9417,19 +9439,19 @@
         <v>465.37099999999998</v>
       </c>
       <c r="B52" s="0">
-        <v>0.00056154710144812575</v>
+        <v>0.17588011612511933</v>
       </c>
       <c r="C52" s="0">
-        <v>0.17588127089400094</v>
+        <v>0.06122024581262301</v>
       </c>
       <c r="D52" s="0">
-        <v>0.032013791863120172</v>
+        <v>0.00056144275596312293</v>
       </c>
       <c r="E52" s="0">
-        <v>0.0059294052459728675</v>
+        <v>0.032013697212014837</v>
       </c>
       <c r="F52" s="0">
-        <v>0.061220253877451732</v>
+        <v>0.0059294098528853085</v>
       </c>
     </row>
     <row r="53">
@@ -9437,19 +9459,19 @@
         <v>468.68599999999998</v>
       </c>
       <c r="B53" s="0">
-        <v>0.0012308847697919656</v>
+        <v>0.17438003305755551</v>
       </c>
       <c r="C53" s="0">
-        <v>0.17438112771557382</v>
+        <v>0.053934925794705081</v>
       </c>
       <c r="D53" s="0">
-        <v>0.027536874175890024</v>
+        <v>0.0012307428916236104</v>
       </c>
       <c r="E53" s="0">
-        <v>0.0052991094785151882</v>
+        <v>0.027536778286789628</v>
       </c>
       <c r="F53" s="0">
-        <v>0.053934934401132416</v>
+        <v>0.0052991133600950573</v>
       </c>
     </row>
     <row r="54">
@@ -9457,19 +9479,19 @@
         <v>472.00200000000001</v>
       </c>
       <c r="B54" s="0">
-        <v>0.00032685698809371393</v>
+        <v>0.15943534790088315</v>
       </c>
       <c r="C54" s="0">
-        <v>0.15943644190623618</v>
+        <v>0.04726190634339008</v>
       </c>
       <c r="D54" s="0">
-        <v>0.025403752191980607</v>
+        <v>0.0003267580020761612</v>
       </c>
       <c r="E54" s="0">
-        <v>0.0046283021130098818</v>
+        <v>0.025403661928580745</v>
       </c>
       <c r="F54" s="0">
-        <v>0.04726191387131027</v>
+        <v>0.0046283068598898273</v>
       </c>
     </row>
     <row r="55">
@@ -9477,19 +9499,19 @@
         <v>475.31900000000002</v>
       </c>
       <c r="B55" s="0">
-        <v>0.0002106779146726155</v>
+        <v>0.15564677693564305</v>
       </c>
       <c r="C55" s="0">
-        <v>0.15564790270822379</v>
+        <v>0.04183391515717895</v>
       </c>
       <c r="D55" s="0">
-        <v>0.022341329488648674</v>
+        <v>0.00021061889181586585</v>
       </c>
       <c r="E55" s="0">
-        <v>0.0038619474575810561</v>
+        <v>0.022341241926190109</v>
       </c>
       <c r="F55" s="0">
-        <v>0.041833923007823022</v>
+        <v>0.0038619519871474573</v>
       </c>
     </row>
     <row r="56">
@@ -9497,19 +9519,19 @@
         <v>478.63799999999998</v>
       </c>
       <c r="B56" s="0">
-        <v>0</v>
+        <v>0.14511240781929474</v>
       </c>
       <c r="C56" s="0">
-        <v>0.14511353620293205</v>
+        <v>0.037006370549860244</v>
       </c>
       <c r="D56" s="0">
-        <v>0.016428951767988649</v>
+        <v>0</v>
       </c>
       <c r="E56" s="0">
-        <v>0.0031048023021587302</v>
+        <v>0.016428868703149874</v>
       </c>
       <c r="F56" s="0">
-        <v>0.037006378071997484</v>
+        <v>0.003104806513031598</v>
       </c>
     </row>
     <row r="57">
@@ -9517,19 +9539,19 @@
         <v>481.95699999999999</v>
       </c>
       <c r="B57" s="0">
-        <v>0.00063077778760401088</v>
+        <v>0.14486382679810714</v>
       </c>
       <c r="C57" s="0">
-        <v>0.14486485993468104</v>
+        <v>0.032520017606198146</v>
       </c>
       <c r="D57" s="0">
-        <v>0.017498636075199445</v>
+        <v>0.00063070473632052598</v>
       </c>
       <c r="E57" s="0">
-        <v>0.00304745010941287</v>
+        <v>0.017498551935432649</v>
       </c>
       <c r="F57" s="0">
-        <v>0.032520025316081225</v>
+        <v>0.003047454037386333</v>
       </c>
     </row>
     <row r="58">
@@ -9537,19 +9559,19 @@
         <v>485.27699999999999</v>
       </c>
       <c r="B58" s="0">
-        <v>0.00025483372997299497</v>
+        <v>0.13560368877201462</v>
       </c>
       <c r="C58" s="0">
-        <v>0.13560474048154511</v>
+        <v>0.028797569366626478</v>
       </c>
       <c r="D58" s="0">
-        <v>0.013272842640176861</v>
+        <v>0.00025477768871342887</v>
       </c>
       <c r="E58" s="0">
-        <v>0.0026355815075329914</v>
+        <v>0.013272737865904508</v>
       </c>
       <c r="F58" s="0">
-        <v>0.028797573977867488</v>
+        <v>0.0026355856815540669</v>
       </c>
     </row>
     <row r="59">
@@ -9557,19 +9579,19 @@
         <v>488.59899999999999</v>
       </c>
       <c r="B59" s="0">
-        <v>0</v>
+        <v>0.13167005011269814</v>
       </c>
       <c r="C59" s="0">
-        <v>0.13167118028697944</v>
+        <v>0.025349974590843021</v>
       </c>
       <c r="D59" s="0">
-        <v>0.010545030279597646</v>
+        <v>0</v>
       </c>
       <c r="E59" s="0">
-        <v>0.0023348465067768026</v>
+        <v>0.010544929235884149</v>
       </c>
       <c r="F59" s="0">
-        <v>0.025349978732714482</v>
+        <v>0.0023348511626695096</v>
       </c>
     </row>
     <row r="60">
@@ -9577,19 +9599,19 @@
         <v>491.92099999999999</v>
       </c>
       <c r="B60" s="0">
-        <v>0.0010258012289685822</v>
+        <v>0.135664968820292</v>
       </c>
       <c r="C60" s="0">
-        <v>0.13566593435289554</v>
+        <v>0.022385047376098009</v>
       </c>
       <c r="D60" s="0">
-        <v>0.0099369480372536716</v>
+        <v>0.0010257018075134341</v>
       </c>
       <c r="E60" s="0">
-        <v>0.0021796027708820809</v>
+        <v>0.0099368406573549419</v>
       </c>
       <c r="F60" s="0">
-        <v>0.022385052977391837</v>
+        <v>0.0021796059084707642</v>
       </c>
     </row>
     <row r="61">
@@ -9597,19 +9619,19 @@
         <v>495.245</v>
       </c>
       <c r="B61" s="0">
-        <v>0.0004814751944203394</v>
+        <v>0.12607575707670077</v>
       </c>
       <c r="C61" s="0">
-        <v>0.12607687776693455</v>
+        <v>0.019541092654012004</v>
       </c>
       <c r="D61" s="0">
-        <v>0.0081792981692706632</v>
+        <v>0.00048145998526784458</v>
       </c>
       <c r="E61" s="0">
-        <v>0.0019835745968630409</v>
+        <v>0.0081791982256635264</v>
       </c>
       <c r="F61" s="0">
-        <v>0.019541095649644003</v>
+        <v>0.0019835785771459232</v>
       </c>
     </row>
     <row r="62">
@@ -9617,19 +9639,19 @@
         <v>498.56900000000002</v>
       </c>
       <c r="B62" s="0">
-        <v>0.00055128663218158595</v>
+        <v>0.12014969253300171</v>
       </c>
       <c r="C62" s="0">
-        <v>0.12015079382951288</v>
+        <v>0.017520388455522132</v>
       </c>
       <c r="D62" s="0">
-        <v>0.0067881085088644178</v>
+        <v>0.00055129674667543009</v>
       </c>
       <c r="E62" s="0">
-        <v>0.0017494976098740623</v>
+        <v>0.0067880161802375966</v>
       </c>
       <c r="F62" s="0">
-        <v>0.017520391460117329</v>
+        <v>0.0017495013191120693</v>
       </c>
     </row>
     <row r="63">
@@ -9637,19 +9659,19 @@
         <v>501.89499999999998</v>
       </c>
       <c r="B63" s="0">
-        <v>0.0016551000780813294</v>
+        <v>0.12370877206384907</v>
       </c>
       <c r="C63" s="0">
-        <v>0.1237097908807101</v>
+        <v>0.015438524735187913</v>
       </c>
       <c r="D63" s="0">
-        <v>0.0069766819447145238</v>
+        <v>0.0016550705473174943</v>
       </c>
       <c r="E63" s="0">
-        <v>0.0016667270724607674</v>
+        <v>0.006976597840130494</v>
       </c>
       <c r="F63" s="0">
-        <v>0.015438529402669239</v>
+        <v>0.0016667296051248591</v>
       </c>
     </row>
     <row r="64">
@@ -9657,19 +9679,19 @@
         <v>505.221</v>
       </c>
       <c r="B64" s="0">
-        <v>0.00092514207582364923</v>
+        <v>0.11310854416487713</v>
       </c>
       <c r="C64" s="0">
-        <v>0.11310960878630165</v>
+        <v>0.01384157968276231</v>
       </c>
       <c r="D64" s="0">
-        <v>0.0056307462156685775</v>
+        <v>0.0009251563935757962</v>
       </c>
       <c r="E64" s="0">
-        <v>0.0013242686322816498</v>
+        <v>0.0056306655535898935</v>
       </c>
       <c r="F64" s="0">
-        <v>0.013841582605371569</v>
+        <v>0.0013242712875168872</v>
       </c>
     </row>
     <row r="65">
@@ -9677,19 +9699,19 @@
         <v>508.54899999999998</v>
       </c>
       <c r="B65" s="0">
-        <v>0.0014076214204319713</v>
+        <v>0.10866540469450814</v>
       </c>
       <c r="C65" s="0">
-        <v>0.10866631569399886</v>
+        <v>0.012199822256245038</v>
       </c>
       <c r="D65" s="0">
-        <v>0.0045768421731179499</v>
+        <v>0.0014075895406285021</v>
       </c>
       <c r="E65" s="0">
-        <v>0.0011786806817227448</v>
+        <v>0.004576762861042658</v>
       </c>
       <c r="F65" s="0">
-        <v>0.012199825875753127</v>
+        <v>0.0011786824001241004</v>
       </c>
     </row>
     <row r="66">
@@ -9697,19 +9719,19 @@
         <v>511.87700000000001</v>
       </c>
       <c r="B66" s="0">
-        <v>0</v>
+        <v>0.10176359633215232</v>
       </c>
       <c r="C66" s="0">
-        <v>0.10176460338872403</v>
+        <v>0.010626971639939069</v>
       </c>
       <c r="D66" s="0">
-        <v>0.0034156780765598367</v>
+        <v>0</v>
       </c>
       <c r="E66" s="0">
-        <v>0.00097620530391374428</v>
+        <v>0.0034155902187249913</v>
       </c>
       <c r="F66" s="0">
-        <v>0.01062697314345626</v>
+        <v>0.00097620870694274794</v>
       </c>
     </row>
     <row r="67">
@@ -9717,19 +9739,19 @@
         <v>515.20600000000002</v>
       </c>
       <c r="B67" s="0">
-        <v>0.0016226263066142232</v>
+        <v>0.10730512493413287</v>
       </c>
       <c r="C67" s="0">
-        <v>0.10730595999661281</v>
+        <v>0.0093477068748713619</v>
       </c>
       <c r="D67" s="0">
-        <v>0.0043485551152105421</v>
+        <v>0.0016225802241372628</v>
       </c>
       <c r="E67" s="0">
-        <v>0.0010966841150780542</v>
+        <v>0.0043484900337755214</v>
       </c>
       <c r="F67" s="0">
-        <v>0.0093477125017109846</v>
+        <v>0.0010966855383315252</v>
       </c>
     </row>
     <row r="68">
@@ -9737,19 +9759,19 @@
         <v>518.53599999999994</v>
       </c>
       <c r="B68" s="0">
-        <v>0.00018194050492926434</v>
+        <v>0.090778511203552473</v>
       </c>
       <c r="C68" s="0">
-        <v>0.090779383537761077</v>
+        <v>0.0087174141438837675</v>
       </c>
       <c r="D68" s="0">
-        <v>0.0019091644105086079</v>
+        <v>0.00018197018456954324</v>
       </c>
       <c r="E68" s="0">
-        <v>0.00073587207514445256</v>
+        <v>0.0019091100021604694</v>
       </c>
       <c r="F68" s="0">
-        <v>0.0087174184023631335</v>
+        <v>0.0007358744489793013</v>
       </c>
     </row>
     <row r="69">
@@ -9757,19 +9779,19 @@
         <v>521.86599999999999</v>
       </c>
       <c r="B69" s="0">
-        <v>0.0006469500510325189</v>
+        <v>0.092259358082179013</v>
       </c>
       <c r="C69" s="0">
-        <v>0.092260150110664907</v>
+        <v>0.0076205909296261426</v>
       </c>
       <c r="D69" s="0">
-        <v>0.0019865289982001024</v>
+        <v>0.00064693174181618021</v>
       </c>
       <c r="E69" s="0">
-        <v>0.00079579841578730271</v>
+        <v>0.0019864691231029539</v>
       </c>
       <c r="F69" s="0">
-        <v>0.0076205955023162112</v>
+        <v>0.00079580029535347642</v>
       </c>
     </row>
     <row r="70">
@@ -9777,19 +9799,19 @@
         <v>525.19799999999998</v>
       </c>
       <c r="B70" s="0">
-        <v>0.0014711205294665756</v>
+        <v>0.084998163134274621</v>
       </c>
       <c r="C70" s="0">
-        <v>0.084998785431139978</v>
+        <v>0.0066902548468697407</v>
       </c>
       <c r="D70" s="0">
-        <v>0.0019377085404944647</v>
+        <v>0.0014711032448291967</v>
       </c>
       <c r="E70" s="0">
-        <v>0.00088799672556425489</v>
+        <v>0.0019376589088983662</v>
       </c>
       <c r="F70" s="0">
-        <v>0.0066902604277167144</v>
+        <v>0.00088799783786196044</v>
       </c>
     </row>
     <row r="71">
@@ -9797,19 +9819,19 @@
         <v>528.52999999999997</v>
       </c>
       <c r="B71" s="0">
-        <v>0.0013425948559395333</v>
+        <v>0.076120124260969715</v>
       </c>
       <c r="C71" s="0">
-        <v>0.076120721143698042</v>
+        <v>0.005746792183709667</v>
       </c>
       <c r="D71" s="0">
-        <v>0.0028617675466731337</v>
+        <v>0.0013426048180589503</v>
       </c>
       <c r="E71" s="0">
-        <v>0.00058385327512154735</v>
+        <v>0.0028617310839462178</v>
       </c>
       <c r="F71" s="0">
-        <v>0.0057467973823124938</v>
+        <v>0.00058385445248013233</v>
       </c>
     </row>
     <row r="72">
@@ -9817,19 +9839,19 @@
         <v>531.86300000000006</v>
       </c>
       <c r="B72" s="0">
-        <v>0.0012715009482270122</v>
+        <v>0.075331949110702665</v>
       </c>
       <c r="C72" s="0">
-        <v>0.075332578299232025</v>
+        <v>0.0052975218026897466</v>
       </c>
       <c r="D72" s="0">
-        <v>0.0016859224815699955</v>
+        <v>0.0012715368137708562</v>
       </c>
       <c r="E72" s="0">
-        <v>0.00050126728308824123</v>
+        <v>0.0016858749553589263</v>
       </c>
       <c r="F72" s="0">
-        <v>0.0052975259476122829</v>
+        <v>0.00050126800013201519</v>
       </c>
     </row>
     <row r="73">
@@ -9837,19 +9859,19 @@
         <v>535.197</v>
       </c>
       <c r="B73" s="0">
-        <v>0.0016050210436321666</v>
+        <v>0.074853006752638091</v>
       </c>
       <c r="C73" s="0">
-        <v>0.074853624381895897</v>
+        <v>0.0046211372300742964</v>
       </c>
       <c r="D73" s="0">
-        <v>0.00084423673754884659</v>
+        <v>0.0016051044003613007</v>
       </c>
       <c r="E73" s="0">
-        <v>0.00044796435315749817</v>
+        <v>0.00084419257434449483</v>
       </c>
       <c r="F73" s="0">
-        <v>0.0046211417464302584</v>
+        <v>0.00044796565188080762</v>
       </c>
     </row>
     <row r="74">
@@ -9857,19 +9879,19 @@
         <v>538.53099999999995</v>
       </c>
       <c r="B74" s="0">
-        <v>0.002371205091799639</v>
+        <v>0.072306263704710633</v>
       </c>
       <c r="C74" s="0">
-        <v>0.072306896904510573</v>
+        <v>0.0040784680223546954</v>
       </c>
       <c r="D74" s="0">
-        <v>0.0010760062467332632</v>
+        <v>0.0023714034964104724</v>
       </c>
       <c r="E74" s="0">
-        <v>0.00046413616532258313</v>
+        <v>0.0010759806447944488</v>
       </c>
       <c r="F74" s="0">
-        <v>0.0040784734100967517</v>
+        <v>0.0004641360616113223</v>
       </c>
     </row>
     <row r="75">
@@ -9877,19 +9899,19 @@
         <v>541.86699999999996</v>
       </c>
       <c r="B75" s="0">
-        <v>0.0018526681606027635</v>
+        <v>0.06391322006170809</v>
       </c>
       <c r="C75" s="0">
-        <v>0.06391367952370744</v>
+        <v>0.0036857325924681719</v>
       </c>
       <c r="D75" s="0">
-        <v>0.00032423077680050104</v>
+        <v>0.0018526937981325066</v>
       </c>
       <c r="E75" s="0">
-        <v>0.00030595709290721299</v>
+        <v>0.00032419561204997884</v>
       </c>
       <c r="F75" s="0">
-        <v>0.003685736871979965</v>
+        <v>0.00030595744296219859</v>
       </c>
     </row>
     <row r="76">
@@ -9897,19 +9919,19 @@
         <v>545.20299999999998</v>
       </c>
       <c r="B76" s="0">
-        <v>0.00030929031003583337</v>
+        <v>0.065667056309385671</v>
       </c>
       <c r="C76" s="0">
-        <v>0.065667802023267399</v>
+        <v>0.0032651610065277999</v>
       </c>
       <c r="D76" s="0">
-        <v>0.0014027708358326214</v>
+        <v>0.00030944325673339557</v>
       </c>
       <c r="E76" s="0">
-        <v>0.00033376813227519787</v>
+        <v>0.0014027251435356476</v>
       </c>
       <c r="F76" s="0">
-        <v>0.0032651627989989081</v>
+        <v>0.00033377155981580115</v>
       </c>
     </row>
     <row r="77">
@@ -9917,19 +9939,19 @@
         <v>548.53899999999999</v>
       </c>
       <c r="B77" s="0">
-        <v>0.00059456961342091636</v>
+        <v>0.059940222496667223</v>
       </c>
       <c r="C77" s="0">
-        <v>0.059940926672682873</v>
+        <v>0.0028226137230275691</v>
       </c>
       <c r="D77" s="0">
-        <v>0.00059072654345416955</v>
+        <v>0.00059478439240992476</v>
       </c>
       <c r="E77" s="0">
-        <v>0.0001890891919409924</v>
+        <v>0.00059069170142735431</v>
       </c>
       <c r="F77" s="0">
-        <v>0.0028226156491077056</v>
+        <v>0.00018909146310129219</v>
       </c>
     </row>
     <row r="78">
@@ -9937,19 +9959,19 @@
         <v>551.87599999999998</v>
       </c>
       <c r="B78" s="0">
-        <v>0</v>
+        <v>0.052534574285201766</v>
       </c>
       <c r="C78" s="0">
-        <v>0.052535101704494484</v>
+        <v>0.0025622366246763526</v>
       </c>
       <c r="D78" s="0">
-        <v>7.0175417567986087e-05</v>
+        <v>0</v>
       </c>
       <c r="E78" s="0">
-        <v>0.0003652138755704275</v>
+        <v>7.0126639702169409e-05</v>
       </c>
       <c r="F78" s="0">
-        <v>0.0025622378104047808</v>
+        <v>0.00036521717506615969</v>
       </c>
     </row>
     <row r="79">
@@ -9957,19 +9979,19 @@
         <v>555.21400000000006</v>
       </c>
       <c r="B79" s="0">
-        <v>0.001451780470611154</v>
+        <v>0.054274297306596338</v>
       </c>
       <c r="C79" s="0">
-        <v>0.054274723493999803</v>
+        <v>0.0022603199085220365</v>
       </c>
       <c r="D79" s="0">
-        <v>0.00058078121383877887</v>
+        <v>0.0014517861044657571</v>
       </c>
       <c r="E79" s="0">
-        <v>0.00019619591390490019</v>
+        <v>0.00058075045270409166</v>
       </c>
       <c r="F79" s="0">
-        <v>0.0022603235369240801</v>
+        <v>0.00019619595541294817</v>
       </c>
     </row>
     <row r="80">
@@ -9977,19 +9999,19 @@
         <v>558.553</v>
       </c>
       <c r="B80" s="0">
-        <v>0.00085876155541683057</v>
+        <v>0.056915011412619711</v>
       </c>
       <c r="C80" s="0">
-        <v>0.056915500516412511</v>
+        <v>0.0019018690258095999</v>
       </c>
       <c r="D80" s="0">
-        <v>0.00030900470995853997</v>
+        <v>0.00085872839187264068</v>
       </c>
       <c r="E80" s="0">
-        <v>0.00044418464795985773</v>
+        <v>0.00030895987775190304</v>
       </c>
       <c r="F80" s="0">
-        <v>0.0019018718198314504</v>
+        <v>0.00044418648951579981</v>
       </c>
     </row>
     <row r="81">
@@ -9997,19 +10019,19 @@
         <v>561.89200000000005</v>
       </c>
       <c r="B81" s="0">
-        <v>0.0013352749228141038</v>
+        <v>0.047467651607729665</v>
       </c>
       <c r="C81" s="0">
-        <v>0.047468095640945972</v>
+        <v>0.0018910752162826132</v>
       </c>
       <c r="D81" s="0">
-        <v>0.00041417182005039837</v>
+        <v>0.0013353796650819106</v>
       </c>
       <c r="E81" s="0">
-        <v>0.00019165438921999635</v>
+        <v>0.0004141572405467846</v>
       </c>
       <c r="F81" s="0">
-        <v>0.0018910786840235982</v>
+        <v>0.00019165419986787188</v>
       </c>
     </row>
     <row r="82">
@@ -10017,19 +10039,19 @@
         <v>565.231</v>
       </c>
       <c r="B82" s="0">
-        <v>0.0018457767722352047</v>
+        <v>0.049338273050995349</v>
       </c>
       <c r="C82" s="0">
-        <v>0.049338608616486104</v>
+        <v>0.0014331812181998674</v>
       </c>
       <c r="D82" s="0">
-        <v>0.00064895700685406053</v>
+        <v>0.0018457679507521512</v>
       </c>
       <c r="E82" s="0">
-        <v>0.00045068088541909765</v>
+        <v>0.00064893589461151541</v>
       </c>
       <c r="F82" s="0">
-        <v>0.0014331863722548441</v>
+        <v>0.00045068002079500137</v>
       </c>
     </row>
     <row r="83">
@@ -10037,19 +10059,19 @@
         <v>568.57100000000003</v>
       </c>
       <c r="B83" s="0">
-        <v>0.0026933638097548199</v>
+        <v>0.04374840379615097</v>
       </c>
       <c r="C83" s="0">
-        <v>0.043748592530460741</v>
+        <v>0.001389654650064286</v>
       </c>
       <c r="D83" s="0">
-        <v>0</v>
+        <v>0.0026933314623884008</v>
       </c>
       <c r="E83" s="0">
-        <v>0.00026094056561914427</v>
+        <v>0</v>
       </c>
       <c r="F83" s="0">
-        <v>0.0013896608736762327</v>
+        <v>0.0002609379652276633</v>
       </c>
     </row>
     <row r="84">
@@ -10057,19 +10079,19 @@
         <v>571.91200000000004</v>
       </c>
       <c r="B84" s="0">
-        <v>0.0028416292875372167</v>
+        <v>0.041774519536918076</v>
       </c>
       <c r="C84" s="0">
-        <v>0.041774759322370285</v>
+        <v>0.0014538202175181912</v>
       </c>
       <c r="D84" s="0">
-        <v>0</v>
+        <v>0.0028417159784705146</v>
       </c>
       <c r="E84" s="0">
-        <v>0.00034124548148303628</v>
+        <v>0</v>
       </c>
       <c r="F84" s="0">
-        <v>0.0014538258027054747</v>
+        <v>0.00034124130356445373</v>
       </c>
     </row>
     <row r="85">
@@ -10077,19 +10099,19 @@
         <v>575.25300000000004</v>
       </c>
       <c r="B85" s="0">
-        <v>0.0028337318553315794</v>
+        <v>0.03516928148417478</v>
       </c>
       <c r="C85" s="0">
-        <v>0.03516939995622035</v>
+        <v>0.0011019297279089989</v>
       </c>
       <c r="D85" s="0">
-        <v>0.0013314612368583556</v>
+        <v>0.0028337308235769016</v>
       </c>
       <c r="E85" s="0">
-        <v>0.00024003348806289157</v>
+        <v>0.0013314611369650532</v>
       </c>
       <c r="F85" s="0">
-        <v>0.0011019348299672088</v>
+        <v>0.0002400305079244958</v>
       </c>
     </row>
     <row r="86">
@@ -10097,19 +10119,19 @@
         <v>578.59400000000005</v>
       </c>
       <c r="B86" s="0">
-        <v>0.0034007898519327006</v>
+        <v>0.035254486624766497</v>
       </c>
       <c r="C86" s="0">
-        <v>0.035254536524574914</v>
+        <v>0.00091429304533389565</v>
       </c>
       <c r="D86" s="0">
-        <v>0.0014101957068145929</v>
+        <v>0.0034007657630237445</v>
       </c>
       <c r="E86" s="0">
-        <v>0.0002077067297788986</v>
+        <v>0.0014101952660660476</v>
       </c>
       <c r="F86" s="0">
-        <v>0.00091429786472915721</v>
+        <v>0.00020770294919234764</v>
       </c>
     </row>
     <row r="87">
@@ -10117,19 +10139,19 @@
         <v>581.93600000000004</v>
       </c>
       <c r="B87" s="0">
-        <v>0.0053549148327951823</v>
+        <v>0.03645859945510331</v>
       </c>
       <c r="C87" s="0">
-        <v>0.036458679160386774</v>
+        <v>0.00067845635797330337</v>
       </c>
       <c r="D87" s="0">
-        <v>0.0014571878569841084</v>
+        <v>0.0053550775343685336</v>
       </c>
       <c r="E87" s="0">
-        <v>0.00050199187908677616</v>
+        <v>0.001457217782856194</v>
       </c>
       <c r="F87" s="0">
-        <v>0.00067846306904047573</v>
+        <v>0.00050198367993033145</v>
       </c>
     </row>
     <row r="88">
@@ -10137,19 +10159,19 @@
         <v>585.279</v>
       </c>
       <c r="B88" s="0">
-        <v>0.008619235382875191</v>
+        <v>0.033514426813301634</v>
       </c>
       <c r="C88" s="0">
-        <v>0.03351411025414467</v>
+        <v>0.00069007282026423958</v>
       </c>
       <c r="D88" s="0">
-        <v>0.0010226529926096295</v>
+        <v>0.0086191781042233816</v>
       </c>
       <c r="E88" s="0">
-        <v>0.00016516884665752977</v>
+        <v>0.0010227047578373954</v>
       </c>
       <c r="F88" s="0">
-        <v>0.00069007475677469244</v>
+        <v>0.00016515814160931029</v>
       </c>
     </row>
     <row r="89">
@@ -10157,19 +10179,19 @@
         <v>588.62199999999996</v>
       </c>
       <c r="B89" s="0">
-        <v>0.0061307465695343479</v>
+        <v>0.034302081636077522</v>
       </c>
       <c r="C89" s="0">
-        <v>0.034302083166391058</v>
+        <v>0.00045086451881137113</v>
       </c>
       <c r="D89" s="0">
-        <v>0.0020765424037054239</v>
+        <v>0.0061308390048380145</v>
       </c>
       <c r="E89" s="0">
-        <v>0.00039774086860018521</v>
+        <v>0.0020765809268105851</v>
       </c>
       <c r="F89" s="0">
-        <v>0.00045086893286449544</v>
+        <v>0.0003977337874129751</v>
       </c>
     </row>
     <row r="90">
@@ -10177,19 +10199,19 @@
         <v>591.96500000000003</v>
       </c>
       <c r="B90" s="0">
-        <v>0.006098374176115526</v>
+        <v>0.025254676180908778</v>
       </c>
       <c r="C90" s="0">
-        <v>0.025254377717718424</v>
+        <v>0.00069614245322127959</v>
       </c>
       <c r="D90" s="0">
-        <v>0</v>
+        <v>0.0060983041404282521</v>
       </c>
       <c r="E90" s="0">
-        <v>0.0001670491269959558</v>
+        <v>0</v>
       </c>
       <c r="F90" s="0">
-        <v>0.00069614028928778442</v>
+        <v>0.00016703988092710322</v>
       </c>
     </row>
     <row r="91">
@@ -10197,19 +10219,19 @@
         <v>595.30899999999997</v>
       </c>
       <c r="B91" s="0">
-        <v>0.0060652661252774036</v>
+        <v>0.030595773301493896</v>
       </c>
       <c r="C91" s="0">
-        <v>0.030595681149501314</v>
+        <v>0.00063940936640376699</v>
       </c>
       <c r="D91" s="0">
-        <v>0.0011691649863919996</v>
+        <v>0.0060653468029929561</v>
       </c>
       <c r="E91" s="0">
-        <v>0.0003489979118477544</v>
+        <v>0.0011692071400433949</v>
       </c>
       <c r="F91" s="0">
-        <v>0.00063941151498650862</v>
+        <v>0.00034898975205118355</v>
       </c>
     </row>
     <row r="92">
@@ -10217,19 +10239,19 @@
         <v>598.65200000000004</v>
       </c>
       <c r="B92" s="0">
-        <v>0.0065756332303658714</v>
+        <v>0.027920791568784648</v>
       </c>
       <c r="C92" s="0">
-        <v>0.027920640133381601</v>
+        <v>0.00034790265269191232</v>
       </c>
       <c r="D92" s="0">
-        <v>0.0019747388688178087</v>
+        <v>0.0065756487532355841</v>
       </c>
       <c r="E92" s="0">
-        <v>0.00032333850503951076</v>
+        <v>0.0019747908997515325</v>
       </c>
       <c r="F92" s="0">
-        <v>0.00034790390324489559</v>
+        <v>0.00032333051858451559</v>
       </c>
     </row>
     <row r="93">
@@ -10237,19 +10259,19 @@
         <v>601.99699999999996</v>
       </c>
       <c r="B93" s="0">
-        <v>0.0057584230215834663</v>
+        <v>0.02241269258870935</v>
       </c>
       <c r="C93" s="0">
-        <v>0.022412550829069254</v>
+        <v>0.00052552782842784924</v>
       </c>
       <c r="D93" s="0">
-        <v>0.0012060533112573572</v>
+        <v>0.0057584609924444339</v>
       </c>
       <c r="E93" s="0">
-        <v>0.00026054566747667993</v>
+        <v>0.0012061012015817413</v>
       </c>
       <c r="F93" s="0">
-        <v>0.00052552928412642915</v>
+        <v>0.00026053823923693467</v>
       </c>
     </row>
     <row r="94">
@@ -10257,19 +10279,19 @@
         <v>605.34100000000001</v>
       </c>
       <c r="B94" s="0">
-        <v>0.0051261000234090496</v>
+        <v>0.024563438300961728</v>
       </c>
       <c r="C94" s="0">
-        <v>0.024563303254200586</v>
+        <v>0.00037737593361426321</v>
       </c>
       <c r="D94" s="0">
-        <v>0.00034525552039774409</v>
+        <v>0.0051260795811883392</v>
       </c>
       <c r="E94" s="0">
-        <v>0.00028679079530987306</v>
+        <v>0.000345285361457333</v>
       </c>
       <c r="F94" s="0">
-        <v>0.00037737827598626394</v>
+        <v>0.00028678383633612669</v>
       </c>
     </row>
     <row r="95">
@@ -10277,19 +10299,19 @@
         <v>608.68600000000004</v>
       </c>
       <c r="B95" s="0">
-        <v>0.0065913384113972066</v>
+        <v>0.024941946743976522</v>
       </c>
       <c r="C95" s="0">
-        <v>0.02494167496998121</v>
+        <v>0.00039726351695146148</v>
       </c>
       <c r="D95" s="0">
-        <v>0</v>
+        <v>0.0065913045704654562</v>
       </c>
       <c r="E95" s="0">
-        <v>0.0003458602141129712</v>
+        <v>0</v>
       </c>
       <c r="F95" s="0">
-        <v>0.00039726406504009336</v>
+        <v>0.0003458507235982477</v>
       </c>
     </row>
     <row r="96">
@@ -10297,19 +10319,19 @@
         <v>612.03099999999995</v>
       </c>
       <c r="B96" s="0">
-        <v>0.0059774430148244115</v>
+        <v>0.020773938368029085</v>
       </c>
       <c r="C96" s="0">
-        <v>0.020773793200021609</v>
+        <v>0.0003526042714307311</v>
       </c>
       <c r="D96" s="0">
-        <v>0.00016032543530721154</v>
+        <v>0.0059774650265316896</v>
       </c>
       <c r="E96" s="0">
-        <v>0.00027938785263713871</v>
+        <v>0.00016037486557516156</v>
       </c>
       <c r="F96" s="0">
-        <v>0.00035260712137610172</v>
+        <v>0.0002793805691677453</v>
       </c>
     </row>
     <row r="97">
@@ -10317,19 +10339,19 @@
         <v>615.37599999999998</v>
       </c>
       <c r="B97" s="0">
-        <v>0.0067498523385579384</v>
+        <v>0.019684526609981847</v>
       </c>
       <c r="C97" s="0">
-        <v>0.019684284579076745</v>
+        <v>0.00033458193669346192</v>
       </c>
       <c r="D97" s="0">
-        <v>0.00029989307795251594</v>
+        <v>0.0067497513315254252</v>
       </c>
       <c r="E97" s="0">
-        <v>0.00034085107976183454</v>
+        <v>0.00029991548574451735</v>
       </c>
       <c r="F97" s="0">
-        <v>0.00033458661259524975</v>
+        <v>0.00034084439449371502</v>
       </c>
     </row>
     <row r="98">
@@ -10337,19 +10359,19 @@
         <v>618.72199999999998</v>
       </c>
       <c r="B98" s="0">
-        <v>0.0023155955103405707</v>
+        <v>0.020263171565014521</v>
       </c>
       <c r="C98" s="0">
-        <v>0.020263319987047772</v>
+        <v>0.00022084169025901354</v>
       </c>
       <c r="D98" s="0">
-        <v>0.00049695649772705803</v>
+        <v>0.0023156902408750721</v>
       </c>
       <c r="E98" s="0">
-        <v>0.0003932750703624516</v>
+        <v>0.00049696718669050948</v>
       </c>
       <c r="F98" s="0">
-        <v>0.00022084374948886003</v>
+        <v>0.000393273291476302</v>
       </c>
     </row>
   </sheetData>
